--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B375EB5E-F1FE-44C2-BB4E-82321851606E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC0A7BD-3FF3-423E-B404-34C46DEBAF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2265" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="450">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -6596,6 +6596,212 @@
     </rPh>
     <rPh sb="139" eb="141">
       <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミラボー先生から覚える</t>
+    <rPh sb="4" eb="6">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジェラットから5回ほどジェラート買って覚える</t>
+    <rPh sb="8" eb="9">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プラトン先生から必ずもらう</t>
+    <rPh sb="4" eb="6">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カナラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぬねと友達になったらもらえる</t>
+    <rPh sb="3" eb="5">
+      <t>トモダチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウィンドアークLV１で自動解放</t>
+    <rPh sb="11" eb="13">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初心者向けお菓子魔法の本に最初から書いてる</t>
+    <rPh sb="0" eb="3">
+      <t>ショシンシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミエールカンデラの賞品</t>
+    <rPh sb="10" eb="12">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミエールエピファニアの賞品</t>
+    <rPh sb="12" eb="14">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガレット・デ・ロワの賞品</t>
+    <rPh sb="10" eb="12">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジックパティスリーの賞品</t>
+    <rPh sb="11" eb="13">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クレープドゥシャノワールの賞品</t>
+    <rPh sb="13" eb="15">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キラキラボンボンズの賞品</t>
+    <rPh sb="10" eb="12">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェドフルラージュの賞品</t>
+    <rPh sb="10" eb="12">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミエールドソレイユの賞品</t>
+    <rPh sb="11" eb="13">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターブレッシングの本と同時に解放</t>
+    <rPh sb="10" eb="11">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秋お店で買う</t>
+    <rPh sb="0" eb="1">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フリージングと同時に解放</t>
+    <rPh sb="7" eb="9">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オランジーナ・パティスリーアワードの賞品</t>
+    <rPh sb="18" eb="20">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春牧場で売ってる</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ボクジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒカリが失敗を10回すると思いつく謎魔法</t>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6699,7 +6905,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6735,6 +6941,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8789,7 +9001,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="5" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -8957,255 +9169,255 @@
         <v>330</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="11">
+    <row r="46" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="13">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="13">
         <v>500</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="13">
         <v>150</v>
       </c>
-      <c r="G46" s="11">
-        <v>0</v>
-      </c>
-      <c r="H46" s="11">
-        <v>0</v>
-      </c>
-      <c r="I46" s="11">
-        <v>0</v>
-      </c>
-      <c r="J46" s="11">
+      <c r="G46" s="13">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13">
         <v>1</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="L46" s="11">
+      <c r="L46" s="13">
         <v>340</v>
       </c>
-      <c r="M46" s="11">
+      <c r="M46" s="13">
         <v>340</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="11">
+    <row r="47" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="13">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="13">
         <v>500</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="13">
         <v>150</v>
       </c>
-      <c r="G47" s="11">
-        <v>0</v>
-      </c>
-      <c r="H47" s="11">
-        <v>0</v>
-      </c>
-      <c r="I47" s="11">
-        <v>0</v>
-      </c>
-      <c r="J47" s="11">
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13">
         <v>1</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="L47" s="11">
+      <c r="L47" s="13">
         <v>350</v>
       </c>
-      <c r="M47" s="11">
+      <c r="M47" s="13">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="11">
+    <row r="48" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="13">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="13">
         <v>500</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="13">
         <v>150</v>
       </c>
-      <c r="G48" s="11">
-        <v>0</v>
-      </c>
-      <c r="H48" s="11">
-        <v>0</v>
-      </c>
-      <c r="I48" s="11">
-        <v>0</v>
-      </c>
-      <c r="J48" s="11">
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13">
         <v>1</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="L48" s="11">
+      <c r="L48" s="13">
         <v>360</v>
       </c>
-      <c r="M48" s="11">
+      <c r="M48" s="13">
         <v>360</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="11">
+    <row r="49" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="13">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="13">
         <v>500</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="13">
         <v>150</v>
       </c>
-      <c r="G49" s="11">
-        <v>0</v>
-      </c>
-      <c r="H49" s="11">
-        <v>0</v>
-      </c>
-      <c r="I49" s="11">
-        <v>0</v>
-      </c>
-      <c r="J49" s="11">
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
+        <v>0</v>
+      </c>
+      <c r="I49" s="13">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13">
         <v>1</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="L49" s="11">
+      <c r="L49" s="13">
         <v>370</v>
       </c>
-      <c r="M49" s="11">
+      <c r="M49" s="13">
         <v>370</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="11">
+    <row r="50" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="13">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="13">
         <v>500</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="13">
         <v>150</v>
       </c>
-      <c r="G50" s="11">
-        <v>0</v>
-      </c>
-      <c r="H50" s="11">
-        <v>0</v>
-      </c>
-      <c r="I50" s="11">
-        <v>0</v>
-      </c>
-      <c r="J50" s="11">
+      <c r="G50" s="13">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13">
+        <v>0</v>
+      </c>
+      <c r="J50" s="13">
         <v>1</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="L50" s="11">
+      <c r="L50" s="13">
         <v>380</v>
       </c>
-      <c r="M50" s="11">
+      <c r="M50" s="13">
         <v>380</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="11">
+    <row r="51" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="13">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E51" s="11">
+      <c r="E51" s="13">
         <v>500</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="13">
         <v>150</v>
       </c>
-      <c r="G51" s="11">
-        <v>0</v>
-      </c>
-      <c r="H51" s="11">
-        <v>0</v>
-      </c>
-      <c r="I51" s="11">
-        <v>0</v>
-      </c>
-      <c r="J51" s="11">
+      <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>0</v>
+      </c>
+      <c r="I51" s="13">
+        <v>0</v>
+      </c>
+      <c r="J51" s="13">
         <v>1</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="L51" s="11">
+      <c r="L51" s="13">
         <v>390</v>
       </c>
-      <c r="M51" s="11">
+      <c r="M51" s="13">
         <v>390</v>
       </c>
     </row>
@@ -9251,129 +9463,129 @@
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="11">
+    <row r="53" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="13">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="13">
         <v>500</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="13">
         <v>150</v>
       </c>
-      <c r="G53" s="11">
-        <v>0</v>
-      </c>
-      <c r="H53" s="11">
-        <v>0</v>
-      </c>
-      <c r="I53" s="11">
-        <v>0</v>
-      </c>
-      <c r="J53" s="11">
+      <c r="G53" s="13">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="13">
         <v>1</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="L53" s="11">
+      <c r="L53" s="13">
         <v>410</v>
       </c>
-      <c r="M53" s="11">
+      <c r="M53" s="13">
         <v>410</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="11">
+    <row r="54" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="13">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="13">
         <v>500</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="13">
         <v>150</v>
       </c>
-      <c r="G54" s="11">
-        <v>0</v>
-      </c>
-      <c r="H54" s="11">
-        <v>0</v>
-      </c>
-      <c r="I54" s="11">
-        <v>0</v>
-      </c>
-      <c r="J54" s="11">
+      <c r="G54" s="13">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13">
         <v>1</v>
       </c>
-      <c r="K54" s="12" t="s">
+      <c r="K54" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="L54" s="11">
+      <c r="L54" s="13">
         <v>500</v>
       </c>
-      <c r="M54" s="11">
+      <c r="M54" s="13">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="11">
+    <row r="55" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="13">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="13">
         <v>500</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="13">
         <v>150</v>
       </c>
-      <c r="G55" s="11">
-        <v>0</v>
-      </c>
-      <c r="H55" s="11">
-        <v>0</v>
-      </c>
-      <c r="I55" s="11">
-        <v>0</v>
-      </c>
-      <c r="J55" s="11">
+      <c r="G55" s="13">
+        <v>0</v>
+      </c>
+      <c r="H55" s="13">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13">
+        <v>0</v>
+      </c>
+      <c r="J55" s="13">
         <v>1</v>
       </c>
-      <c r="K55" s="12" t="s">
+      <c r="K55" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="L55" s="11">
+      <c r="L55" s="13">
         <v>510</v>
       </c>
-      <c r="M55" s="11">
+      <c r="M55" s="13">
         <v>510</v>
       </c>
     </row>
@@ -9545,171 +9757,171 @@
         <v>550</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="11">
+    <row r="60" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="13">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="13">
         <v>500</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="13">
         <v>150</v>
       </c>
-      <c r="G60" s="11">
-        <v>0</v>
-      </c>
-      <c r="H60" s="11">
-        <v>0</v>
-      </c>
-      <c r="I60" s="11">
-        <v>0</v>
-      </c>
-      <c r="J60" s="11">
+      <c r="G60" s="13">
+        <v>0</v>
+      </c>
+      <c r="H60" s="13">
+        <v>0</v>
+      </c>
+      <c r="I60" s="13">
+        <v>0</v>
+      </c>
+      <c r="J60" s="13">
         <v>1</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="L60" s="11">
+      <c r="L60" s="13">
         <v>560</v>
       </c>
-      <c r="M60" s="11">
+      <c r="M60" s="13">
         <v>560</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="11">
+    <row r="61" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="13">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="13">
         <v>500</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="13">
         <v>150</v>
       </c>
-      <c r="G61" s="11">
-        <v>0</v>
-      </c>
-      <c r="H61" s="11">
-        <v>0</v>
-      </c>
-      <c r="I61" s="11">
-        <v>0</v>
-      </c>
-      <c r="J61" s="11">
+      <c r="G61" s="13">
+        <v>0</v>
+      </c>
+      <c r="H61" s="13">
+        <v>0</v>
+      </c>
+      <c r="I61" s="13">
+        <v>0</v>
+      </c>
+      <c r="J61" s="13">
         <v>1</v>
       </c>
-      <c r="K61" s="12" t="s">
+      <c r="K61" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="L61" s="11">
+      <c r="L61" s="13">
         <v>570</v>
       </c>
-      <c r="M61" s="11">
+      <c r="M61" s="13">
         <v>570</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="11">
+    <row r="62" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="13">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="13">
         <v>500</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="13">
         <v>150</v>
       </c>
-      <c r="G62" s="11">
-        <v>0</v>
-      </c>
-      <c r="H62" s="11">
-        <v>0</v>
-      </c>
-      <c r="I62" s="11">
-        <v>0</v>
-      </c>
-      <c r="J62" s="11">
+      <c r="G62" s="13">
+        <v>0</v>
+      </c>
+      <c r="H62" s="13">
+        <v>0</v>
+      </c>
+      <c r="I62" s="13">
+        <v>0</v>
+      </c>
+      <c r="J62" s="13">
         <v>1</v>
       </c>
-      <c r="K62" s="12" t="s">
+      <c r="K62" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="L62" s="11">
+      <c r="L62" s="13">
         <v>580</v>
       </c>
-      <c r="M62" s="11">
+      <c r="M62" s="13">
         <v>580</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="11">
+    <row r="63" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="13">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="13">
         <v>500</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="13">
         <v>150</v>
       </c>
-      <c r="G63" s="11">
-        <v>0</v>
-      </c>
-      <c r="H63" s="11">
-        <v>0</v>
-      </c>
-      <c r="I63" s="11">
-        <v>0</v>
-      </c>
-      <c r="J63" s="11">
+      <c r="G63" s="13">
+        <v>0</v>
+      </c>
+      <c r="H63" s="13">
+        <v>0</v>
+      </c>
+      <c r="I63" s="13">
+        <v>0</v>
+      </c>
+      <c r="J63" s="13">
         <v>1</v>
       </c>
-      <c r="K63" s="12" t="s">
+      <c r="K63" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="L63" s="11">
+      <c r="L63" s="13">
         <v>590</v>
       </c>
-      <c r="M63" s="11">
+      <c r="M63" s="13">
         <v>590</v>
       </c>
     </row>
@@ -9755,45 +9967,45 @@
         <v>600</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="11">
+    <row r="65" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="13">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="13">
         <v>500</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="13">
         <v>150</v>
       </c>
-      <c r="G65" s="11">
-        <v>0</v>
-      </c>
-      <c r="H65" s="11">
-        <v>0</v>
-      </c>
-      <c r="I65" s="11">
-        <v>0</v>
-      </c>
-      <c r="J65" s="11">
+      <c r="G65" s="13">
+        <v>0</v>
+      </c>
+      <c r="H65" s="13">
+        <v>0</v>
+      </c>
+      <c r="I65" s="13">
+        <v>0</v>
+      </c>
+      <c r="J65" s="13">
         <v>1</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K65" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="L65" s="11">
+      <c r="L65" s="13">
         <v>610</v>
       </c>
-      <c r="M65" s="11">
+      <c r="M65" s="13">
         <v>610</v>
       </c>
     </row>
@@ -9839,381 +10051,381 @@
         <v>620</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="11">
+    <row r="67" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="13">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="13">
         <v>500</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="13">
         <v>150</v>
       </c>
-      <c r="G67" s="11">
-        <v>0</v>
-      </c>
-      <c r="H67" s="11">
-        <v>0</v>
-      </c>
-      <c r="I67" s="11">
-        <v>0</v>
-      </c>
-      <c r="J67" s="11">
+      <c r="G67" s="13">
+        <v>0</v>
+      </c>
+      <c r="H67" s="13">
+        <v>0</v>
+      </c>
+      <c r="I67" s="13">
+        <v>0</v>
+      </c>
+      <c r="J67" s="13">
         <v>1</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="L67" s="11">
+      <c r="L67" s="13">
         <v>700</v>
       </c>
-      <c r="M67" s="11">
+      <c r="M67" s="13">
         <v>700</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="11">
+    <row r="68" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="13">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="13">
         <v>500</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="13">
         <v>150</v>
       </c>
-      <c r="G68" s="11">
-        <v>0</v>
-      </c>
-      <c r="H68" s="11">
-        <v>0</v>
-      </c>
-      <c r="I68" s="11">
-        <v>0</v>
-      </c>
-      <c r="J68" s="11">
+      <c r="G68" s="13">
+        <v>0</v>
+      </c>
+      <c r="H68" s="13">
+        <v>0</v>
+      </c>
+      <c r="I68" s="13">
+        <v>0</v>
+      </c>
+      <c r="J68" s="13">
         <v>1</v>
       </c>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="L68" s="11">
+      <c r="L68" s="13">
         <v>710</v>
       </c>
-      <c r="M68" s="11">
+      <c r="M68" s="13">
         <v>710</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="11">
+    <row r="69" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="13">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="13">
         <v>500</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="13">
         <v>150</v>
       </c>
-      <c r="G69" s="11">
-        <v>0</v>
-      </c>
-      <c r="H69" s="11">
-        <v>0</v>
-      </c>
-      <c r="I69" s="11">
-        <v>0</v>
-      </c>
-      <c r="J69" s="11">
+      <c r="G69" s="13">
+        <v>0</v>
+      </c>
+      <c r="H69" s="13">
+        <v>0</v>
+      </c>
+      <c r="I69" s="13">
+        <v>0</v>
+      </c>
+      <c r="J69" s="13">
         <v>1</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L69" s="13">
         <v>720</v>
       </c>
-      <c r="M69" s="11">
+      <c r="M69" s="13">
         <v>720</v>
       </c>
     </row>
-    <row r="70" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="11">
+    <row r="70" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="13">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="13">
         <v>500</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="13">
         <v>150</v>
       </c>
-      <c r="G70" s="11">
-        <v>0</v>
-      </c>
-      <c r="H70" s="11">
-        <v>0</v>
-      </c>
-      <c r="I70" s="11">
-        <v>0</v>
-      </c>
-      <c r="J70" s="11">
+      <c r="G70" s="13">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13">
+        <v>0</v>
+      </c>
+      <c r="I70" s="13">
+        <v>0</v>
+      </c>
+      <c r="J70" s="13">
         <v>1</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="L70" s="11">
+      <c r="L70" s="13">
         <v>730</v>
       </c>
-      <c r="M70" s="11">
+      <c r="M70" s="13">
         <v>730</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="11">
+    <row r="71" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="13">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="13">
         <v>500</v>
       </c>
-      <c r="F71" s="11">
+      <c r="F71" s="13">
         <v>150</v>
       </c>
-      <c r="G71" s="11">
-        <v>0</v>
-      </c>
-      <c r="H71" s="11">
-        <v>0</v>
-      </c>
-      <c r="I71" s="11">
-        <v>0</v>
-      </c>
-      <c r="J71" s="11">
+      <c r="G71" s="13">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13">
+        <v>0</v>
+      </c>
+      <c r="J71" s="13">
         <v>1</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="L71" s="11">
+      <c r="L71" s="13">
         <v>740</v>
       </c>
-      <c r="M71" s="11">
+      <c r="M71" s="13">
         <v>740</v>
       </c>
     </row>
-    <row r="72" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="11">
+    <row r="72" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="13">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="13">
         <v>500</v>
       </c>
-      <c r="F72" s="11">
+      <c r="F72" s="13">
         <v>150</v>
       </c>
-      <c r="G72" s="11">
-        <v>0</v>
-      </c>
-      <c r="H72" s="11">
-        <v>0</v>
-      </c>
-      <c r="I72" s="11">
-        <v>0</v>
-      </c>
-      <c r="J72" s="11">
+      <c r="G72" s="13">
+        <v>0</v>
+      </c>
+      <c r="H72" s="13">
+        <v>0</v>
+      </c>
+      <c r="I72" s="13">
+        <v>0</v>
+      </c>
+      <c r="J72" s="13">
         <v>1</v>
       </c>
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="L72" s="11">
+      <c r="L72" s="13">
         <v>750</v>
       </c>
-      <c r="M72" s="11">
+      <c r="M72" s="13">
         <v>750</v>
       </c>
     </row>
-    <row r="73" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="11">
+    <row r="73" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="13">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="13">
         <v>500</v>
       </c>
-      <c r="F73" s="11">
+      <c r="F73" s="13">
         <v>150</v>
       </c>
-      <c r="G73" s="11">
-        <v>0</v>
-      </c>
-      <c r="H73" s="11">
-        <v>0</v>
-      </c>
-      <c r="I73" s="11">
-        <v>0</v>
-      </c>
-      <c r="J73" s="11">
+      <c r="G73" s="13">
+        <v>0</v>
+      </c>
+      <c r="H73" s="13">
+        <v>0</v>
+      </c>
+      <c r="I73" s="13">
+        <v>0</v>
+      </c>
+      <c r="J73" s="13">
         <v>1</v>
       </c>
-      <c r="K73" s="12" t="s">
+      <c r="K73" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="L73" s="11">
+      <c r="L73" s="13">
         <v>760</v>
       </c>
-      <c r="M73" s="11">
+      <c r="M73" s="13">
         <v>760</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="11">
+    <row r="74" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="13">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="13">
         <v>500</v>
       </c>
-      <c r="F74" s="11">
+      <c r="F74" s="13">
         <v>150</v>
       </c>
-      <c r="G74" s="11">
-        <v>0</v>
-      </c>
-      <c r="H74" s="11">
-        <v>0</v>
-      </c>
-      <c r="I74" s="11">
-        <v>0</v>
-      </c>
-      <c r="J74" s="11">
+      <c r="G74" s="13">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13">
+        <v>0</v>
+      </c>
+      <c r="I74" s="13">
+        <v>0</v>
+      </c>
+      <c r="J74" s="13">
         <v>1</v>
       </c>
-      <c r="K74" s="12" t="s">
+      <c r="K74" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="L74" s="11">
+      <c r="L74" s="13">
         <v>770</v>
       </c>
-      <c r="M74" s="11">
+      <c r="M74" s="13">
         <v>770</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="11">
+    <row r="75" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="13">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="13">
         <v>500</v>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="13">
         <v>150</v>
       </c>
-      <c r="G75" s="11">
-        <v>0</v>
-      </c>
-      <c r="H75" s="11">
-        <v>0</v>
-      </c>
-      <c r="I75" s="11">
-        <v>0</v>
-      </c>
-      <c r="J75" s="11">
+      <c r="G75" s="13">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13">
+        <v>0</v>
+      </c>
+      <c r="I75" s="13">
+        <v>0</v>
+      </c>
+      <c r="J75" s="13">
         <v>1</v>
       </c>
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="L75" s="11">
+      <c r="L75" s="13">
         <v>780</v>
       </c>
-      <c r="M75" s="11">
+      <c r="M75" s="13">
         <v>780</v>
       </c>
     </row>
@@ -10553,171 +10765,171 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84">
+    <row r="84" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="13">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="13">
         <v>500</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="13">
         <v>150</v>
       </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L84">
+      <c r="G84" s="13">
+        <v>0</v>
+      </c>
+      <c r="H84" s="13">
+        <v>0</v>
+      </c>
+      <c r="I84" s="13">
+        <v>0</v>
+      </c>
+      <c r="J84" s="13">
+        <v>0</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="L84" s="13">
         <v>5000</v>
       </c>
-      <c r="M84">
+      <c r="M84" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85">
+    <row r="85" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="13">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="13">
         <v>500</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="13">
         <v>150</v>
       </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L85">
+      <c r="G85" s="13">
+        <v>0</v>
+      </c>
+      <c r="H85" s="13">
+        <v>0</v>
+      </c>
+      <c r="I85" s="13">
+        <v>0</v>
+      </c>
+      <c r="J85" s="13">
+        <v>0</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="L85" s="13">
         <v>5000</v>
       </c>
-      <c r="M85">
+      <c r="M85" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86">
+    <row r="86" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="13">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="13">
         <v>500</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="13">
         <v>150</v>
       </c>
-      <c r="G86">
-        <v>0</v>
-      </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L86">
+      <c r="G86" s="13">
+        <v>0</v>
+      </c>
+      <c r="H86" s="13">
+        <v>0</v>
+      </c>
+      <c r="I86" s="13">
+        <v>0</v>
+      </c>
+      <c r="J86" s="13">
+        <v>0</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="L86" s="13">
         <v>5000</v>
       </c>
-      <c r="M86">
+      <c r="M86" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87">
+    <row r="87" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="13">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="13">
         <v>500</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="13">
         <v>150</v>
       </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
+      <c r="G87" s="13">
+        <v>0</v>
+      </c>
+      <c r="H87" s="13">
+        <v>0</v>
+      </c>
+      <c r="I87" s="13">
+        <v>0</v>
+      </c>
+      <c r="J87" s="13">
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L87">
+        <v>430</v>
+      </c>
+      <c r="L87" s="13">
         <v>5000</v>
       </c>
-      <c r="M87">
+      <c r="M87" s="13">
         <v>5000</v>
       </c>
     </row>
@@ -10754,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>287</v>
+        <v>435</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -10796,7 +11008,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>287</v>
+        <v>430</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -10805,87 +11017,87 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90">
+    <row r="90" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="13">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="13">
         <v>500</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="13">
         <v>150</v>
       </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L90">
+      <c r="G90" s="13">
+        <v>0</v>
+      </c>
+      <c r="H90" s="13">
+        <v>0</v>
+      </c>
+      <c r="I90" s="13">
+        <v>0</v>
+      </c>
+      <c r="J90" s="13">
+        <v>0</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="L90" s="13">
         <v>5000</v>
       </c>
-      <c r="M90">
+      <c r="M90" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91">
+    <row r="91" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="13">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="13">
         <v>500</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="13">
         <v>150</v>
       </c>
-      <c r="G91">
-        <v>0</v>
-      </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L91">
+      <c r="G91" s="13">
+        <v>0</v>
+      </c>
+      <c r="H91" s="13">
+        <v>0</v>
+      </c>
+      <c r="I91" s="13">
+        <v>0</v>
+      </c>
+      <c r="J91" s="13">
+        <v>0</v>
+      </c>
+      <c r="K91" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="L91" s="13">
         <v>5000</v>
       </c>
-      <c r="M91">
+      <c r="M91" s="13">
         <v>5000</v>
       </c>
     </row>
@@ -10922,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>287</v>
+        <v>430</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -10931,45 +11143,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93">
+    <row r="93" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="13">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="13">
         <v>500</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="13">
         <v>150</v>
       </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L93">
+      <c r="G93" s="13">
+        <v>0</v>
+      </c>
+      <c r="H93" s="13">
+        <v>0</v>
+      </c>
+      <c r="I93" s="13">
+        <v>0</v>
+      </c>
+      <c r="J93" s="13">
+        <v>0</v>
+      </c>
+      <c r="K93" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="L93" s="13">
         <v>5000</v>
       </c>
-      <c r="M93">
+      <c r="M93" s="13">
         <v>5000</v>
       </c>
     </row>
@@ -11006,7 +11218,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>287</v>
+        <v>430</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11048,7 +11260,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11057,129 +11269,129 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96">
+    <row r="96" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="13">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="13">
         <v>500</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="13">
         <v>150</v>
       </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="J96">
-        <v>0</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L96">
+      <c r="G96" s="13">
+        <v>0</v>
+      </c>
+      <c r="H96" s="13">
+        <v>0</v>
+      </c>
+      <c r="I96" s="13">
+        <v>0</v>
+      </c>
+      <c r="J96" s="13">
+        <v>0</v>
+      </c>
+      <c r="K96" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="L96" s="13">
         <v>5000</v>
       </c>
-      <c r="M96">
+      <c r="M96" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97">
+    <row r="97" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="13">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="13">
         <v>500</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="13">
         <v>150</v>
       </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L97">
+      <c r="G97" s="13">
+        <v>0</v>
+      </c>
+      <c r="H97" s="13">
+        <v>0</v>
+      </c>
+      <c r="I97" s="13">
+        <v>0</v>
+      </c>
+      <c r="J97" s="13">
+        <v>0</v>
+      </c>
+      <c r="K97" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="L97" s="13">
         <v>5000</v>
       </c>
-      <c r="M97">
+      <c r="M97" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98">
+    <row r="98" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="13">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="13">
         <v>500</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="13">
         <v>150</v>
       </c>
-      <c r="G98">
-        <v>0</v>
-      </c>
-      <c r="H98">
-        <v>0</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L98">
+      <c r="G98" s="13">
+        <v>0</v>
+      </c>
+      <c r="H98" s="13">
+        <v>0</v>
+      </c>
+      <c r="I98" s="13">
+        <v>0</v>
+      </c>
+      <c r="J98" s="13">
+        <v>0</v>
+      </c>
+      <c r="K98" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="L98" s="13">
         <v>5000</v>
       </c>
-      <c r="M98">
+      <c r="M98" s="13">
         <v>5000</v>
       </c>
     </row>
@@ -11216,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>287</v>
+        <v>433</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -11258,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>287</v>
+        <v>434</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -11300,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>287</v>
+        <v>434</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -11309,339 +11521,339 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102">
+    <row r="102" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="13">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="13">
         <v>500</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="13">
         <v>150</v>
       </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L102">
+      <c r="G102" s="13">
+        <v>0</v>
+      </c>
+      <c r="H102" s="13">
+        <v>0</v>
+      </c>
+      <c r="I102" s="13">
+        <v>0</v>
+      </c>
+      <c r="J102" s="13">
+        <v>0</v>
+      </c>
+      <c r="K102" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="L102" s="13">
         <v>5000</v>
       </c>
-      <c r="M102">
+      <c r="M102" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103">
+    <row r="103" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="13">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="13">
         <v>500</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="13">
         <v>150</v>
       </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L103">
+      <c r="G103" s="13">
+        <v>0</v>
+      </c>
+      <c r="H103" s="13">
+        <v>0</v>
+      </c>
+      <c r="I103" s="13">
+        <v>0</v>
+      </c>
+      <c r="J103" s="13">
+        <v>0</v>
+      </c>
+      <c r="K103" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="L103" s="13">
         <v>5000</v>
       </c>
-      <c r="M103">
+      <c r="M103" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104">
+    <row r="104" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="13">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="13">
         <v>500</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="13">
         <v>150</v>
       </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104" s="2" t="s">
+      <c r="G104" s="13">
+        <v>0</v>
+      </c>
+      <c r="H104" s="13">
+        <v>0</v>
+      </c>
+      <c r="I104" s="13">
+        <v>0</v>
+      </c>
+      <c r="J104" s="13">
+        <v>0</v>
+      </c>
+      <c r="K104" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="L104">
+      <c r="L104" s="13">
         <v>5000</v>
       </c>
-      <c r="M104">
+      <c r="M104" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105">
+    <row r="105" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="13">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="13">
         <v>500</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="13">
         <v>150</v>
       </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-      <c r="H105">
-        <v>0</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L105">
+      <c r="G105" s="13">
+        <v>0</v>
+      </c>
+      <c r="H105" s="13">
+        <v>0</v>
+      </c>
+      <c r="I105" s="13">
+        <v>0</v>
+      </c>
+      <c r="J105" s="13">
+        <v>0</v>
+      </c>
+      <c r="K105" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="L105" s="13">
         <v>5000</v>
       </c>
-      <c r="M105">
+      <c r="M105" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106">
+    <row r="106" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="13">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="13">
         <v>500</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="13">
         <v>150</v>
       </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
-      <c r="H106">
-        <v>0</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L106">
+      <c r="G106" s="13">
+        <v>0</v>
+      </c>
+      <c r="H106" s="13">
+        <v>0</v>
+      </c>
+      <c r="I106" s="13">
+        <v>0</v>
+      </c>
+      <c r="J106" s="13">
+        <v>0</v>
+      </c>
+      <c r="K106" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="L106" s="13">
         <v>5000</v>
       </c>
-      <c r="M106">
+      <c r="M106" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107">
+    <row r="107" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="13">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="13">
         <v>500</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="13">
         <v>150</v>
       </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107" s="2" t="s">
+      <c r="G107" s="13">
+        <v>0</v>
+      </c>
+      <c r="H107" s="13">
+        <v>0</v>
+      </c>
+      <c r="I107" s="13">
+        <v>0</v>
+      </c>
+      <c r="J107" s="13">
+        <v>0</v>
+      </c>
+      <c r="K107" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="L107">
+      <c r="L107" s="13">
         <v>5000</v>
       </c>
-      <c r="M107">
+      <c r="M107" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108">
+    <row r="108" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="13">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="13">
         <v>500</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="13">
         <v>150</v>
       </c>
-      <c r="G108">
-        <v>0</v>
-      </c>
-      <c r="H108">
-        <v>0</v>
-      </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L108">
+      <c r="G108" s="13">
+        <v>0</v>
+      </c>
+      <c r="H108" s="13">
+        <v>0</v>
+      </c>
+      <c r="I108" s="13">
+        <v>0</v>
+      </c>
+      <c r="J108" s="13">
+        <v>0</v>
+      </c>
+      <c r="K108" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="L108" s="13">
         <v>5000</v>
       </c>
-      <c r="M108">
+      <c r="M108" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109">
+    <row r="109" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="13">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="13">
         <v>500</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="13">
         <v>150</v>
       </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109" s="2" t="s">
+      <c r="G109" s="13">
+        <v>0</v>
+      </c>
+      <c r="H109" s="13">
+        <v>0</v>
+      </c>
+      <c r="I109" s="13">
+        <v>0</v>
+      </c>
+      <c r="J109" s="13">
+        <v>0</v>
+      </c>
+      <c r="K109" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="L109">
+      <c r="L109" s="13">
         <v>5000</v>
       </c>
-      <c r="M109">
+      <c r="M109" s="13">
         <v>5000</v>
       </c>
     </row>
@@ -11678,7 +11890,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>287</v>
+        <v>430</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -11720,7 +11932,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>287</v>
+        <v>432</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -11729,255 +11941,255 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112">
+    <row r="112" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="11">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="11">
         <v>500</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="11">
         <v>150</v>
       </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112" s="2" t="s">
+      <c r="G112" s="11">
+        <v>0</v>
+      </c>
+      <c r="H112" s="11">
+        <v>0</v>
+      </c>
+      <c r="I112" s="11">
+        <v>0</v>
+      </c>
+      <c r="J112" s="11">
+        <v>0</v>
+      </c>
+      <c r="K112" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="L112">
+      <c r="L112" s="11">
         <v>5000</v>
       </c>
-      <c r="M112">
+      <c r="M112" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113">
+    <row r="113" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="11">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="11">
         <v>500</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="11">
         <v>150</v>
       </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
-      </c>
-      <c r="K113" s="2" t="s">
+      <c r="G113" s="11">
+        <v>0</v>
+      </c>
+      <c r="H113" s="11">
+        <v>0</v>
+      </c>
+      <c r="I113" s="11">
+        <v>0</v>
+      </c>
+      <c r="J113" s="11">
+        <v>0</v>
+      </c>
+      <c r="K113" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="L113">
+      <c r="L113" s="11">
         <v>5000</v>
       </c>
-      <c r="M113">
+      <c r="M113" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114">
+    <row r="114" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="11">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="11">
         <v>500</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="11">
         <v>150</v>
       </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
-        <v>0</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2" t="s">
+      <c r="G114" s="11">
+        <v>0</v>
+      </c>
+      <c r="H114" s="11">
+        <v>0</v>
+      </c>
+      <c r="I114" s="11">
+        <v>0</v>
+      </c>
+      <c r="J114" s="11">
+        <v>0</v>
+      </c>
+      <c r="K114" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="L114">
+      <c r="L114" s="11">
         <v>5000</v>
       </c>
-      <c r="M114">
+      <c r="M114" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115">
+    <row r="115" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="13">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="13">
         <v>500</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="13">
         <v>150</v>
       </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L115">
+      <c r="G115" s="13">
+        <v>0</v>
+      </c>
+      <c r="H115" s="13">
+        <v>0</v>
+      </c>
+      <c r="I115" s="13">
+        <v>0</v>
+      </c>
+      <c r="J115" s="13">
+        <v>0</v>
+      </c>
+      <c r="K115" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="L115" s="13">
         <v>5000</v>
       </c>
-      <c r="M115">
+      <c r="M115" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116">
+    <row r="116" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="13">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="13">
         <v>500</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="13">
         <v>150</v>
       </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116" s="2" t="s">
+      <c r="G116" s="13">
+        <v>0</v>
+      </c>
+      <c r="H116" s="13">
+        <v>0</v>
+      </c>
+      <c r="I116" s="13">
+        <v>0</v>
+      </c>
+      <c r="J116" s="13">
+        <v>0</v>
+      </c>
+      <c r="K116" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="L116">
+      <c r="L116" s="13">
         <v>5000</v>
       </c>
-      <c r="M116">
+      <c r="M116" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117">
+    <row r="117" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="11">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="11">
         <v>500</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="11">
         <v>150</v>
       </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L117">
+      <c r="G117" s="11">
+        <v>0</v>
+      </c>
+      <c r="H117" s="11">
+        <v>0</v>
+      </c>
+      <c r="I117" s="11">
+        <v>0</v>
+      </c>
+      <c r="J117" s="11">
+        <v>0</v>
+      </c>
+      <c r="K117" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="L117" s="11">
         <v>5000</v>
       </c>
-      <c r="M117">
+      <c r="M117" s="11">
         <v>5000</v>
       </c>
     </row>
@@ -12014,7 +12226,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>287</v>
+        <v>432</v>
       </c>
       <c r="L118">
         <v>5000</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC0A7BD-3FF3-423E-B404-34C46DEBAF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0808EB-94FD-43B1-A165-CE0A61BCC7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -6905,7 +6905,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6941,12 +6941,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9169,255 +9163,255 @@
         <v>330</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="13">
+    <row r="46" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" t="s">
         <v>385</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" t="s">
         <v>209</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" t="s">
         <v>210</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46">
         <v>500</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46">
         <v>150</v>
       </c>
-      <c r="G46" s="13">
-        <v>0</v>
-      </c>
-      <c r="H46" s="13">
-        <v>0</v>
-      </c>
-      <c r="I46" s="13">
-        <v>0</v>
-      </c>
-      <c r="J46" s="13">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
         <v>1</v>
       </c>
-      <c r="K46" s="14" t="s">
+      <c r="K46" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="L46" s="13">
+      <c r="L46">
         <v>340</v>
       </c>
-      <c r="M46" s="13">
+      <c r="M46">
         <v>340</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="13">
+    <row r="47" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" t="s">
         <v>386</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" t="s">
         <v>270</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" t="s">
         <v>268</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47">
         <v>500</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47">
         <v>150</v>
       </c>
-      <c r="G47" s="13">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13">
-        <v>0</v>
-      </c>
-      <c r="I47" s="13">
-        <v>0</v>
-      </c>
-      <c r="J47" s="13">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
         <v>1</v>
       </c>
-      <c r="K47" s="14" t="s">
+      <c r="K47" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="L47" s="13">
+      <c r="L47">
         <v>350</v>
       </c>
-      <c r="M47" s="13">
+      <c r="M47">
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="13">
+    <row r="48" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" t="s">
         <v>387</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" t="s">
         <v>271</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" t="s">
         <v>269</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48">
         <v>500</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48">
         <v>150</v>
       </c>
-      <c r="G48" s="13">
-        <v>0</v>
-      </c>
-      <c r="H48" s="13">
-        <v>0</v>
-      </c>
-      <c r="I48" s="13">
-        <v>0</v>
-      </c>
-      <c r="J48" s="13">
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
         <v>1</v>
       </c>
-      <c r="K48" s="14" t="s">
+      <c r="K48" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="L48" s="13">
+      <c r="L48">
         <v>360</v>
       </c>
-      <c r="M48" s="13">
+      <c r="M48">
         <v>360</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="13">
+    <row r="49" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" t="s">
         <v>388</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" t="s">
         <v>301</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" t="s">
         <v>303</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49">
         <v>500</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49">
         <v>150</v>
       </c>
-      <c r="G49" s="13">
-        <v>0</v>
-      </c>
-      <c r="H49" s="13">
-        <v>0</v>
-      </c>
-      <c r="I49" s="13">
-        <v>0</v>
-      </c>
-      <c r="J49" s="13">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
         <v>1</v>
       </c>
-      <c r="K49" s="14" t="s">
+      <c r="K49" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="L49" s="13">
+      <c r="L49">
         <v>370</v>
       </c>
-      <c r="M49" s="13">
+      <c r="M49">
         <v>370</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="13">
+    <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" t="s">
         <v>389</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" t="s">
         <v>302</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" t="s">
         <v>304</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50">
         <v>500</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50">
         <v>150</v>
       </c>
-      <c r="G50" s="13">
-        <v>0</v>
-      </c>
-      <c r="H50" s="13">
-        <v>0</v>
-      </c>
-      <c r="I50" s="13">
-        <v>0</v>
-      </c>
-      <c r="J50" s="13">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
         <v>1</v>
       </c>
-      <c r="K50" s="14" t="s">
+      <c r="K50" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="L50" s="13">
+      <c r="L50">
         <v>380</v>
       </c>
-      <c r="M50" s="13">
+      <c r="M50">
         <v>380</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="13">
+    <row r="51" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" t="s">
         <v>390</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" t="s">
         <v>279</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" t="s">
         <v>278</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51">
         <v>500</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51">
         <v>150</v>
       </c>
-      <c r="G51" s="13">
-        <v>0</v>
-      </c>
-      <c r="H51" s="13">
-        <v>0</v>
-      </c>
-      <c r="I51" s="13">
-        <v>0</v>
-      </c>
-      <c r="J51" s="13">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
         <v>1</v>
       </c>
-      <c r="K51" s="14" t="s">
+      <c r="K51" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="L51" s="13">
+      <c r="L51">
         <v>390</v>
       </c>
-      <c r="M51" s="13">
+      <c r="M51">
         <v>390</v>
       </c>
     </row>
@@ -9463,129 +9457,129 @@
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="13">
+    <row r="53" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" t="s">
         <v>391</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" t="s">
         <v>214</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" t="s">
         <v>213</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53">
         <v>500</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53">
         <v>150</v>
       </c>
-      <c r="G53" s="13">
-        <v>0</v>
-      </c>
-      <c r="H53" s="13">
-        <v>0</v>
-      </c>
-      <c r="I53" s="13">
-        <v>0</v>
-      </c>
-      <c r="J53" s="13">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
         <v>1</v>
       </c>
-      <c r="K53" s="14" t="s">
+      <c r="K53" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="L53" s="13">
+      <c r="L53">
         <v>410</v>
       </c>
-      <c r="M53" s="13">
+      <c r="M53">
         <v>410</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="13">
+    <row r="54" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" t="s">
         <v>392</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" t="s">
         <v>216</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" t="s">
         <v>215</v>
       </c>
-      <c r="E54" s="13">
+      <c r="E54">
         <v>500</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54">
         <v>150</v>
       </c>
-      <c r="G54" s="13">
-        <v>0</v>
-      </c>
-      <c r="H54" s="13">
-        <v>0</v>
-      </c>
-      <c r="I54" s="13">
-        <v>0</v>
-      </c>
-      <c r="J54" s="13">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
         <v>1</v>
       </c>
-      <c r="K54" s="14" t="s">
+      <c r="K54" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="L54" s="13">
+      <c r="L54">
         <v>500</v>
       </c>
-      <c r="M54" s="13">
+      <c r="M54">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="13">
+    <row r="55" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" t="s">
         <v>393</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" t="s">
         <v>218</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55">
         <v>500</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55">
         <v>150</v>
       </c>
-      <c r="G55" s="13">
-        <v>0</v>
-      </c>
-      <c r="H55" s="13">
-        <v>0</v>
-      </c>
-      <c r="I55" s="13">
-        <v>0</v>
-      </c>
-      <c r="J55" s="13">
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
         <v>1</v>
       </c>
-      <c r="K55" s="14" t="s">
+      <c r="K55" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L55" s="13">
+      <c r="L55">
         <v>510</v>
       </c>
-      <c r="M55" s="13">
+      <c r="M55">
         <v>510</v>
       </c>
     </row>
@@ -9757,171 +9751,171 @@
         <v>550</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="13">
+    <row r="60" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" t="s">
         <v>396</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" t="s">
         <v>228</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" t="s">
         <v>226</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60">
         <v>500</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60">
         <v>150</v>
       </c>
-      <c r="G60" s="13">
-        <v>0</v>
-      </c>
-      <c r="H60" s="13">
-        <v>0</v>
-      </c>
-      <c r="I60" s="13">
-        <v>0</v>
-      </c>
-      <c r="J60" s="13">
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
         <v>1</v>
       </c>
-      <c r="K60" s="14" t="s">
+      <c r="K60" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="L60" s="13">
+      <c r="L60">
         <v>560</v>
       </c>
-      <c r="M60" s="13">
+      <c r="M60">
         <v>560</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="13">
+    <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" t="s">
         <v>397</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" t="s">
         <v>232</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" t="s">
         <v>229</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61">
         <v>500</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61">
         <v>150</v>
       </c>
-      <c r="G61" s="13">
-        <v>0</v>
-      </c>
-      <c r="H61" s="13">
-        <v>0</v>
-      </c>
-      <c r="I61" s="13">
-        <v>0</v>
-      </c>
-      <c r="J61" s="13">
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
         <v>1</v>
       </c>
-      <c r="K61" s="14" t="s">
+      <c r="K61" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L61" s="13">
+      <c r="L61">
         <v>570</v>
       </c>
-      <c r="M61" s="13">
+      <c r="M61">
         <v>570</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="13">
+    <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" t="s">
         <v>398</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" t="s">
         <v>231</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" t="s">
         <v>230</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62">
         <v>500</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62">
         <v>150</v>
       </c>
-      <c r="G62" s="13">
-        <v>0</v>
-      </c>
-      <c r="H62" s="13">
-        <v>0</v>
-      </c>
-      <c r="I62" s="13">
-        <v>0</v>
-      </c>
-      <c r="J62" s="13">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
         <v>1</v>
       </c>
-      <c r="K62" s="14" t="s">
+      <c r="K62" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="L62" s="13">
+      <c r="L62">
         <v>580</v>
       </c>
-      <c r="M62" s="13">
+      <c r="M62">
         <v>580</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="13">
+    <row r="63" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" t="s">
         <v>399</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" t="s">
         <v>233</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63">
         <v>500</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63">
         <v>150</v>
       </c>
-      <c r="G63" s="13">
-        <v>0</v>
-      </c>
-      <c r="H63" s="13">
-        <v>0</v>
-      </c>
-      <c r="I63" s="13">
-        <v>0</v>
-      </c>
-      <c r="J63" s="13">
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
         <v>1</v>
       </c>
-      <c r="K63" s="14" t="s">
+      <c r="K63" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="L63" s="13">
+      <c r="L63">
         <v>590</v>
       </c>
-      <c r="M63" s="13">
+      <c r="M63">
         <v>590</v>
       </c>
     </row>
@@ -9967,45 +9961,45 @@
         <v>600</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="13">
+    <row r="65" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" t="s">
         <v>409</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" t="s">
         <v>238</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" t="s">
         <v>239</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65">
         <v>500</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65">
         <v>150</v>
       </c>
-      <c r="G65" s="13">
-        <v>0</v>
-      </c>
-      <c r="H65" s="13">
-        <v>0</v>
-      </c>
-      <c r="I65" s="13">
-        <v>0</v>
-      </c>
-      <c r="J65" s="13">
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
         <v>1</v>
       </c>
-      <c r="K65" s="14" t="s">
+      <c r="K65" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="L65" s="13">
+      <c r="L65">
         <v>610</v>
       </c>
-      <c r="M65" s="13">
+      <c r="M65">
         <v>610</v>
       </c>
     </row>
@@ -10051,381 +10045,381 @@
         <v>620</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="13">
+    <row r="67" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" t="s">
         <v>400</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" t="s">
         <v>241</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" t="s">
         <v>240</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67">
         <v>500</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67">
         <v>150</v>
       </c>
-      <c r="G67" s="13">
-        <v>0</v>
-      </c>
-      <c r="H67" s="13">
-        <v>0</v>
-      </c>
-      <c r="I67" s="13">
-        <v>0</v>
-      </c>
-      <c r="J67" s="13">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
         <v>1</v>
       </c>
-      <c r="K67" s="14" t="s">
+      <c r="K67" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="L67" s="13">
+      <c r="L67">
         <v>700</v>
       </c>
-      <c r="M67" s="13">
+      <c r="M67">
         <v>700</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="13">
+    <row r="68" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" t="s">
         <v>401</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" t="s">
         <v>264</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" t="s">
         <v>263</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68">
         <v>500</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68">
         <v>150</v>
       </c>
-      <c r="G68" s="13">
-        <v>0</v>
-      </c>
-      <c r="H68" s="13">
-        <v>0</v>
-      </c>
-      <c r="I68" s="13">
-        <v>0</v>
-      </c>
-      <c r="J68" s="13">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
         <v>1</v>
       </c>
-      <c r="K68" s="14" t="s">
+      <c r="K68" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="L68" s="13">
+      <c r="L68">
         <v>710</v>
       </c>
-      <c r="M68" s="13">
+      <c r="M68">
         <v>710</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="13">
+    <row r="69" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" t="s">
         <v>402</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" t="s">
         <v>243</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="D69" t="s">
         <v>242</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69">
         <v>500</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69">
         <v>150</v>
       </c>
-      <c r="G69" s="13">
-        <v>0</v>
-      </c>
-      <c r="H69" s="13">
-        <v>0</v>
-      </c>
-      <c r="I69" s="13">
-        <v>0</v>
-      </c>
-      <c r="J69" s="13">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
         <v>1</v>
       </c>
-      <c r="K69" s="14" t="s">
+      <c r="K69" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="L69" s="13">
+      <c r="L69">
         <v>720</v>
       </c>
-      <c r="M69" s="13">
+      <c r="M69">
         <v>720</v>
       </c>
     </row>
-    <row r="70" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="13">
+    <row r="70" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" t="s">
         <v>403</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" t="s">
         <v>245</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" t="s">
         <v>244</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70">
         <v>500</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70">
         <v>150</v>
       </c>
-      <c r="G70" s="13">
-        <v>0</v>
-      </c>
-      <c r="H70" s="13">
-        <v>0</v>
-      </c>
-      <c r="I70" s="13">
-        <v>0</v>
-      </c>
-      <c r="J70" s="13">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
         <v>1</v>
       </c>
-      <c r="K70" s="14" t="s">
+      <c r="K70" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="L70" s="13">
+      <c r="L70">
         <v>730</v>
       </c>
-      <c r="M70" s="13">
+      <c r="M70">
         <v>730</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="13">
+    <row r="71" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" t="s">
         <v>404</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" t="s">
         <v>246</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" t="s">
         <v>247</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71">
         <v>500</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71">
         <v>150</v>
       </c>
-      <c r="G71" s="13">
-        <v>0</v>
-      </c>
-      <c r="H71" s="13">
-        <v>0</v>
-      </c>
-      <c r="I71" s="13">
-        <v>0</v>
-      </c>
-      <c r="J71" s="13">
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
         <v>1</v>
       </c>
-      <c r="K71" s="14" t="s">
+      <c r="K71" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="L71" s="13">
+      <c r="L71">
         <v>740</v>
       </c>
-      <c r="M71" s="13">
+      <c r="M71">
         <v>740</v>
       </c>
     </row>
-    <row r="72" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="13">
+    <row r="72" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" t="s">
         <v>405</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" t="s">
         <v>253</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" t="s">
         <v>252</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72">
         <v>500</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72">
         <v>150</v>
       </c>
-      <c r="G72" s="13">
-        <v>0</v>
-      </c>
-      <c r="H72" s="13">
-        <v>0</v>
-      </c>
-      <c r="I72" s="13">
-        <v>0</v>
-      </c>
-      <c r="J72" s="13">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
         <v>1</v>
       </c>
-      <c r="K72" s="14" t="s">
+      <c r="K72" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="L72" s="13">
+      <c r="L72">
         <v>750</v>
       </c>
-      <c r="M72" s="13">
+      <c r="M72">
         <v>750</v>
       </c>
     </row>
-    <row r="73" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="13">
+    <row r="73" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" t="s">
         <v>406</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" t="s">
         <v>249</v>
       </c>
-      <c r="D73" s="13" t="s">
+      <c r="D73" t="s">
         <v>248</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73">
         <v>500</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73">
         <v>150</v>
       </c>
-      <c r="G73" s="13">
-        <v>0</v>
-      </c>
-      <c r="H73" s="13">
-        <v>0</v>
-      </c>
-      <c r="I73" s="13">
-        <v>0</v>
-      </c>
-      <c r="J73" s="13">
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
         <v>1</v>
       </c>
-      <c r="K73" s="14" t="s">
+      <c r="K73" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="L73" s="13">
+      <c r="L73">
         <v>760</v>
       </c>
-      <c r="M73" s="13">
+      <c r="M73">
         <v>760</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="13">
+    <row r="74" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" t="s">
         <v>407</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" t="s">
         <v>266</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" t="s">
         <v>265</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74">
         <v>500</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74">
         <v>150</v>
       </c>
-      <c r="G74" s="13">
-        <v>0</v>
-      </c>
-      <c r="H74" s="13">
-        <v>0</v>
-      </c>
-      <c r="I74" s="13">
-        <v>0</v>
-      </c>
-      <c r="J74" s="13">
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
         <v>1</v>
       </c>
-      <c r="K74" s="14" t="s">
+      <c r="K74" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="L74" s="13">
+      <c r="L74">
         <v>770</v>
       </c>
-      <c r="M74" s="13">
+      <c r="M74">
         <v>770</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="13">
+    <row r="75" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" t="s">
         <v>410</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" t="s">
         <v>273</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" t="s">
         <v>272</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75">
         <v>500</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75">
         <v>150</v>
       </c>
-      <c r="G75" s="13">
-        <v>0</v>
-      </c>
-      <c r="H75" s="13">
-        <v>0</v>
-      </c>
-      <c r="I75" s="13">
-        <v>0</v>
-      </c>
-      <c r="J75" s="13">
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
         <v>1</v>
       </c>
-      <c r="K75" s="14" t="s">
+      <c r="K75" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="L75" s="13">
+      <c r="L75">
         <v>780</v>
       </c>
-      <c r="M75" s="13">
+      <c r="M75">
         <v>780</v>
       </c>
     </row>
@@ -10765,171 +10759,171 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="84" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="13">
+    <row r="84" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" t="s">
         <v>381</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" t="s">
         <v>293</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" t="s">
         <v>292</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84">
         <v>500</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84">
         <v>150</v>
       </c>
-      <c r="G84" s="13">
-        <v>0</v>
-      </c>
-      <c r="H84" s="13">
-        <v>0</v>
-      </c>
-      <c r="I84" s="13">
-        <v>0</v>
-      </c>
-      <c r="J84" s="13">
-        <v>0</v>
-      </c>
-      <c r="K84" s="14" t="s">
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="L84" s="13">
+      <c r="L84">
         <v>5000</v>
       </c>
-      <c r="M84" s="13">
+      <c r="M84">
         <v>5000</v>
       </c>
     </row>
-    <row r="85" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="13">
+    <row r="85" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" t="s">
         <v>381</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" t="s">
         <v>340</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D85" t="s">
         <v>339</v>
       </c>
-      <c r="E85" s="13">
+      <c r="E85">
         <v>500</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85">
         <v>150</v>
       </c>
-      <c r="G85" s="13">
-        <v>0</v>
-      </c>
-      <c r="H85" s="13">
-        <v>0</v>
-      </c>
-      <c r="I85" s="13">
-        <v>0</v>
-      </c>
-      <c r="J85" s="13">
-        <v>0</v>
-      </c>
-      <c r="K85" s="14" t="s">
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="L85" s="13">
+      <c r="L85">
         <v>5000</v>
       </c>
-      <c r="M85" s="13">
+      <c r="M85">
         <v>5000</v>
       </c>
     </row>
-    <row r="86" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="13">
+    <row r="86" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" t="s">
         <v>381</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" t="s">
         <v>342</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" t="s">
         <v>341</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86">
         <v>500</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86">
         <v>150</v>
       </c>
-      <c r="G86" s="13">
-        <v>0</v>
-      </c>
-      <c r="H86" s="13">
-        <v>0</v>
-      </c>
-      <c r="I86" s="13">
-        <v>0</v>
-      </c>
-      <c r="J86" s="13">
-        <v>0</v>
-      </c>
-      <c r="K86" s="14" t="s">
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="L86" s="13">
+      <c r="L86">
         <v>5000</v>
       </c>
-      <c r="M86" s="13">
+      <c r="M86">
         <v>5000</v>
       </c>
     </row>
-    <row r="87" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="13">
+    <row r="87" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" t="s">
         <v>381</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" t="s">
         <v>379</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" t="s">
         <v>378</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87">
         <v>500</v>
       </c>
-      <c r="F87" s="13">
+      <c r="F87">
         <v>150</v>
       </c>
-      <c r="G87" s="13">
-        <v>0</v>
-      </c>
-      <c r="H87" s="13">
-        <v>0</v>
-      </c>
-      <c r="I87" s="13">
-        <v>0</v>
-      </c>
-      <c r="J87" s="13">
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="L87" s="13">
+      <c r="L87">
         <v>5000</v>
       </c>
-      <c r="M87" s="13">
+      <c r="M87">
         <v>5000</v>
       </c>
     </row>
@@ -11017,87 +11011,87 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="13">
+    <row r="90" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" t="s">
         <v>381</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" t="s">
         <v>329</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" t="s">
         <v>330</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90">
         <v>500</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90">
         <v>150</v>
       </c>
-      <c r="G90" s="13">
-        <v>0</v>
-      </c>
-      <c r="H90" s="13">
-        <v>0</v>
-      </c>
-      <c r="I90" s="13">
-        <v>0</v>
-      </c>
-      <c r="J90" s="13">
-        <v>0</v>
-      </c>
-      <c r="K90" s="14" t="s">
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="L90" s="13">
+      <c r="L90">
         <v>5000</v>
       </c>
-      <c r="M90" s="13">
+      <c r="M90">
         <v>5000</v>
       </c>
     </row>
-    <row r="91" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="13">
+    <row r="91" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" t="s">
         <v>381</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" t="s">
         <v>332</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" t="s">
         <v>331</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91">
         <v>500</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91">
         <v>150</v>
       </c>
-      <c r="G91" s="13">
-        <v>0</v>
-      </c>
-      <c r="H91" s="13">
-        <v>0</v>
-      </c>
-      <c r="I91" s="13">
-        <v>0</v>
-      </c>
-      <c r="J91" s="13">
-        <v>0</v>
-      </c>
-      <c r="K91" s="14" t="s">
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="L91" s="13">
+      <c r="L91">
         <v>5000</v>
       </c>
-      <c r="M91" s="13">
+      <c r="M91">
         <v>5000</v>
       </c>
     </row>
@@ -11143,45 +11137,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="93" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="13">
+    <row r="93" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A93">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" t="s">
         <v>381</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" t="s">
         <v>335</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" t="s">
         <v>336</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93">
         <v>500</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93">
         <v>150</v>
       </c>
-      <c r="G93" s="13">
-        <v>0</v>
-      </c>
-      <c r="H93" s="13">
-        <v>0</v>
-      </c>
-      <c r="I93" s="13">
-        <v>0</v>
-      </c>
-      <c r="J93" s="13">
-        <v>0</v>
-      </c>
-      <c r="K93" s="14" t="s">
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="L93" s="13">
+      <c r="L93">
         <v>5000</v>
       </c>
-      <c r="M93" s="13">
+      <c r="M93">
         <v>5000</v>
       </c>
     </row>
@@ -11269,129 +11263,129 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="96" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="13">
+    <row r="96" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A96">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" t="s">
         <v>381</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" t="s">
         <v>345</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" t="s">
         <v>343</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96">
         <v>500</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96">
         <v>150</v>
       </c>
-      <c r="G96" s="13">
-        <v>0</v>
-      </c>
-      <c r="H96" s="13">
-        <v>0</v>
-      </c>
-      <c r="I96" s="13">
-        <v>0</v>
-      </c>
-      <c r="J96" s="13">
-        <v>0</v>
-      </c>
-      <c r="K96" s="14" t="s">
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="L96" s="13">
+      <c r="L96">
         <v>5000</v>
       </c>
-      <c r="M96" s="13">
+      <c r="M96">
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="13">
+    <row r="97" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A97">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" t="s">
         <v>381</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" t="s">
         <v>346</v>
       </c>
-      <c r="D97" s="13" t="s">
+      <c r="D97" t="s">
         <v>344</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97">
         <v>500</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97">
         <v>150</v>
       </c>
-      <c r="G97" s="13">
-        <v>0</v>
-      </c>
-      <c r="H97" s="13">
-        <v>0</v>
-      </c>
-      <c r="I97" s="13">
-        <v>0</v>
-      </c>
-      <c r="J97" s="13">
-        <v>0</v>
-      </c>
-      <c r="K97" s="14" t="s">
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="L97" s="13">
+      <c r="L97">
         <v>5000</v>
       </c>
-      <c r="M97" s="13">
+      <c r="M97">
         <v>5000</v>
       </c>
     </row>
-    <row r="98" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="13">
+    <row r="98" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A98">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" t="s">
         <v>334</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" t="s">
         <v>333</v>
       </c>
-      <c r="E98" s="13">
+      <c r="E98">
         <v>500</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98">
         <v>150</v>
       </c>
-      <c r="G98" s="13">
-        <v>0</v>
-      </c>
-      <c r="H98" s="13">
-        <v>0</v>
-      </c>
-      <c r="I98" s="13">
-        <v>0</v>
-      </c>
-      <c r="J98" s="13">
-        <v>0</v>
-      </c>
-      <c r="K98" s="14" t="s">
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="L98" s="13">
+      <c r="L98">
         <v>5000</v>
       </c>
-      <c r="M98" s="13">
+      <c r="M98">
         <v>5000</v>
       </c>
     </row>
@@ -11521,339 +11515,339 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="102" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="13">
+    <row r="102" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A102">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" t="s">
         <v>381</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" t="s">
         <v>353</v>
       </c>
-      <c r="D102" s="13" t="s">
+      <c r="D102" t="s">
         <v>351</v>
       </c>
-      <c r="E102" s="13">
+      <c r="E102">
         <v>500</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102">
         <v>150</v>
       </c>
-      <c r="G102" s="13">
-        <v>0</v>
-      </c>
-      <c r="H102" s="13">
-        <v>0</v>
-      </c>
-      <c r="I102" s="13">
-        <v>0</v>
-      </c>
-      <c r="J102" s="13">
-        <v>0</v>
-      </c>
-      <c r="K102" s="14" t="s">
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="L102" s="13">
+      <c r="L102">
         <v>5000</v>
       </c>
-      <c r="M102" s="13">
+      <c r="M102">
         <v>5000</v>
       </c>
     </row>
-    <row r="103" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="13">
+    <row r="103" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A103">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" t="s">
         <v>381</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" t="s">
         <v>354</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" t="s">
         <v>352</v>
       </c>
-      <c r="E103" s="13">
+      <c r="E103">
         <v>500</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103">
         <v>150</v>
       </c>
-      <c r="G103" s="13">
-        <v>0</v>
-      </c>
-      <c r="H103" s="13">
-        <v>0</v>
-      </c>
-      <c r="I103" s="13">
-        <v>0</v>
-      </c>
-      <c r="J103" s="13">
-        <v>0</v>
-      </c>
-      <c r="K103" s="14" t="s">
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="L103" s="13">
+      <c r="L103">
         <v>5000</v>
       </c>
-      <c r="M103" s="13">
+      <c r="M103">
         <v>5000</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="13">
+    <row r="104" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A104">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" t="s">
         <v>381</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" t="s">
         <v>356</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D104" t="s">
         <v>355</v>
       </c>
-      <c r="E104" s="13">
+      <c r="E104">
         <v>500</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104">
         <v>150</v>
       </c>
-      <c r="G104" s="13">
-        <v>0</v>
-      </c>
-      <c r="H104" s="13">
-        <v>0</v>
-      </c>
-      <c r="I104" s="13">
-        <v>0</v>
-      </c>
-      <c r="J104" s="13">
-        <v>0</v>
-      </c>
-      <c r="K104" s="14" t="s">
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="L104" s="13">
+      <c r="L104">
         <v>5000</v>
       </c>
-      <c r="M104" s="13">
+      <c r="M104">
         <v>5000</v>
       </c>
     </row>
-    <row r="105" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="13">
+    <row r="105" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A105">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" t="s">
         <v>381</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" t="s">
         <v>358</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D105" t="s">
         <v>357</v>
       </c>
-      <c r="E105" s="13">
+      <c r="E105">
         <v>500</v>
       </c>
-      <c r="F105" s="13">
+      <c r="F105">
         <v>150</v>
       </c>
-      <c r="G105" s="13">
-        <v>0</v>
-      </c>
-      <c r="H105" s="13">
-        <v>0</v>
-      </c>
-      <c r="I105" s="13">
-        <v>0</v>
-      </c>
-      <c r="J105" s="13">
-        <v>0</v>
-      </c>
-      <c r="K105" s="14" t="s">
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="L105" s="13">
+      <c r="L105">
         <v>5000</v>
       </c>
-      <c r="M105" s="13">
+      <c r="M105">
         <v>5000</v>
       </c>
     </row>
-    <row r="106" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="13">
+    <row r="106" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A106">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" t="s">
         <v>381</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" t="s">
         <v>360</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" t="s">
         <v>359</v>
       </c>
-      <c r="E106" s="13">
+      <c r="E106">
         <v>500</v>
       </c>
-      <c r="F106" s="13">
+      <c r="F106">
         <v>150</v>
       </c>
-      <c r="G106" s="13">
-        <v>0</v>
-      </c>
-      <c r="H106" s="13">
-        <v>0</v>
-      </c>
-      <c r="I106" s="13">
-        <v>0</v>
-      </c>
-      <c r="J106" s="13">
-        <v>0</v>
-      </c>
-      <c r="K106" s="14" t="s">
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="L106" s="13">
+      <c r="L106">
         <v>5000</v>
       </c>
-      <c r="M106" s="13">
+      <c r="M106">
         <v>5000</v>
       </c>
     </row>
-    <row r="107" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="13">
+    <row r="107" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A107">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" t="s">
         <v>381</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" t="s">
         <v>364</v>
       </c>
-      <c r="D107" s="13" t="s">
+      <c r="D107" t="s">
         <v>361</v>
       </c>
-      <c r="E107" s="13">
+      <c r="E107">
         <v>500</v>
       </c>
-      <c r="F107" s="13">
+      <c r="F107">
         <v>150</v>
       </c>
-      <c r="G107" s="13">
-        <v>0</v>
-      </c>
-      <c r="H107" s="13">
-        <v>0</v>
-      </c>
-      <c r="I107" s="13">
-        <v>0</v>
-      </c>
-      <c r="J107" s="13">
-        <v>0</v>
-      </c>
-      <c r="K107" s="14" t="s">
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="L107" s="13">
+      <c r="L107">
         <v>5000</v>
       </c>
-      <c r="M107" s="13">
+      <c r="M107">
         <v>5000</v>
       </c>
     </row>
-    <row r="108" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="13">
+    <row r="108" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A108">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" t="s">
         <v>381</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" t="s">
         <v>365</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D108" t="s">
         <v>362</v>
       </c>
-      <c r="E108" s="13">
+      <c r="E108">
         <v>500</v>
       </c>
-      <c r="F108" s="13">
+      <c r="F108">
         <v>150</v>
       </c>
-      <c r="G108" s="13">
-        <v>0</v>
-      </c>
-      <c r="H108" s="13">
-        <v>0</v>
-      </c>
-      <c r="I108" s="13">
-        <v>0</v>
-      </c>
-      <c r="J108" s="13">
-        <v>0</v>
-      </c>
-      <c r="K108" s="14" t="s">
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="L108" s="13">
+      <c r="L108">
         <v>5000</v>
       </c>
-      <c r="M108" s="13">
+      <c r="M108">
         <v>5000</v>
       </c>
     </row>
-    <row r="109" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="13">
+    <row r="109" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A109">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" t="s">
         <v>381</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" t="s">
         <v>366</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" t="s">
         <v>363</v>
       </c>
-      <c r="E109" s="13">
+      <c r="E109">
         <v>500</v>
       </c>
-      <c r="F109" s="13">
+      <c r="F109">
         <v>150</v>
       </c>
-      <c r="G109" s="13">
-        <v>0</v>
-      </c>
-      <c r="H109" s="13">
-        <v>0</v>
-      </c>
-      <c r="I109" s="13">
-        <v>0</v>
-      </c>
-      <c r="J109" s="13">
-        <v>0</v>
-      </c>
-      <c r="K109" s="14" t="s">
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="L109" s="13">
+      <c r="L109">
         <v>5000</v>
       </c>
-      <c r="M109" s="13">
+      <c r="M109">
         <v>5000</v>
       </c>
     </row>
@@ -12067,87 +12061,87 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="115" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="13">
+    <row r="115" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" t="s">
         <v>381</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" t="s">
         <v>373</v>
       </c>
-      <c r="D115" s="13" t="s">
+      <c r="D115" t="s">
         <v>372</v>
       </c>
-      <c r="E115" s="13">
+      <c r="E115">
         <v>500</v>
       </c>
-      <c r="F115" s="13">
+      <c r="F115">
         <v>150</v>
       </c>
-      <c r="G115" s="13">
-        <v>0</v>
-      </c>
-      <c r="H115" s="13">
-        <v>0</v>
-      </c>
-      <c r="I115" s="13">
-        <v>0</v>
-      </c>
-      <c r="J115" s="13">
-        <v>0</v>
-      </c>
-      <c r="K115" s="14" t="s">
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="L115" s="13">
+      <c r="L115">
         <v>5000</v>
       </c>
-      <c r="M115" s="13">
+      <c r="M115">
         <v>5000</v>
       </c>
     </row>
-    <row r="116" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="13">
+    <row r="116" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A116">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" t="s">
         <v>381</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" t="s">
         <v>375</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" t="s">
         <v>374</v>
       </c>
-      <c r="E116" s="13">
+      <c r="E116">
         <v>500</v>
       </c>
-      <c r="F116" s="13">
+      <c r="F116">
         <v>150</v>
       </c>
-      <c r="G116" s="13">
-        <v>0</v>
-      </c>
-      <c r="H116" s="13">
-        <v>0</v>
-      </c>
-      <c r="I116" s="13">
-        <v>0</v>
-      </c>
-      <c r="J116" s="13">
-        <v>0</v>
-      </c>
-      <c r="K116" s="14" t="s">
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="L116" s="13">
+      <c r="L116">
         <v>5000</v>
       </c>
-      <c r="M116" s="13">
+      <c r="M116">
         <v>5000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0808EB-94FD-43B1-A165-CE0A61BCC7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE47FC8-65C2-4F79-8456-E5AFB6AF011C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1875" yWindow="870" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="452">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -6803,6 +6803,17 @@
     <rPh sb="18" eb="20">
       <t>マホウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイアーフラワーの本</t>
+    <rPh sb="10" eb="11">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_fire_flowers_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7257,7 +7268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -7317,7 +7328,7 @@
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A118" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A119" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -10978,10 +10989,10 @@
         <v>381</v>
       </c>
       <c r="C89" t="s">
-        <v>285</v>
+        <v>451</v>
       </c>
       <c r="D89" t="s">
-        <v>286</v>
+        <v>450</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11002,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11020,10 +11031,10 @@
         <v>381</v>
       </c>
       <c r="C90" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="D90" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11044,7 +11055,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11062,10 +11073,10 @@
         <v>381</v>
       </c>
       <c r="C91" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D91" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11086,7 +11097,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11104,10 +11115,10 @@
         <v>381</v>
       </c>
       <c r="C92" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="D92" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11128,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11146,10 +11157,10 @@
         <v>381</v>
       </c>
       <c r="C93" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D93" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11170,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11188,10 +11199,10 @@
         <v>381</v>
       </c>
       <c r="C94" t="s">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="D94" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11212,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11230,10 +11241,10 @@
         <v>381</v>
       </c>
       <c r="C95" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="D95" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11254,7 +11265,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11272,10 +11283,10 @@
         <v>381</v>
       </c>
       <c r="C96" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D96" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -11296,7 +11307,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11314,10 +11325,10 @@
         <v>381</v>
       </c>
       <c r="C97" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D97" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -11338,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11356,10 +11367,10 @@
         <v>381</v>
       </c>
       <c r="C98" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D98" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -11380,7 +11391,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -11398,10 +11409,10 @@
         <v>381</v>
       </c>
       <c r="C99" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="D99" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -11422,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -11440,10 +11451,10 @@
         <v>381</v>
       </c>
       <c r="C100" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="D100" t="s">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -11464,7 +11475,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -11482,10 +11493,10 @@
         <v>381</v>
       </c>
       <c r="C101" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D101" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -11524,10 +11535,10 @@
         <v>381</v>
       </c>
       <c r="C102" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -11548,7 +11559,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -11566,10 +11577,10 @@
         <v>381</v>
       </c>
       <c r="C103" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D103" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -11590,7 +11601,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -11608,10 +11619,10 @@
         <v>381</v>
       </c>
       <c r="C104" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D104" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -11632,7 +11643,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>287</v>
+        <v>445</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -11650,10 +11661,10 @@
         <v>381</v>
       </c>
       <c r="C105" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -11674,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>444</v>
+        <v>287</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -11692,10 +11703,10 @@
         <v>381</v>
       </c>
       <c r="C106" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -11716,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -11734,10 +11745,10 @@
         <v>381</v>
       </c>
       <c r="C107" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -11758,7 +11769,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>287</v>
+        <v>442</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -11776,10 +11787,10 @@
         <v>381</v>
       </c>
       <c r="C108" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -11800,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>439</v>
+        <v>287</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -11818,10 +11829,10 @@
         <v>381</v>
       </c>
       <c r="C109" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -11842,7 +11853,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>287</v>
+        <v>439</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -11860,10 +11871,10 @@
         <v>381</v>
       </c>
       <c r="C110" t="s">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="D110" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -11884,7 +11895,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>430</v>
+        <v>287</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -11902,10 +11913,10 @@
         <v>381</v>
       </c>
       <c r="C111" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D111" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -11926,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -11935,45 +11946,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="11">
+    <row r="112" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A112">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" t="s">
         <v>381</v>
       </c>
-      <c r="C112" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="E112" s="11">
+      <c r="C112" t="s">
+        <v>313</v>
+      </c>
+      <c r="D112" t="s">
+        <v>314</v>
+      </c>
+      <c r="E112">
         <v>500</v>
       </c>
-      <c r="F112" s="11">
+      <c r="F112">
         <v>150</v>
       </c>
-      <c r="G112" s="11">
-        <v>0</v>
-      </c>
-      <c r="H112" s="11">
-        <v>0</v>
-      </c>
-      <c r="I112" s="11">
-        <v>0</v>
-      </c>
-      <c r="J112" s="11">
-        <v>0</v>
-      </c>
-      <c r="K112" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="L112" s="11">
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L112">
         <v>5000</v>
       </c>
-      <c r="M112" s="11">
+      <c r="M112">
         <v>5000</v>
       </c>
     </row>
@@ -11986,10 +11997,10 @@
         <v>381</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E113" s="11">
         <v>500</v>
@@ -12028,10 +12039,10 @@
         <v>381</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E114" s="11">
         <v>500</v>
@@ -12061,45 +12072,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115">
+    <row r="115" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="11">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C115" t="s">
-        <v>373</v>
-      </c>
-      <c r="D115" t="s">
-        <v>372</v>
-      </c>
-      <c r="E115">
+      <c r="C115" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="E115" s="11">
         <v>500</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="11">
         <v>150</v>
       </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="L115">
+      <c r="G115" s="11">
+        <v>0</v>
+      </c>
+      <c r="H115" s="11">
+        <v>0</v>
+      </c>
+      <c r="I115" s="11">
+        <v>0</v>
+      </c>
+      <c r="J115" s="11">
+        <v>0</v>
+      </c>
+      <c r="K115" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="L115" s="11">
         <v>5000</v>
       </c>
-      <c r="M115">
+      <c r="M115" s="11">
         <v>5000</v>
       </c>
     </row>
@@ -12112,10 +12123,10 @@
         <v>381</v>
       </c>
       <c r="C116" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D116" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -12136,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>287</v>
+        <v>443</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12145,102 +12156,103 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="117" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="11">
+    <row r="117" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A117">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" t="s">
         <v>381</v>
       </c>
-      <c r="C117" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="E117" s="11">
+      <c r="C117" t="s">
+        <v>375</v>
+      </c>
+      <c r="D117" t="s">
+        <v>374</v>
+      </c>
+      <c r="E117">
         <v>500</v>
       </c>
-      <c r="F117" s="11">
+      <c r="F117">
         <v>150</v>
       </c>
-      <c r="G117" s="11">
-        <v>0</v>
-      </c>
-      <c r="H117" s="11">
-        <v>0</v>
-      </c>
-      <c r="I117" s="11">
-        <v>0</v>
-      </c>
-      <c r="J117" s="11">
-        <v>0</v>
-      </c>
-      <c r="K117" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="L117" s="11">
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L117">
         <v>5000</v>
       </c>
-      <c r="M117" s="11">
+      <c r="M117">
         <v>5000</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118">
+    <row r="118" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="11">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E118" s="11">
+        <v>500</v>
+      </c>
+      <c r="F118" s="11">
+        <v>150</v>
+      </c>
+      <c r="G118" s="11">
+        <v>0</v>
+      </c>
+      <c r="H118" s="11">
+        <v>0</v>
+      </c>
+      <c r="I118" s="11">
+        <v>0</v>
+      </c>
+      <c r="J118" s="11">
+        <v>0</v>
+      </c>
+      <c r="K118" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="L118" s="11">
+        <v>5000</v>
+      </c>
+      <c r="M118" s="11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="B119" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" t="s">
         <v>315</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D119" t="s">
         <v>316</v>
-      </c>
-      <c r="E118">
-        <v>500</v>
-      </c>
-      <c r="F118">
-        <v>150</v>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L118">
-        <v>5000</v>
-      </c>
-      <c r="M118">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119">
-        <v>10000</v>
-      </c>
-      <c r="B119" t="s">
-        <v>170</v>
-      </c>
-      <c r="C119" t="s">
-        <v>174</v>
-      </c>
-      <c r="D119" t="s">
-        <v>175</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -12258,15 +12270,56 @@
         <v>0</v>
       </c>
       <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="L119">
+        <v>5000</v>
+      </c>
+      <c r="M119">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>10000</v>
+      </c>
+      <c r="B120" t="s">
+        <v>170</v>
+      </c>
+      <c r="C120" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" t="s">
+        <v>175</v>
+      </c>
+      <c r="E120">
+        <v>500</v>
+      </c>
+      <c r="F120">
+        <v>150</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
         <v>1</v>
       </c>
-      <c r="K119" s="2" t="s">
+      <c r="K120" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L119">
+      <c r="L120">
         <v>9000</v>
       </c>
-      <c r="M119">
+      <c r="M120">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE47FC8-65C2-4F79-8456-E5AFB6AF011C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B64F11-2FA1-4AB5-8E28-DA92170583F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="870" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B64F11-2FA1-4AB5-8E28-DA92170583F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5147A3C3-0DC1-4044-B7F8-2950A9FB964A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView minimized="1" xWindow="2340" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5147A3C3-0DC1-4044-B7F8-2950A9FB964A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A460657C-D11B-4193-8969-6A781589ADFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2340" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -6682,13 +6682,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ルミエールエピファニアの賞品</t>
-    <rPh sb="12" eb="14">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ガレット・デ・ロワの賞品</t>
     <rPh sb="10" eb="12">
       <t>ショウヒン</t>
@@ -6814,6 +6807,19 @@
   </si>
   <si>
     <t>mg_fire_flowers_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミエールエピファニアの賞品or秋エリアのお店</t>
+    <rPh sb="12" eb="14">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ミセ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10845,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L85">
         <v>5000</v>
@@ -10887,7 +10893,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L86">
         <v>5000</v>
@@ -10989,10 +10995,10 @@
         <v>381</v>
       </c>
       <c r="C89" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D89" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11013,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11097,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11139,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11223,7 +11229,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11349,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11601,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -11643,7 +11649,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -11727,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -11769,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -11853,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12147,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12231,7 +12237,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L118" s="11">
         <v>5000</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A460657C-D11B-4193-8969-6A781589ADFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63045AC7-C4F0-4314-8919-1CD5482B4804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2340" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="462">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -3117,63 +3117,6 @@
     </rPh>
     <rPh sb="916" eb="919">
       <t>ユメキブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【ブラックチョコレートのレシピ】
-①&lt;color=#BA9535FF&gt;カカオ豆&lt;/color&gt;　→　ローストする。　魔法&lt;color=#FF5CA1FF&gt;「豆焼き」&lt;/color&gt;を使う
-焼いた豆の殻むき　→　カカオニブができる。
-②&lt;color=#BA9535FF&gt;カカオニブ&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;をまぜる。
-&lt;color=#FF5CA1FF&gt;すりばち&lt;/color&gt;で、豆をつぶしながらまぜる。
-③溶けたカカオ＜カカオマス＞　→　&lt;color=#FF5CA1FF&gt;魔法「テンパリング」&lt;/color&gt;
-50°　→　26°　→　31°
-31°は超えてはいけない
-④液体チョコレート　→　&lt;color=#FF5CA1FF&gt;魔法ふりーじんぐ&lt;/color&gt; or &lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;
-ブラックチョコレート完成！
-ほろ苦くて甘い♪　カカオがよく効いた絶品のお菓子でございます。
-</t>
-    <rPh sb="39" eb="40">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>マメヤ</t>
-    </rPh>
-    <rPh sb="92" eb="93">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="96" eb="97">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="168" eb="170">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="216" eb="217">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="264" eb="266">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="268" eb="269">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="321" eb="322">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="343" eb="345">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="405" eb="407">
-      <t>ヒムロ</t>
-    </rPh>
-    <rPh sb="419" eb="421">
-      <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6819,6 +6762,112 @@
     </rPh>
     <rPh sb="22" eb="23">
       <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/eden_recipi_1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/eden_recipi_2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/eden_recipi_3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/eden_recipi_4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/eden_recipi_5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【ブラックチョコレートのレシピ】
+①&lt;color=#BA9535FF&gt;カカオ豆&lt;/color&gt;　→　ローストする。　魔法&lt;color=#FF5CA1FF&gt;「豆焼き」&lt;/color&gt;を使う
+カカオニブができる。
+②&lt;color=#BA9535FF&gt;カカオニブ&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;をまぜる。
+&lt;color=#FF5CA1FF&gt;すりばち&lt;/color&gt;で、豆をつぶしながらまぜる。
+③溶けたカカオ＜カカオマス＞　→　&lt;color=#FF5CA1FF&gt;魔法「テンパリング」&lt;/color&gt;
+50°　→　26°　→　31°
+各温度は、超えてはいけない
+④液体チョコレート　→　&lt;color=#FF5CA1FF&gt;魔法ふりーじんぐ&lt;/color&gt; or &lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;
+ブラックチョコレート完成！
+ほろ苦くて甘い♪　カカオがよく効いた絶品のお菓子でございます。
+</t>
+    <rPh sb="39" eb="40">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>マメヤ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="204" eb="205">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="252" eb="254">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="256" eb="257">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="288" eb="291">
+      <t>カクオンド</t>
+    </rPh>
+    <rPh sb="310" eb="311">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="332" eb="334">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="394" eb="396">
+      <t>ヒムロ</t>
+    </rPh>
+    <rPh sb="408" eb="410">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シュガーポットの本</t>
+    <rPh sb="8" eb="9">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_sugerpot_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MemoWhite</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白紙のメモ</t>
+    <rPh sb="0" eb="2">
+      <t>ハクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白紙メモ　なんでも書ける</t>
+    <rPh sb="0" eb="2">
+      <t>ハクシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7274,7 +7323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -7334,7 +7383,7 @@
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A119" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A120" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -7407,7 +7456,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -7554,7 +7603,7 @@
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -7575,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L7">
         <v>3000</v>
@@ -8499,7 +8548,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L29">
         <v>130</v>
@@ -8877,7 +8926,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L38">
         <v>270</v>
@@ -9045,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L42" s="5">
         <v>9999</v>
@@ -9060,7 +9109,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C43" t="s">
         <v>199</v>
@@ -9087,7 +9136,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>262</v>
+        <v>456</v>
       </c>
       <c r="L43">
         <v>310</v>
@@ -9102,7 +9151,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C44" t="s">
         <v>204</v>
@@ -9144,7 +9193,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>207</v>
@@ -9186,7 +9235,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C46" t="s">
         <v>209</v>
@@ -9213,7 +9262,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L46">
         <v>340</v>
@@ -9228,13 +9277,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E47">
         <v>500</v>
@@ -9255,7 +9304,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L47">
         <v>350</v>
@@ -9270,13 +9319,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C48" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -9297,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L48">
         <v>360</v>
@@ -9312,13 +9361,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -9339,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L49">
         <v>370</v>
@@ -9354,13 +9403,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -9381,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L50">
         <v>380</v>
@@ -9396,13 +9445,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C51" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D51" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -9423,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L51">
         <v>390</v>
@@ -9480,7 +9529,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C53" t="s">
         <v>214</v>
@@ -9522,7 +9571,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C54" t="s">
         <v>216</v>
@@ -9564,7 +9613,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C55" t="s">
         <v>218</v>
@@ -9606,7 +9655,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C56" t="s">
         <v>221</v>
@@ -9633,7 +9682,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L56">
         <v>520</v>
@@ -9648,7 +9697,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C57" t="s">
         <v>222</v>
@@ -9675,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L57">
         <v>530</v>
@@ -9717,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L58">
         <v>540</v>
@@ -9732,7 +9781,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C59" t="s">
         <v>227</v>
@@ -9759,7 +9808,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L59">
         <v>550</v>
@@ -9774,7 +9823,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C60" t="s">
         <v>228</v>
@@ -9801,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L60">
         <v>560</v>
@@ -9816,7 +9865,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C61" t="s">
         <v>232</v>
@@ -9843,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L61">
         <v>570</v>
@@ -9858,7 +9907,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C62" t="s">
         <v>231</v>
@@ -9900,7 +9949,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C63" t="s">
         <v>234</v>
@@ -9927,7 +9976,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L63">
         <v>590</v>
@@ -9984,7 +10033,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C65" t="s">
         <v>238</v>
@@ -10011,7 +10060,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L65">
         <v>610</v>
@@ -10029,10 +10078,10 @@
         <v>196</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E66" s="7">
         <v>500</v>
@@ -10053,7 +10102,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L66" s="7">
         <v>620</v>
@@ -10068,7 +10117,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C67" t="s">
         <v>241</v>
@@ -10095,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L67">
         <v>700</v>
@@ -10110,13 +10159,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -10137,7 +10186,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L68">
         <v>710</v>
@@ -10152,7 +10201,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C69" t="s">
         <v>243</v>
@@ -10179,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L69">
         <v>720</v>
@@ -10194,7 +10243,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s">
         <v>245</v>
@@ -10221,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L70">
         <v>730</v>
@@ -10236,7 +10285,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C71" t="s">
         <v>246</v>
@@ -10263,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L71">
         <v>740</v>
@@ -10278,7 +10327,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C72" t="s">
         <v>253</v>
@@ -10305,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L72">
         <v>750</v>
@@ -10320,7 +10369,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C73" t="s">
         <v>249</v>
@@ -10362,13 +10411,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -10389,7 +10438,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L74">
         <v>770</v>
@@ -10404,13 +10453,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -10431,7 +10480,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L75">
         <v>780</v>
@@ -10449,10 +10498,10 @@
         <v>196</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E76" s="7">
         <v>500</v>
@@ -10473,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L76" s="7">
         <v>790</v>
@@ -10491,10 +10540,10 @@
         <v>196</v>
       </c>
       <c r="C77" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D77" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -10515,7 +10564,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L77">
         <v>9999</v>
@@ -10524,213 +10573,213 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="9">
+    <row r="78" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="B78" t="s">
+        <v>451</v>
+      </c>
+      <c r="C78" t="s">
+        <v>293</v>
+      </c>
+      <c r="D78" t="s">
+        <v>311</v>
+      </c>
+      <c r="E78">
+        <v>500</v>
+      </c>
+      <c r="F78">
+        <v>150</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="E78" s="9">
-        <v>500</v>
-      </c>
-      <c r="F78" s="9">
-        <v>150</v>
-      </c>
-      <c r="G78" s="9">
-        <v>0</v>
-      </c>
-      <c r="H78" s="9">
-        <v>1</v>
-      </c>
-      <c r="I78" s="9">
-        <v>0</v>
-      </c>
-      <c r="J78" s="9">
-        <v>1</v>
-      </c>
-      <c r="K78" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="L78" s="9">
+      <c r="L78">
         <v>2000</v>
       </c>
-      <c r="M78" s="9">
+      <c r="M78">
         <v>2000</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="9">
+    <row r="79" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E79" s="9">
+      <c r="B79" t="s">
+        <v>452</v>
+      </c>
+      <c r="C79" t="s">
+        <v>295</v>
+      </c>
+      <c r="D79" t="s">
+        <v>308</v>
+      </c>
+      <c r="E79">
         <v>500</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79">
         <v>150</v>
       </c>
-      <c r="G79" s="9">
-        <v>0</v>
-      </c>
-      <c r="H79" s="9">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
         <v>1</v>
       </c>
-      <c r="I79" s="9">
-        <v>0</v>
-      </c>
-      <c r="J79" s="9">
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
         <v>1</v>
       </c>
-      <c r="K79" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="L79" s="9">
+      <c r="K79" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L79">
         <v>2100</v>
       </c>
-      <c r="M79" s="9">
+      <c r="M79">
         <v>2100</v>
       </c>
     </row>
-    <row r="80" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="9">
+    <row r="80" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="E80" s="9">
+      <c r="B80" t="s">
+        <v>453</v>
+      </c>
+      <c r="C80" t="s">
+        <v>296</v>
+      </c>
+      <c r="D80" t="s">
+        <v>310</v>
+      </c>
+      <c r="E80">
         <v>500</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80">
         <v>150</v>
       </c>
-      <c r="G80" s="9">
-        <v>0</v>
-      </c>
-      <c r="H80" s="9">
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
         <v>1</v>
       </c>
-      <c r="I80" s="9">
-        <v>0</v>
-      </c>
-      <c r="J80" s="9">
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
         <v>1</v>
       </c>
-      <c r="K80" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="L80" s="9">
+      <c r="K80" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L80">
         <v>2200</v>
       </c>
-      <c r="M80" s="9">
+      <c r="M80">
         <v>2200</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="9">
+    <row r="81" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E81" s="9">
+      <c r="B81" t="s">
+        <v>454</v>
+      </c>
+      <c r="C81" t="s">
+        <v>297</v>
+      </c>
+      <c r="D81" t="s">
+        <v>309</v>
+      </c>
+      <c r="E81">
         <v>500</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81">
         <v>150</v>
       </c>
-      <c r="G81" s="9">
-        <v>0</v>
-      </c>
-      <c r="H81" s="9">
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
         <v>1</v>
       </c>
-      <c r="I81" s="9">
-        <v>0</v>
-      </c>
-      <c r="J81" s="9">
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
         <v>1</v>
       </c>
-      <c r="K81" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="L81" s="9">
+      <c r="K81" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L81">
         <v>2300</v>
       </c>
-      <c r="M81" s="9">
+      <c r="M81">
         <v>2300</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="9">
+    <row r="82" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="E82" s="9">
+      <c r="B82" t="s">
+        <v>455</v>
+      </c>
+      <c r="C82" t="s">
+        <v>298</v>
+      </c>
+      <c r="D82" t="s">
+        <v>316</v>
+      </c>
+      <c r="E82">
         <v>500</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82">
         <v>150</v>
       </c>
-      <c r="G82" s="9">
-        <v>0</v>
-      </c>
-      <c r="H82" s="9">
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
         <v>1</v>
       </c>
-      <c r="I82" s="9">
-        <v>0</v>
-      </c>
-      <c r="J82" s="9">
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
         <v>1</v>
       </c>
-      <c r="K82" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="L82" s="9">
+      <c r="K82" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L82">
         <v>2400</v>
       </c>
-      <c r="M82" s="9">
+      <c r="M82">
         <v>2400</v>
       </c>
     </row>
@@ -10740,13 +10789,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C83" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E83">
         <v>500</v>
@@ -10767,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L83">
         <v>5000</v>
@@ -10782,13 +10831,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C84" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D84" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -10809,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L84">
         <v>5000</v>
@@ -10824,13 +10873,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C85" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D85" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -10851,7 +10900,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L85">
         <v>5000</v>
@@ -10866,13 +10915,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C86" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D86" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -10893,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L86">
         <v>5000</v>
@@ -10908,13 +10957,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C87" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D87" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -10935,7 +10984,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -10950,13 +10999,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C88" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D88" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -10977,7 +11026,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -10992,13 +11041,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C89" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D89" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11019,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11034,13 +11083,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C90" t="s">
+        <v>284</v>
+      </c>
+      <c r="D90" t="s">
         <v>285</v>
-      </c>
-      <c r="D90" t="s">
-        <v>286</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11061,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11076,13 +11125,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C91" t="s">
+        <v>328</v>
+      </c>
+      <c r="D91" t="s">
         <v>329</v>
-      </c>
-      <c r="D91" t="s">
-        <v>330</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11103,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11118,13 +11167,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C92" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D92" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11145,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11160,13 +11209,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C93" t="s">
+        <v>317</v>
+      </c>
+      <c r="D93" t="s">
         <v>318</v>
-      </c>
-      <c r="D93" t="s">
-        <v>319</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11187,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11202,13 +11251,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C94" t="s">
+        <v>334</v>
+      </c>
+      <c r="D94" t="s">
         <v>335</v>
-      </c>
-      <c r="D94" t="s">
-        <v>336</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11229,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11244,13 +11293,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C95" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D95" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11271,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11286,13 +11335,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C96" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D96" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -11313,7 +11362,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11328,13 +11377,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C97" t="s">
-        <v>345</v>
+        <v>458</v>
       </c>
       <c r="D97" t="s">
-        <v>343</v>
+        <v>457</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -11355,7 +11404,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11370,13 +11419,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C98" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D98" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -11397,7 +11446,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -11412,13 +11461,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C99" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D99" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -11439,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -11454,13 +11503,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C100" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="D100" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -11481,7 +11530,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -11496,13 +11545,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C101" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="D101" t="s">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -11523,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -11538,13 +11587,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C102" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D102" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -11565,7 +11614,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -11580,13 +11629,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C103" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D103" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -11607,7 +11656,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -11622,13 +11671,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C104" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D104" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -11649,7 +11698,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -11664,13 +11713,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C105" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -11691,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>287</v>
+        <v>443</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -11706,13 +11755,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C106" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -11733,7 +11782,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>443</v>
+        <v>286</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -11748,13 +11797,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C107" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -11775,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -11790,13 +11839,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C108" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -11817,7 +11866,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -11832,13 +11881,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C109" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -11859,7 +11908,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>438</v>
+        <v>286</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -11874,13 +11923,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C110" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -11901,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>287</v>
+        <v>437</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -11916,13 +11965,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C111" t="s">
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="D111" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -11943,7 +11992,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>430</v>
+        <v>286</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -11958,13 +12007,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C112" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D112" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -11985,7 +12034,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -11994,45 +12043,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="11">
+    <row r="113" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A113">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="B113" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="E113" s="11">
+      <c r="B113" t="s">
+        <v>380</v>
+      </c>
+      <c r="C113" t="s">
+        <v>312</v>
+      </c>
+      <c r="D113" t="s">
+        <v>313</v>
+      </c>
+      <c r="E113">
         <v>500</v>
       </c>
-      <c r="F113" s="11">
+      <c r="F113">
         <v>150</v>
       </c>
-      <c r="G113" s="11">
-        <v>0</v>
-      </c>
-      <c r="H113" s="11">
-        <v>0</v>
-      </c>
-      <c r="I113" s="11">
-        <v>0</v>
-      </c>
-      <c r="J113" s="11">
-        <v>0</v>
-      </c>
-      <c r="K113" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="L113" s="11">
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="L113">
         <v>5000</v>
       </c>
-      <c r="M113" s="11">
+      <c r="M113">
         <v>5000</v>
       </c>
     </row>
@@ -12042,13 +12091,13 @@
         <v>112</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E114" s="11">
         <v>500</v>
@@ -12069,7 +12118,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L114" s="11">
         <v>5000</v>
@@ -12084,13 +12133,13 @@
         <v>113</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E115" s="11">
         <v>500</v>
@@ -12111,7 +12160,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L115" s="11">
         <v>5000</v>
@@ -12120,45 +12169,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116">
+    <row r="116" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="11">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="B116" t="s">
-        <v>381</v>
-      </c>
-      <c r="C116" t="s">
-        <v>373</v>
-      </c>
-      <c r="D116" t="s">
-        <v>372</v>
-      </c>
-      <c r="E116">
+      <c r="B116" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="E116" s="11">
         <v>500</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="11">
         <v>150</v>
       </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="L116">
+      <c r="G116" s="11">
+        <v>0</v>
+      </c>
+      <c r="H116" s="11">
+        <v>0</v>
+      </c>
+      <c r="I116" s="11">
+        <v>0</v>
+      </c>
+      <c r="J116" s="11">
+        <v>0</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="L116" s="11">
         <v>5000</v>
       </c>
-      <c r="M116">
+      <c r="M116" s="11">
         <v>5000</v>
       </c>
     </row>
@@ -12168,13 +12217,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C117" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D117" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -12195,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="L117">
         <v>5000</v>
@@ -12204,102 +12253,103 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="118" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="11">
+    <row r="118" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A118">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="B118" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="E118" s="11">
+      <c r="B118" t="s">
+        <v>380</v>
+      </c>
+      <c r="C118" t="s">
+        <v>374</v>
+      </c>
+      <c r="D118" t="s">
+        <v>373</v>
+      </c>
+      <c r="E118">
         <v>500</v>
       </c>
-      <c r="F118" s="11">
+      <c r="F118">
         <v>150</v>
       </c>
-      <c r="G118" s="11">
-        <v>0</v>
-      </c>
-      <c r="H118" s="11">
-        <v>0</v>
-      </c>
-      <c r="I118" s="11">
-        <v>0</v>
-      </c>
-      <c r="J118" s="11">
-        <v>0</v>
-      </c>
-      <c r="K118" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="L118" s="11">
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L118">
         <v>5000</v>
       </c>
-      <c r="M118" s="11">
+      <c r="M118">
         <v>5000</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119">
+    <row r="119" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="11">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="B119" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B119" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="E119" s="11">
+        <v>500</v>
+      </c>
+      <c r="F119" s="11">
+        <v>150</v>
+      </c>
+      <c r="G119" s="11">
+        <v>0</v>
+      </c>
+      <c r="H119" s="11">
+        <v>0</v>
+      </c>
+      <c r="I119" s="11">
+        <v>0</v>
+      </c>
+      <c r="J119" s="11">
+        <v>0</v>
+      </c>
+      <c r="K119" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="L119" s="11">
+        <v>5000</v>
+      </c>
+      <c r="M119" s="11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>380</v>
+      </c>
+      <c r="C120" t="s">
+        <v>314</v>
+      </c>
+      <c r="D120" t="s">
         <v>315</v>
-      </c>
-      <c r="D119" t="s">
-        <v>316</v>
-      </c>
-      <c r="E119">
-        <v>500</v>
-      </c>
-      <c r="F119">
-        <v>150</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L119">
-        <v>5000</v>
-      </c>
-      <c r="M119">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120">
-        <v>10000</v>
-      </c>
-      <c r="B120" t="s">
-        <v>170</v>
-      </c>
-      <c r="C120" t="s">
-        <v>174</v>
-      </c>
-      <c r="D120" t="s">
-        <v>175</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -12317,15 +12367,98 @@
         <v>0</v>
       </c>
       <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="L120">
+        <v>5000</v>
+      </c>
+      <c r="M120">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <f>ROW()-2</f>
+        <v>119</v>
+      </c>
+      <c r="B121" t="s">
+        <v>380</v>
+      </c>
+      <c r="C121" t="s">
+        <v>459</v>
+      </c>
+      <c r="D121" t="s">
+        <v>460</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
         <v>1</v>
       </c>
-      <c r="K120" s="2" t="s">
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121" t="s">
+        <v>461</v>
+      </c>
+      <c r="L121">
+        <v>9999</v>
+      </c>
+      <c r="M121">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <v>10000</v>
+      </c>
+      <c r="B122" t="s">
+        <v>170</v>
+      </c>
+      <c r="C122" t="s">
+        <v>174</v>
+      </c>
+      <c r="D122" t="s">
+        <v>175</v>
+      </c>
+      <c r="E122">
+        <v>500</v>
+      </c>
+      <c r="F122">
+        <v>150</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L120">
+      <c r="L122">
         <v>9000</v>
       </c>
-      <c r="M120">
+      <c r="M122">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63045AC7-C4F0-4314-8919-1CD5482B4804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B023B943-6386-4CFD-AAFF-A2303D8626C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3150" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="463">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -6869,6 +6869,10 @@
     <rPh sb="9" eb="10">
       <t>カ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/memo_white</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12385,7 +12389,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="C121" t="s">
         <v>459</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B023B943-6386-4CFD-AAFF-A2303D8626C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18FBA49-DEBD-4A77-BEA0-6CE6C89B0BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3240" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18FBA49-DEBD-4A77-BEA0-6CE6C89B0BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63436B29-93A8-476F-8F1F-60A89A1CAB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63436B29-93A8-476F-8F1F-60A89A1CAB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D427B0C0-AACE-4287-8234-CB67D049A96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="31110" yWindow="855" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="467">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -6873,6 +6873,326 @@
   </si>
   <si>
     <t>Items/memo_white</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- 太陽のレシピ -
+ケーキ生地のつくりかた
+i. はくりきこ　×　ココアパウダー
+ii. たまご　×　さとう　×　バターを混ぜ、アパレイユを作る
+iii. &lt;color=#BA9535FF&gt;ブラックロータスポーション&lt;/color&gt;
+iの粉生地とiiのアパレイユに、iiiブラックロータスポーションを入れ、３つを混ぜる。
+→　出来上がった生地を、&lt;color=#FF5CA1FF&gt;ウィンドミキサー&lt;/color&gt;でよく混ぜて、焼き上げる。
+ブラックロータスココアケーキ（生地）の完成。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="164" eb="167">
+      <t>コナキジ</t>
+    </rPh>
+    <rPh sb="195" eb="196">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="201" eb="202">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="209" eb="212">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="215" eb="217">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="255" eb="256">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="259" eb="260">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="261" eb="262">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="282" eb="284">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="286" eb="288">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- 星のレシピ -
+クリームの作り方
+太陽と月のしずくをまぜたクリーム
+i. 作りたてクリームを事前に作っておく
+ii. クリームに、&lt;color=#BA9535FF&gt;太陽の実&lt;/color&gt;と&lt;color=#BA9535FF&gt;月の実&lt;/color&gt;を同時に入れ、混ぜ合わせる。
+夢見のクリームの完成
+＜太陽の実は、さわやかですっぱいオレンジ色の果実＞
+＜月の実は、銀色に輝く寒い場所でしか採れない果実＞</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="130" eb="131">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="157" eb="158">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="172" eb="173">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="175" eb="176">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="192" eb="194">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="197" eb="199">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="200" eb="201">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="218" eb="220">
+      <t>カジツ</t>
+    </rPh>
+    <rPh sb="223" eb="224">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="225" eb="226">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="228" eb="230">
+      <t>ギンイロ</t>
+    </rPh>
+    <rPh sb="231" eb="232">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="233" eb="234">
+      <t>サム</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="240" eb="241">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="244" eb="246">
+      <t>カジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- 月のレシピ -
+トッピング方法のレシピ
+ケーキ全体にクリームをぬったあと、最後の仕上げに&lt;color=#BA9535FF&gt;２つの果物&lt;/color&gt;を同時にのせる。
+・&lt;color=#BA9535FF&gt;スカーレットベリー&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;ジェムナッツ&lt;/color&gt;
+仕上げに、もりだくさんのせること。
+また、同時にトッピングすること。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>クダモノ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="197" eb="199">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="218" eb="220">
+      <t>ドウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- ハートのレシピ -
+エデンの手順のレシピ
+完成までの手順がかかれている。
+◆事前に、スポンジ生地を&lt;color=#FF5CA1FF&gt;スライサー&lt;/color&gt;で３つに分ける。
+◆i. 一段目　スライスしたスポンジ生地に、&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;と、&lt;color=#BA9535FF&gt;白いクリーム&lt;/color&gt;を塗る。
+◆ii. 二段目　スライスしたスポンジ生地に、&lt;color=#BA9535FF&gt;レインボーベリー&lt;/color&gt;と、&lt;color=#BA9535FF&gt;白いクリーム&lt;/color&gt;を塗る。
+◆iii. iとiiの生地、さらにスポンジ生地でふたをし、&lt;color=#BA9535FF&gt;三段重ね&lt;/color&gt;にする。
+そのあと、全体を&lt;color=#BA9535FF&gt;夢見クリーム&lt;/color&gt;できれいに塗り仕上げる。
+※クリームは、絞り袋に入れず、直接ぬってよい。
+◆iiii. 月のレシ.. どおりに、２種類の果実をふんだんに.. トッピング。
+◆.. （かすれて読みづらい）
+しあげ.. に.. &lt;color=#FF5CA1FF&gt;ハートの魔法&lt;/color&gt;を.. 
+◆.. .. ま.. げつ.. の夜.. たべ.. ..と。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="202" eb="203">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="227" eb="230">
+      <t>ニダンメ</t>
+    </rPh>
+    <rPh sb="241" eb="243">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="297" eb="298">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="312" eb="313">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="328" eb="330">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="338" eb="340">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="363" eb="366">
+      <t>サンダンガサ</t>
+    </rPh>
+    <rPh sb="386" eb="388">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="406" eb="408">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="425" eb="426">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="427" eb="429">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="440" eb="441">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="442" eb="443">
+      <t>ブクロ</t>
+    </rPh>
+    <rPh sb="444" eb="445">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="448" eb="450">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="465" eb="466">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="478" eb="480">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="481" eb="483">
+      <t>カジツ</t>
+    </rPh>
+    <rPh sb="509" eb="510">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="547" eb="549">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="580" eb="581">
+      <t>ヨル</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10652,7 +10972,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>294</v>
+        <v>463</v>
       </c>
       <c r="L79">
         <v>2100</v>
@@ -10694,7 +11014,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="L80">
         <v>2200</v>
@@ -10736,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>294</v>
+        <v>465</v>
       </c>
       <c r="L81">
         <v>2300</v>
@@ -10778,7 +11098,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>294</v>
+        <v>466</v>
       </c>
       <c r="L82">
         <v>2400</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D427B0C0-AACE-4287-8234-CB67D049A96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9849043B-2B78-44D0-A2FE-28EE22B1B20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31110" yWindow="855" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2610" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9849043B-2B78-44D0-A2FE-28EE22B1B20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F51BDD-37A5-4221-A0BA-E98D11FA4673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2340" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F51BDD-37A5-4221-A0BA-E98D11FA4673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C02FDBE-3561-401D-BD02-9403C2EBFBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="470">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -3607,412 +3607,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【オペラのレシピ】
-難易度・・　超高
-濃厚かつしっとりとした、まさに正統派なチョコレートケーキです。
-かなり手順が複雑で多いのですが、がんばってみてくださいね。
-以下、
-A, スポンジ生地作り
-B. コーヒーシロップ
-C. コーヒーバタークリーム
-D. ガナッシュクリーム
-E. チョコレートソースグラサージュ
-の５つを先に準備します。
-全部できたら、最後に仕上げていきましょう。
-★メレンゲも作れるようになっておきましょう。
-★焦がしバターも使います。作り方を事前に覚えておきましょう。
-A. 生地作り
-※事前に、&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;とココアパウダーを混ぜておきます。
-また、メレンゲ、焦がしバターも準備しておきましょう。
-①&lt;color=#BA9535FF&gt;砂糖、卵&lt;/color&gt;に、アーモンドパウダーを入れ、混ぜ合わせます。
-②①でできたアパレイユに、事前に用意した粉類とメレンゲを入れて、よく混ぜましょう。
-③焦がしバターを最後に加えて混ぜます。
-焼き上げれば、オペラケーキ生地が完成です。
-B. コーヒーシロップ
-水・砂糖・コーヒーパウダーを加えて、煮詰めればコーヒーシロップができます。準備しておきます。
-C. コーヒーのバタークリーム
-①卵黄に砂糖を混ぜます。＜アパレイユ黄身＞
-さらに、少量のコーヒーを入れよく混ぜます。
-②ある程度混ざったら、バターを入れて、よく混ぜます。
-香り高いコーヒークリームの完成です。
-D. ガナッシュクリーム
-①お鍋に、生クリームを入れ、液体状のチョコレート入れ、火にかけながら混ぜます。
-濃厚なガナッシュクリームの完成です。
-E. チョコレートソースグラサージュ
-ケーキに最後にかけるコーティング用のチョコソースを作っていきます。
-①生クリームに、砂糖・ココアパウダーを入れ、混ぜながら火にかけます。
-②水・ゼラチンを加えて、さらに混ぜ合わせます。
-濃厚でとろりとした、真っ黒のチョコソースが完成です。
-【仕上げ】
-①Aで作ったケーキ生地を、四角いセルクルでスライスし切り分けます。
-②生地に、液体状チョコレートを塗ります。これが底生地になります。
-ここから上にどんどん生地・クリームを重ねていきます。
-③底生地に、Bのコーヒーシロップをぬって、味付けをし、その上にコーヒーバタークリームを塗り、層を作ります。
-④③の上に、スライスしたケーキ生地をのせます。
-⑤④の生地の表面に、コーヒーシロップをさらにつけ、その上に、Dのガナッシュクリームを塗っていきます。
-ソースは平坦にぬると、きれいになります。
-⑥⑤の生地の上に、さらにコーヒーバタークリームを塗ります。平に塗っていきます。
-⑦ベースは完成です。あとは、氷室、もしくは魔法「フリージング」で冷やしていきましょう。
-⑧最後に、真っ黒なEのチョコソースグラサージュをかけてコーティングすれば..
-高貴なチョコケーキ「オペラ」完成です♪
-仕上げに、「金箔」を一つまみのせると、王様も大喜びのリッチな仕上げになります。</t>
-    <rPh sb="11" eb="14">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="36" eb="39">
-      <t>セイトウハ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="97" eb="98">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="163" eb="164">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="172" eb="174">
-      <t>ゼンブ</t>
-    </rPh>
-    <rPh sb="179" eb="181">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="182" eb="184">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="201" eb="202">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="219" eb="220">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="226" eb="227">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="231" eb="232">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="233" eb="234">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="238" eb="239">
-      <t>オボ</t>
-    </rPh>
-    <rPh sb="253" eb="255">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="255" eb="256">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="280" eb="283">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="300" eb="301">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="317" eb="318">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="324" eb="326">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="355" eb="357">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="379" eb="380">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="382" eb="383">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="384" eb="385">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="405" eb="407">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="408" eb="410">
-      <t>ヨウイ</t>
-    </rPh>
-    <rPh sb="412" eb="414">
-      <t>コナルイ</t>
-    </rPh>
-    <rPh sb="420" eb="421">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="426" eb="427">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="456" eb="457">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="458" eb="459">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="469" eb="471">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="472" eb="474">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="491" eb="492">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="493" eb="495">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="505" eb="506">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="509" eb="511">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="528" eb="530">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="556" eb="558">
-      <t>ランオウ</t>
-    </rPh>
-    <rPh sb="573" eb="575">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="581" eb="583">
-      <t>ショウリョウ</t>
-    </rPh>
-    <rPh sb="589" eb="590">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="593" eb="594">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="628" eb="629">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="630" eb="631">
-      <t>ダカ</t>
-    </rPh>
-    <rPh sb="663" eb="664">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="666" eb="667">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="672" eb="673">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="675" eb="678">
-      <t>エキタイジョウ</t>
-    </rPh>
-    <rPh sb="685" eb="686">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="688" eb="689">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="695" eb="696">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="702" eb="704">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="745" eb="747">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="757" eb="758">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="766" eb="767">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="777" eb="778">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="784" eb="786">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="795" eb="796">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="798" eb="799">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="803" eb="804">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="813" eb="814">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="820" eb="821">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="827" eb="828">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="829" eb="830">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="837" eb="839">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="847" eb="848">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="849" eb="850">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="858" eb="860">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="866" eb="868">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="875" eb="876">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="881" eb="883">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="885" eb="887">
-      <t>シカク</t>
-    </rPh>
-    <rPh sb="898" eb="899">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="900" eb="901">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="908" eb="910">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="912" eb="915">
-      <t>エキタイジョウ</t>
-    </rPh>
-    <rPh sb="922" eb="923">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="930" eb="933">
-      <t>ソコキジ</t>
-    </rPh>
-    <rPh sb="945" eb="946">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="951" eb="953">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="959" eb="960">
-      <t>カサ</t>
-    </rPh>
-    <rPh sb="970" eb="973">
-      <t>ソコキジ</t>
-    </rPh>
-    <rPh sb="990" eb="992">
-      <t>アジツ</t>
-    </rPh>
-    <rPh sb="998" eb="999">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1027" eb="1028">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1039" eb="1041">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1052" eb="1054">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1055" eb="1057">
-      <t>ヒョウメン</t>
-    </rPh>
-    <rPh sb="1076" eb="1077">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1091" eb="1092">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1104" eb="1106">
-      <t>ヘイタン</t>
-    </rPh>
-    <rPh sb="1125" eb="1127">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1128" eb="1129">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1146" eb="1147">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1151" eb="1152">
-      <t>タイラ</t>
-    </rPh>
-    <rPh sb="1153" eb="1154">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1168" eb="1170">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1177" eb="1179">
-      <t>ヒムロ</t>
-    </rPh>
-    <rPh sb="1184" eb="1186">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="1195" eb="1196">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="1209" eb="1211">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="1213" eb="1214">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="1215" eb="1216">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="1248" eb="1250">
-      <t>コウキ</t>
-    </rPh>
-    <rPh sb="1262" eb="1264">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1269" eb="1271">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="1275" eb="1277">
-      <t>キンパク</t>
-    </rPh>
-    <rPh sb="1279" eb="1280">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="1288" eb="1290">
-      <t>オウサマ</t>
-    </rPh>
-    <rPh sb="1291" eb="1293">
-      <t>オオヨロコ</t>
-    </rPh>
-    <rPh sb="1299" eb="1301">
-      <t>シア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">【コーヒーのレシピ】
 おいしいコーヒーの淹れ方
 ①&lt;color=#BA9535FF&gt;コーヒー豆&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;すり鉢&lt;/color&gt;でひき、粉にします。
@@ -4051,257 +3645,6 @@
     </rPh>
     <rPh sb="252" eb="253">
       <t>ニガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【ブッシュドノエルのレシピ】
-難易度・・　中～高　ぐらい
-木を模した伝統的なケーキ菓子です。チョコレートやココアの風味が、森を思わせる・・
-森のケーキをお楽しみください。
-下準備として、
-A. ココアケーキ生地
-B. チョコレートクリーム
-の２つを先に作ります。
-あとで、生地をまきまきしていきましょう♪
-★作る前に、魔法「ウィンドロール」を覚えておきましょう。
-★模様をつけるため、器材「フォーク」も買っておきましょう。
-【作り方】
-A. ココアケーキ生地
-①&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;と、&lt;color=#BA9535FF&gt;ココアパウダー&lt;/color&gt;を先に混ぜておきます。
-②アパレイユを作る・・・
- &lt;color=#BA9535FF&gt;砂糖、卵、バター&lt;/color&gt;を混ぜ、アパレイユを作ります。
-③アパレイユに先ほどの粉類をふるい入れ、ウィンドミキサーで混ぜます。焼き上げれば生地の完成です。
-※180度で10~12分ほど焼くといい感じです。
-B.チョコレートバタークリーム
-①卵黄に砂糖を混ぜます。＜アパレイユ黄身＞
-さらに、少量の液体状チョコレートを入れよく混ぜます。
-②ある程度混ざったら、バターを入れて、よく混ぜます。
-芳醇で味わい深いチョコレートバタークリームの完成です。
-【仕上げ】
-※Aの生地を事前にスライスします。
-①スライスした生地の片面に、Bのチョコレートクリームをぬっていきます。
-②できた生地に、魔法「ウィンドロール」をかけて、きれいに巻きましょう！
-③巻いたロール生地に、さらにBチョコレートクリームをぬります。このとき、「フォーク」を使って、木の模様をつけていきます。
-④上にマジパンで作ったお花や、動物などのトッピングでデコレーションして..
-ブッシュドノエル完成で～す♪
-まさに、木を模した伝統的で豪華なお菓子です。
-ぜひ自分の手で作ってみてくださいね。
-【あとがき】
-ブッシュドノエルは、ちょうちょとの相性がいいようです。
-</t>
-    <rPh sb="16" eb="19">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="36" eb="39">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>フウミ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>モリ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>モリ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>タノ</t>
-    </rPh>
-    <rPh sb="89" eb="92">
-      <t>シタジュンビ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="127" eb="128">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="129" eb="130">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="158" eb="159">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="160" eb="161">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="163" eb="165">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="175" eb="176">
-      <t>オボ</t>
-    </rPh>
-    <rPh sb="187" eb="189">
-      <t>モヨウ</t>
-    </rPh>
-    <rPh sb="196" eb="198">
-      <t>キザイ</t>
-    </rPh>
-    <rPh sb="205" eb="206">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="218" eb="219">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="220" eb="221">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="253" eb="256">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="342" eb="344">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="359" eb="360">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="382" eb="383">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="386" eb="388">
-      <t>コナルイ</t>
-    </rPh>
-    <rPh sb="404" eb="405">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="409" eb="410">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="411" eb="412">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="415" eb="417">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="418" eb="420">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="428" eb="429">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="435" eb="436">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="438" eb="439">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="443" eb="444">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="495" eb="498">
-      <t>エキタイジョウ</t>
-    </rPh>
-    <rPh sb="543" eb="545">
-      <t>ホウジュン</t>
-    </rPh>
-    <rPh sb="546" eb="547">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="549" eb="550">
-      <t>ブカ</t>
-    </rPh>
-    <rPh sb="565" eb="567">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="573" eb="575">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="581" eb="583">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="584" eb="586">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="604" eb="606">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="607" eb="609">
-      <t>カタメン</t>
-    </rPh>
-    <rPh sb="638" eb="640">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="642" eb="644">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="662" eb="663">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="672" eb="673">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="678" eb="680">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="714" eb="715">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="718" eb="719">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="720" eb="722">
-      <t>モヨウ</t>
-    </rPh>
-    <rPh sb="734" eb="735">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="741" eb="742">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="745" eb="746">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="748" eb="750">
-      <t>ドウブツ</t>
-    </rPh>
-    <rPh sb="780" eb="782">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="792" eb="793">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="794" eb="795">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="797" eb="800">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="801" eb="803">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="805" eb="807">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="813" eb="815">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="816" eb="817">
-      <t>テ</t>
-    </rPh>
-    <rPh sb="818" eb="819">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="855" eb="857">
-      <t>アイショウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5088,305 +4431,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【ザッハトルテのレシピ】
-難易度・・　高
-つやつやの滑らかで、伝統的なチョコレートケーキです。
-以下、３つの生地を作り、あとで合わせて仕上げていきます。
-A. ザッハトルテ生地
-B. コーティングチョコ生地
-C. あんずジャム
-A.
-①チョコの生地・・・卵黄・砂糖に、バターを入れて混ぜ合わせます。
-できたバタークリームに、溶けた液体のチョコレートをいれて混ぜます。
-チョコレートの生地ができます。
-②事前にメレンゲを作っておきます。・・・
-&lt;color=#BA9535FF&gt;卵白&lt;/color&gt;と砂糖を角が立つまで、混ぜ合わせます。
-③先ほど作った、チョコ生地とメレンゲを混ぜ合わせ、そこに薄力粉を加えて、しっかり混ぜます。
-焼き上げれば、ザッハトルテ生地は完成です！！
-※170度で約40~50分。
-あとで、スライスして、他のソースをつけていきます。今は置いておきましょう。
-B. コーティング用チョコ生地＜ザッハトルテソース＞
-①水と砂糖をお鍋にかけ、水あめを先に作ります。
-②水あめに、液体チョコレートを混ぜ、お鍋にかけて、とろとろに煮詰めましょう。
-これで、とろりとしたチョコのコーティング生地の完成です。
-C. あんずジャムの作り方
-①あんずと砂糖を、お鍋に入れて、とろとろと煮詰めていきます。
-とろりしたら、完成です。
-【完成まで】
-①Aで作った生地をスライスします。
-②スライスした生地の上面に、あんずジャムを塗り、再度スライスしたザッハトルテ生地を上からかぶせます。
-③できあがったケーキベースに、あんずジャムを、全体的に塗ってコーティングします。
-※2時間ほど乾燥させます。
-④コーティングした生地に、上からBのチョコレート生地をかけて、コーティングします。
-きれいに全体がチョコでコーティングされたら、完成です♪
-なめらかなチョコの艶や光沢、そしてあんずの芳醇な香り.. それらの調和をお楽しみ頂ければ幸いです。</t>
-    <rPh sb="14" eb="17">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ナメ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="127" eb="129">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>ランオウ</t>
-    </rPh>
-    <rPh sb="135" eb="137">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="146" eb="147">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="148" eb="149">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="184" eb="185">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="198" eb="200">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="246" eb="248">
-      <t>ランパク</t>
-    </rPh>
-    <rPh sb="257" eb="259">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="260" eb="261">
-      <t>ツノ</t>
-    </rPh>
-    <rPh sb="262" eb="263">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="267" eb="268">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="269" eb="270">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="278" eb="279">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="281" eb="282">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="288" eb="290">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="296" eb="297">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="298" eb="299">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="305" eb="308">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="309" eb="310">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="317" eb="318">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="324" eb="325">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="326" eb="327">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="337" eb="339">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="340" eb="342">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="351" eb="352">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="353" eb="354">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="359" eb="360">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="374" eb="375">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="388" eb="389">
-      <t>イマ</t>
-    </rPh>
-    <rPh sb="390" eb="391">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="412" eb="413">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="416" eb="418">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="431" eb="432">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="433" eb="435">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="437" eb="438">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="442" eb="443">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="446" eb="447">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="448" eb="449">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="456" eb="457">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="461" eb="463">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="470" eb="471">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="474" eb="475">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="485" eb="487">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="515" eb="517">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="518" eb="520">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="536" eb="537">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="538" eb="539">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="545" eb="547">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="550" eb="551">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="552" eb="553">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="561" eb="563">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="578" eb="580">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="586" eb="588">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="596" eb="597">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="599" eb="601">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="619" eb="621">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="622" eb="624">
-      <t>ジョウメン</t>
-    </rPh>
-    <rPh sb="633" eb="634">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="636" eb="638">
-      <t>サイド</t>
-    </rPh>
-    <rPh sb="687" eb="690">
-      <t>ゼンタイテキ</t>
-    </rPh>
-    <rPh sb="691" eb="692">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="707" eb="709">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="711" eb="713">
-      <t>カンソウ</t>
-    </rPh>
-    <rPh sb="729" eb="731">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="733" eb="734">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="744" eb="746">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="767" eb="769">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="785" eb="787">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="801" eb="802">
-      <t>ツヤ</t>
-    </rPh>
-    <rPh sb="803" eb="805">
-      <t>コウタク</t>
-    </rPh>
-    <rPh sb="813" eb="815">
-      <t>ホウジュン</t>
-    </rPh>
-    <rPh sb="816" eb="817">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="825" eb="827">
-      <t>チョウワ</t>
-    </rPh>
-    <rPh sb="829" eb="830">
-      <t>タノ</t>
-    </rPh>
-    <rPh sb="832" eb="833">
-      <t>イタダ</t>
-    </rPh>
-    <rPh sb="836" eb="837">
-      <t>サイワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【チーズケーキのレシピ】
 難易度・・　中～高　ぐらい
 少し手順が複雑ですが、がんばって作ってみてくださいね！
@@ -7192,6 +6236,952 @@
     </rPh>
     <rPh sb="580" eb="581">
       <t>ヨル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_rare_findUP_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンテストで手に入る？</t>
+    <rPh sb="6" eb="7">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レアアイテム発見+1の本</t>
+    <rPh sb="6" eb="8">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ザッハトルテのレシピ】
+難易度・・　高
+つやつやの滑らかで、伝統的なチョコレートケーキです。
+以下、３つの生地を作り、あとで合わせて仕上げていきます。
+A. ザッハトルテ生地
+B. コーティングチョコ生地
+C. あんずジャム
+A.
+①チョコの生地・・・卵黄・砂糖に、バターを入れて混ぜ合わせます。
+できたバタークリームに、&lt;color=#BA9535FF&gt;溶けた液体のチョコレート&lt;/color&gt;をいれて混ぜます。
+チョコレートの生地ができます。
+②事前にメレンゲを作っておきます。・・・
+&lt;color=#BA9535FF&gt;卵白&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;泡だて器&lt;/color&gt;で角が立つまで、混ぜ合わせます。
+③先ほど作った、チョコ生地とメレンゲを混ぜ合わせ、そこに薄力粉を加えて、しっかり混ぜます。
+焼き上げれば、ザッハトルテ生地は完成です！！
+※170度で約40~50分。
+あとで、スライスして、他のソースをつけていきます。今は置いておきましょう。
+B. コーティング用チョコ生地＜ザッハトルテソース＞
+①&lt;color=#BA9535FF&gt;水&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;にかけ、水あめを先に作ります。
+②水あめに、液体チョコレートを混ぜ、お鍋にかけて、とろとろに煮詰めましょう。
+これで、とろりとしたチョコのコーティング生地の完成です。
+C. あんずジャムの作り方
+①&lt;color=#BA9535FF&gt;あんず&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;に入れて、とろとろと煮詰めていきます。
+とろりしたら、完成です。
+【完成まで】
+①Aで作った生地をスライスします。
+②スライスした生地の上面に、&lt;color=#BA9535FF&gt;あんずジャム&lt;/color&gt;を塗り、再度スライスしたザッハトルテ生地を上からかぶせます。
+③できあがったケーキベースに、あんずジャムを、全体的に塗ってコーティングします。
+※2時間ほど乾燥させます。
+④コーティングした生地に、上から&lt;color=#BA9535FF&gt;Bのチョコレート生地&lt;/color&gt;をかけて、コーティングします。
+きれいに全体がチョコでコーティングされたら、完成です♪
+なめらかなチョコの艶や光沢、そしてあんずの芳醇な香り.. それらの調和をお楽しみ頂ければ幸いです。</t>
+    <rPh sb="14" eb="17">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナメ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>ランオウ</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="146" eb="147">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="148" eb="149">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="209" eb="210">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="223" eb="225">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="271" eb="273">
+      <t>ランパク</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="340" eb="341">
+      <t>ツノ</t>
+    </rPh>
+    <rPh sb="342" eb="343">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="347" eb="348">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="349" eb="350">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="358" eb="359">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="361" eb="362">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="368" eb="370">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="376" eb="377">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="378" eb="379">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="385" eb="388">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="389" eb="390">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="397" eb="398">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="404" eb="405">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="406" eb="407">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="417" eb="419">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="420" eb="422">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="431" eb="432">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="433" eb="434">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="439" eb="440">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="454" eb="455">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="468" eb="469">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="470" eb="471">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="492" eb="493">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="496" eb="498">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="528" eb="529">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="555" eb="557">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="584" eb="585">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="597" eb="598">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="601" eb="602">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="603" eb="604">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="611" eb="612">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="616" eb="618">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="625" eb="626">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="629" eb="630">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="640" eb="642">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="670" eb="672">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="673" eb="675">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="691" eb="692">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="693" eb="694">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="742" eb="744">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="782" eb="783">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="791" eb="793">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="808" eb="810">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="816" eb="818">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="826" eb="827">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="829" eb="831">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="849" eb="851">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="852" eb="854">
+      <t>ジョウメン</t>
+    </rPh>
+    <rPh sb="888" eb="889">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="891" eb="893">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="942" eb="945">
+      <t>ゼンタイテキ</t>
+    </rPh>
+    <rPh sb="946" eb="947">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="962" eb="964">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="966" eb="968">
+      <t>カンソウ</t>
+    </rPh>
+    <rPh sb="984" eb="986">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="988" eb="989">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1016" eb="1018">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1047" eb="1049">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="1065" eb="1067">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1081" eb="1082">
+      <t>ツヤ</t>
+    </rPh>
+    <rPh sb="1083" eb="1085">
+      <t>コウタク</t>
+    </rPh>
+    <rPh sb="1093" eb="1095">
+      <t>ホウジュン</t>
+    </rPh>
+    <rPh sb="1096" eb="1097">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="1105" eb="1107">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="1109" eb="1110">
+      <t>タノ</t>
+    </rPh>
+    <rPh sb="1112" eb="1113">
+      <t>イタダ</t>
+    </rPh>
+    <rPh sb="1116" eb="1117">
+      <t>サイワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【オペラのレシピ】
+難易度・・　超高
+濃厚かつしっとりとした、まさに正統派なチョコレートケーキです。
+かなり手順が複雑で多いのですが、がんばってみてくださいね。
+◆必要器材
+四角いセルクル
+★メレンゲも作れるようになっておきましょう。
+★焦がしバターも使います。作り方を事前に覚えておきましょう。
+以下、
+A, スポンジ生地作り
+B. コーヒーシロップ
+C. コーヒーバタークリーム
+D. ガナッシュクリーム
+E. チョコレートソースグラサージュ
+の５つを先に準備します。
+全部できたら、最後に仕上げていきましょう。
+A. 生地作り
+※事前に、&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;とココアパウダーを混ぜておきます。
+また、&lt;color=#BA9535FF&gt;メレンゲ、焦がしバター&lt;/color&gt;も準備しておきましょう。
+①&lt;color=#BA9535FF&gt;砂糖、卵&lt;/color&gt;に、アーモンドパウダーを入れ、混ぜ合わせます。
+②①でできたアパレイユに、事前に用意した粉類とメレンゲを入れて、よく混ぜましょう。
+③&lt;color=#BA9535FF&gt;焦がしバター&lt;/color&gt;を最後に加えて混ぜます。
+焼き上げれば、オペラケーキ生地が完成です。
+B. コーヒーシロップ
+&lt;color=#BA9535FF&gt;水・砂糖・コーヒーパウダー&lt;/color&gt;を加えて、煮詰めればコーヒーシロップができます。準備しておきます。
+C. コーヒーのバタークリーム
+①&lt;color=#BA9535FF&gt;卵黄&lt;/color&gt;に&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を混ぜます。＜アパレイユ黄身＞
+さらに、少量の&lt;color=#BA9535FF&gt;コーヒー&lt;/color&gt;を入れよく混ぜます。
+②ある程度混ざったら、&lt;color=#BA9535FF&gt;バター&lt;/color&gt;を入れて、よく混ぜます。
+香り高いコーヒークリームの完成です。
+D. ガナッシュクリーム
+①お鍋に、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;を入れ、&lt;color=#BA9535FF&gt;液体状のチョコレート&lt;/color&gt;を入れ、火にかけながら混ぜます。
+濃厚なガナッシュクリームの完成です。
+E. チョコレートソースグラサージュ
+ケーキに最後にかけるコーティング用のチョコソースを作っていきます。
+①&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;に、&lt;color=#BA9535FF&gt;砂糖・ココアパウダー&lt;/color&gt;を入れ、混ぜながら火にかけます。
+②&lt;color=#BA9535FF&gt;水・ゼラチン&lt;/color&gt;を加えて、さらに混ぜ合わせます。
+濃厚でとろりとした、真っ黒のチョコソースが完成です。
+【仕上げ】
+①Aで作ったケーキ生地を、&lt;color=#FF5CA1FF&gt;四角いセルクル&lt;/color&gt;でスライスし切り分けます。
+②生地に、&lt;color=#BA9535FF&gt;液体状チョコレート&lt;/color&gt;を塗ります。これが底生地になります。
+ここから上にどんどん生地・クリームを重ねていきます。
+③底生地に、&lt;color=#BA9535FF&gt;Bのコーヒーシロップ&lt;/color&gt;をぬって、味付けをし、その上に&lt;color=#BA9535FF&gt;コーヒーバタークリーム&lt;/color&gt;を塗り、層を作ります。
+④③の上に、スライスしたケーキ生地をのせます。
+⑤④の生地の表面に、&lt;color=#BA9535FF&gt;コーヒーシロップ&lt;/color&gt;をさらにつけ、その上に、&lt;color=#BA9535FF&gt;Dのガナッシュクリーム&lt;/color&gt;を塗っていきます。
+ソースは平坦にぬると、きれいになります。
+⑥⑤の生地の上に、さらに&lt;color=#BA9535FF&gt;コーヒーバタークリーム&lt;/color&gt;を塗ります。平に塗っていきます。
+⑦ベースは完成です。あとは、&lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;、もしくは&lt;color=#FF5CA1FF&gt;魔法「フリージング」&lt;/color&gt;で冷やしていきましょう。
+⑧最後に、真っ黒な&lt;color=#BA9535FF&gt;Eのチョコソースグラサージュ&lt;/color&gt;をかけてコーティングすれば..
+高貴なチョコケーキ「オペラ」完成です♪
+仕上げに、&lt;color=#BA9535FF&gt;「金箔」&lt;/color&gt;を一つまみのせると、王様も大喜びのリッチな仕上げになります。</t>
+    <rPh sb="11" eb="14">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>セイトウハ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>キザイ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="167" eb="168">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="233" eb="234">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="242" eb="244">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="249" eb="251">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="252" eb="254">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="269" eb="271">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="271" eb="272">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="296" eb="299">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="316" eb="317">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="350" eb="351">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="365" eb="367">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="396" eb="398">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="420" eb="421">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="423" eb="424">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="425" eb="426">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="446" eb="448">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="449" eb="451">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="453" eb="455">
+      <t>コナルイ</t>
+    </rPh>
+    <rPh sb="461" eb="462">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="467" eb="468">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="522" eb="523">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="524" eb="525">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="535" eb="537">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="538" eb="540">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="574" eb="575">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="576" eb="578">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="596" eb="597">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="600" eb="602">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="619" eb="621">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="664" eb="666">
+      <t>ランオウ</t>
+    </rPh>
+    <rPh sb="714" eb="716">
+      <t>キミ</t>
+    </rPh>
+    <rPh sb="722" eb="724">
+      <t>ショウリョウ</t>
+    </rPh>
+    <rPh sb="755" eb="756">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="759" eb="760">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="819" eb="820">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="821" eb="822">
+      <t>ダカ</t>
+    </rPh>
+    <rPh sb="854" eb="855">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="874" eb="875">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="888" eb="889">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="908" eb="911">
+      <t>エキタイジョウ</t>
+    </rPh>
+    <rPh sb="927" eb="928">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="930" eb="931">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="937" eb="938">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="944" eb="946">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="987" eb="989">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="999" eb="1000">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1008" eb="1009">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="1036" eb="1037">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="1068" eb="1070">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="1087" eb="1088">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="1090" eb="1091">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1095" eb="1096">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1122" eb="1123">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="1137" eb="1138">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1144" eb="1145">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1146" eb="1147">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="1154" eb="1156">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="1164" eb="1165">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1166" eb="1167">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1175" eb="1177">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1183" eb="1185">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="1192" eb="1193">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="1198" eb="1200">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1219" eb="1221">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="1240" eb="1241">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="1242" eb="1243">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="1250" eb="1252">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1271" eb="1274">
+      <t>エキタイジョウ</t>
+    </rPh>
+    <rPh sb="1289" eb="1290">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1297" eb="1300">
+      <t>ソコキジ</t>
+    </rPh>
+    <rPh sb="1312" eb="1313">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1318" eb="1320">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1326" eb="1327">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="1337" eb="1340">
+      <t>ソコキジ</t>
+    </rPh>
+    <rPh sb="1382" eb="1384">
+      <t>アジツ</t>
+    </rPh>
+    <rPh sb="1390" eb="1391">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1444" eb="1445">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1456" eb="1458">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1469" eb="1471">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1472" eb="1474">
+      <t>ヒョウメン</t>
+    </rPh>
+    <rPh sb="1518" eb="1519">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1558" eb="1559">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1571" eb="1573">
+      <t>ヘイタン</t>
+    </rPh>
+    <rPh sb="1592" eb="1594">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1595" eb="1596">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1638" eb="1639">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1643" eb="1644">
+      <t>タイラ</t>
+    </rPh>
+    <rPh sb="1645" eb="1646">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1660" eb="1662">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1686" eb="1688">
+      <t>ヒムロ</t>
+    </rPh>
+    <rPh sb="1718" eb="1720">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="1737" eb="1738">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1751" eb="1753">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="1755" eb="1756">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1757" eb="1758">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1815" eb="1817">
+      <t>コウキ</t>
+    </rPh>
+    <rPh sb="1829" eb="1831">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1836" eb="1838">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="1859" eb="1861">
+      <t>キンパク</t>
+    </rPh>
+    <rPh sb="1871" eb="1872">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="1880" eb="1882">
+      <t>オウサマ</t>
+    </rPh>
+    <rPh sb="1883" eb="1885">
+      <t>オオヨロコ</t>
+    </rPh>
+    <rPh sb="1891" eb="1893">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【ブッシュドノエルのレシピ】
+難易度・・　中～高　ぐらい
+木を模した伝統的なケーキ菓子です。チョコレートやココアの風味が、森を思わせる・・
+森のケーキをお楽しみください。
+★魔法「ウィンドロール」を覚えておきましょう。
+★模様をつけるため、器材「フォーク」も買っておきましょう。
+下準備として、
+A. ココアケーキ生地
+B. チョコレートクリーム
+の２つを先に作ります。
+あとで、生地をまきまきしていきましょう♪
+【作り方】
+A. ココアケーキ生地
+①&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;と、&lt;color=#BA9535FF&gt;ココアパウダー&lt;/color&gt;を先に混ぜておきます。
+②アパレイユを作る・・・
+ &lt;color=#BA9535FF&gt;砂糖、卵、バター&lt;/color&gt;を混ぜ、アパレイユを作ります。
+③アパレイユに先ほどの粉類をふるい入れ、ウィンドミキサーで混ぜます。焼き上げれば生地の完成です。
+※180度で10~12分ほど焼くといい感じです。
+B.チョコレートバタークリーム
+①卵黄に砂糖を混ぜます。＜アパレイユ黄身＞
+さらに、少量の液体状チョコレートを入れよく混ぜます。
+②ある程度混ざったら、バターを入れて、よく混ぜます。
+芳醇で味わい深いチョコレートバタークリームの完成です。
+【仕上げ】
+※Aの生地を事前にスライスします。
+①スライスした生地の片面に、Bのチョコレートクリームをぬっていきます。
+②できた生地に、魔法「ウィンドロール」をかけて、きれいに巻きましょう！
+③巻いたロール生地に、さらにBチョコレートクリームをぬります。このとき、「フォーク」を使って、木の模様をつけていきます。
+④上にマジパンで作ったお花や、動物などのトッピングでデコレーションして..
+ブッシュドノエル完成で～す♪
+まさに、木を模した伝統的で豪華なお菓子です。
+ぜひ自分の手で作ってみてくださいね。
+【あとがき】
+ブッシュドノエルは、ちょうちょとの相性がいいようです。
+</t>
+    <rPh sb="16" eb="19">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>フウミ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>タノ</t>
+    </rPh>
+    <rPh sb="144" eb="147">
+      <t>シタジュンビ</t>
+    </rPh>
+    <rPh sb="161" eb="163">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="182" eb="183">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="214" eb="215">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="249" eb="252">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="338" eb="340">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="355" eb="356">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="378" eb="379">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="382" eb="384">
+      <t>コナルイ</t>
+    </rPh>
+    <rPh sb="400" eb="401">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="405" eb="406">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="407" eb="408">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="411" eb="413">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="414" eb="416">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="424" eb="425">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="431" eb="432">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="434" eb="435">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="439" eb="440">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="491" eb="494">
+      <t>エキタイジョウ</t>
+    </rPh>
+    <rPh sb="539" eb="541">
+      <t>ホウジュン</t>
+    </rPh>
+    <rPh sb="542" eb="543">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="545" eb="546">
+      <t>ブカ</t>
+    </rPh>
+    <rPh sb="561" eb="563">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="569" eb="571">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="577" eb="579">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="580" eb="582">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="600" eb="602">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="603" eb="605">
+      <t>カタメン</t>
+    </rPh>
+    <rPh sb="634" eb="636">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="638" eb="640">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="658" eb="659">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="668" eb="669">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="674" eb="676">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="710" eb="711">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="714" eb="715">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="716" eb="718">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="730" eb="731">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="737" eb="738">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="741" eb="742">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="744" eb="746">
+      <t>ドウブツ</t>
+    </rPh>
+    <rPh sb="776" eb="778">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="788" eb="789">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="790" eb="791">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="793" eb="796">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="797" eb="799">
+      <t>ゴウカ</t>
+    </rPh>
+    <rPh sb="801" eb="803">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="809" eb="811">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="812" eb="813">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="814" eb="815">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="851" eb="853">
+      <t>アイショウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7647,7 +7637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -7707,7 +7697,7 @@
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A120" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A121" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -7780,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -7927,7 +7917,7 @@
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -7948,7 +7938,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L7">
         <v>3000</v>
@@ -8872,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="L29">
         <v>130</v>
@@ -9250,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L38">
         <v>270</v>
@@ -9418,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="L42" s="5">
         <v>9999</v>
@@ -9433,7 +9423,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C43" t="s">
         <v>199</v>
@@ -9460,7 +9450,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="L43">
         <v>310</v>
@@ -9475,7 +9465,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C44" t="s">
         <v>204</v>
@@ -9517,7 +9507,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>207</v>
@@ -9559,7 +9549,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C46" t="s">
         <v>209</v>
@@ -9586,7 +9576,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L46">
         <v>340</v>
@@ -9601,7 +9591,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C47" t="s">
         <v>269</v>
@@ -9628,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="L47">
         <v>350</v>
@@ -9643,7 +9633,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C48" t="s">
         <v>270</v>
@@ -9670,7 +9660,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L48">
         <v>360</v>
@@ -9685,7 +9675,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C49" t="s">
         <v>300</v>
@@ -9712,7 +9702,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="L49">
         <v>370</v>
@@ -9727,7 +9717,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C50" t="s">
         <v>301</v>
@@ -9754,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>321</v>
+        <v>468</v>
       </c>
       <c r="L50">
         <v>380</v>
@@ -9769,7 +9759,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C51" t="s">
         <v>278</v>
@@ -9796,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>323</v>
+        <v>469</v>
       </c>
       <c r="L51">
         <v>390</v>
@@ -9853,7 +9843,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C53" t="s">
         <v>214</v>
@@ -9895,7 +9885,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C54" t="s">
         <v>216</v>
@@ -9937,7 +9927,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C55" t="s">
         <v>218</v>
@@ -9979,7 +9969,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C56" t="s">
         <v>221</v>
@@ -10006,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L56">
         <v>520</v>
@@ -10021,7 +10011,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C57" t="s">
         <v>222</v>
@@ -10048,7 +10038,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="L57">
         <v>530</v>
@@ -10090,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="L58">
         <v>540</v>
@@ -10105,7 +10095,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C59" t="s">
         <v>227</v>
@@ -10132,7 +10122,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L59">
         <v>550</v>
@@ -10147,7 +10137,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C60" t="s">
         <v>228</v>
@@ -10174,7 +10164,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L60">
         <v>560</v>
@@ -10189,7 +10179,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s">
         <v>232</v>
@@ -10216,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L61">
         <v>570</v>
@@ -10231,7 +10221,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C62" t="s">
         <v>231</v>
@@ -10273,7 +10263,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C63" t="s">
         <v>234</v>
@@ -10357,7 +10347,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C65" t="s">
         <v>238</v>
@@ -10384,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L65">
         <v>610</v>
@@ -10441,7 +10431,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C67" t="s">
         <v>241</v>
@@ -10468,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L67">
         <v>700</v>
@@ -10483,7 +10473,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C68" t="s">
         <v>263</v>
@@ -10510,7 +10500,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L68">
         <v>710</v>
@@ -10525,7 +10515,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C69" t="s">
         <v>243</v>
@@ -10552,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L69">
         <v>720</v>
@@ -10567,7 +10557,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C70" t="s">
         <v>245</v>
@@ -10594,7 +10584,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="L70">
         <v>730</v>
@@ -10609,7 +10599,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C71" t="s">
         <v>246</v>
@@ -10636,7 +10626,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L71">
         <v>740</v>
@@ -10651,7 +10641,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C72" t="s">
         <v>253</v>
@@ -10678,7 +10668,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L72">
         <v>750</v>
@@ -10693,7 +10683,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C73" t="s">
         <v>249</v>
@@ -10735,7 +10725,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C74" t="s">
         <v>265</v>
@@ -10777,7 +10767,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C75" t="s">
         <v>272</v>
@@ -10804,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="L75">
         <v>780</v>
@@ -10903,7 +10893,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C78" t="s">
         <v>293</v>
@@ -10945,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C79" t="s">
         <v>295</v>
@@ -10972,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="L79">
         <v>2100</v>
@@ -10987,7 +10977,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C80" t="s">
         <v>296</v>
@@ -11014,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="L80">
         <v>2200</v>
@@ -11029,7 +11019,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C81" t="s">
         <v>297</v>
@@ -11056,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L81">
         <v>2300</v>
@@ -11071,7 +11061,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C82" t="s">
         <v>298</v>
@@ -11098,7 +11088,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="L82">
         <v>2400</v>
@@ -11113,7 +11103,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C83" t="s">
         <v>281</v>
@@ -11155,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C84" t="s">
         <v>292</v>
@@ -11182,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="L84">
         <v>5000</v>
@@ -11197,13 +11187,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C85" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D85" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -11224,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L85">
         <v>5000</v>
@@ -11239,13 +11229,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C86" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D86" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -11266,7 +11256,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L86">
         <v>5000</v>
@@ -11281,13 +11271,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C87" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="D87" t="s">
-        <v>377</v>
+        <v>466</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -11308,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -11323,13 +11313,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C88" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="D88" t="s">
-        <v>280</v>
+        <v>375</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -11350,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11365,13 +11355,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C89" t="s">
-        <v>449</v>
+        <v>282</v>
       </c>
       <c r="D89" t="s">
-        <v>448</v>
+        <v>280</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11392,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11407,13 +11397,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C90" t="s">
-        <v>284</v>
+        <v>446</v>
       </c>
       <c r="D90" t="s">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11434,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11449,13 +11439,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C91" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="D91" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11476,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11491,13 +11481,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C92" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D92" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11518,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11533,13 +11523,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C93" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D93" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11560,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11575,13 +11565,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C94" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="D94" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11602,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11617,13 +11607,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C95" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="D95" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11644,7 +11634,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11659,13 +11649,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C96" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
       <c r="D96" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -11686,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11701,13 +11691,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C97" t="s">
-        <v>458</v>
+        <v>335</v>
       </c>
       <c r="D97" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -11728,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11743,13 +11733,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C98" t="s">
-        <v>344</v>
+        <v>455</v>
       </c>
       <c r="D98" t="s">
-        <v>342</v>
+        <v>454</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -11770,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -11785,13 +11775,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C99" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D99" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -11812,7 +11802,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -11827,13 +11817,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C100" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="D100" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -11854,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -11869,13 +11859,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C101" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="D101" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -11896,7 +11886,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -11911,13 +11901,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C102" t="s">
-        <v>348</v>
+        <v>287</v>
       </c>
       <c r="D102" t="s">
-        <v>346</v>
+        <v>288</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -11938,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -11953,13 +11943,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C103" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D103" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -11980,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -11995,13 +11985,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C104" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D104" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -12022,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12037,13 +12027,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C105" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D105" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12064,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12079,13 +12069,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C106" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -12106,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12121,13 +12111,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C107" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -12148,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>442</v>
+        <v>286</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -12163,13 +12153,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C108" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -12190,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12205,13 +12195,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C109" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -12232,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>286</v>
+        <v>437</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12247,13 +12237,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C110" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -12274,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>437</v>
+        <v>286</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -12289,13 +12279,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C111" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -12316,7 +12306,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>286</v>
+        <v>434</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12331,13 +12321,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C112" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="D112" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -12358,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>429</v>
+        <v>286</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12373,13 +12363,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C113" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D113" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -12400,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12409,45 +12399,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="114" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="11">
+    <row r="114" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A114">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="B114" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="E114" s="11">
+      <c r="B114" t="s">
+        <v>378</v>
+      </c>
+      <c r="C114" t="s">
+        <v>312</v>
+      </c>
+      <c r="D114" t="s">
+        <v>313</v>
+      </c>
+      <c r="E114">
         <v>500</v>
       </c>
-      <c r="F114" s="11">
+      <c r="F114">
         <v>150</v>
       </c>
-      <c r="G114" s="11">
-        <v>0</v>
-      </c>
-      <c r="H114" s="11">
-        <v>0</v>
-      </c>
-      <c r="I114" s="11">
-        <v>0</v>
-      </c>
-      <c r="J114" s="11">
-        <v>0</v>
-      </c>
-      <c r="K114" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="L114" s="11">
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="L114">
         <v>5000</v>
       </c>
-      <c r="M114" s="11">
+      <c r="M114">
         <v>5000</v>
       </c>
     </row>
@@ -12457,13 +12447,13 @@
         <v>113</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E115" s="11">
         <v>500</v>
@@ -12499,13 +12489,13 @@
         <v>114</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E116" s="11">
         <v>500</v>
@@ -12535,45 +12525,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117">
+    <row r="117" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="11">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="B117" t="s">
-        <v>380</v>
-      </c>
-      <c r="C117" t="s">
-        <v>372</v>
-      </c>
-      <c r="D117" t="s">
-        <v>371</v>
-      </c>
-      <c r="E117">
+      <c r="B117" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E117" s="11">
         <v>500</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="11">
         <v>150</v>
       </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="L117">
+      <c r="G117" s="11">
+        <v>0</v>
+      </c>
+      <c r="H117" s="11">
+        <v>0</v>
+      </c>
+      <c r="I117" s="11">
+        <v>0</v>
+      </c>
+      <c r="J117" s="11">
+        <v>0</v>
+      </c>
+      <c r="K117" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="L117" s="11">
         <v>5000</v>
       </c>
-      <c r="M117">
+      <c r="M117" s="11">
         <v>5000</v>
       </c>
     </row>
@@ -12583,13 +12573,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C118" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D118" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -12610,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>286</v>
+        <v>438</v>
       </c>
       <c r="L118">
         <v>5000</v>
@@ -12619,170 +12609,212 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="119" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="11">
+    <row r="119" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="B119" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="E119" s="11">
+      <c r="B119" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" t="s">
+        <v>372</v>
+      </c>
+      <c r="D119" t="s">
+        <v>371</v>
+      </c>
+      <c r="E119">
         <v>500</v>
       </c>
-      <c r="F119" s="11">
+      <c r="F119">
         <v>150</v>
       </c>
-      <c r="G119" s="11">
-        <v>0</v>
-      </c>
-      <c r="H119" s="11">
-        <v>0</v>
-      </c>
-      <c r="I119" s="11">
-        <v>0</v>
-      </c>
-      <c r="J119" s="11">
-        <v>0</v>
-      </c>
-      <c r="K119" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="L119" s="11">
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L119">
         <v>5000</v>
       </c>
-      <c r="M119" s="11">
+      <c r="M119">
         <v>5000</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120">
+    <row r="120" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="11">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="B120" t="s">
-        <v>380</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="E120" s="11">
+        <v>500</v>
+      </c>
+      <c r="F120" s="11">
+        <v>150</v>
+      </c>
+      <c r="G120" s="11">
+        <v>0</v>
+      </c>
+      <c r="H120" s="11">
+        <v>0</v>
+      </c>
+      <c r="I120" s="11">
+        <v>0</v>
+      </c>
+      <c r="J120" s="11">
+        <v>0</v>
+      </c>
+      <c r="K120" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="L120" s="11">
+        <v>5000</v>
+      </c>
+      <c r="M120" s="11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <f t="shared" si="0"/>
+        <v>119</v>
+      </c>
+      <c r="B121" t="s">
+        <v>378</v>
+      </c>
+      <c r="C121" t="s">
         <v>314</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D121" t="s">
         <v>315</v>
       </c>
-      <c r="E120">
+      <c r="E121">
         <v>500</v>
       </c>
-      <c r="F120">
+      <c r="F121">
         <v>150</v>
       </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="L120">
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="L121">
         <v>5000</v>
       </c>
-      <c r="M120">
+      <c r="M121">
         <v>5000</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121">
+    <row r="122" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122">
         <f>ROW()-2</f>
-        <v>119</v>
-      </c>
-      <c r="B121" t="s">
-        <v>462</v>
-      </c>
-      <c r="C121" t="s">
+        <v>120</v>
+      </c>
+      <c r="B122" t="s">
         <v>459</v>
       </c>
-      <c r="D121" t="s">
-        <v>460</v>
-      </c>
-      <c r="E121">
-        <v>0</v>
-      </c>
-      <c r="F121">
-        <v>0</v>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
+      <c r="C122" t="s">
+        <v>456</v>
+      </c>
+      <c r="D122" t="s">
+        <v>457</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
         <v>1</v>
       </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121" t="s">
-        <v>461</v>
-      </c>
-      <c r="L121">
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122" t="s">
+        <v>458</v>
+      </c>
+      <c r="L122">
         <v>9999</v>
       </c>
-      <c r="M121">
+      <c r="M122">
         <v>9999</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122">
+    <row r="123" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123">
         <v>10000</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B123" t="s">
         <v>170</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>174</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D123" t="s">
         <v>175</v>
       </c>
-      <c r="E122">
+      <c r="E123">
         <v>500</v>
       </c>
-      <c r="F122">
+      <c r="F123">
         <v>150</v>
       </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
         <v>1</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="K123" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L122">
+      <c r="L123">
         <v>9000</v>
       </c>
-      <c r="M122">
+      <c r="M123">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C02FDBE-3561-401D-BD02-9403C2EBFBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1860A536-CE6F-4743-99AE-7FAB7FD1E8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -3984,16 +3984,6 @@
     </rPh>
     <rPh sb="110" eb="111">
       <t>ハナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">小麦粉とバターと砂糖
-&lt;color=#BA9535FF&gt;2 : 2 : 1 &lt;/color&gt;
-で混ぜると良いらしいぜ！
-</t>
-    <rPh sb="8" eb="10">
-      <t>サトウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7182,6 +7172,16 @@
     </rPh>
     <rPh sb="851" eb="853">
       <t>アイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">小麦粉とバターと砂糖
+&lt;color=#BA9535FF&gt;2 : 2 : 2 &lt;/color&gt;
+で混ぜると良いらしいぜ！
+</t>
+    <rPh sb="8" eb="10">
+      <t>サトウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7770,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>325</v>
+        <v>469</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -8862,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L29">
         <v>130</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L42" s="5">
         <v>9999</v>
@@ -9423,7 +9423,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C43" t="s">
         <v>199</v>
@@ -9450,7 +9450,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L43">
         <v>310</v>
@@ -9465,7 +9465,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C44" t="s">
         <v>204</v>
@@ -9501,45 +9501,45 @@
         <v>320</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="11">
+    <row r="45" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="C45" s="11" t="s">
+      <c r="B45" t="s">
+        <v>380</v>
+      </c>
+      <c r="C45" t="s">
         <v>207</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" t="s">
         <v>206</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45">
         <v>500</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45">
         <v>150</v>
       </c>
-      <c r="G45" s="11">
-        <v>0</v>
-      </c>
-      <c r="H45" s="11">
-        <v>0</v>
-      </c>
-      <c r="I45" s="11">
-        <v>0</v>
-      </c>
-      <c r="J45" s="11">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
         <v>1</v>
       </c>
-      <c r="K45" s="12" t="s">
+      <c r="K45" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="L45" s="11">
+      <c r="L45">
         <v>330</v>
       </c>
-      <c r="M45" s="11">
+      <c r="M45">
         <v>330</v>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C46" t="s">
         <v>209</v>
@@ -9576,7 +9576,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L46">
         <v>340</v>
@@ -9591,7 +9591,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C47" t="s">
         <v>269</v>
@@ -9618,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L47">
         <v>350</v>
@@ -9633,7 +9633,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C48" t="s">
         <v>270</v>
@@ -9675,7 +9675,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C49" t="s">
         <v>300</v>
@@ -9702,7 +9702,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L49">
         <v>370</v>
@@ -9717,7 +9717,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C50" t="s">
         <v>301</v>
@@ -9744,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L50">
         <v>380</v>
@@ -9759,7 +9759,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C51" t="s">
         <v>278</v>
@@ -9786,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L51">
         <v>390</v>
@@ -9843,7 +9843,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C53" t="s">
         <v>214</v>
@@ -9885,7 +9885,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C54" t="s">
         <v>216</v>
@@ -9927,7 +9927,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C55" t="s">
         <v>218</v>
@@ -9969,7 +9969,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C56" t="s">
         <v>221</v>
@@ -9996,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L56">
         <v>520</v>
@@ -10011,7 +10011,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C57" t="s">
         <v>222</v>
@@ -10038,7 +10038,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L57">
         <v>530</v>
@@ -10080,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L58">
         <v>540</v>
@@ -10095,7 +10095,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C59" t="s">
         <v>227</v>
@@ -10122,7 +10122,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L59">
         <v>550</v>
@@ -10137,7 +10137,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C60" t="s">
         <v>228</v>
@@ -10164,7 +10164,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L60">
         <v>560</v>
@@ -10179,7 +10179,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C61" t="s">
         <v>232</v>
@@ -10206,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L61">
         <v>570</v>
@@ -10221,7 +10221,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
         <v>231</v>
@@ -10263,7 +10263,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C63" t="s">
         <v>234</v>
@@ -10347,7 +10347,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C65" t="s">
         <v>238</v>
@@ -10374,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L65">
         <v>610</v>
@@ -10431,7 +10431,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C67" t="s">
         <v>241</v>
@@ -10458,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L67">
         <v>700</v>
@@ -10473,7 +10473,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C68" t="s">
         <v>263</v>
@@ -10500,7 +10500,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L68">
         <v>710</v>
@@ -10515,7 +10515,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C69" t="s">
         <v>243</v>
@@ -10542,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L69">
         <v>720</v>
@@ -10557,7 +10557,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C70" t="s">
         <v>245</v>
@@ -10584,7 +10584,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L70">
         <v>730</v>
@@ -10599,7 +10599,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C71" t="s">
         <v>246</v>
@@ -10626,7 +10626,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L71">
         <v>740</v>
@@ -10641,7 +10641,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C72" t="s">
         <v>253</v>
@@ -10668,7 +10668,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L72">
         <v>750</v>
@@ -10683,7 +10683,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C73" t="s">
         <v>249</v>
@@ -10725,7 +10725,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C74" t="s">
         <v>265</v>
@@ -10767,7 +10767,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C75" t="s">
         <v>272</v>
@@ -10794,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L75">
         <v>780</v>
@@ -10893,7 +10893,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C78" t="s">
         <v>293</v>
@@ -10935,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C79" t="s">
         <v>295</v>
@@ -10962,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L79">
         <v>2100</v>
@@ -10977,7 +10977,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C80" t="s">
         <v>296</v>
@@ -11004,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L80">
         <v>2200</v>
@@ -11019,7 +11019,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C81" t="s">
         <v>297</v>
@@ -11046,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L81">
         <v>2300</v>
@@ -11061,7 +11061,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C82" t="s">
         <v>298</v>
@@ -11088,7 +11088,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L82">
         <v>2400</v>
@@ -11103,7 +11103,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C83" t="s">
         <v>281</v>
@@ -11145,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C84" t="s">
         <v>292</v>
@@ -11172,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L84">
         <v>5000</v>
@@ -11187,13 +11187,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C85" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D85" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L85">
         <v>5000</v>
@@ -11229,13 +11229,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C86" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D86" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -11256,7 +11256,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L86">
         <v>5000</v>
@@ -11271,13 +11271,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C87" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D87" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -11298,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -11313,13 +11313,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -11340,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11355,7 +11355,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C89" t="s">
         <v>282</v>
@@ -11382,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11397,13 +11397,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C90" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D90" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11424,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11439,7 +11439,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C91" t="s">
         <v>284</v>
@@ -11466,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11481,13 +11481,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C92" t="s">
+        <v>325</v>
+      </c>
+      <c r="D92" t="s">
         <v>326</v>
-      </c>
-      <c r="D92" t="s">
-        <v>327</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11523,13 +11523,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C93" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D93" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11550,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11565,7 +11565,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C94" t="s">
         <v>317</v>
@@ -11592,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11607,13 +11607,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C95" t="s">
+        <v>331</v>
+      </c>
+      <c r="D95" t="s">
         <v>332</v>
-      </c>
-      <c r="D95" t="s">
-        <v>333</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11634,7 +11634,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11649,7 +11649,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C96" t="s">
         <v>290</v>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11691,13 +11691,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D97" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -11718,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11733,13 +11733,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C98" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D98" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -11760,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -11775,13 +11775,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C99" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D99" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -11802,7 +11802,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -11817,13 +11817,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C100" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D100" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -11844,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -11859,13 +11859,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C101" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D101" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -11886,7 +11886,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -11901,7 +11901,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C102" t="s">
         <v>287</v>
@@ -11928,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -11943,13 +11943,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C103" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D103" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -11970,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -11985,13 +11985,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C104" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D104" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -12012,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12027,13 +12027,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C105" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D105" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12054,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12069,13 +12069,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C106" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D106" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12111,13 +12111,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C107" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D107" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -12153,13 +12153,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C108" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D108" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -12180,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12195,13 +12195,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C109" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -12222,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12237,13 +12237,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C110" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -12279,13 +12279,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C111" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -12306,7 +12306,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12321,13 +12321,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C112" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -12363,7 +12363,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C113" t="s">
         <v>319</v>
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12405,7 +12405,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C114" t="s">
         <v>312</v>
@@ -12432,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12447,13 +12447,13 @@
         <v>113</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E115" s="11">
         <v>500</v>
@@ -12489,13 +12489,13 @@
         <v>114</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E116" s="11">
         <v>500</v>
@@ -12531,13 +12531,13 @@
         <v>115</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E117" s="11">
         <v>500</v>
@@ -12573,13 +12573,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C118" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L118">
         <v>5000</v>
@@ -12615,13 +12615,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C119" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -12657,13 +12657,13 @@
         <v>118</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E120" s="11">
         <v>500</v>
@@ -12684,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L120" s="11">
         <v>5000</v>
@@ -12699,7 +12699,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C121" t="s">
         <v>314</v>
@@ -12726,7 +12726,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -12741,13 +12741,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C122" t="s">
+        <v>455</v>
+      </c>
+      <c r="D122" t="s">
         <v>456</v>
-      </c>
-      <c r="D122" t="s">
-        <v>457</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -12768,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L122">
         <v>9999</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1860A536-CE6F-4743-99AE-7FAB7FD1E8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211F5E3E-A82D-4189-9950-2ADF3F1780E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="480">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7183,6 +7183,210 @@
     <rPh sb="8" eb="10">
       <t>サトウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_parfe_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコばななパフェのレシピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>☆チョコばななパフェのレシピ
+★チョコを使ったパフェの作り方
+・&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;
+を準備しておきます。
+※パフェを作るときは、ガラスの器がないと、失敗しやすくなります。器を用意しましょう。
+①&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;と&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;を先にのせます。
+②できた土台の上に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;をのせ、たっぷりの&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;をかけたら完成！
+★カステラの代わりに、
+ロールクッキー、もしくは、バナナやアイスをのせても、
+おいしいパフェができます！</t>
+    <rPh sb="164" eb="166">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="179" eb="180">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>ウツワ</t>
+    </rPh>
+    <rPh sb="195" eb="197">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="206" eb="207">
+      <t>ウツワ</t>
+    </rPh>
+    <rPh sb="208" eb="210">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="265" eb="267">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="315" eb="316">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="389" eb="391">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="421" eb="422">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/parfe_chocolate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコの秘密　～その１～</t>
+    <rPh sb="4" eb="6">
+      <t>ヒミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコの秘密　～その２～</t>
+    <rPh sb="4" eb="6">
+      <t>ヒミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【チョコレートの秘密　～その１～】
+チョコレートを作る際のカカオマス
+このカカオマスに色んな材料を加えると、チョコに様々な変化が現れます。
+アレンジレシピをこっそりご紹介☆
+【苦味を加える】
+・カカオマスの状態で、いろんな材料を加えることができます。
+たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。
+【砂糖を変える】
+・通常、砂糖をいれて混ぜると思いますが、&lt;color=#BA9535FF&gt;エメラルドシュガー&lt;/color&gt;や&lt;color=#BA9535FF&gt;サファイアシュガー&lt;/color&gt;に変えると..？
+</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="118" eb="119">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="189" eb="191">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="192" eb="193">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="199" eb="201">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="202" eb="204">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="208" eb="209">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="212" eb="213">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="288" eb="289">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【チョコレートの秘密　～その２～】
+チョコレートのアレンジレシピご紹介第二弾です。
+【白いチョコの作り方】
+・液体状チョコレートに、&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
+お花のエキスがよく混ざって、なんとチョコレートが真っ白に・・！
+</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>ダイニダン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>スウテキ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="125" eb="126">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_arrange1_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_arrange2_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7285,7 +7489,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7321,6 +7525,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7637,7 +7847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -7697,7 +7907,7 @@
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A121" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A124" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -8871,46 +9081,46 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30">
+    <row r="30" spans="1:13" s="13" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="13">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30">
+      <c r="B30" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="E30" s="13">
         <v>500</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="13">
         <v>150</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
+      <c r="G30" s="13">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13">
         <v>1</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="L30">
-        <v>140</v>
-      </c>
-      <c r="M30">
-        <v>140</v>
+      <c r="K30" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="L30" s="13">
+        <v>150</v>
+      </c>
+      <c r="M30" s="13">
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8919,13 +9129,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="E31">
         <v>500</v>
@@ -8946,13 +9156,13 @@
         <v>1</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="L31">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="M31">
-        <v>200</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8961,13 +9171,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="E32">
         <v>500</v>
@@ -8988,13 +9198,13 @@
         <v>1</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L32">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="M32">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9003,13 +9213,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E33">
         <v>500</v>
@@ -9030,13 +9240,13 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="L33">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="M33">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9045,13 +9255,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9072,13 +9282,13 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L34">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="M34">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9087,13 +9297,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -9114,13 +9324,13 @@
         <v>1</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="L35">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="M35">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9129,13 +9339,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36">
         <v>500</v>
@@ -9156,13 +9366,13 @@
         <v>1</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L36">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M36">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9171,13 +9381,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="E37">
         <v>500</v>
@@ -9198,13 +9408,13 @@
         <v>1</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L37">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M37">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9213,13 +9423,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="E38">
         <v>500</v>
@@ -9240,13 +9450,13 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>321</v>
+        <v>161</v>
       </c>
       <c r="L38">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M38">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9255,13 +9465,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -9282,13 +9492,13 @@
         <v>1</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>181</v>
+        <v>321</v>
       </c>
       <c r="L39">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="M39">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9297,13 +9507,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="D40" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -9324,13 +9534,13 @@
         <v>1</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="L40">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="M40">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9339,13 +9549,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -9366,112 +9576,112 @@
         <v>1</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L41">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="M41">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="5">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" t="s">
         <v>196</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E42" s="5">
+      <c r="C42" t="s">
+        <v>192</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42">
         <v>500</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42">
         <v>150</v>
       </c>
-      <c r="G42" s="5">
-        <v>0</v>
-      </c>
-      <c r="H42" s="5">
-        <v>0</v>
-      </c>
-      <c r="I42" s="5">
-        <v>0</v>
-      </c>
-      <c r="J42" s="5">
-        <v>0</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="L42" s="5">
-        <v>9999</v>
-      </c>
-      <c r="M42" s="5">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L42">
+        <v>300</v>
+      </c>
+      <c r="M42">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" t="s">
-        <v>378</v>
-      </c>
-      <c r="C43" t="s">
-        <v>199</v>
-      </c>
-      <c r="D43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43">
+      <c r="B43" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="5">
         <v>500</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="5">
         <v>150</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="L43">
-        <v>310</v>
-      </c>
-      <c r="M43">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="L43" s="5">
+        <v>9999</v>
+      </c>
+      <c r="M43" s="5">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -9492,13 +9702,13 @@
         <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>205</v>
+        <v>452</v>
       </c>
       <c r="L44">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="M44">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9507,13 +9717,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D45" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -9534,13 +9744,13 @@
         <v>1</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L45">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="M45">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9549,13 +9759,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D46" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -9576,13 +9786,13 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>407</v>
+        <v>208</v>
       </c>
       <c r="L46">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="M46">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9591,13 +9801,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" t="s">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="E47">
         <v>500</v>
@@ -9618,13 +9828,13 @@
         <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L47">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="M47">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9633,13 +9843,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -9660,13 +9870,13 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>322</v>
+        <v>408</v>
       </c>
       <c r="L48">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="M48">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9675,13 +9885,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C49" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="D49" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -9702,13 +9912,13 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>466</v>
+        <v>322</v>
       </c>
       <c r="L49">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="M49">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9717,13 +9927,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -9744,13 +9954,13 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L50">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="M50">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9759,13 +9969,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C51" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="D51" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -9786,97 +9996,97 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L51">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="M51">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="E52" s="9">
+      <c r="B52" t="s">
+        <v>386</v>
+      </c>
+      <c r="C52" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" t="s">
+        <v>277</v>
+      </c>
+      <c r="E52">
         <v>500</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52">
         <v>150</v>
       </c>
-      <c r="G52" s="9">
-        <v>0</v>
-      </c>
-      <c r="H52" s="9">
-        <v>0</v>
-      </c>
-      <c r="I52" s="9">
-        <v>0</v>
-      </c>
-      <c r="J52" s="9">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
         <v>1</v>
       </c>
-      <c r="K52" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="L52" s="9">
-        <v>400</v>
-      </c>
-      <c r="M52" s="9">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53">
+      <c r="K52" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="L52">
+        <v>390</v>
+      </c>
+      <c r="M52">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="9">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" t="s">
-        <v>387</v>
-      </c>
-      <c r="C53" t="s">
-        <v>214</v>
-      </c>
-      <c r="D53" t="s">
-        <v>213</v>
-      </c>
-      <c r="E53">
+      <c r="B53" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E53" s="9">
         <v>500</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="9">
         <v>150</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>0</v>
+      </c>
+      <c r="I53" s="9">
+        <v>0</v>
+      </c>
+      <c r="J53" s="9">
         <v>1</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="L53">
-        <v>410</v>
-      </c>
-      <c r="M53">
-        <v>410</v>
+      <c r="K53" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="L53" s="9">
+        <v>400</v>
+      </c>
+      <c r="M53" s="9">
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9885,13 +10095,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D54" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -9912,13 +10122,13 @@
         <v>1</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L54">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="M54">
-        <v>500</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9927,13 +10137,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D55" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -9954,13 +10164,13 @@
         <v>1</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L55">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="M55">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9969,13 +10179,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="C56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -9996,13 +10206,13 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>409</v>
+        <v>257</v>
       </c>
       <c r="L56">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="M56">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10011,13 +10221,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -10038,13 +10248,13 @@
         <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L57">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="M57">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10053,13 +10263,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>196</v>
+        <v>390</v>
       </c>
       <c r="C58" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D58" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -10080,13 +10290,13 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L58">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="M58">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10095,13 +10305,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>391</v>
+        <v>196</v>
       </c>
       <c r="C59" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D59" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -10122,13 +10332,13 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L59">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="M59">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10137,13 +10347,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D60" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -10164,13 +10374,13 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L60">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="M60">
-        <v>560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10179,13 +10389,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C61" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D61" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -10206,13 +10416,13 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L61">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="M61">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10221,13 +10431,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C62" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D62" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -10248,13 +10458,13 @@
         <v>1</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>259</v>
+        <v>414</v>
       </c>
       <c r="L62">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="M62">
-        <v>580</v>
+        <v>570</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10263,13 +10473,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -10290,181 +10500,181 @@
         <v>1</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="L63">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="M63">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="7">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E64" s="7">
+      <c r="B64" t="s">
+        <v>395</v>
+      </c>
+      <c r="C64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" t="s">
+        <v>233</v>
+      </c>
+      <c r="E64">
         <v>500</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64">
         <v>150</v>
       </c>
-      <c r="G64" s="7">
-        <v>0</v>
-      </c>
-      <c r="H64" s="7">
-        <v>0</v>
-      </c>
-      <c r="I64" s="7">
-        <v>0</v>
-      </c>
-      <c r="J64" s="7">
-        <v>0</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="L64" s="7">
-        <v>600</v>
-      </c>
-      <c r="M64" s="7">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L64">
+        <v>590</v>
+      </c>
+      <c r="M64">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="7">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" t="s">
-        <v>405</v>
-      </c>
-      <c r="C65" t="s">
-        <v>238</v>
-      </c>
-      <c r="D65" t="s">
-        <v>239</v>
-      </c>
-      <c r="E65">
+      <c r="B65" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E65" s="7">
         <v>500</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="7">
         <v>150</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="L65">
-        <v>610</v>
-      </c>
-      <c r="M65">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="7">
+      <c r="G65" s="7">
+        <v>0</v>
+      </c>
+      <c r="H65" s="7">
+        <v>0</v>
+      </c>
+      <c r="I65" s="7">
+        <v>0</v>
+      </c>
+      <c r="J65" s="7">
+        <v>0</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="L65" s="7">
+        <v>600</v>
+      </c>
+      <c r="M65" s="7">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="E66" s="7">
+      <c r="B66" t="s">
+        <v>405</v>
+      </c>
+      <c r="C66" t="s">
+        <v>238</v>
+      </c>
+      <c r="D66" t="s">
+        <v>239</v>
+      </c>
+      <c r="E66">
         <v>500</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66">
         <v>150</v>
       </c>
-      <c r="G66" s="7">
-        <v>0</v>
-      </c>
-      <c r="H66" s="7">
-        <v>0</v>
-      </c>
-      <c r="I66" s="7">
-        <v>0</v>
-      </c>
-      <c r="J66" s="7">
-        <v>0</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="L66" s="7">
-        <v>620</v>
-      </c>
-      <c r="M66" s="7">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67">
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L66">
+        <v>610</v>
+      </c>
+      <c r="M66">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="7">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" t="s">
-        <v>396</v>
-      </c>
-      <c r="C67" t="s">
-        <v>241</v>
-      </c>
-      <c r="D67" t="s">
-        <v>240</v>
-      </c>
-      <c r="E67">
+      <c r="B67" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E67" s="7">
         <v>500</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="7">
         <v>150</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="L67">
-        <v>700</v>
-      </c>
-      <c r="M67">
-        <v>700</v>
+      <c r="G67" s="7">
+        <v>0</v>
+      </c>
+      <c r="H67" s="7">
+        <v>0</v>
+      </c>
+      <c r="I67" s="7">
+        <v>0</v>
+      </c>
+      <c r="J67" s="7">
+        <v>0</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="L67" s="7">
+        <v>620</v>
+      </c>
+      <c r="M67" s="7">
+        <v>620</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10473,13 +10683,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C68" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="D68" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -10500,13 +10710,13 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L68">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="M68">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10515,13 +10725,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C69" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="D69" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="E69">
         <v>500</v>
@@ -10542,13 +10752,13 @@
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L69">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="M69">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10557,13 +10767,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C70" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D70" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -10584,13 +10794,13 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L70">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="M70">
-        <v>730</v>
+        <v>720</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10599,13 +10809,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C71" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D71" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E71">
         <v>500</v>
@@ -10626,13 +10836,13 @@
         <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L71">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="M71">
-        <v>740</v>
+        <v>730</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10641,13 +10851,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C72" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D72" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -10668,13 +10878,13 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L72">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="M72">
-        <v>750</v>
+        <v>740</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10683,13 +10893,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C73" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D73" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E73">
         <v>500</v>
@@ -10710,13 +10920,13 @@
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>256</v>
+        <v>423</v>
       </c>
       <c r="L73">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="M73">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10725,13 +10935,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C74" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D74" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -10752,13 +10962,13 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L74">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="M74">
-        <v>770</v>
+        <v>760</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10767,13 +10977,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D75" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -10794,181 +11004,181 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="L75">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="M75">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="7">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E76" s="7">
+      <c r="B76" t="s">
+        <v>406</v>
+      </c>
+      <c r="C76" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76" t="s">
+        <v>271</v>
+      </c>
+      <c r="E76">
         <v>500</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76">
         <v>150</v>
       </c>
-      <c r="G76" s="7">
-        <v>0</v>
-      </c>
-      <c r="H76" s="7">
-        <v>0</v>
-      </c>
-      <c r="I76" s="7">
-        <v>0</v>
-      </c>
-      <c r="J76" s="7">
-        <v>0</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="L76" s="7">
-        <v>790</v>
-      </c>
-      <c r="M76" s="7">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="L76">
+        <v>780</v>
+      </c>
+      <c r="M76">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="7">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C77" t="s">
-        <v>299</v>
-      </c>
-      <c r="D77" t="s">
-        <v>299</v>
-      </c>
-      <c r="E77">
+      <c r="C77" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E77" s="7">
         <v>500</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="7">
         <v>150</v>
       </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L77">
-        <v>9999</v>
-      </c>
-      <c r="M77">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78">
+      <c r="G77" s="7">
+        <v>0</v>
+      </c>
+      <c r="H77" s="7">
+        <v>0</v>
+      </c>
+      <c r="I77" s="7">
+        <v>0</v>
+      </c>
+      <c r="J77" s="7">
+        <v>0</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="L77" s="7">
+        <v>790</v>
+      </c>
+      <c r="M77" s="7">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="13">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="B78" t="s">
-        <v>447</v>
-      </c>
-      <c r="C78" t="s">
-        <v>293</v>
-      </c>
-      <c r="D78" t="s">
-        <v>311</v>
-      </c>
-      <c r="E78">
+      <c r="B78" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="E78" s="13">
         <v>500</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="13">
         <v>150</v>
       </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
-      <c r="H78">
+      <c r="G78" s="13">
+        <v>0</v>
+      </c>
+      <c r="H78" s="13">
+        <v>0</v>
+      </c>
+      <c r="I78" s="13">
+        <v>0</v>
+      </c>
+      <c r="J78" s="13">
         <v>1</v>
       </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="L78">
-        <v>2000</v>
-      </c>
-      <c r="M78">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79">
+      <c r="K78" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="L78" s="13">
+        <v>800</v>
+      </c>
+      <c r="M78" s="13">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="13">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="B79" t="s">
-        <v>448</v>
-      </c>
-      <c r="C79" t="s">
-        <v>295</v>
-      </c>
-      <c r="D79" t="s">
-        <v>308</v>
-      </c>
-      <c r="E79">
+      <c r="B79" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="E79" s="13">
         <v>500</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="13">
         <v>150</v>
       </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-      <c r="H79">
+      <c r="G79" s="13">
+        <v>0</v>
+      </c>
+      <c r="H79" s="13">
+        <v>0</v>
+      </c>
+      <c r="I79" s="13">
+        <v>0</v>
+      </c>
+      <c r="J79" s="13">
         <v>1</v>
       </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="L79">
-        <v>2100</v>
-      </c>
-      <c r="M79">
-        <v>2100</v>
+      <c r="K79" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="L79" s="13">
+        <v>800</v>
+      </c>
+      <c r="M79" s="13">
+        <v>800</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10977,13 +11187,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>449</v>
+        <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D80" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -10995,22 +11205,22 @@
         <v>0</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80">
         <v>0</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>460</v>
+        <v>307</v>
       </c>
       <c r="L80">
-        <v>2200</v>
+        <v>9999</v>
       </c>
       <c r="M80">
-        <v>2200</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11019,13 +11229,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C81" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D81" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E81">
         <v>500</v>
@@ -11046,13 +11256,13 @@
         <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>461</v>
+        <v>294</v>
       </c>
       <c r="L81">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="M81">
-        <v>2300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11061,13 +11271,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C82" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D82" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -11088,13 +11298,13 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="L82">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="M82">
-        <v>2400</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11103,13 +11313,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="C83" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D83" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="E83">
         <v>500</v>
@@ -11121,22 +11331,22 @@
         <v>0</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83">
         <v>0</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>279</v>
+        <v>460</v>
       </c>
       <c r="L83">
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="M83">
-        <v>5000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11145,13 +11355,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>377</v>
+        <v>450</v>
       </c>
       <c r="C84" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D84" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -11163,22 +11373,22 @@
         <v>0</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84">
         <v>0</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="L84">
-        <v>5000</v>
+        <v>2300</v>
       </c>
       <c r="M84">
-        <v>5000</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11187,13 +11397,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>377</v>
+        <v>451</v>
       </c>
       <c r="C85" t="s">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="D85" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -11205,22 +11415,22 @@
         <v>0</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85">
         <v>0</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="L85">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="M85">
-        <v>5000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11232,10 +11442,10 @@
         <v>377</v>
       </c>
       <c r="C86" t="s">
-        <v>338</v>
+        <v>281</v>
       </c>
       <c r="D86" t="s">
-        <v>337</v>
+        <v>283</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -11256,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>442</v>
+        <v>279</v>
       </c>
       <c r="L86">
         <v>5000</v>
@@ -11274,10 +11484,10 @@
         <v>377</v>
       </c>
       <c r="C87" t="s">
-        <v>463</v>
+        <v>292</v>
       </c>
       <c r="D87" t="s">
-        <v>465</v>
+        <v>291</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -11298,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -11316,10 +11526,10 @@
         <v>377</v>
       </c>
       <c r="C88" t="s">
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="D88" t="s">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -11340,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11358,10 +11568,10 @@
         <v>377</v>
       </c>
       <c r="C89" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
       <c r="D89" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11382,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11400,10 +11610,10 @@
         <v>377</v>
       </c>
       <c r="C90" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D90" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11424,7 +11634,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11442,10 +11652,10 @@
         <v>377</v>
       </c>
       <c r="C91" t="s">
-        <v>284</v>
+        <v>375</v>
       </c>
       <c r="D91" t="s">
-        <v>285</v>
+        <v>374</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11484,10 +11694,10 @@
         <v>377</v>
       </c>
       <c r="C92" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="D92" t="s">
-        <v>326</v>
+        <v>280</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11508,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11526,10 +11736,10 @@
         <v>377</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>445</v>
       </c>
       <c r="D93" t="s">
-        <v>327</v>
+        <v>444</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11550,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11568,10 +11778,10 @@
         <v>377</v>
       </c>
       <c r="C94" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="D94" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11610,10 +11820,10 @@
         <v>377</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D95" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11634,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11652,10 +11862,10 @@
         <v>377</v>
       </c>
       <c r="C96" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="D96" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -11676,7 +11886,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11694,10 +11904,10 @@
         <v>377</v>
       </c>
       <c r="C97" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="D97" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -11718,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11736,10 +11946,10 @@
         <v>377</v>
       </c>
       <c r="C98" t="s">
-        <v>454</v>
+        <v>331</v>
       </c>
       <c r="D98" t="s">
-        <v>453</v>
+        <v>332</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -11760,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -11778,10 +11988,10 @@
         <v>377</v>
       </c>
       <c r="C99" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="D99" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -11802,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -11820,10 +12030,10 @@
         <v>377</v>
       </c>
       <c r="C100" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="D100" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -11844,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -11862,10 +12072,10 @@
         <v>377</v>
       </c>
       <c r="C101" t="s">
-        <v>330</v>
+        <v>454</v>
       </c>
       <c r="D101" t="s">
-        <v>329</v>
+        <v>453</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -11904,10 +12114,10 @@
         <v>377</v>
       </c>
       <c r="C102" t="s">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="D102" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -11928,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -11946,10 +12156,10 @@
         <v>377</v>
       </c>
       <c r="C103" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D103" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -11970,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -11988,10 +12198,10 @@
         <v>377</v>
       </c>
       <c r="C104" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="D104" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -12012,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12030,10 +12240,10 @@
         <v>377</v>
       </c>
       <c r="C105" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="D105" t="s">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12054,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12072,10 +12282,10 @@
         <v>377</v>
       </c>
       <c r="C106" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D106" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -12096,7 +12306,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12114,10 +12324,10 @@
         <v>377</v>
       </c>
       <c r="C107" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D107" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -12138,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>286</v>
+        <v>429</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -12156,10 +12366,10 @@
         <v>377</v>
       </c>
       <c r="C108" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D108" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -12180,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12198,10 +12408,10 @@
         <v>377</v>
       </c>
       <c r="C109" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D109" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -12222,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12240,10 +12450,10 @@
         <v>377</v>
       </c>
       <c r="C110" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D110" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -12282,10 +12492,10 @@
         <v>377</v>
       </c>
       <c r="C111" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D111" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -12306,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12324,10 +12534,10 @@
         <v>377</v>
       </c>
       <c r="C112" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D112" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -12348,7 +12558,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>286</v>
+        <v>436</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12366,10 +12576,10 @@
         <v>377</v>
       </c>
       <c r="C113" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="D113" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -12390,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>425</v>
+        <v>286</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12408,10 +12618,10 @@
         <v>377</v>
       </c>
       <c r="C114" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="D114" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -12432,7 +12642,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12441,213 +12651,213 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="115" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="11">
+    <row r="115" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A115">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" t="s">
         <v>377</v>
       </c>
-      <c r="C115" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="E115" s="11">
+      <c r="C115" t="s">
+        <v>362</v>
+      </c>
+      <c r="D115" t="s">
+        <v>359</v>
+      </c>
+      <c r="E115">
         <v>500</v>
       </c>
-      <c r="F115" s="11">
+      <c r="F115">
         <v>150</v>
       </c>
-      <c r="G115" s="11">
-        <v>0</v>
-      </c>
-      <c r="H115" s="11">
-        <v>0</v>
-      </c>
-      <c r="I115" s="11">
-        <v>0</v>
-      </c>
-      <c r="J115" s="11">
-        <v>0</v>
-      </c>
-      <c r="K115" s="12" t="s">
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="L115" s="11">
+      <c r="L115">
         <v>5000</v>
       </c>
-      <c r="M115" s="11">
+      <c r="M115">
         <v>5000</v>
       </c>
     </row>
-    <row r="116" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="11">
+    <row r="116" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A116">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" t="s">
         <v>377</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E116" s="11">
+      <c r="C116" t="s">
+        <v>319</v>
+      </c>
+      <c r="D116" t="s">
+        <v>320</v>
+      </c>
+      <c r="E116">
         <v>500</v>
       </c>
-      <c r="F116" s="11">
+      <c r="F116">
         <v>150</v>
       </c>
-      <c r="G116" s="11">
-        <v>0</v>
-      </c>
-      <c r="H116" s="11">
-        <v>0</v>
-      </c>
-      <c r="I116" s="11">
-        <v>0</v>
-      </c>
-      <c r="J116" s="11">
-        <v>0</v>
-      </c>
-      <c r="K116" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="L116" s="11">
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L116">
         <v>5000</v>
       </c>
-      <c r="M116" s="11">
+      <c r="M116">
         <v>5000</v>
       </c>
     </row>
-    <row r="117" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="11">
+    <row r="117" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A117">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" t="s">
         <v>377</v>
       </c>
-      <c r="C117" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="E117" s="11">
+      <c r="C117" t="s">
+        <v>312</v>
+      </c>
+      <c r="D117" t="s">
+        <v>313</v>
+      </c>
+      <c r="E117">
         <v>500</v>
       </c>
-      <c r="F117" s="11">
+      <c r="F117">
         <v>150</v>
       </c>
-      <c r="G117" s="11">
-        <v>0</v>
-      </c>
-      <c r="H117" s="11">
-        <v>0</v>
-      </c>
-      <c r="I117" s="11">
-        <v>0</v>
-      </c>
-      <c r="J117" s="11">
-        <v>0</v>
-      </c>
-      <c r="K117" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="L117" s="11">
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="L117">
         <v>5000</v>
       </c>
-      <c r="M117" s="11">
+      <c r="M117">
         <v>5000</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118">
+    <row r="118" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="11">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="C118" t="s">
-        <v>369</v>
-      </c>
-      <c r="D118" t="s">
-        <v>368</v>
-      </c>
-      <c r="E118">
+      <c r="C118" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="E118" s="11">
         <v>500</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="11">
         <v>150</v>
       </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="L118">
+      <c r="G118" s="11">
+        <v>0</v>
+      </c>
+      <c r="H118" s="11">
+        <v>0</v>
+      </c>
+      <c r="I118" s="11">
+        <v>0</v>
+      </c>
+      <c r="J118" s="11">
+        <v>0</v>
+      </c>
+      <c r="K118" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="L118" s="11">
         <v>5000</v>
       </c>
-      <c r="M118">
+      <c r="M118" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119">
+    <row r="119" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="11">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="C119" t="s">
-        <v>371</v>
-      </c>
-      <c r="D119" t="s">
-        <v>370</v>
-      </c>
-      <c r="E119">
+      <c r="C119" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E119" s="11">
         <v>500</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="11">
         <v>150</v>
       </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119" s="2" t="s">
+      <c r="G119" s="11">
+        <v>0</v>
+      </c>
+      <c r="H119" s="11">
+        <v>0</v>
+      </c>
+      <c r="I119" s="11">
+        <v>0</v>
+      </c>
+      <c r="J119" s="11">
+        <v>0</v>
+      </c>
+      <c r="K119" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="L119">
+      <c r="L119" s="11">
         <v>5000</v>
       </c>
-      <c r="M119">
+      <c r="M119" s="11">
         <v>5000</v>
       </c>
     </row>
@@ -12660,10 +12870,10 @@
         <v>377</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E120" s="11">
         <v>500</v>
@@ -12684,7 +12894,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="12" t="s">
-        <v>443</v>
+        <v>286</v>
       </c>
       <c r="L120" s="11">
         <v>5000</v>
@@ -12702,10 +12912,10 @@
         <v>377</v>
       </c>
       <c r="C121" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="D121" t="s">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -12726,7 +12936,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -12735,86 +12945,212 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="B122" t="s">
+        <v>377</v>
+      </c>
+      <c r="C122" t="s">
+        <v>371</v>
+      </c>
+      <c r="D122" t="s">
+        <v>370</v>
+      </c>
+      <c r="E122">
+        <v>500</v>
+      </c>
+      <c r="F122">
+        <v>150</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L122">
+        <v>5000</v>
+      </c>
+      <c r="M122">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="11">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="E123" s="11">
+        <v>500</v>
+      </c>
+      <c r="F123" s="11">
+        <v>150</v>
+      </c>
+      <c r="G123" s="11">
+        <v>0</v>
+      </c>
+      <c r="H123" s="11">
+        <v>0</v>
+      </c>
+      <c r="I123" s="11">
+        <v>0</v>
+      </c>
+      <c r="J123" s="11">
+        <v>0</v>
+      </c>
+      <c r="K123" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="L123" s="11">
+        <v>5000</v>
+      </c>
+      <c r="M123" s="11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124">
+        <f t="shared" si="0"/>
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" t="s">
+        <v>314</v>
+      </c>
+      <c r="D124" t="s">
+        <v>315</v>
+      </c>
+      <c r="E124">
+        <v>500</v>
+      </c>
+      <c r="F124">
+        <v>150</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="L124">
+        <v>5000</v>
+      </c>
+      <c r="M124">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125">
         <f>ROW()-2</f>
-        <v>120</v>
-      </c>
-      <c r="B122" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
         <v>458</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C125" t="s">
         <v>455</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D125" t="s">
         <v>456</v>
       </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-      <c r="F122">
-        <v>0</v>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
         <v>1</v>
       </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122" t="s">
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125" t="s">
         <v>457</v>
       </c>
-      <c r="L122">
+      <c r="L125">
         <v>9999</v>
       </c>
-      <c r="M122">
+      <c r="M125">
         <v>9999</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123">
+    <row r="126" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126">
         <v>10000</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B126" t="s">
         <v>170</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C126" t="s">
         <v>174</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D126" t="s">
         <v>175</v>
       </c>
-      <c r="E123">
+      <c r="E126">
         <v>500</v>
       </c>
-      <c r="F123">
+      <c r="F126">
         <v>150</v>
       </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
         <v>1</v>
       </c>
-      <c r="K123" s="2" t="s">
+      <c r="K126" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L123">
+      <c r="L126">
         <v>9000</v>
       </c>
-      <c r="M123">
+      <c r="M126">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211F5E3E-A82D-4189-9950-2ADF3F1780E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD304FDD-FAB5-464E-BBAE-647CA20E21EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -5546,33 +5546,6 @@
     </rPh>
     <rPh sb="257" eb="258">
       <t>アメ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">☆ストロベリーパフェのレシピ
-★事前に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;と、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;、&lt;color=#BA9535FF&gt;ガラスの器&lt;/color&gt;は準備しておきましょう！
-※ガラスの器がないと、失敗しやすくなります。
-①&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;と&lt;color=#BA9535FF&gt;ヨーグルト&lt;/color&gt;、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;を敷きます。
-②できた土台の上に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;をのせ、さらに、山盛りの&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;をのせたら完成！
-※アレンジレシピ
-①の時に、いちごの代わりにコーンフレークを使い、
-②のいちごを、アイスクリームに変えると..。
-</t>
-    <rPh sb="17" eb="19">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>ウツワ</t>
-    </rPh>
-    <rPh sb="116" eb="118">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="133" eb="134">
-      <t>ウツワ</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7194,199 +7167,288 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Items/parfe_chocolate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコの秘密　～その１～</t>
+    <rPh sb="4" eb="6">
+      <t>ヒミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコの秘密　～その２～</t>
+    <rPh sb="4" eb="6">
+      <t>ヒミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_arrange1_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_arrange2_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【チョコレートの秘密　～その１～】
+今回の特集は.. チョコレート作りの秘訣！！
+チョコを作る際のアレンジレシピをご紹介いたします！
+※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
+今回のテーマは、「カカオマス」。
+この「カカオマス」に色んな材料を加えると、チョコに様々な変化が現れます。
+いくつか秘密をご紹介しますね☆
+【苦味を加える】
+・「カカオマス」の状態で、いろんな材料を加えることができます。
+たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。
+【砂糖を変える】
+・通常使う砂糖を、&lt;color=#BA9535FF&gt;エメラルドシュガー&lt;/color&gt;や&lt;color=#BA9535FF&gt;サファイアシュガー&lt;/color&gt;に変えると..？
+</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トクシュウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒケツ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="139" eb="140">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="185" eb="187">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="188" eb="189">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="203" eb="205">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="211" eb="213">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="214" eb="215">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="265" eb="266">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="270" eb="272">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="273" eb="274">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="285" eb="287">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="288" eb="289">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="295" eb="297">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="297" eb="298">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="373" eb="374">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">☆ストロベリーパフェのレシピ
+★事前に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;と、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;、&lt;color=#FF5CA1FF&gt;ガラスの器&lt;/color&gt;は準備しておきましょう！
+※ガラスの器がないと、失敗しやすくなります。
+①&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;と&lt;color=#BA9535FF&gt;ヨーグルト&lt;/color&gt;、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;を敷きます。
+②できた土台の上に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;をのせ、さらに、山盛りの&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;をのせたら完成！
+※アレンジレシピ
+①の時に、いちごの代わりにコーンフレークを使い、
+②のいちごを、アイスクリームに変えると..。
+</t>
+    <rPh sb="17" eb="19">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>ウツワ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>ウツワ</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>☆チョコばななパフェのレシピ
 ★チョコを使ったパフェの作り方
 ・&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;
 ・&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;
 ・&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;
 ・&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;
+・&lt;color=#FF5CA1FF&gt;ガラスの器&lt;/color&gt;
 を準備しておきます。
 ※パフェを作るときは、ガラスの器がないと、失敗しやすくなります。器を用意しましょう。
 ①&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;と&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;を先にのせます。
 ②できた土台の上に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;をのせ、たっぷりの&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;をかけたら完成！
 ★カステラの代わりに、
-ロールクッキー、もしくは、バナナやアイスをのせても、
+&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;、もしくは、バナナやアイスをのせても、
 おいしいパフェができます！</t>
-    <rPh sb="164" eb="166">
+    <rPh sb="185" eb="186">
+      <t>ウツワ</t>
+    </rPh>
+    <rPh sb="196" eb="198">
       <t>ジュンビ</t>
     </rPh>
-    <rPh sb="179" eb="180">
+    <rPh sb="211" eb="212">
       <t>ツク</t>
     </rPh>
-    <rPh sb="189" eb="190">
+    <rPh sb="221" eb="222">
       <t>ウツワ</t>
     </rPh>
-    <rPh sb="195" eb="197">
+    <rPh sb="227" eb="229">
       <t>シッパイ</t>
     </rPh>
-    <rPh sb="206" eb="207">
+    <rPh sb="238" eb="239">
       <t>ウツワ</t>
     </rPh>
-    <rPh sb="208" eb="210">
+    <rPh sb="240" eb="242">
       <t>ヨウイ</t>
     </rPh>
-    <rPh sb="265" eb="267">
+    <rPh sb="297" eb="299">
       <t>エキタイ</t>
     </rPh>
-    <rPh sb="315" eb="316">
+    <rPh sb="347" eb="348">
       <t>サキ</t>
     </rPh>
-    <rPh sb="389" eb="391">
+    <rPh sb="421" eb="423">
       <t>エキタイ</t>
     </rPh>
-    <rPh sb="421" eb="422">
+    <rPh sb="453" eb="454">
       <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Items/parfe_chocolate</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チョコの秘密　～その１～</t>
-    <rPh sb="4" eb="6">
-      <t>ヒミツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チョコの秘密　～その２～</t>
-    <rPh sb="4" eb="6">
-      <t>ヒミツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【チョコレートの秘密　～その１～】
-チョコレートを作る際のカカオマス
-このカカオマスに色んな材料を加えると、チョコに様々な変化が現れます。
-アレンジレシピをこっそりご紹介☆
-【苦味を加える】
-・カカオマスの状態で、いろんな材料を加えることができます。
-たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。
-【砂糖を変える】
-・通常、砂糖をいれて混ぜると思いますが、&lt;color=#BA9535FF&gt;エメラルドシュガー&lt;/color&gt;や&lt;color=#BA9535FF&gt;サファイアシュガー&lt;/color&gt;に変えると..？
-</t>
-    <rPh sb="8" eb="10">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>アラワ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>ニガミ</t>
-    </rPh>
-    <rPh sb="94" eb="95">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="118" eb="119">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="169" eb="170">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>ニガミ</t>
-    </rPh>
-    <rPh sb="177" eb="178">
-      <t>ツヨ</t>
-    </rPh>
-    <rPh sb="189" eb="191">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="192" eb="193">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="199" eb="201">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="202" eb="204">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="208" eb="209">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="212" eb="213">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="288" eb="289">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">【チョコレートの秘密　～その２～】
-チョコレートのアレンジレシピご紹介第二弾です。
-【白いチョコの作り方】
-・液体状チョコレートに、&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
+今回の特集は.. チョコレート作りの秘訣！！第二弾！！
+※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
+今回のテーマは、「白いチョコレート」の作り方。
+真っ黒のチョコもおいしいですが、少し飽きてきたそこのアナタにぜひ！
+ヒア・ウィ・ゴーー！！
+【ホワイトチョコの作り方】
+・液体状チョコレートの状態で、&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
 お花のエキスがよく混ざって、なんとチョコレートが真っ白に・・！
 </t>
     <rPh sb="8" eb="10">
       <t>ヒミツ</t>
     </rPh>
-    <rPh sb="34" eb="36">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="36" eb="39">
+    <rPh sb="41" eb="44">
       <t>ダイニダン</t>
     </rPh>
-    <rPh sb="58" eb="60">
+    <rPh sb="100" eb="101">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="178" eb="180">
       <t>エキタイ</t>
     </rPh>
-    <rPh sb="60" eb="61">
+    <rPh sb="180" eb="181">
       <t>ジョウ</t>
     </rPh>
-    <rPh sb="87" eb="88">
+    <rPh sb="188" eb="190">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="210" eb="211">
       <t>ハナ</t>
     </rPh>
-    <rPh sb="104" eb="106">
+    <rPh sb="227" eb="229">
       <t>スウテキ</t>
     </rPh>
-    <rPh sb="106" eb="107">
+    <rPh sb="229" eb="230">
       <t>クワ</t>
     </rPh>
-    <rPh sb="117" eb="118">
+    <rPh sb="240" eb="241">
       <t>ハナ</t>
     </rPh>
-    <rPh sb="125" eb="126">
+    <rPh sb="248" eb="249">
       <t>マ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>chocolate_arrange1_recipi</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>chocolate_arrange2_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7489,7 +7551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7525,12 +7587,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7980,7 +8036,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -9072,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>424</v>
+        <v>477</v>
       </c>
       <c r="L29">
         <v>130</v>
@@ -9081,45 +9137,45 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="13" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="13">
+    <row r="30" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>473</v>
-      </c>
-      <c r="C30" s="13" t="s">
+      <c r="B30" t="s">
+        <v>471</v>
+      </c>
+      <c r="C30" t="s">
+        <v>469</v>
+      </c>
+      <c r="D30" t="s">
         <v>470</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="E30" s="13">
+      <c r="E30">
         <v>500</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30">
         <v>150</v>
       </c>
-      <c r="G30" s="13">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13">
-        <v>0</v>
-      </c>
-      <c r="I30" s="13">
-        <v>0</v>
-      </c>
-      <c r="J30" s="13">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>1</v>
       </c>
-      <c r="K30" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="L30" s="13">
+      <c r="K30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="L30">
         <v>150</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30">
         <v>150</v>
       </c>
     </row>
@@ -9702,7 +9758,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L44">
         <v>310</v>
@@ -9954,7 +10010,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L50">
         <v>370</v>
@@ -9996,7 +10052,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L51">
         <v>380</v>
@@ -10038,7 +10094,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L52">
         <v>390</v>
@@ -11097,88 +11153,88 @@
         <v>790</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="13">
+    <row r="78" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="D78" s="13" t="s">
+      <c r="C78" t="s">
         <v>474</v>
       </c>
-      <c r="E78" s="13">
+      <c r="D78" t="s">
+        <v>472</v>
+      </c>
+      <c r="E78">
         <v>500</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78">
         <v>150</v>
       </c>
-      <c r="G78" s="13">
-        <v>0</v>
-      </c>
-      <c r="H78" s="13">
-        <v>0</v>
-      </c>
-      <c r="I78" s="13">
-        <v>0</v>
-      </c>
-      <c r="J78" s="13">
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
         <v>1</v>
       </c>
-      <c r="K78" s="14" t="s">
+      <c r="K78" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="L78" s="13">
+      <c r="L78">
         <v>800</v>
       </c>
-      <c r="M78" s="13">
+      <c r="M78">
         <v>800</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="13">
+    <row r="79" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" t="s">
         <v>93</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" t="s">
+        <v>475</v>
+      </c>
+      <c r="D79" t="s">
+        <v>473</v>
+      </c>
+      <c r="E79">
+        <v>500</v>
+      </c>
+      <c r="F79">
+        <v>150</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="E79" s="13">
-        <v>500</v>
-      </c>
-      <c r="F79" s="13">
-        <v>150</v>
-      </c>
-      <c r="G79" s="13">
-        <v>0</v>
-      </c>
-      <c r="H79" s="13">
-        <v>0</v>
-      </c>
-      <c r="I79" s="13">
-        <v>0</v>
-      </c>
-      <c r="J79" s="13">
-        <v>1</v>
-      </c>
-      <c r="K79" s="14" t="s">
-        <v>477</v>
-      </c>
-      <c r="L79" s="13">
-        <v>800</v>
-      </c>
-      <c r="M79" s="13">
-        <v>800</v>
+      <c r="L79">
+        <v>810</v>
+      </c>
+      <c r="M79">
+        <v>810</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11229,7 +11285,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C81" t="s">
         <v>293</v>
@@ -11271,7 +11327,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C82" t="s">
         <v>295</v>
@@ -11298,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L82">
         <v>2100</v>
@@ -11313,7 +11369,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C83" t="s">
         <v>296</v>
@@ -11340,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L83">
         <v>2200</v>
@@ -11355,7 +11411,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C84" t="s">
         <v>297</v>
@@ -11382,7 +11438,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L84">
         <v>2300</v>
@@ -11397,7 +11453,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C85" t="s">
         <v>298</v>
@@ -11424,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L85">
         <v>2400</v>
@@ -11508,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -11550,7 +11606,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11592,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11610,10 +11666,10 @@
         <v>377</v>
       </c>
       <c r="C90" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D90" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11634,7 +11690,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11676,7 +11732,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11718,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11736,10 +11792,10 @@
         <v>377</v>
       </c>
       <c r="C93" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D93" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11760,7 +11816,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11802,7 +11858,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11844,7 +11900,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11886,7 +11942,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11928,7 +11984,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11970,7 +12026,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -12012,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -12054,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -12072,10 +12128,10 @@
         <v>377</v>
       </c>
       <c r="C101" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D101" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12096,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -12138,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -12180,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -12222,7 +12278,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12264,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12306,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12348,7 +12404,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -12390,7 +12446,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12432,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12516,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12558,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12642,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12726,7 +12782,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12768,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L117">
         <v>5000</v>
@@ -12936,7 +12992,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -13020,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L123" s="11">
         <v>5000</v>
@@ -13062,7 +13118,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L124">
         <v>5000</v>
@@ -13077,13 +13133,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C125" t="s">
+        <v>454</v>
+      </c>
+      <c r="D125" t="s">
         <v>455</v>
-      </c>
-      <c r="D125" t="s">
-        <v>456</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -13104,7 +13160,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L125">
         <v>9999</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD304FDD-FAB5-464E-BBAE-647CA20E21EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938C80EE-A151-4D68-9070-255C7723D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3120" yWindow="1245" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="491">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -243,20 +243,6 @@
   </si>
   <si>
     <t>Items/creampuff</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">①&lt;color=#BA9535FF&gt;たまご・砂糖・はちみつ&lt;/color&gt;を混ぜたアパレイユ＜ハニー＞を作る。
-②&lt;color=#BA9535FF&gt;＜小麦粉＞＋＜アーモンドプードル＞&lt;/color&gt;を混ぜる。
-①と②を合わせ、じっくり混ぜつつ、&lt;color=#BA9535FF&gt;＜焦がしバター＞&lt;/color&gt;を加えて仕上げる。
-生地を寝かせ、焼き上げたら完成。
-</t>
-    <rPh sb="119" eb="120">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>シア</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -6204,26 +6190,6 @@
   </si>
   <si>
     <t>mg_rare_findUP_book</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コンテストで手に入る？</t>
-    <rPh sb="6" eb="7">
-      <t>テ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>レアアイテム発見+1の本</t>
-    <rPh sb="6" eb="8">
-      <t>ハッケン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ホン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7449,6 +7415,109 @@
     <rPh sb="248" eb="249">
       <t>マ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グリッターの本</t>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_glitter_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリング・ファーマシーの本</t>
+    <rPh sb="13" eb="14">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セイント・フルールの本</t>
+    <rPh sb="10" eb="11">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_spring_pharmacy_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_saint_fleur_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未定</t>
+    <rPh sb="0" eb="2">
+      <t>ミテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニーモニックの本</t>
+    <rPh sb="7" eb="8">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_mnemonic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">①&lt;color=#BA9535FF&gt;たまご・砂糖・はちみつ&lt;/color&gt;を混ぜたアパレイユ＜ハニー＞を作る。
+②&lt;color=#BA9535FF&gt;＜小麦粉＞＋＜アーモンドプードル＞&lt;/color&gt;を混ぜる。
+粉類のみで混ぜる。
+①と②を合わせ、じっくり混ぜつつ、&lt;color=#BA9535FF&gt;＜焦がしバター＞&lt;/color&gt;を加えて仕上げる。
+生地を寝かせ、焼き上げたら完成。
+</t>
+    <rPh sb="106" eb="108">
+      <t>コナルイ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルミエールエピファニアの賞品</t>
+    <rPh sb="12" eb="14">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初から覚えてる</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レアもの発見+1の本</t>
+    <rPh sb="4" eb="6">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エメラルショップ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7903,7 +7972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -7946,7 +8015,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>11</v>
@@ -7955,19 +8024,19 @@
         <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A124" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A128" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -8009,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -8036,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -8051,7 +8120,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -8093,7 +8162,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -8135,13 +8204,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>500</v>
@@ -8162,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -8177,13 +8246,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8204,7 +8273,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L7">
         <v>3000</v>
@@ -8219,13 +8288,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" t="s">
         <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
       </c>
       <c r="E8">
         <v>500</v>
@@ -8246,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L8">
         <v>3020</v>
@@ -8261,13 +8330,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E9">
         <v>500</v>
@@ -8288,7 +8357,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L9">
         <v>3050</v>
@@ -8303,13 +8372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10">
         <v>500</v>
@@ -8330,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L10">
         <v>3070</v>
@@ -8345,13 +8414,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" t="s">
         <v>171</v>
-      </c>
-      <c r="D11" t="s">
-        <v>172</v>
       </c>
       <c r="E11">
         <v>500</v>
@@ -8372,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L11">
         <v>3080</v>
@@ -8387,13 +8456,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12">
         <v>500</v>
@@ -8414,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L12">
         <v>3090</v>
@@ -8429,13 +8498,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" t="s">
         <v>185</v>
-      </c>
-      <c r="D13" t="s">
-        <v>186</v>
       </c>
       <c r="E13">
         <v>500</v>
@@ -8456,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L13">
         <v>3100</v>
@@ -8471,13 +8540,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -8498,7 +8567,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L14">
         <v>3010</v>
@@ -8516,10 +8585,10 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
         <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -8540,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L15">
         <v>3030</v>
@@ -8555,13 +8624,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16">
         <v>500</v>
@@ -8582,7 +8651,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L16">
         <v>3040</v>
@@ -8597,13 +8666,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
         <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>95</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -8624,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L17">
         <v>3060</v>
@@ -8645,7 +8714,7 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -8666,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L18">
         <v>20</v>
@@ -8708,7 +8777,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>48</v>
+        <v>486</v>
       </c>
       <c r="L19">
         <v>30</v>
@@ -8729,7 +8798,7 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E20">
         <v>500</v>
@@ -8750,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L20">
         <v>40</v>
@@ -8765,13 +8834,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" t="s">
         <v>162</v>
-      </c>
-      <c r="C21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" t="s">
-        <v>163</v>
       </c>
       <c r="E21">
         <v>500</v>
@@ -8792,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L21">
         <v>50</v>
@@ -8834,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L22">
         <v>60</v>
@@ -8876,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L23">
         <v>70</v>
@@ -8918,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L24">
         <v>80</v>
@@ -8939,7 +9008,7 @@
         <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -8960,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L25">
         <v>90</v>
@@ -9002,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -9017,13 +9086,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -9044,7 +9113,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L27">
         <v>110</v>
@@ -9059,13 +9128,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -9086,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L28">
         <v>120</v>
@@ -9101,13 +9170,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -9128,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L29">
         <v>130</v>
@@ -9143,13 +9212,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C30" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D30" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E30">
         <v>500</v>
@@ -9170,7 +9239,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="L30">
         <v>150</v>
@@ -9185,13 +9254,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E31">
         <v>500</v>
@@ -9212,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L31">
         <v>140</v>
@@ -9227,7 +9296,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
         <v>28</v>
@@ -9254,7 +9323,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L32">
         <v>200</v>
@@ -9269,13 +9338,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33">
         <v>500</v>
@@ -9296,7 +9365,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L33">
         <v>210</v>
@@ -9311,13 +9380,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9338,7 +9407,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L34">
         <v>220</v>
@@ -9353,13 +9422,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -9380,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L35">
         <v>230</v>
@@ -9395,13 +9464,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E36">
         <v>500</v>
@@ -9422,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L36">
         <v>240</v>
@@ -9437,13 +9506,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E37">
         <v>500</v>
@@ -9464,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L37">
         <v>250</v>
@@ -9506,7 +9575,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L38">
         <v>260</v>
@@ -9521,13 +9590,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" t="s">
         <v>165</v>
-      </c>
-      <c r="D39" t="s">
-        <v>166</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -9548,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L39">
         <v>270</v>
@@ -9563,13 +9632,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -9590,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L40">
         <v>280</v>
@@ -9605,13 +9674,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -9632,7 +9701,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L41">
         <v>290</v>
@@ -9647,13 +9716,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E42">
         <v>500</v>
@@ -9674,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L42">
         <v>300</v>
@@ -9689,13 +9758,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E43" s="5">
         <v>500</v>
@@ -9716,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L43" s="5">
         <v>9999</v>
@@ -9731,13 +9800,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -9758,7 +9827,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L44">
         <v>310</v>
@@ -9773,13 +9842,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -9800,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L45">
         <v>320</v>
@@ -9815,13 +9884,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -9842,7 +9911,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L46">
         <v>330</v>
@@ -9857,13 +9926,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C47" t="s">
+        <v>208</v>
+      </c>
+      <c r="D47" t="s">
         <v>209</v>
-      </c>
-      <c r="D47" t="s">
-        <v>210</v>
       </c>
       <c r="E47">
         <v>500</v>
@@ -9884,7 +9953,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L47">
         <v>340</v>
@@ -9899,13 +9968,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -9926,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L48">
         <v>350</v>
@@ -9941,13 +10010,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -9968,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L49">
         <v>360</v>
@@ -9983,13 +10052,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10010,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L50">
         <v>370</v>
@@ -10025,13 +10094,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10052,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="L51">
         <v>380</v>
@@ -10067,13 +10136,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10094,7 +10163,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L52">
         <v>390</v>
@@ -10109,13 +10178,13 @@
         <v>51</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C53" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="E53" s="9">
         <v>500</v>
@@ -10136,7 +10205,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L53" s="9">
         <v>400</v>
@@ -10151,13 +10220,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -10178,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L54">
         <v>410</v>
@@ -10193,13 +10262,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -10220,7 +10289,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L55">
         <v>500</v>
@@ -10235,13 +10304,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -10262,7 +10331,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L56">
         <v>510</v>
@@ -10277,13 +10346,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -10304,7 +10373,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L57">
         <v>520</v>
@@ -10319,13 +10388,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D58" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -10346,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L58">
         <v>530</v>
@@ -10361,13 +10430,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -10388,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L59">
         <v>540</v>
@@ -10403,13 +10472,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C60" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -10430,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L60">
         <v>550</v>
@@ -10445,13 +10514,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -10472,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L61">
         <v>560</v>
@@ -10487,13 +10556,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -10514,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L62">
         <v>570</v>
@@ -10529,13 +10598,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -10556,7 +10625,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L63">
         <v>580</v>
@@ -10571,13 +10640,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D64" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -10598,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L64">
         <v>590</v>
@@ -10613,13 +10682,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E65" s="7">
         <v>500</v>
@@ -10640,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L65" s="7">
         <v>600</v>
@@ -10655,13 +10724,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C66" t="s">
+        <v>237</v>
+      </c>
+      <c r="D66" t="s">
         <v>238</v>
-      </c>
-      <c r="D66" t="s">
-        <v>239</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -10682,7 +10751,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L66">
         <v>610</v>
@@ -10697,13 +10766,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E67" s="7">
         <v>500</v>
@@ -10724,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L67" s="7">
         <v>620</v>
@@ -10739,13 +10808,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -10766,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L68">
         <v>700</v>
@@ -10781,13 +10850,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E69">
         <v>500</v>
@@ -10808,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L69">
         <v>710</v>
@@ -10823,13 +10892,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -10850,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L70">
         <v>720</v>
@@ -10865,13 +10934,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E71">
         <v>500</v>
@@ -10892,7 +10961,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L71">
         <v>730</v>
@@ -10907,13 +10976,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C72" t="s">
+        <v>245</v>
+      </c>
+      <c r="D72" t="s">
         <v>246</v>
-      </c>
-      <c r="D72" t="s">
-        <v>247</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -10934,7 +11003,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L72">
         <v>740</v>
@@ -10949,13 +11018,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D73" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E73">
         <v>500</v>
@@ -10976,7 +11045,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L73">
         <v>750</v>
@@ -10991,13 +11060,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C74" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -11018,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L74">
         <v>760</v>
@@ -11033,13 +11102,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D75" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -11060,7 +11129,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L75">
         <v>770</v>
@@ -11075,13 +11144,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C76" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -11102,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L76">
         <v>780</v>
@@ -11117,13 +11186,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E77" s="7">
         <v>500</v>
@@ -11144,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L77" s="7">
         <v>790</v>
@@ -11159,13 +11228,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C78" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D78" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -11186,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L78">
         <v>800</v>
@@ -11201,13 +11270,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C79" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D79" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E79">
         <v>500</v>
@@ -11228,7 +11297,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="L79">
         <v>810</v>
@@ -11243,13 +11312,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -11270,7 +11339,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L80">
         <v>9999</v>
@@ -11285,13 +11354,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C81" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D81" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E81">
         <v>500</v>
@@ -11312,7 +11381,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L81">
         <v>2000</v>
@@ -11327,13 +11396,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D82" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -11354,7 +11423,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L82">
         <v>2100</v>
@@ -11369,13 +11438,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C83" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D83" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E83">
         <v>500</v>
@@ -11396,7 +11465,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L83">
         <v>2200</v>
@@ -11411,13 +11480,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C84" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D84" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -11438,7 +11507,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L84">
         <v>2300</v>
@@ -11453,13 +11522,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C85" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D85" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -11480,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L85">
         <v>2400</v>
@@ -11495,13 +11564,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C86" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D86" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -11522,7 +11591,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L86">
         <v>5000</v>
@@ -11537,13 +11606,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D87" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -11564,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -11579,13 +11648,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D88" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -11606,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11621,13 +11690,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>338</v>
+        <v>478</v>
       </c>
       <c r="D89" t="s">
-        <v>337</v>
+        <v>477</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11648,7 +11717,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11663,13 +11732,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C90" t="s">
-        <v>462</v>
+        <v>337</v>
       </c>
       <c r="D90" t="s">
-        <v>464</v>
+        <v>336</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11690,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11705,13 +11774,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C91" t="s">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="D91" t="s">
-        <v>374</v>
+        <v>489</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11732,7 +11801,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11747,13 +11816,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C92" t="s">
-        <v>282</v>
+        <v>374</v>
       </c>
       <c r="D92" t="s">
-        <v>280</v>
+        <v>373</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11774,7 +11843,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11789,13 +11858,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C93" t="s">
-        <v>444</v>
+        <v>281</v>
       </c>
       <c r="D93" t="s">
-        <v>443</v>
+        <v>279</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11816,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11831,13 +11900,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C94" t="s">
-        <v>284</v>
+        <v>443</v>
       </c>
       <c r="D94" t="s">
-        <v>285</v>
+        <v>442</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11858,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11873,13 +11942,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C95" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="D95" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11900,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11915,13 +11984,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C96" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D96" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -11942,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -11957,13 +12026,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C97" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="D97" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -11984,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -11999,13 +12068,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C98" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D98" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12026,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -12041,13 +12110,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C99" t="s">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="D99" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12068,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -12083,13 +12152,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C100" t="s">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="D100" t="s">
-        <v>333</v>
+        <v>288</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -12110,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -12125,13 +12194,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C101" t="s">
-        <v>453</v>
+        <v>333</v>
       </c>
       <c r="D101" t="s">
-        <v>452</v>
+        <v>332</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12167,13 +12236,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C102" t="s">
-        <v>341</v>
+        <v>452</v>
       </c>
       <c r="D102" t="s">
-        <v>339</v>
+        <v>451</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -12194,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -12209,13 +12278,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C103" t="s">
-        <v>342</v>
+        <v>485</v>
       </c>
       <c r="D103" t="s">
-        <v>340</v>
+        <v>484</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -12236,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -12251,13 +12320,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C104" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D104" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -12278,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12293,13 +12362,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C105" t="s">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="D105" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12320,7 +12389,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12335,13 +12404,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C106" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="D106" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -12362,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12377,13 +12446,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C107" t="s">
-        <v>346</v>
+        <v>286</v>
       </c>
       <c r="D107" t="s">
-        <v>344</v>
+        <v>287</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -12404,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -12419,13 +12488,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C108" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D108" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -12446,7 +12515,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12461,13 +12530,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C109" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D109" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -12488,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12503,13 +12572,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C110" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D110" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -12530,7 +12599,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>286</v>
+        <v>433</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -12545,13 +12614,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C111" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D111" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -12587,13 +12656,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C112" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D112" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -12614,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>435</v>
+        <v>285</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12629,13 +12698,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C113" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D113" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -12656,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>286</v>
+        <v>436</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12671,13 +12740,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C114" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D114" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -12698,7 +12767,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12713,13 +12782,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C115" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D115" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -12740,7 +12809,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L115">
         <v>5000</v>
@@ -12755,13 +12824,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C116" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="D116" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -12782,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12797,13 +12866,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C117" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="D117" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -12824,7 +12893,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>426</v>
+        <v>285</v>
       </c>
       <c r="L117">
         <v>5000</v>
@@ -12833,129 +12902,129 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="118" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="11">
+    <row r="118" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A118">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="B118" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="E118" s="11">
+      <c r="B118" t="s">
+        <v>376</v>
+      </c>
+      <c r="C118" t="s">
+        <v>318</v>
+      </c>
+      <c r="D118" t="s">
+        <v>319</v>
+      </c>
+      <c r="E118">
         <v>500</v>
       </c>
-      <c r="F118" s="11">
+      <c r="F118">
         <v>150</v>
       </c>
-      <c r="G118" s="11">
-        <v>0</v>
-      </c>
-      <c r="H118" s="11">
-        <v>0</v>
-      </c>
-      <c r="I118" s="11">
-        <v>0</v>
-      </c>
-      <c r="J118" s="11">
-        <v>0</v>
-      </c>
-      <c r="K118" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="L118" s="11">
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="L118">
         <v>5000</v>
       </c>
-      <c r="M118" s="11">
+      <c r="M118">
         <v>5000</v>
       </c>
     </row>
-    <row r="119" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="11">
+    <row r="119" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A119">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="B119" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E119" s="11">
+      <c r="B119" t="s">
+        <v>376</v>
+      </c>
+      <c r="C119" t="s">
+        <v>311</v>
+      </c>
+      <c r="D119" t="s">
+        <v>312</v>
+      </c>
+      <c r="E119">
         <v>500</v>
       </c>
-      <c r="F119" s="11">
+      <c r="F119">
         <v>150</v>
       </c>
-      <c r="G119" s="11">
-        <v>0</v>
-      </c>
-      <c r="H119" s="11">
-        <v>0</v>
-      </c>
-      <c r="I119" s="11">
-        <v>0</v>
-      </c>
-      <c r="J119" s="11">
-        <v>0</v>
-      </c>
-      <c r="K119" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="L119" s="11">
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L119">
         <v>5000</v>
       </c>
-      <c r="M119" s="11">
+      <c r="M119">
         <v>5000</v>
       </c>
     </row>
-    <row r="120" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="11">
+    <row r="120" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A120">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="B120" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="C120" s="11" t="s">
+      <c r="B120" t="s">
         <v>376</v>
       </c>
-      <c r="D120" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="E120" s="11">
+      <c r="C120" t="s">
+        <v>481</v>
+      </c>
+      <c r="D120" t="s">
+        <v>479</v>
+      </c>
+      <c r="E120">
         <v>500</v>
       </c>
-      <c r="F120" s="11">
+      <c r="F120">
         <v>150</v>
       </c>
-      <c r="G120" s="11">
-        <v>0</v>
-      </c>
-      <c r="H120" s="11">
-        <v>0</v>
-      </c>
-      <c r="I120" s="11">
-        <v>0</v>
-      </c>
-      <c r="J120" s="11">
-        <v>0</v>
-      </c>
-      <c r="K120" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="L120" s="11">
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="L120">
         <v>5000</v>
       </c>
-      <c r="M120" s="11">
+      <c r="M120">
         <v>5000</v>
       </c>
     </row>
@@ -12965,13 +13034,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>369</v>
+        <v>482</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>480</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -12992,7 +13061,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -13001,45 +13070,45 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122">
+    <row r="122" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="11">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="B122" t="s">
-        <v>377</v>
-      </c>
-      <c r="C122" t="s">
-        <v>371</v>
-      </c>
-      <c r="D122" t="s">
-        <v>370</v>
-      </c>
-      <c r="E122">
+      <c r="B122" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="E122" s="11">
         <v>500</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="11">
         <v>150</v>
       </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="L122">
+      <c r="G122" s="11">
+        <v>0</v>
+      </c>
+      <c r="H122" s="11">
+        <v>0</v>
+      </c>
+      <c r="I122" s="11">
+        <v>0</v>
+      </c>
+      <c r="J122" s="11">
+        <v>0</v>
+      </c>
+      <c r="K122" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="L122" s="11">
         <v>5000</v>
       </c>
-      <c r="M122">
+      <c r="M122" s="11">
         <v>5000</v>
       </c>
     </row>
@@ -13049,13 +13118,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E123" s="11">
         <v>500</v>
@@ -13076,7 +13145,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>442</v>
+        <v>285</v>
       </c>
       <c r="L123" s="11">
         <v>5000</v>
@@ -13085,73 +13154,73 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124">
+    <row r="124" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="11">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="B124" t="s">
-        <v>377</v>
-      </c>
-      <c r="C124" t="s">
-        <v>314</v>
-      </c>
-      <c r="D124" t="s">
-        <v>315</v>
-      </c>
-      <c r="E124">
+      <c r="B124" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E124" s="11">
         <v>500</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="11">
         <v>150</v>
       </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="L124">
+      <c r="G124" s="11">
+        <v>0</v>
+      </c>
+      <c r="H124" s="11">
+        <v>0</v>
+      </c>
+      <c r="I124" s="11">
+        <v>0</v>
+      </c>
+      <c r="J124" s="11">
+        <v>0</v>
+      </c>
+      <c r="K124" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="L124" s="11">
         <v>5000</v>
       </c>
-      <c r="M124">
+      <c r="M124" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="C125" t="s">
-        <v>454</v>
+        <v>368</v>
       </c>
       <c r="D125" t="s">
-        <v>455</v>
+        <v>367</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G125">
         <v>0</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -13159,28 +13228,29 @@
       <c r="J125">
         <v>0</v>
       </c>
-      <c r="K125" t="s">
-        <v>456</v>
+      <c r="K125" s="2" t="s">
+        <v>435</v>
       </c>
       <c r="L125">
-        <v>9999</v>
+        <v>5000</v>
       </c>
       <c r="M125">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126">
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>170</v>
+        <v>376</v>
       </c>
       <c r="C126" t="s">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="D126" t="s">
-        <v>175</v>
+        <v>369</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -13198,15 +13268,182 @@
         <v>0</v>
       </c>
       <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L126">
+        <v>5000</v>
+      </c>
+      <c r="M126">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="11">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="E127" s="11">
+        <v>500</v>
+      </c>
+      <c r="F127" s="11">
+        <v>150</v>
+      </c>
+      <c r="G127" s="11">
+        <v>0</v>
+      </c>
+      <c r="H127" s="11">
+        <v>0</v>
+      </c>
+      <c r="I127" s="11">
+        <v>0</v>
+      </c>
+      <c r="J127" s="11">
+        <v>0</v>
+      </c>
+      <c r="K127" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="L127" s="11">
+        <v>5000</v>
+      </c>
+      <c r="M127" s="11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A128">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" t="s">
+        <v>313</v>
+      </c>
+      <c r="D128" t="s">
+        <v>314</v>
+      </c>
+      <c r="E128">
+        <v>500</v>
+      </c>
+      <c r="F128">
+        <v>150</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L128">
+        <v>5000</v>
+      </c>
+      <c r="M128">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129">
+        <f>ROW()-2</f>
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>456</v>
+      </c>
+      <c r="C129" t="s">
+        <v>453</v>
+      </c>
+      <c r="D129" t="s">
+        <v>454</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
         <v>1</v>
       </c>
-      <c r="K126" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="L126">
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129" t="s">
+        <v>455</v>
+      </c>
+      <c r="L129">
+        <v>9999</v>
+      </c>
+      <c r="M129">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130">
+        <v>10000</v>
+      </c>
+      <c r="B130" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" t="s">
+        <v>173</v>
+      </c>
+      <c r="D130" t="s">
+        <v>174</v>
+      </c>
+      <c r="E130">
+        <v>500</v>
+      </c>
+      <c r="F130">
+        <v>150</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="L130">
         <v>9000</v>
       </c>
-      <c r="M126">
+      <c r="M130">
         <v>9000</v>
       </c>
     </row>
@@ -13262,7 +13499,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>11</v>
@@ -13271,10 +13508,10 @@
         <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -13283,13 +13520,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -13310,7 +13547,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L2">
         <v>9999</v>
@@ -13325,13 +13562,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -13352,7 +13589,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -13367,13 +13604,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -13394,7 +13631,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L4">
         <v>9999</v>
@@ -13409,13 +13646,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -13436,7 +13673,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L5">
         <v>9999</v>
@@ -13451,13 +13688,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -13478,7 +13715,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L6">
         <v>9999</v>
@@ -13493,13 +13730,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -13520,7 +13757,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L7">
         <v>9999</v>
@@ -13535,13 +13772,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -13562,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L8">
         <v>9999</v>
@@ -13577,13 +13814,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -13604,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L9">
         <v>9999</v>
@@ -13619,13 +13856,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -13646,7 +13883,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L10">
         <v>9999</v>
@@ -13661,13 +13898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
         <v>146</v>
-      </c>
-      <c r="D11" t="s">
-        <v>147</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -13688,7 +13925,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L11">
         <v>9999</v>
@@ -13703,13 +13940,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -13730,7 +13967,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L12">
         <v>9999</v>
@@ -13745,13 +13982,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -13772,7 +14009,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L13">
         <v>9999</v>
@@ -13787,13 +14024,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -13814,7 +14051,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L14" s="4">
         <v>9999</v>
@@ -13832,10 +14069,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -13856,7 +14093,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L15">
         <v>9999</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938C80EE-A151-4D68-9070-255C7723D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368F7927-7568-435E-A5ED-2194B87A8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1245" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1920" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368F7927-7568-435E-A5ED-2194B87A8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906A931A-59CE-4268-9AF0-C94F24B83BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2715" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="485">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -5576,16 +5576,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ウィンドアークLV１で自動解放</t>
-    <rPh sb="11" eb="13">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カイホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>初心者向けお菓子魔法の本に最初から書いてる</t>
     <rPh sb="0" eb="3">
       <t>ショシンシャ</t>
@@ -5611,20 +5601,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ルミエールカンデラの賞品</t>
-    <rPh sb="10" eb="12">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ガレット・デ・ロワの賞品</t>
-    <rPh sb="10" eb="12">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マジックパティスリーの賞品</t>
     <rPh sb="11" eb="13">
       <t>ショウヒン</t>
@@ -5639,20 +5615,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>キラキラボンボンズの賞品</t>
-    <rPh sb="10" eb="12">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フェドフルラージュの賞品</t>
-    <rPh sb="10" eb="12">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ルミエールドソレイユの賞品</t>
     <rPh sb="11" eb="13">
       <t>ショウヒン</t>
@@ -5660,49 +5622,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スターブレッシングの本と同時に解放</t>
-    <rPh sb="10" eb="11">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ドウジ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カイホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>秋お店で買う</t>
-    <rPh sb="0" eb="1">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フリージングと同時に解放</t>
-    <rPh sb="7" eb="9">
-      <t>ドウジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カイホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オランジーナ・パティスリーアワードの賞品</t>
-    <rPh sb="18" eb="20">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>春牧場で売ってる</t>
     <rPh sb="0" eb="1">
       <t>ハル</t>
@@ -5743,19 +5662,6 @@
   </si>
   <si>
     <t>mg_fire_flowers_book</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ルミエールエピファニアの賞品or秋エリアのお店</t>
-    <rPh sb="12" eb="14">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ミセ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7520,6 +7426,40 @@
     <t>エメラルショップ</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>魔法自体が消えた</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェド・フルラージュの賞品</t>
+    <rPh sb="11" eb="13">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハートLVで覚える</t>
+    <rPh sb="6" eb="7">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピエスモンテの賞品</t>
+    <rPh sb="7" eb="9">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -7562,7 +7502,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7605,6 +7545,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -7620,7 +7566,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7656,6 +7602,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8105,7 +8057,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -8702,25 +8654,25 @@
         <v>3060</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>461</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>459</v>
       </c>
       <c r="E18">
         <v>500</v>
       </c>
       <c r="F18">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -8735,28 +8687,28 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>201</v>
+        <v>463</v>
       </c>
       <c r="L18">
-        <v>20</v>
+        <v>3110</v>
       </c>
       <c r="M18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>462</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>460</v>
       </c>
       <c r="E19">
         <v>500</v>
@@ -8777,13 +8729,13 @@
         <v>1</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="L19">
-        <v>30</v>
+        <v>3120</v>
       </c>
       <c r="M19">
-        <v>30</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8792,13 +8744,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="E20">
         <v>500</v>
@@ -8819,13 +8771,13 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="L20">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M20">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8834,19 +8786,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>500</v>
       </c>
       <c r="F21">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -8861,13 +8813,13 @@
         <v>1</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>253</v>
+        <v>476</v>
       </c>
       <c r="L21">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M21">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8876,19 +8828,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="E22">
         <v>500</v>
       </c>
       <c r="F22">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -8903,13 +8855,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L22">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M22">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8918,19 +8870,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="E23">
         <v>500</v>
       </c>
       <c r="F23">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -8945,13 +8897,13 @@
         <v>1</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>89</v>
+        <v>253</v>
       </c>
       <c r="L23">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M23">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8960,13 +8912,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E24">
         <v>500</v>
@@ -8987,13 +8939,13 @@
         <v>1</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="L24">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9002,13 +8954,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -9029,13 +8981,13 @@
         <v>1</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>254</v>
+        <v>89</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="M25">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9044,13 +8996,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -9071,13 +9023,13 @@
         <v>1</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9086,13 +9038,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -9113,13 +9065,13 @@
         <v>1</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>57</v>
+        <v>254</v>
       </c>
       <c r="L27">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="M27">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9128,13 +9080,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -9155,13 +9107,13 @@
         <v>1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9170,13 +9122,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -9197,13 +9149,13 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>474</v>
+        <v>57</v>
       </c>
       <c r="L29">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="M29">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9212,13 +9164,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>468</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>466</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>467</v>
+        <v>53</v>
       </c>
       <c r="E30">
         <v>500</v>
@@ -9239,13 +9191,13 @@
         <v>1</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>475</v>
+        <v>56</v>
       </c>
       <c r="L30">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M30">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9254,13 +9206,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E31">
         <v>500</v>
@@ -9281,13 +9233,13 @@
         <v>1</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>124</v>
+        <v>464</v>
       </c>
       <c r="L31">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M31">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9296,13 +9248,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>458</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>456</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>457</v>
       </c>
       <c r="E32">
         <v>500</v>
@@ -9323,13 +9275,13 @@
         <v>1</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>178</v>
+        <v>465</v>
       </c>
       <c r="L32">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M32">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9338,13 +9290,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E33">
         <v>500</v>
@@ -9365,13 +9317,13 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="L33">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="M33">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9380,13 +9332,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9407,13 +9359,13 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="L34">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="M34">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9422,13 +9374,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -9449,13 +9401,13 @@
         <v>1</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="L35">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="M35">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9464,13 +9416,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E36">
         <v>500</v>
@@ -9491,13 +9443,13 @@
         <v>1</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="L36">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="M36">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9506,13 +9458,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E37">
         <v>500</v>
@@ -9533,13 +9485,13 @@
         <v>1</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L37">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="M37">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9548,13 +9500,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="E38">
         <v>500</v>
@@ -9575,13 +9527,13 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="L38">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="M38">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9590,13 +9542,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -9617,13 +9569,13 @@
         <v>1</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="L39">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="M39">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9632,13 +9584,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -9659,13 +9611,13 @@
         <v>1</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="L40">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="M40">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9674,13 +9626,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D41" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -9701,13 +9653,13 @@
         <v>1</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="L41">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="M41">
-        <v>290</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9716,13 +9668,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="E42">
         <v>500</v>
@@ -9743,70 +9695,70 @@
         <v>1</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="L42">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="M42">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="5">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="B43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43">
         <v>500</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43">
         <v>150</v>
       </c>
-      <c r="G43" s="5">
-        <v>0</v>
-      </c>
-      <c r="H43" s="5">
-        <v>0</v>
-      </c>
-      <c r="I43" s="5">
-        <v>0</v>
-      </c>
-      <c r="J43" s="5">
-        <v>0</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="L43" s="5">
-        <v>9999</v>
-      </c>
-      <c r="M43" s="5">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="L43">
+        <v>290</v>
+      </c>
+      <c r="M43">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>377</v>
+        <v>195</v>
       </c>
       <c r="C44" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -9827,70 +9779,70 @@
         <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>450</v>
+        <v>193</v>
       </c>
       <c r="L44">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="M44">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="5">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" t="s">
-        <v>378</v>
-      </c>
-      <c r="C45" t="s">
-        <v>203</v>
-      </c>
-      <c r="D45" t="s">
-        <v>202</v>
-      </c>
-      <c r="E45">
+      <c r="B45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" s="5">
         <v>500</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="5">
         <v>150</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="L45">
-        <v>320</v>
-      </c>
-      <c r="M45">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="L45" s="5">
+        <v>9999</v>
+      </c>
+      <c r="M45" s="5">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -9911,13 +9863,13 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>207</v>
+        <v>440</v>
       </c>
       <c r="L46">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="M46">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9926,13 +9878,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C47" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D47" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E47">
         <v>500</v>
@@ -9953,13 +9905,13 @@
         <v>1</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>406</v>
+        <v>204</v>
       </c>
       <c r="L47">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="M47">
-        <v>340</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9968,13 +9920,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C48" t="s">
-        <v>268</v>
+        <v>206</v>
       </c>
       <c r="D48" t="s">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -9995,13 +9947,13 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>407</v>
+        <v>207</v>
       </c>
       <c r="L48">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="M48">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10010,13 +9962,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>208</v>
       </c>
       <c r="D49" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -10037,13 +9989,13 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
       <c r="L49">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="M49">
-        <v>360</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10052,13 +10004,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C50" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D50" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10079,13 +10031,13 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>462</v>
+        <v>407</v>
       </c>
       <c r="L50">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="M50">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10094,13 +10046,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C51" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10121,13 +10073,13 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>463</v>
+        <v>321</v>
       </c>
       <c r="L51">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="M51">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10136,13 +10088,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="D52" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10163,55 +10115,55 @@
         <v>1</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="L52">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="M52">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="9">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E53" s="9">
+      <c r="B53" t="s">
+        <v>384</v>
+      </c>
+      <c r="C53" t="s">
+        <v>300</v>
+      </c>
+      <c r="D53" t="s">
+        <v>302</v>
+      </c>
+      <c r="E53">
         <v>500</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53">
         <v>150</v>
       </c>
-      <c r="G53" s="9">
-        <v>0</v>
-      </c>
-      <c r="H53" s="9">
-        <v>0</v>
-      </c>
-      <c r="I53" s="9">
-        <v>0</v>
-      </c>
-      <c r="J53" s="9">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
         <v>1</v>
       </c>
-      <c r="K53" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="L53" s="9">
-        <v>400</v>
-      </c>
-      <c r="M53" s="9">
-        <v>400</v>
+      <c r="K53" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L53">
+        <v>380</v>
+      </c>
+      <c r="M53">
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10220,13 +10172,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C54" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="D54" t="s">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -10247,55 +10199,55 @@
         <v>1</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>259</v>
+        <v>454</v>
       </c>
       <c r="L54">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="M54">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="9">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" t="s">
-        <v>387</v>
-      </c>
-      <c r="C55" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" t="s">
-        <v>214</v>
-      </c>
-      <c r="E55">
+      <c r="B55" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="9">
         <v>500</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="9">
         <v>150</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>0</v>
+      </c>
+      <c r="I55" s="9">
+        <v>0</v>
+      </c>
+      <c r="J55" s="9">
         <v>1</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L55">
-        <v>500</v>
-      </c>
-      <c r="M55">
-        <v>500</v>
+      <c r="K55" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="L55" s="9">
+        <v>400</v>
+      </c>
+      <c r="M55" s="9">
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10304,13 +10256,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C56" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D56" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -10331,13 +10283,13 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="L56">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="M56">
-        <v>510</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10346,13 +10298,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C57" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -10373,13 +10325,13 @@
         <v>1</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>408</v>
+        <v>257</v>
       </c>
       <c r="L57">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="M57">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10388,13 +10340,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D58" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -10415,13 +10367,13 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>409</v>
+        <v>256</v>
       </c>
       <c r="L58">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="M58">
-        <v>530</v>
+        <v>510</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10430,13 +10382,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>195</v>
+        <v>403</v>
       </c>
       <c r="C59" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -10457,13 +10409,13 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L59">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="M59">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10472,13 +10424,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C60" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D60" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -10499,13 +10451,13 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L60">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="M60">
-        <v>550</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10514,13 +10466,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>391</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D61" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -10541,13 +10493,13 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L61">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="M61">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10556,13 +10508,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C62" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D62" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -10583,13 +10535,13 @@
         <v>1</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L62">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="M62">
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10598,13 +10550,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C63" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D63" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -10625,13 +10577,13 @@
         <v>1</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>258</v>
+        <v>412</v>
       </c>
       <c r="L63">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="M63">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10640,13 +10592,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -10667,55 +10619,55 @@
         <v>1</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>275</v>
+        <v>413</v>
       </c>
       <c r="L64">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="M64">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="7">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="E65" s="7">
+      <c r="B65" t="s">
+        <v>393</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" t="s">
+        <v>229</v>
+      </c>
+      <c r="E65">
         <v>500</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65">
         <v>150</v>
       </c>
-      <c r="G65" s="7">
-        <v>0</v>
-      </c>
-      <c r="H65" s="7">
-        <v>0</v>
-      </c>
-      <c r="I65" s="7">
-        <v>0</v>
-      </c>
-      <c r="J65" s="7">
-        <v>0</v>
-      </c>
-      <c r="K65" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L65" s="7">
-        <v>600</v>
-      </c>
-      <c r="M65" s="7">
-        <v>600</v>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L65">
+        <v>580</v>
+      </c>
+      <c r="M65">
+        <v>580</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10724,13 +10676,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C66" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D66" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -10751,13 +10703,13 @@
         <v>1</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>416</v>
+        <v>275</v>
       </c>
       <c r="L66">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="M66">
-        <v>610</v>
+        <v>590</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10769,10 +10721,10 @@
         <v>195</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>304</v>
+        <v>236</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="E67" s="7">
         <v>500</v>
@@ -10793,13 +10745,13 @@
         <v>0</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>305</v>
+        <v>235</v>
       </c>
       <c r="L67" s="7">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="M67" s="7">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10808,13 +10760,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C68" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -10835,55 +10787,55 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L68">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="M68">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="7">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" t="s">
-        <v>396</v>
-      </c>
-      <c r="C69" t="s">
-        <v>262</v>
-      </c>
-      <c r="D69" t="s">
-        <v>261</v>
-      </c>
-      <c r="E69">
+      <c r="B69" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E69" s="7">
         <v>500</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="7">
         <v>150</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="L69">
-        <v>710</v>
-      </c>
-      <c r="M69">
-        <v>710</v>
+      <c r="G69" s="7">
+        <v>0</v>
+      </c>
+      <c r="H69" s="7">
+        <v>0</v>
+      </c>
+      <c r="I69" s="7">
+        <v>0</v>
+      </c>
+      <c r="J69" s="7">
+        <v>0</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="L69" s="7">
+        <v>620</v>
+      </c>
+      <c r="M69" s="7">
+        <v>620</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10892,13 +10844,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C70" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D70" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -10919,13 +10871,13 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L70">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="M70">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10934,13 +10886,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C71" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E71">
         <v>500</v>
@@ -10961,13 +10913,13 @@
         <v>1</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L71">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="M71">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10976,13 +10928,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D72" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -11003,13 +10955,13 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L72">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="M72">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11018,13 +10970,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C73" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D73" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E73">
         <v>500</v>
@@ -11045,13 +10997,13 @@
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L73">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="M73">
-        <v>750</v>
+        <v>730</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11060,13 +11012,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C74" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -11087,13 +11039,13 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>255</v>
+        <v>421</v>
       </c>
       <c r="L74">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="M74">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11102,13 +11054,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C75" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D75" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -11129,13 +11081,13 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>265</v>
+        <v>422</v>
       </c>
       <c r="L75">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="M75">
-        <v>770</v>
+        <v>750</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11144,13 +11096,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C76" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="D76" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -11171,55 +11123,55 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>415</v>
+        <v>255</v>
       </c>
       <c r="L76">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="M76">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="7">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="E77" s="7">
+      <c r="B77" t="s">
+        <v>402</v>
+      </c>
+      <c r="C77" t="s">
+        <v>264</v>
+      </c>
+      <c r="D77" t="s">
+        <v>263</v>
+      </c>
+      <c r="E77">
         <v>500</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77">
         <v>150</v>
       </c>
-      <c r="G77" s="7">
-        <v>0</v>
-      </c>
-      <c r="H77" s="7">
-        <v>0</v>
-      </c>
-      <c r="I77" s="7">
-        <v>0</v>
-      </c>
-      <c r="J77" s="7">
-        <v>0</v>
-      </c>
-      <c r="K77" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L77" s="7">
-        <v>790</v>
-      </c>
-      <c r="M77" s="7">
-        <v>790</v>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L77">
+        <v>770</v>
+      </c>
+      <c r="M77">
+        <v>770</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11228,13 +11180,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>405</v>
       </c>
       <c r="C78" t="s">
-        <v>471</v>
+        <v>271</v>
       </c>
       <c r="D78" t="s">
-        <v>469</v>
+        <v>270</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -11255,96 +11207,96 @@
         <v>1</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="L78">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="M78">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="7">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="B79" t="s">
-        <v>92</v>
-      </c>
-      <c r="C79" t="s">
-        <v>472</v>
-      </c>
-      <c r="D79" t="s">
-        <v>470</v>
-      </c>
-      <c r="E79">
+      <c r="B79" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" s="7">
         <v>500</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="7">
         <v>150</v>
       </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="L79">
-        <v>810</v>
-      </c>
-      <c r="M79">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80">
+      <c r="G79" s="7">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7">
+        <v>0</v>
+      </c>
+      <c r="I79" s="7">
+        <v>0</v>
+      </c>
+      <c r="J79" s="7">
+        <v>0</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L79" s="7">
+        <v>790</v>
+      </c>
+      <c r="M79" s="7">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="13">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="13">
         <v>500</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="13">
         <v>150</v>
       </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80" s="2" t="s">
+      <c r="G80" s="13">
+        <v>0</v>
+      </c>
+      <c r="H80" s="13">
+        <v>0</v>
+      </c>
+      <c r="I80" s="13">
+        <v>0</v>
+      </c>
+      <c r="J80" s="13">
+        <v>0</v>
+      </c>
+      <c r="K80" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="L80">
+      <c r="L80" s="13">
         <v>9999</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="13">
         <v>9999</v>
       </c>
     </row>
@@ -11354,7 +11306,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C81" t="s">
         <v>292</v>
@@ -11396,7 +11348,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C82" t="s">
         <v>294</v>
@@ -11423,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="L82">
         <v>2100</v>
@@ -11438,7 +11390,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C83" t="s">
         <v>295</v>
@@ -11465,7 +11417,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="L83">
         <v>2200</v>
@@ -11480,7 +11432,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C84" t="s">
         <v>296</v>
@@ -11507,7 +11459,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="L84">
         <v>2300</v>
@@ -11522,7 +11474,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C85" t="s">
         <v>297</v>
@@ -11549,7 +11501,7 @@
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="L85">
         <v>2400</v>
@@ -11633,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>429</v>
+        <v>484</v>
       </c>
       <c r="L87">
         <v>5000</v>
@@ -11675,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>430</v>
+        <v>478</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11693,10 +11645,10 @@
         <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="D89" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11717,7 +11669,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11759,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11777,10 +11729,10 @@
         <v>376</v>
       </c>
       <c r="C91" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D91" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11801,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11885,7 +11837,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11903,10 +11855,10 @@
         <v>376</v>
       </c>
       <c r="C94" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D94" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11927,7 +11879,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -12011,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -12053,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -12095,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -12137,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -12179,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>423</v>
+        <v>483</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -12239,10 +12191,10 @@
         <v>376</v>
       </c>
       <c r="C102" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D102" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -12263,7 +12215,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -12281,10 +12233,10 @@
         <v>376</v>
       </c>
       <c r="C103" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D103" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -12305,7 +12257,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -12347,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12389,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12431,7 +12383,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12515,7 +12467,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>427</v>
+        <v>478</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12557,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>427</v>
+        <v>478</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12599,7 +12551,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>433</v>
+        <v>481</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -12641,7 +12593,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12683,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>285</v>
+        <v>481</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12725,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>436</v>
+        <v>481</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12767,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12809,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>285</v>
+        <v>478</v>
       </c>
       <c r="L115">
         <v>5000</v>
@@ -12851,7 +12803,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12893,7 +12845,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>285</v>
+        <v>478</v>
       </c>
       <c r="L117">
         <v>5000</v>
@@ -12935,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>423</v>
+        <v>483</v>
       </c>
       <c r="L118">
         <v>5000</v>
@@ -12995,10 +12947,10 @@
         <v>376</v>
       </c>
       <c r="C120" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D120" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -13019,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L120">
         <v>5000</v>
@@ -13037,10 +12989,10 @@
         <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="D121" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -13061,7 +13013,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -13229,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L125">
         <v>5000</v>
@@ -13313,7 +13265,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="12" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="L127" s="11">
         <v>5000</v>
@@ -13370,13 +13322,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C129" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D129" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -13397,7 +13349,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="L129">
         <v>9999</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906A931A-59CE-4268-9AF0-C94F24B83BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FF2CA0-F184-4965-B887-866B88006C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3495" yWindow="1125" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FF2CA0-F184-4965-B887-866B88006C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61FF7BD-D740-4FCE-AA06-4A0BD0914C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="1125" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2085" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -8486,25 +8486,25 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>461</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>459</v>
       </c>
       <c r="E14">
         <v>500</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -8519,28 +8519,28 @@
         <v>1</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>101</v>
+        <v>463</v>
       </c>
       <c r="L14">
-        <v>3010</v>
+        <v>3110</v>
       </c>
       <c r="M14">
-        <v>3010</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>462</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>460</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -8561,13 +8561,13 @@
         <v>1</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>66</v>
+        <v>466</v>
       </c>
       <c r="L15">
-        <v>3030</v>
+        <v>3120</v>
       </c>
       <c r="M15">
-        <v>3030</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8576,19 +8576,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>500</v>
       </c>
       <c r="F16">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -8603,13 +8603,13 @@
         <v>1</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="L16">
-        <v>3040</v>
+        <v>3010</v>
       </c>
       <c r="M16">
-        <v>3040</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8618,19 +8618,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="E17">
         <v>500</v>
       </c>
       <c r="F17">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -8645,34 +8645,34 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="L17">
-        <v>3060</v>
+        <v>3030</v>
       </c>
       <c r="M17">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>461</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>459</v>
+        <v>71</v>
       </c>
       <c r="E18">
         <v>500</v>
       </c>
       <c r="F18">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -8687,34 +8687,34 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>463</v>
+        <v>176</v>
       </c>
       <c r="L18">
-        <v>3110</v>
+        <v>3040</v>
       </c>
       <c r="M18">
-        <v>3110</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>462</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>460</v>
+        <v>94</v>
       </c>
       <c r="E19">
         <v>500</v>
       </c>
       <c r="F19">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -8729,13 +8729,13 @@
         <v>1</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>466</v>
+        <v>95</v>
       </c>
       <c r="L19">
-        <v>3120</v>
+        <v>3060</v>
       </c>
       <c r="M19">
-        <v>3120</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61FF7BD-D740-4FCE-AA06-4A0BD0914C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09661B67-574F-413E-9404-F76D4D63D56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3195" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="491">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7457,6 +7457,107 @@
     <t>ピエスモンテの賞品</t>
     <rPh sb="7" eb="9">
       <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チーズケーキのレシピ＜上級＞</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cheesecake_recipi_high</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンケーキの秘訣</t>
+    <rPh sb="6" eb="8">
+      <t>ヒケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pancake_recipi_high</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【パンケーキの秘訣】
+パンケーキは、トッピングを2種類同時にのせることで、より夢のあるパンケーキになります。
+今回は、特別にそれらの作り方をご紹介しましょう！
+まずは、シンプルなパンケーキを作ります。
+以下、&lt;color=#BA9535FF&gt;2種類のくだものを同時に&lt;/color&gt;トッピングしましょう。
+・チョコバナナパンケーキ　・・・　&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;に&lt;color=#BA9535FF&gt;チョコソース&lt;/color&gt;をかける。
+・パンケーキいちごとブルーベリーフロマージュ　・・・　&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;と&lt;color=#BA9535FF&gt;ブルーベリー&lt;/color&gt;をのせる。
+ホイップクリームをさらにトッピングすると、よりマッチするかも？
+・2種のベリーバナナホイップパンケーキ　・・・　先ほどのパンケーキに、さらに&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;に&lt;color=#BA9535FF&gt;ホイップクリームを&lt;/color&gt;をのせる。
+・ベリーとバニラアイスのパンケーキ　・・・　&lt;color=#BA9535FF&gt;ベリー&lt;/color&gt;に&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;をのせる。
+</t>
+    <rPh sb="57" eb="59">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="391" eb="392">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【チーズケーキのレシピ＜上級＞】
+魔法を使ったチーズケーキの作り方
+※秘伝のレシピです。
+チーズケーキのトッピングに以下の4種類のフルーツをのせると、
+不思議なチーズケーキに・・？
+・&lt;color=#BA9535FF&gt;光るブルーベリー&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;光るラズベリー&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;光るオレンジ&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;黒く光るカシスの実&lt;/color&gt;
+見た目もオシャレなかわいいチーズケーキのできあがり♪
+</t>
+    <rPh sb="18" eb="20">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒデン</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="78" eb="81">
+      <t>フシギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7541,13 +7642,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7924,7 +8025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -7984,7 +8085,7 @@
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A128" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A130" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -8570,25 +8671,25 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>486</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>485</v>
       </c>
       <c r="E16">
         <v>500</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -8603,28 +8704,28 @@
         <v>1</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>101</v>
+        <v>490</v>
       </c>
       <c r="L16">
-        <v>3010</v>
+        <v>3130</v>
       </c>
       <c r="M16">
-        <v>3010</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>488</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>487</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -8645,13 +8746,13 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>66</v>
+        <v>489</v>
       </c>
       <c r="L17">
-        <v>3030</v>
+        <v>3140</v>
       </c>
       <c r="M17">
-        <v>3030</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8660,19 +8761,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>500</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -8687,13 +8788,13 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="L18">
-        <v>3040</v>
+        <v>3010</v>
       </c>
       <c r="M18">
-        <v>3040</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8702,19 +8803,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="E19">
         <v>500</v>
       </c>
       <c r="F19">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -8729,13 +8830,13 @@
         <v>1</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="L19">
-        <v>3060</v>
+        <v>3030</v>
       </c>
       <c r="M19">
-        <v>3060</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8744,19 +8845,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="E20">
         <v>500</v>
       </c>
       <c r="F20">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -8771,13 +8872,13 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="L20">
-        <v>20</v>
+        <v>3040</v>
       </c>
       <c r="M20">
-        <v>20</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8786,19 +8887,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="E21">
         <v>500</v>
       </c>
       <c r="F21">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -8813,13 +8914,13 @@
         <v>1</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>476</v>
+        <v>95</v>
       </c>
       <c r="L21">
-        <v>30</v>
+        <v>3060</v>
       </c>
       <c r="M21">
-        <v>30</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8828,13 +8929,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="E22">
         <v>500</v>
@@ -8855,13 +8956,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="L22">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M22">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8870,19 +8971,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>500</v>
       </c>
       <c r="F23">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -8897,13 +8998,13 @@
         <v>1</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>253</v>
+        <v>476</v>
       </c>
       <c r="L23">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M23">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8912,19 +9013,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="E24">
         <v>500</v>
       </c>
       <c r="F24">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -8939,13 +9040,13 @@
         <v>1</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L24">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M24">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8954,19 +9055,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="E25">
         <v>500</v>
       </c>
       <c r="F25">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -8981,13 +9082,13 @@
         <v>1</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>89</v>
+        <v>253</v>
       </c>
       <c r="L25">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M25">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8996,13 +9097,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -9023,13 +9124,13 @@
         <v>1</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="L26">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M26">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9038,13 +9139,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -9065,13 +9166,13 @@
         <v>1</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>254</v>
+        <v>89</v>
       </c>
       <c r="L27">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="M27">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9080,13 +9181,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -9107,13 +9208,13 @@
         <v>1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9122,13 +9223,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -9149,13 +9250,13 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>57</v>
+        <v>254</v>
       </c>
       <c r="L29">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="M29">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9164,13 +9265,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E30">
         <v>500</v>
@@ -9191,13 +9292,13 @@
         <v>1</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9206,13 +9307,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E31">
         <v>500</v>
@@ -9233,13 +9334,13 @@
         <v>1</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>464</v>
+        <v>57</v>
       </c>
       <c r="L31">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="M31">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9248,13 +9349,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>456</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>457</v>
+        <v>53</v>
       </c>
       <c r="E32">
         <v>500</v>
@@ -9275,13 +9376,13 @@
         <v>1</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>465</v>
+        <v>56</v>
       </c>
       <c r="L32">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M32">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9290,13 +9391,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E33">
         <v>500</v>
@@ -9317,13 +9418,13 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>124</v>
+        <v>464</v>
       </c>
       <c r="L33">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M33">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9332,13 +9433,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>458</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>456</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>457</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9359,13 +9460,13 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>178</v>
+        <v>465</v>
       </c>
       <c r="L34">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M34">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9374,13 +9475,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -9401,13 +9502,13 @@
         <v>1</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="L35">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="M35">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9416,13 +9517,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="E36">
         <v>500</v>
@@ -9443,13 +9544,13 @@
         <v>1</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="L36">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="M36">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9458,13 +9559,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E37">
         <v>500</v>
@@ -9485,13 +9586,13 @@
         <v>1</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="L37">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="M37">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9500,13 +9601,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E38">
         <v>500</v>
@@ -9527,13 +9628,13 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="L38">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="M38">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9542,13 +9643,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -9569,13 +9670,13 @@
         <v>1</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L39">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="M39">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9584,13 +9685,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -9611,13 +9712,13 @@
         <v>1</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="L40">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="M40">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9626,13 +9727,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -9653,13 +9754,13 @@
         <v>1</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="L41">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="M41">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9668,13 +9769,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="E42">
         <v>500</v>
@@ -9695,13 +9796,13 @@
         <v>1</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="L42">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="M42">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9710,13 +9811,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D43" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E43">
         <v>500</v>
@@ -9737,13 +9838,13 @@
         <v>1</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="L43">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="M43">
-        <v>290</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9752,13 +9853,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="D44" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -9779,70 +9880,70 @@
         <v>1</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="L44">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="M44">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="5">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E45" s="5">
+      <c r="B45" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45">
         <v>500</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45">
         <v>150</v>
       </c>
-      <c r="G45" s="5">
-        <v>0</v>
-      </c>
-      <c r="H45" s="5">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5">
-        <v>0</v>
-      </c>
-      <c r="J45" s="5">
-        <v>0</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="L45" s="5">
-        <v>9999</v>
-      </c>
-      <c r="M45" s="5">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="L45">
+        <v>290</v>
+      </c>
+      <c r="M45">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>377</v>
+        <v>195</v>
       </c>
       <c r="C46" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -9863,70 +9964,70 @@
         <v>1</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>440</v>
+        <v>193</v>
       </c>
       <c r="L46">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="M46">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" t="s">
-        <v>378</v>
-      </c>
-      <c r="C47" t="s">
-        <v>203</v>
-      </c>
-      <c r="D47" t="s">
-        <v>202</v>
-      </c>
-      <c r="E47">
+      <c r="B47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="5">
         <v>500</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="5">
         <v>150</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="L47">
-        <v>320</v>
-      </c>
-      <c r="M47">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G47" s="5">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="L47" s="5">
+        <v>9999</v>
+      </c>
+      <c r="M47" s="5">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C48" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -9947,13 +10048,13 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>207</v>
+        <v>440</v>
       </c>
       <c r="L48">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="M48">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9962,13 +10063,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D49" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -9989,13 +10090,13 @@
         <v>1</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>406</v>
+        <v>204</v>
       </c>
       <c r="L49">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="M49">
-        <v>340</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10004,13 +10105,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>206</v>
       </c>
       <c r="D50" t="s">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10031,13 +10132,13 @@
         <v>1</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>407</v>
+        <v>207</v>
       </c>
       <c r="L50">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="M50">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10046,13 +10147,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>208</v>
       </c>
       <c r="D51" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10073,13 +10174,13 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
       <c r="L51">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="M51">
-        <v>360</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10088,13 +10189,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C52" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D52" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10115,13 +10216,13 @@
         <v>1</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="L52">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="M52">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10130,13 +10231,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C53" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D53" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -10157,13 +10258,13 @@
         <v>1</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>453</v>
+        <v>321</v>
       </c>
       <c r="L53">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="M53">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10172,13 +10273,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C54" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -10199,55 +10300,55 @@
         <v>1</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L54">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="M54">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="9">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E55" s="9">
+      <c r="B55" t="s">
+        <v>384</v>
+      </c>
+      <c r="C55" t="s">
+        <v>300</v>
+      </c>
+      <c r="D55" t="s">
+        <v>302</v>
+      </c>
+      <c r="E55">
         <v>500</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55">
         <v>150</v>
       </c>
-      <c r="G55" s="9">
-        <v>0</v>
-      </c>
-      <c r="H55" s="9">
-        <v>0</v>
-      </c>
-      <c r="I55" s="9">
-        <v>0</v>
-      </c>
-      <c r="J55" s="9">
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
         <v>1</v>
       </c>
-      <c r="K55" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="L55" s="9">
-        <v>400</v>
-      </c>
-      <c r="M55" s="9">
-        <v>400</v>
+      <c r="K55" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L55">
+        <v>380</v>
+      </c>
+      <c r="M55">
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10256,13 +10357,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="D56" t="s">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -10283,55 +10384,55 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>259</v>
+        <v>454</v>
       </c>
       <c r="L56">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="M56">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="9">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" t="s">
-        <v>387</v>
-      </c>
-      <c r="C57" t="s">
-        <v>215</v>
-      </c>
-      <c r="D57" t="s">
-        <v>214</v>
-      </c>
-      <c r="E57">
+      <c r="B57" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E57" s="9">
         <v>500</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="9">
         <v>150</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
+      <c r="G57" s="9">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>0</v>
+      </c>
+      <c r="I57" s="9">
+        <v>0</v>
+      </c>
+      <c r="J57" s="9">
         <v>1</v>
       </c>
-      <c r="K57" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L57">
-        <v>500</v>
-      </c>
-      <c r="M57">
-        <v>500</v>
+      <c r="K57" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="L57" s="9">
+        <v>400</v>
+      </c>
+      <c r="M57" s="9">
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10340,13 +10441,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C58" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D58" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -10367,13 +10468,13 @@
         <v>1</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="L58">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="M58">
-        <v>510</v>
+        <v>410</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10382,13 +10483,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C59" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D59" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -10409,13 +10510,13 @@
         <v>1</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>408</v>
+        <v>257</v>
       </c>
       <c r="L59">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="M59">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10424,13 +10525,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C60" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -10451,13 +10552,13 @@
         <v>1</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>409</v>
+        <v>256</v>
       </c>
       <c r="L60">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="M60">
-        <v>530</v>
+        <v>510</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10466,13 +10567,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>403</v>
       </c>
       <c r="C61" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D61" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -10493,13 +10594,13 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L61">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="M61">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10508,13 +10609,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C62" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D62" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -10535,13 +10636,13 @@
         <v>1</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L62">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="M62">
-        <v>550</v>
+        <v>530</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10550,13 +10651,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>391</v>
+        <v>195</v>
       </c>
       <c r="C63" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D63" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -10577,13 +10678,13 @@
         <v>1</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L63">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="M63">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10592,13 +10693,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D64" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -10619,13 +10720,13 @@
         <v>1</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L64">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="M64">
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10634,13 +10735,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D65" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E65">
         <v>500</v>
@@ -10661,13 +10762,13 @@
         <v>1</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>258</v>
+        <v>412</v>
       </c>
       <c r="L65">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="M65">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10676,13 +10777,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D66" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -10703,55 +10804,55 @@
         <v>1</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>275</v>
+        <v>413</v>
       </c>
       <c r="L66">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="M66">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="7">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="E67" s="7">
+      <c r="B67" t="s">
+        <v>393</v>
+      </c>
+      <c r="C67" t="s">
+        <v>230</v>
+      </c>
+      <c r="D67" t="s">
+        <v>229</v>
+      </c>
+      <c r="E67">
         <v>500</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67">
         <v>150</v>
       </c>
-      <c r="G67" s="7">
-        <v>0</v>
-      </c>
-      <c r="H67" s="7">
-        <v>0</v>
-      </c>
-      <c r="I67" s="7">
-        <v>0</v>
-      </c>
-      <c r="J67" s="7">
-        <v>0</v>
-      </c>
-      <c r="K67" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L67" s="7">
-        <v>600</v>
-      </c>
-      <c r="M67" s="7">
-        <v>600</v>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L67">
+        <v>580</v>
+      </c>
+      <c r="M67">
+        <v>580</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10760,13 +10861,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C68" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D68" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -10787,13 +10888,13 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>416</v>
+        <v>275</v>
       </c>
       <c r="L68">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="M68">
-        <v>610</v>
+        <v>590</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10805,10 +10906,10 @@
         <v>195</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>304</v>
+        <v>236</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="E69" s="7">
         <v>500</v>
@@ -10829,13 +10930,13 @@
         <v>0</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>305</v>
+        <v>235</v>
       </c>
       <c r="L69" s="7">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="M69" s="7">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10844,13 +10945,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D70" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -10871,55 +10972,55 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L70">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="M70">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="7">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="B71" t="s">
-        <v>396</v>
-      </c>
-      <c r="C71" t="s">
-        <v>262</v>
-      </c>
-      <c r="D71" t="s">
-        <v>261</v>
-      </c>
-      <c r="E71">
+      <c r="B71" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E71" s="7">
         <v>500</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="7">
         <v>150</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="L71">
-        <v>710</v>
-      </c>
-      <c r="M71">
-        <v>710</v>
+      <c r="G71" s="7">
+        <v>0</v>
+      </c>
+      <c r="H71" s="7">
+        <v>0</v>
+      </c>
+      <c r="I71" s="7">
+        <v>0</v>
+      </c>
+      <c r="J71" s="7">
+        <v>0</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="L71" s="7">
+        <v>620</v>
+      </c>
+      <c r="M71" s="7">
+        <v>620</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10928,13 +11029,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C72" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D72" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -10955,13 +11056,13 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L72">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="M72">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10970,13 +11071,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C73" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E73">
         <v>500</v>
@@ -10997,13 +11098,13 @@
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L73">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="M73">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11012,13 +11113,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C74" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -11039,13 +11140,13 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L74">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="M74">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11054,13 +11155,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C75" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D75" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -11081,13 +11182,13 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L75">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="M75">
-        <v>750</v>
+        <v>730</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11096,13 +11197,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C76" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D76" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -11123,13 +11224,13 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>255</v>
+        <v>421</v>
       </c>
       <c r="L76">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="M76">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11138,13 +11239,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C77" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D77" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -11165,13 +11266,13 @@
         <v>1</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>265</v>
+        <v>422</v>
       </c>
       <c r="L77">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="M77">
-        <v>770</v>
+        <v>750</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11180,13 +11281,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C78" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="D78" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -11207,181 +11308,181 @@
         <v>1</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>415</v>
+        <v>255</v>
       </c>
       <c r="L78">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="M78">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="7">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="E79" s="7">
+      <c r="B79" t="s">
+        <v>402</v>
+      </c>
+      <c r="C79" t="s">
+        <v>264</v>
+      </c>
+      <c r="D79" t="s">
+        <v>263</v>
+      </c>
+      <c r="E79">
         <v>500</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79">
         <v>150</v>
       </c>
-      <c r="G79" s="7">
-        <v>0</v>
-      </c>
-      <c r="H79" s="7">
-        <v>0</v>
-      </c>
-      <c r="I79" s="7">
-        <v>0</v>
-      </c>
-      <c r="J79" s="7">
-        <v>0</v>
-      </c>
-      <c r="K79" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L79" s="7">
-        <v>790</v>
-      </c>
-      <c r="M79" s="7">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="13">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L79">
+        <v>770</v>
+      </c>
+      <c r="M79">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="B80" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="E80" s="13">
+      <c r="B80" t="s">
+        <v>405</v>
+      </c>
+      <c r="C80" t="s">
+        <v>271</v>
+      </c>
+      <c r="D80" t="s">
+        <v>270</v>
+      </c>
+      <c r="E80">
         <v>500</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80">
         <v>150</v>
       </c>
-      <c r="G80" s="13">
-        <v>0</v>
-      </c>
-      <c r="H80" s="13">
-        <v>0</v>
-      </c>
-      <c r="I80" s="13">
-        <v>0</v>
-      </c>
-      <c r="J80" s="13">
-        <v>0</v>
-      </c>
-      <c r="K80" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="L80" s="13">
-        <v>9999</v>
-      </c>
-      <c r="M80" s="13">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81">
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="L80">
+        <v>780</v>
+      </c>
+      <c r="M80">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="7">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="B81" t="s">
-        <v>435</v>
-      </c>
-      <c r="C81" t="s">
-        <v>292</v>
-      </c>
-      <c r="D81" t="s">
-        <v>310</v>
-      </c>
-      <c r="E81">
+      <c r="B81" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E81" s="7">
         <v>500</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="7">
         <v>150</v>
       </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
-      <c r="H81">
-        <v>1</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="L81">
-        <v>2000</v>
-      </c>
-      <c r="M81">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82">
+      <c r="G81" s="7">
+        <v>0</v>
+      </c>
+      <c r="H81" s="7">
+        <v>0</v>
+      </c>
+      <c r="I81" s="7">
+        <v>0</v>
+      </c>
+      <c r="J81" s="7">
+        <v>0</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L81" s="7">
+        <v>790</v>
+      </c>
+      <c r="M81" s="7">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="11">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B82" t="s">
-        <v>436</v>
-      </c>
-      <c r="C82" t="s">
-        <v>294</v>
-      </c>
-      <c r="D82" t="s">
-        <v>307</v>
-      </c>
-      <c r="E82">
+      <c r="B82" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="E82" s="11">
         <v>500</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="11">
         <v>150</v>
       </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82">
-        <v>1</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>1</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="L82">
-        <v>2100</v>
-      </c>
-      <c r="M82">
-        <v>2100</v>
+      <c r="G82" s="11">
+        <v>0</v>
+      </c>
+      <c r="H82" s="11">
+        <v>0</v>
+      </c>
+      <c r="I82" s="11">
+        <v>0</v>
+      </c>
+      <c r="J82" s="11">
+        <v>0</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="L82" s="11">
+        <v>9999</v>
+      </c>
+      <c r="M82" s="11">
+        <v>9999</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11390,13 +11491,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C83" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D83" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E83">
         <v>500</v>
@@ -11417,13 +11518,13 @@
         <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>448</v>
+        <v>293</v>
       </c>
       <c r="L83">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="M83">
-        <v>2200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11432,13 +11533,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C84" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -11459,13 +11560,13 @@
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L84">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="M84">
-        <v>2300</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11474,13 +11575,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C85" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D85" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -11501,13 +11602,13 @@
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L85">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="M85">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11516,13 +11617,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>376</v>
+        <v>438</v>
       </c>
       <c r="C86" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="D86" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -11534,22 +11635,22 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>278</v>
+        <v>449</v>
       </c>
       <c r="L86">
-        <v>5000</v>
+        <v>2300</v>
       </c>
       <c r="M86">
-        <v>5000</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11558,13 +11659,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
       <c r="C87" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D87" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -11576,22 +11677,22 @@
         <v>0</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87">
         <v>0</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="L87">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="M87">
-        <v>5000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11603,10 +11704,10 @@
         <v>376</v>
       </c>
       <c r="C88" t="s">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="D88" t="s">
-        <v>334</v>
+        <v>282</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -11627,7 +11728,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>478</v>
+        <v>278</v>
       </c>
       <c r="L88">
         <v>5000</v>
@@ -11645,10 +11746,10 @@
         <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>468</v>
+        <v>291</v>
       </c>
       <c r="D89" t="s">
-        <v>467</v>
+        <v>290</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -11669,7 +11770,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11687,10 +11788,10 @@
         <v>376</v>
       </c>
       <c r="C90" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D90" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11711,7 +11812,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>431</v>
+        <v>478</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11729,10 +11830,10 @@
         <v>376</v>
       </c>
       <c r="C91" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="D91" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11753,7 +11854,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11771,10 +11872,10 @@
         <v>376</v>
       </c>
       <c r="C92" t="s">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="D92" t="s">
-        <v>373</v>
+        <v>336</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11795,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11813,10 +11914,10 @@
         <v>376</v>
       </c>
       <c r="C93" t="s">
-        <v>281</v>
+        <v>451</v>
       </c>
       <c r="D93" t="s">
-        <v>279</v>
+        <v>479</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11837,7 +11938,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>427</v>
+        <v>480</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11855,10 +11956,10 @@
         <v>376</v>
       </c>
       <c r="C94" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="D94" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -11879,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>478</v>
+        <v>423</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -11897,10 +11998,10 @@
         <v>376</v>
       </c>
       <c r="C95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D95" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -11921,7 +12022,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -11939,10 +12040,10 @@
         <v>376</v>
       </c>
       <c r="C96" t="s">
-        <v>324</v>
+        <v>434</v>
       </c>
       <c r="D96" t="s">
-        <v>325</v>
+        <v>433</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -11981,10 +12082,10 @@
         <v>376</v>
       </c>
       <c r="C97" t="s">
-        <v>327</v>
+        <v>283</v>
       </c>
       <c r="D97" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -12005,7 +12106,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>478</v>
+        <v>423</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -12023,10 +12124,10 @@
         <v>376</v>
       </c>
       <c r="C98" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D98" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12065,10 +12166,10 @@
         <v>376</v>
       </c>
       <c r="C99" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D99" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12107,10 +12208,10 @@
         <v>376</v>
       </c>
       <c r="C100" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="D100" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -12131,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -12149,10 +12250,10 @@
         <v>376</v>
       </c>
       <c r="C101" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D101" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12173,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>424</v>
+        <v>478</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -12191,10 +12292,10 @@
         <v>376</v>
       </c>
       <c r="C102" t="s">
-        <v>442</v>
+        <v>289</v>
       </c>
       <c r="D102" t="s">
-        <v>441</v>
+        <v>288</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -12215,7 +12316,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -12233,10 +12334,10 @@
         <v>376</v>
       </c>
       <c r="C103" t="s">
-        <v>475</v>
+        <v>333</v>
       </c>
       <c r="D103" t="s">
-        <v>474</v>
+        <v>332</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -12257,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>478</v>
+        <v>424</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -12275,10 +12376,10 @@
         <v>376</v>
       </c>
       <c r="C104" t="s">
-        <v>340</v>
+        <v>442</v>
       </c>
       <c r="D104" t="s">
-        <v>338</v>
+        <v>441</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -12299,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12317,10 +12418,10 @@
         <v>376</v>
       </c>
       <c r="C105" t="s">
-        <v>341</v>
+        <v>475</v>
       </c>
       <c r="D105" t="s">
-        <v>339</v>
+        <v>474</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12341,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>427</v>
+        <v>478</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12359,10 +12460,10 @@
         <v>376</v>
       </c>
       <c r="C106" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -12383,7 +12484,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>478</v>
+        <v>429</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12401,10 +12502,10 @@
         <v>376</v>
       </c>
       <c r="C107" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="D107" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -12425,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -12443,10 +12544,10 @@
         <v>376</v>
       </c>
       <c r="C108" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="D108" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -12485,10 +12586,10 @@
         <v>376</v>
       </c>
       <c r="C109" t="s">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="D109" t="s">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -12509,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12527,10 +12628,10 @@
         <v>376</v>
       </c>
       <c r="C110" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D110" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -12551,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -12569,10 +12670,10 @@
         <v>376</v>
       </c>
       <c r="C111" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D111" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -12611,10 +12712,10 @@
         <v>376</v>
       </c>
       <c r="C112" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D112" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -12653,10 +12754,10 @@
         <v>376</v>
       </c>
       <c r="C113" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D113" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -12677,7 +12778,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12695,10 +12796,10 @@
         <v>376</v>
       </c>
       <c r="C114" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D114" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -12719,7 +12820,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12737,10 +12838,10 @@
         <v>376</v>
       </c>
       <c r="C115" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D115" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -12761,7 +12862,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L115">
         <v>5000</v>
@@ -12779,10 +12880,10 @@
         <v>376</v>
       </c>
       <c r="C116" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D116" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -12803,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12821,10 +12922,10 @@
         <v>376</v>
       </c>
       <c r="C117" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D117" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -12863,10 +12964,10 @@
         <v>376</v>
       </c>
       <c r="C118" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="D118" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -12887,7 +12988,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>483</v>
+        <v>428</v>
       </c>
       <c r="L118">
         <v>5000</v>
@@ -12905,10 +13006,10 @@
         <v>376</v>
       </c>
       <c r="C119" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="D119" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -12929,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>425</v>
+        <v>478</v>
       </c>
       <c r="L119">
         <v>5000</v>
@@ -12947,10 +13048,10 @@
         <v>376</v>
       </c>
       <c r="C120" t="s">
-        <v>471</v>
+        <v>318</v>
       </c>
       <c r="D120" t="s">
-        <v>469</v>
+        <v>319</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -12971,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L120">
         <v>5000</v>
@@ -12989,10 +13090,10 @@
         <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>472</v>
+        <v>311</v>
       </c>
       <c r="D121" t="s">
-        <v>470</v>
+        <v>312</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -13013,7 +13114,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>473</v>
+        <v>425</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -13022,255 +13123,255 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="122" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="11">
+    <row r="122" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" t="s">
         <v>376</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="E122" s="11">
+      <c r="C122" t="s">
+        <v>471</v>
+      </c>
+      <c r="D122" t="s">
+        <v>469</v>
+      </c>
+      <c r="E122">
         <v>500</v>
       </c>
-      <c r="F122" s="11">
+      <c r="F122">
         <v>150</v>
       </c>
-      <c r="G122" s="11">
-        <v>0</v>
-      </c>
-      <c r="H122" s="11">
-        <v>0</v>
-      </c>
-      <c r="I122" s="11">
-        <v>0</v>
-      </c>
-      <c r="J122" s="11">
-        <v>0</v>
-      </c>
-      <c r="K122" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="L122" s="11">
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="L122">
         <v>5000</v>
       </c>
-      <c r="M122" s="11">
+      <c r="M122">
         <v>5000</v>
       </c>
     </row>
-    <row r="123" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="11">
+    <row r="123" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="E123" s="11">
+      <c r="C123" t="s">
+        <v>472</v>
+      </c>
+      <c r="D123" t="s">
+        <v>470</v>
+      </c>
+      <c r="E123">
         <v>500</v>
       </c>
-      <c r="F123" s="11">
+      <c r="F123">
         <v>150</v>
       </c>
-      <c r="G123" s="11">
-        <v>0</v>
-      </c>
-      <c r="H123" s="11">
-        <v>0</v>
-      </c>
-      <c r="I123" s="11">
-        <v>0</v>
-      </c>
-      <c r="J123" s="11">
-        <v>0</v>
-      </c>
-      <c r="K123" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="L123" s="11">
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L123">
         <v>5000</v>
       </c>
-      <c r="M123" s="11">
+      <c r="M123">
         <v>5000</v>
       </c>
     </row>
-    <row r="124" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="11">
+    <row r="124" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="13">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C124" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E124" s="11">
+      <c r="C124" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E124" s="13">
         <v>500</v>
       </c>
-      <c r="F124" s="11">
+      <c r="F124" s="13">
         <v>150</v>
       </c>
-      <c r="G124" s="11">
-        <v>0</v>
-      </c>
-      <c r="H124" s="11">
-        <v>0</v>
-      </c>
-      <c r="I124" s="11">
-        <v>0</v>
-      </c>
-      <c r="J124" s="11">
-        <v>0</v>
-      </c>
-      <c r="K124" s="12" t="s">
+      <c r="G124" s="13">
+        <v>0</v>
+      </c>
+      <c r="H124" s="13">
+        <v>0</v>
+      </c>
+      <c r="I124" s="13">
+        <v>0</v>
+      </c>
+      <c r="J124" s="13">
+        <v>0</v>
+      </c>
+      <c r="K124" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L124" s="11">
+      <c r="L124" s="13">
         <v>5000</v>
       </c>
-      <c r="M124" s="11">
+      <c r="M124" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125">
+    <row r="125" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="13">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C125" t="s">
-        <v>368</v>
-      </c>
-      <c r="D125" t="s">
-        <v>367</v>
-      </c>
-      <c r="E125">
+      <c r="C125" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="E125" s="13">
         <v>500</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="13">
         <v>150</v>
       </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="L125">
+      <c r="G125" s="13">
+        <v>0</v>
+      </c>
+      <c r="H125" s="13">
+        <v>0</v>
+      </c>
+      <c r="I125" s="13">
+        <v>0</v>
+      </c>
+      <c r="J125" s="13">
+        <v>0</v>
+      </c>
+      <c r="K125" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L125" s="13">
         <v>5000</v>
       </c>
-      <c r="M125">
+      <c r="M125" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126">
+    <row r="126" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="13">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C126" t="s">
-        <v>370</v>
-      </c>
-      <c r="D126" t="s">
-        <v>369</v>
-      </c>
-      <c r="E126">
+      <c r="C126" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E126" s="13">
         <v>500</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="13">
         <v>150</v>
       </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126" s="2" t="s">
+      <c r="G126" s="13">
+        <v>0</v>
+      </c>
+      <c r="H126" s="13">
+        <v>0</v>
+      </c>
+      <c r="I126" s="13">
+        <v>0</v>
+      </c>
+      <c r="J126" s="13">
+        <v>0</v>
+      </c>
+      <c r="K126" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L126">
+      <c r="L126" s="13">
         <v>5000</v>
       </c>
-      <c r="M126">
+      <c r="M126" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="11">
+    <row r="127" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" t="s">
         <v>376</v>
       </c>
-      <c r="C127" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="E127" s="11">
+      <c r="C127" t="s">
+        <v>368</v>
+      </c>
+      <c r="D127" t="s">
+        <v>367</v>
+      </c>
+      <c r="E127">
         <v>500</v>
       </c>
-      <c r="F127" s="11">
+      <c r="F127">
         <v>150</v>
       </c>
-      <c r="G127" s="11">
-        <v>0</v>
-      </c>
-      <c r="H127" s="11">
-        <v>0</v>
-      </c>
-      <c r="I127" s="11">
-        <v>0</v>
-      </c>
-      <c r="J127" s="11">
-        <v>0</v>
-      </c>
-      <c r="K127" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="L127" s="11">
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="L127">
         <v>5000</v>
       </c>
-      <c r="M127" s="11">
+      <c r="M127">
         <v>5000</v>
       </c>
     </row>
@@ -13283,10 +13384,10 @@
         <v>376</v>
       </c>
       <c r="C128" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="D128" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -13307,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>425</v>
+        <v>285</v>
       </c>
       <c r="L128">
         <v>5000</v>
@@ -13316,60 +13417,61 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129">
-        <f>ROW()-2</f>
+    <row r="129" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="13">
+        <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="B129" t="s">
-        <v>446</v>
-      </c>
-      <c r="C129" t="s">
-        <v>443</v>
-      </c>
-      <c r="D129" t="s">
-        <v>444</v>
-      </c>
-      <c r="E129">
-        <v>0</v>
-      </c>
-      <c r="F129">
-        <v>0</v>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129" t="s">
-        <v>445</v>
-      </c>
-      <c r="L129">
-        <v>9999</v>
-      </c>
-      <c r="M129">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B129" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="E129" s="13">
+        <v>500</v>
+      </c>
+      <c r="F129" s="13">
+        <v>150</v>
+      </c>
+      <c r="G129" s="13">
+        <v>0</v>
+      </c>
+      <c r="H129" s="13">
+        <v>0</v>
+      </c>
+      <c r="I129" s="13">
+        <v>0</v>
+      </c>
+      <c r="J129" s="13">
+        <v>0</v>
+      </c>
+      <c r="K129" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="L129" s="13">
+        <v>5000</v>
+      </c>
+      <c r="M129" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130">
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>169</v>
+        <v>376</v>
       </c>
       <c r="C130" t="s">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="D130" t="s">
-        <v>174</v>
+        <v>314</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -13387,15 +13489,98 @@
         <v>0</v>
       </c>
       <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="L130">
+        <v>5000</v>
+      </c>
+      <c r="M130">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <f>ROW()-2</f>
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>446</v>
+      </c>
+      <c r="C131" t="s">
+        <v>443</v>
+      </c>
+      <c r="D131" t="s">
+        <v>444</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
         <v>1</v>
       </c>
-      <c r="K130" s="2" t="s">
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131" t="s">
+        <v>445</v>
+      </c>
+      <c r="L131">
+        <v>9999</v>
+      </c>
+      <c r="M131">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132">
+        <v>10000</v>
+      </c>
+      <c r="B132" t="s">
+        <v>169</v>
+      </c>
+      <c r="C132" t="s">
+        <v>173</v>
+      </c>
+      <c r="D132" t="s">
+        <v>174</v>
+      </c>
+      <c r="E132">
+        <v>500</v>
+      </c>
+      <c r="F132">
+        <v>150</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="L130">
+      <c r="L132">
         <v>9000</v>
       </c>
-      <c r="M130">
+      <c r="M132">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09661B67-574F-413E-9404-F76D4D63D56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315F0F00-61B8-4D32-AA23-166CE9055FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2970" yWindow="1140" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="492">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7357,13 +7357,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未定</t>
-    <rPh sb="0" eb="2">
-      <t>ミテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ニーモニックの本</t>
     <rPh sb="7" eb="8">
       <t>ホン</t>
@@ -7558,6 +7551,38 @@
     </rPh>
     <rPh sb="78" eb="81">
       <t>フシギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏エリアお店で本買える</t>
+    <rPh sb="0" eb="1">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本で覚えるor無し予定</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オボ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8680,10 +8705,10 @@
         <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D16" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E16">
         <v>500</v>
@@ -8704,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L16">
         <v>3130</v>
@@ -8722,10 +8747,10 @@
         <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -8746,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L17">
         <v>3140</v>
@@ -8998,7 +9023,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L23">
         <v>30</v>
@@ -11770,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11812,7 +11837,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11854,7 +11879,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11917,7 +11942,7 @@
         <v>451</v>
       </c>
       <c r="D93" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11938,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -12064,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -12106,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>423</v>
+        <v>491</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -12148,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -12190,7 +12215,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -12232,7 +12257,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -12274,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -12316,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -12400,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12418,10 +12443,10 @@
         <v>376</v>
       </c>
       <c r="C105" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D105" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12442,7 +12467,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12568,7 +12593,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12652,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -12694,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12736,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12778,7 +12803,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12820,7 +12845,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12862,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L115">
         <v>5000</v>
@@ -12904,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12946,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L117">
         <v>5000</v>
@@ -13030,7 +13055,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L119">
         <v>5000</v>
@@ -13072,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L120">
         <v>5000</v>
@@ -13156,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L122">
         <v>5000</v>
@@ -13198,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="L123">
         <v>5000</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315F0F00-61B8-4D32-AA23-166CE9055FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9211040-AB3A-41FC-8217-1685FDAAB720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="1140" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="491">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -3589,48 +3589,6 @@
     <t>レインボーレインの本</t>
     <rPh sb="9" eb="10">
       <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【コーヒーのレシピ】
-おいしいコーヒーの淹れ方
-①&lt;color=#BA9535FF&gt;コーヒー豆&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;すり鉢&lt;/color&gt;でひき、粉にします。
-②&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;と&lt;color=#BA9535FF&gt;水&lt;/color&gt;をいれ、&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;でひと煮立ちしたら出来上がり。
-コーヒー粉と水は、&lt;color=#BA9535FF&gt;4:1&lt;/color&gt;ぐらいがほどよい苦さでマイルドです。
-</t>
-    <rPh sb="21" eb="22">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>バチ</t>
-    </rPh>
-    <rPh sb="90" eb="91">
-      <t>コナ</t>
-    </rPh>
-    <rPh sb="150" eb="151">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="181" eb="182">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="193" eb="195">
-      <t>ニタ</t>
-    </rPh>
-    <rPh sb="199" eb="202">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="211" eb="212">
-      <t>コナ</t>
-    </rPh>
-    <rPh sb="213" eb="214">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="252" eb="253">
-      <t>ニガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7065,124 +7023,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">【チョコレートの秘密　～その１～】
-今回の特集は.. チョコレート作りの秘訣！！
-チョコを作る際のアレンジレシピをご紹介いたします！
-※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
-今回のテーマは、「カカオマス」。
-この「カカオマス」に色んな材料を加えると、チョコに様々な変化が現れます。
-いくつか秘密をご紹介しますね☆
-【苦味を加える】
-・「カカオマス」の状態で、いろんな材料を加えることができます。
-たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。
-【砂糖を変える】
-・通常使う砂糖を、&lt;color=#BA9535FF&gt;エメラルドシュガー&lt;/color&gt;や&lt;color=#BA9535FF&gt;サファイアシュガー&lt;/color&gt;に変えると..？
-</t>
-    <rPh sb="8" eb="10">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>コンカイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>トクシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ヒケツ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="90" eb="91">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>コンカイ</t>
-    </rPh>
-    <rPh sb="139" eb="140">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="142" eb="144">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="145" eb="146">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="160" eb="161">
-      <t>アラワ</t>
-    </rPh>
-    <rPh sb="170" eb="172">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="185" eb="187">
-      <t>ニガミ</t>
-    </rPh>
-    <rPh sb="188" eb="189">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="203" eb="205">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="211" eb="213">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="214" eb="215">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="265" eb="266">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="270" eb="272">
-      <t>ニガミ</t>
-    </rPh>
-    <rPh sb="273" eb="274">
-      <t>ツヨ</t>
-    </rPh>
-    <rPh sb="285" eb="287">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="288" eb="289">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="295" eb="297">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="297" eb="298">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="299" eb="301">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="373" eb="374">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">☆ストロベリーパフェのレシピ
 ★事前に、&lt;color=#BA9535FF&gt;カステラ&lt;/color&gt;と、&lt;color=#BA9535FF&gt;アイスクリーム&lt;/color&gt;、&lt;color=#FF5CA1FF&gt;ガラスの器&lt;/color&gt;は準備しておきましょう！
 ※ガラスの器がないと、失敗しやすくなります。
@@ -7260,70 +7100,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">【チョコレートの秘密　～その２～】
-今回の特集は.. チョコレート作りの秘訣！！第二弾！！
-※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
-今回のテーマは、「白いチョコレート」の作り方。
-真っ黒のチョコもおいしいですが、少し飽きてきたそこのアナタにぜひ！
-ヒア・ウィ・ゴーー！！
-【ホワイトチョコの作り方】
-・液体状チョコレートの状態で、&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
-お花のエキスがよく混ざって、なんとチョコレートが真っ白に・・！
-</t>
-    <rPh sb="8" eb="10">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>ダイニダン</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="110" eb="111">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="112" eb="113">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="117" eb="118">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="131" eb="132">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="133" eb="134">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="178" eb="180">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="180" eb="181">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="188" eb="190">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="210" eb="211">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="227" eb="229">
-      <t>スウテキ</t>
-    </rPh>
-    <rPh sb="229" eb="230">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="240" eb="241">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="248" eb="249">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>グリッターの本</t>
     <rPh sb="6" eb="7">
       <t>ホン</t>
@@ -7555,22 +7331,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>夏エリアお店で本買える</t>
-    <rPh sb="0" eb="1">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>本で覚えるor無し予定</t>
     <rPh sb="0" eb="1">
       <t>ホン</t>
@@ -7583,6 +7343,283 @@
     </rPh>
     <rPh sb="9" eb="11">
       <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【チョコレートの秘密　～その１～】
+今回の特集は.. チョコレート作りの秘訣！！
+チョコを作る際のアレンジレシピをご紹介いたします！
+※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
+今回のテーマは、「カカオマス」。
+この「カカオマス」に色んな材料を加えると、チョコに様々な変化が現れます。
+いくつか秘密をご紹介☆
+◆お抹茶チョコレート
+カカオマス　×　へんな草
+カカオマス　×　ミント
+混ぜると、緑色のチョコレートに変化します。
+◆海のチョコレート
+カカオマス　×　すみれのお花
+カカオマス　×　ブルーベリー
+カカオマス　×　ブラックベリー
+海を感じさせる青色のチョコレートに変化！
+◆純愛のチョコレート
+カカオマス　×　ストロベリー
+カカオマス　×　ラズベリー
+愛情をあらわす赤色のチョコレートに変化します！
+【苦味を加える】
+・「カカオマス」の状態で、いろんな材料を加えることができます。
+たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トクシュウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒケツ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="139" eb="140">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="181" eb="183">
+      <t>マッチャ</t>
+    </rPh>
+    <rPh sb="202" eb="203">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="222" eb="224">
+      <t>ミドリイロ</t>
+    </rPh>
+    <rPh sb="232" eb="234">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="241" eb="242">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="264" eb="265">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="298" eb="299">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="300" eb="301">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="305" eb="307">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="315" eb="317">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="321" eb="323">
+      <t>ジュンアイ</t>
+    </rPh>
+    <rPh sb="362" eb="364">
+      <t>アイジョウ</t>
+    </rPh>
+    <rPh sb="369" eb="371">
+      <t>アカイロ</t>
+    </rPh>
+    <rPh sb="389" eb="391">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="392" eb="393">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="407" eb="409">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="415" eb="417">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="418" eb="419">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="469" eb="470">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="474" eb="476">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="477" eb="478">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【チョコレートの秘密　～その２～】
+今回の特集は.. チョコレート作りの秘訣！！第二弾！！
+※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
+今回のテーマは、「白いチョコレート」の作り方。
+真っ黒のチョコもおいしいですが、少し飽きてきたそこのアナタにぜひ！
+ヒア・ウィ・ゴーー！！
+【ホワイトチョコの作り方】
+・カカオマスの状態で、
+&lt;color=#BA9535FF&gt;ジャスミンのお花&lt;/color&gt;　や　&lt;color=#BA9535FF&gt;エルダフラワー&lt;/color&gt;
+&lt;color=#BA9535FF&gt;銀色の草&lt;/color&gt;　を混ぜる。
+・液体状チョコレートの状態で、
+&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
+お花のエキスがよく混ざって、なんとチョコレートが真っ白に・・！
+</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>ダイニダン</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="214" eb="215">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="276" eb="278">
+      <t>ギンイロ</t>
+    </rPh>
+    <rPh sb="279" eb="280">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="290" eb="291">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="298" eb="300">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="300" eb="301">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="308" eb="310">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="332" eb="333">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="349" eb="351">
+      <t>スウテキ</t>
+    </rPh>
+    <rPh sb="351" eb="352">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="362" eb="363">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="370" eb="371">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【コーヒーのレシピ】
+おいしいコーヒーの淹れ方
+①&lt;color=#BA9535FF&gt;コーヒー豆&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;すり鉢orコーヒーミル&lt;/color&gt;でひき、粉にします。
+②&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;と&lt;color=#BA9535FF&gt;水&lt;/color&gt;をいれ、&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;でひと煮立ちしたら出来上がり。
+コーヒー粉と水は、&lt;color=#BA9535FF&gt;4:1&lt;/color&gt;ぐらいがほどよい苦さでマイルドです。
+</t>
+    <rPh sb="21" eb="22">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>バチ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>コナ</t>
+    </rPh>
+    <rPh sb="158" eb="159">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="201" eb="203">
+      <t>ニタ</t>
+    </rPh>
+    <rPh sb="207" eb="210">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="219" eb="220">
+      <t>コナ</t>
+    </rPh>
+    <rPh sb="221" eb="222">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="260" eb="261">
+      <t>ニガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8183,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L3">
         <v>9999</v>
@@ -8330,7 +8367,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8351,7 +8388,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L7">
         <v>3000</v>
@@ -8621,10 +8658,10 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -8645,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="L14">
         <v>3110</v>
@@ -8663,10 +8700,10 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -8687,7 +8724,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="L15">
         <v>3120</v>
@@ -8705,10 +8742,10 @@
         <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D16" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E16">
         <v>500</v>
@@ -8729,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="L16">
         <v>3130</v>
@@ -8747,10 +8784,10 @@
         <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D17" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -8771,7 +8808,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="L17">
         <v>3140</v>
@@ -9023,7 +9060,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L23">
         <v>30</v>
@@ -9443,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L33">
         <v>130</v>
@@ -9458,13 +9495,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C34" t="s">
+        <v>455</v>
+      </c>
+      <c r="D34" t="s">
         <v>456</v>
-      </c>
-      <c r="D34" t="s">
-        <v>457</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9485,7 +9522,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L34">
         <v>150</v>
@@ -9863,7 +9900,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>320</v>
+        <v>490</v>
       </c>
       <c r="L43">
         <v>270</v>
@@ -10031,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L47" s="5">
         <v>9999</v>
@@ -10046,7 +10083,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C48" t="s">
         <v>198</v>
@@ -10073,7 +10110,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L48">
         <v>310</v>
@@ -10088,7 +10125,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
         <v>203</v>
@@ -10130,7 +10167,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C50" t="s">
         <v>206</v>
@@ -10172,7 +10209,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C51" t="s">
         <v>208</v>
@@ -10199,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L51">
         <v>340</v>
@@ -10214,7 +10251,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C52" t="s">
         <v>268</v>
@@ -10241,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L52">
         <v>350</v>
@@ -10256,7 +10293,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C53" t="s">
         <v>269</v>
@@ -10283,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L53">
         <v>360</v>
@@ -10298,7 +10335,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C54" t="s">
         <v>299</v>
@@ -10325,7 +10362,7 @@
         <v>1</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L54">
         <v>370</v>
@@ -10340,7 +10377,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C55" t="s">
         <v>300</v>
@@ -10367,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L55">
         <v>380</v>
@@ -10382,7 +10419,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C56" t="s">
         <v>277</v>
@@ -10409,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L56">
         <v>390</v>
@@ -10466,7 +10503,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C58" t="s">
         <v>213</v>
@@ -10508,7 +10545,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C59" t="s">
         <v>215</v>
@@ -10550,7 +10587,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C60" t="s">
         <v>217</v>
@@ -10592,7 +10629,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C61" t="s">
         <v>220</v>
@@ -10619,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L61">
         <v>520</v>
@@ -10634,7 +10671,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C62" t="s">
         <v>221</v>
@@ -10661,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L62">
         <v>530</v>
@@ -10703,7 +10740,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L63">
         <v>540</v>
@@ -10718,7 +10755,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C64" t="s">
         <v>226</v>
@@ -10745,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L64">
         <v>550</v>
@@ -10760,7 +10797,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C65" t="s">
         <v>227</v>
@@ -10787,7 +10824,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L65">
         <v>560</v>
@@ -10802,7 +10839,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s">
         <v>231</v>
@@ -10829,7 +10866,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L66">
         <v>570</v>
@@ -10844,7 +10881,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C67" t="s">
         <v>230</v>
@@ -10886,7 +10923,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C68" t="s">
         <v>233</v>
@@ -10970,7 +11007,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C70" t="s">
         <v>237</v>
@@ -10997,7 +11034,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L70">
         <v>610</v>
@@ -11054,7 +11091,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C72" t="s">
         <v>240</v>
@@ -11081,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L72">
         <v>700</v>
@@ -11096,7 +11133,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C73" t="s">
         <v>262</v>
@@ -11123,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L73">
         <v>710</v>
@@ -11138,7 +11175,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C74" t="s">
         <v>242</v>
@@ -11165,7 +11202,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L74">
         <v>720</v>
@@ -11180,7 +11217,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C75" t="s">
         <v>244</v>
@@ -11207,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L75">
         <v>730</v>
@@ -11222,7 +11259,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C76" t="s">
         <v>245</v>
@@ -11249,7 +11286,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L76">
         <v>740</v>
@@ -11264,7 +11301,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C77" t="s">
         <v>252</v>
@@ -11291,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L77">
         <v>750</v>
@@ -11306,7 +11343,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C78" t="s">
         <v>248</v>
@@ -11348,7 +11385,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C79" t="s">
         <v>264</v>
@@ -11390,7 +11427,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C80" t="s">
         <v>271</v>
@@ -11417,7 +11454,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L80">
         <v>780</v>
@@ -11516,7 +11553,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C83" t="s">
         <v>292</v>
@@ -11558,7 +11595,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C84" t="s">
         <v>294</v>
@@ -11585,7 +11622,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L84">
         <v>2100</v>
@@ -11600,7 +11637,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C85" t="s">
         <v>295</v>
@@ -11627,7 +11664,7 @@
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L85">
         <v>2200</v>
@@ -11642,7 +11679,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C86" t="s">
         <v>296</v>
@@ -11669,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L86">
         <v>2300</v>
@@ -11684,7 +11721,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C87" t="s">
         <v>297</v>
@@ -11711,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L87">
         <v>2400</v>
@@ -11726,7 +11763,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C88" t="s">
         <v>280</v>
@@ -11768,7 +11805,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C89" t="s">
         <v>291</v>
@@ -11795,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="L89">
         <v>5000</v>
@@ -11810,13 +11847,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C90" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D90" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -11837,7 +11874,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L90">
         <v>5000</v>
@@ -11852,13 +11889,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C91" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D91" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -11879,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L91">
         <v>5000</v>
@@ -11894,13 +11931,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C92" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D92" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -11921,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L92">
         <v>5000</v>
@@ -11936,13 +11973,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C93" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D93" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -11963,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="L93">
         <v>5000</v>
@@ -11978,13 +12015,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C94" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D94" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12005,7 +12042,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L94">
         <v>5000</v>
@@ -12020,7 +12057,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C95" t="s">
         <v>281</v>
@@ -12047,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L95">
         <v>5000</v>
@@ -12062,13 +12099,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C96" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D96" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12089,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L96">
         <v>5000</v>
@@ -12104,7 +12141,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C97" t="s">
         <v>283</v>
@@ -12131,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="L97">
         <v>5000</v>
@@ -12146,13 +12183,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C98" t="s">
+        <v>323</v>
+      </c>
+      <c r="D98" t="s">
         <v>324</v>
-      </c>
-      <c r="D98" t="s">
-        <v>325</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12173,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L98">
         <v>5000</v>
@@ -12188,13 +12225,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C99" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D99" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12215,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L99">
         <v>5000</v>
@@ -12230,7 +12267,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C100" t="s">
         <v>316</v>
@@ -12257,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L100">
         <v>5000</v>
@@ -12272,13 +12309,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C101" t="s">
+        <v>329</v>
+      </c>
+      <c r="D101" t="s">
         <v>330</v>
-      </c>
-      <c r="D101" t="s">
-        <v>331</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12299,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L101">
         <v>5000</v>
@@ -12314,7 +12351,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C102" t="s">
         <v>289</v>
@@ -12341,7 +12378,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="L102">
         <v>5000</v>
@@ -12356,13 +12393,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C103" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -12383,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L103">
         <v>5000</v>
@@ -12398,13 +12435,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C104" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D104" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -12425,7 +12462,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L104">
         <v>5000</v>
@@ -12440,13 +12477,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C105" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D105" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -12467,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L105">
         <v>5000</v>
@@ -12482,13 +12519,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D106" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -12509,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L106">
         <v>5000</v>
@@ -12524,13 +12561,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -12551,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L107">
         <v>5000</v>
@@ -12566,13 +12603,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C108" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D108" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -12593,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L108">
         <v>5000</v>
@@ -12608,7 +12645,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C109" t="s">
         <v>286</v>
@@ -12635,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L109">
         <v>5000</v>
@@ -12650,13 +12687,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D110" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -12677,7 +12714,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L110">
         <v>5000</v>
@@ -12692,13 +12729,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C111" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D111" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -12719,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L111">
         <v>5000</v>
@@ -12734,13 +12771,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C112" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D112" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -12761,7 +12798,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="L112">
         <v>5000</v>
@@ -12776,13 +12813,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C113" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -12803,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L113">
         <v>5000</v>
@@ -12818,13 +12855,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C114" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D114" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -12845,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="L114">
         <v>5000</v>
@@ -12860,13 +12897,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C115" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D115" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -12887,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="L115">
         <v>5000</v>
@@ -12902,13 +12939,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C116" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D116" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -12929,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L116">
         <v>5000</v>
@@ -12944,13 +12981,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C117" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D117" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -12971,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L117">
         <v>5000</v>
@@ -12986,13 +13023,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C118" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D118" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -13013,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L118">
         <v>5000</v>
@@ -13028,13 +13065,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C119" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D119" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -13055,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L119">
         <v>5000</v>
@@ -13070,7 +13107,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C120" t="s">
         <v>318</v>
@@ -13097,7 +13134,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L120">
         <v>5000</v>
@@ -13112,7 +13149,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C121" t="s">
         <v>311</v>
@@ -13139,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L121">
         <v>5000</v>
@@ -13154,13 +13191,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C122" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D122" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -13181,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L122">
         <v>5000</v>
@@ -13196,13 +13233,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C123" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D123" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -13223,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L123">
         <v>5000</v>
@@ -13238,13 +13275,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E124" s="13">
         <v>500</v>
@@ -13280,13 +13317,13 @@
         <v>123</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E125" s="13">
         <v>500</v>
@@ -13322,13 +13359,13 @@
         <v>124</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E126" s="13">
         <v>500</v>
@@ -13364,13 +13401,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C127" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D127" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -13391,7 +13428,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L127">
         <v>5000</v>
@@ -13406,13 +13443,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C128" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D128" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -13448,13 +13485,13 @@
         <v>127</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E129" s="13">
         <v>500</v>
@@ -13475,7 +13512,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L129" s="13">
         <v>5000</v>
@@ -13490,7 +13527,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C130" t="s">
         <v>313</v>
@@ -13517,7 +13554,7 @@
         <v>0</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L130">
         <v>5000</v>
@@ -13532,13 +13569,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C131" t="s">
+        <v>442</v>
+      </c>
+      <c r="D131" t="s">
         <v>443</v>
-      </c>
-      <c r="D131" t="s">
-        <v>444</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -13559,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L131">
         <v>9999</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9211040-AB3A-41FC-8217-1685FDAAB720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F03584-EB1F-49EC-98B8-A1FAE7492D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="493">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7621,6 +7621,14 @@
     <rPh sb="260" eb="261">
       <t>ニガ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>costume_Num</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cos_Equip</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8087,7 +8095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8097,14 +8105,14 @@
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="7.75" customWidth="1"/>
     <col min="7" max="7" width="4.625" customWidth="1"/>
-    <col min="8" max="9" width="7.5" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="11" max="11" width="41.125" customWidth="1"/>
-    <col min="12" max="12" width="9.875" customWidth="1"/>
-    <col min="13" max="13" width="10.125" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="10.375" customWidth="1"/>
+    <col min="13" max="13" width="41.125" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
+    <col min="15" max="15" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -8133,19 +8141,25 @@
         <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f t="shared" ref="A2:A130" si="0">ROW()-2</f>
         <v>0</v>
@@ -8175,19 +8189,25 @@
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>9999</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -8217,19 +8237,25 @@
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>9999</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -8259,19 +8285,25 @@
         <v>0</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>9999</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>9999</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -8303,17 +8335,23 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
         <v>20</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
         <v>9999</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -8343,19 +8381,25 @@
         <v>0</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>10</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -8385,19 +8429,25 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>3000</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>3000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -8427,19 +8477,25 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>1</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>3020</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>3020</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -8469,19 +8525,25 @@
         <v>0</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>1</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>3050</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>3050</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -8511,19 +8573,25 @@
         <v>0</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>1</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>3070</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>3070</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -8553,19 +8621,25 @@
         <v>0</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>1</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>3080</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>3080</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -8595,19 +8669,25 @@
         <v>0</v>
       </c>
       <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>1</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>3090</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>3090</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -8637,19 +8717,25 @@
         <v>0</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>1</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>3100</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>3100</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8679,19 +8765,25 @@
         <v>0</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>1</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>3110</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>3110</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -8721,19 +8813,25 @@
         <v>0</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>1</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>3120</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>3120</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -8763,19 +8861,25 @@
         <v>0</v>
       </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
         <v>1</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>3130</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>3130</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -8805,19 +8909,25 @@
         <v>0</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>1</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>3140</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>3140</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -8847,19 +8957,25 @@
         <v>0</v>
       </c>
       <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>1</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>3010</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>3010</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -8889,19 +9005,25 @@
         <v>0</v>
       </c>
       <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>1</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>3030</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>3030</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -8931,19 +9053,25 @@
         <v>0</v>
       </c>
       <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
         <v>1</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>3040</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>3040</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -8973,19 +9101,25 @@
         <v>0</v>
       </c>
       <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>1</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>3060</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>3060</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9015,19 +9149,25 @@
         <v>0</v>
       </c>
       <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
         <v>1</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>20</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -9057,19 +9197,25 @@
         <v>0</v>
       </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
         <v>1</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>30</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9099,19 +9245,25 @@
         <v>0</v>
       </c>
       <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>1</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>40</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -9141,19 +9293,25 @@
         <v>0</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>1</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>50</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -9183,19 +9341,25 @@
         <v>0</v>
       </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>1</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>60</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9225,19 +9389,25 @@
         <v>0</v>
       </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>1</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>70</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9267,19 +9437,25 @@
         <v>0</v>
       </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>1</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>80</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -9309,19 +9485,25 @@
         <v>0</v>
       </c>
       <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
         <v>1</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>90</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9351,19 +9533,25 @@
         <v>0</v>
       </c>
       <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
         <v>1</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>100</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -9393,19 +9581,25 @@
         <v>0</v>
       </c>
       <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
         <v>1</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>110</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -9435,19 +9629,25 @@
         <v>0</v>
       </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
         <v>1</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>120</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -9477,19 +9677,25 @@
         <v>0</v>
       </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
         <v>1</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>130</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -9519,19 +9725,25 @@
         <v>0</v>
       </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
         <v>1</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>150</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -9561,19 +9773,25 @@
         <v>0</v>
       </c>
       <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>1</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L35">
+      <c r="N35">
         <v>140</v>
       </c>
-      <c r="M35">
+      <c r="O35">
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -9603,19 +9821,25 @@
         <v>0</v>
       </c>
       <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
         <v>1</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>200</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -9645,19 +9869,25 @@
         <v>0</v>
       </c>
       <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
         <v>1</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>210</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -9687,19 +9917,25 @@
         <v>0</v>
       </c>
       <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
         <v>1</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>220</v>
       </c>
-      <c r="M38">
+      <c r="O38">
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -9729,19 +9965,25 @@
         <v>0</v>
       </c>
       <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
         <v>1</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>230</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -9771,19 +10013,25 @@
         <v>0</v>
       </c>
       <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
         <v>1</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>240</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -9813,19 +10061,25 @@
         <v>0</v>
       </c>
       <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
         <v>1</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="L41">
+      <c r="N41">
         <v>250</v>
       </c>
-      <c r="M41">
+      <c r="O41">
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -9855,19 +10109,25 @@
         <v>0</v>
       </c>
       <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
         <v>1</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="L42">
+      <c r="N42">
         <v>260</v>
       </c>
-      <c r="M42">
+      <c r="O42">
         <v>260</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -9897,19 +10157,25 @@
         <v>0</v>
       </c>
       <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
         <v>1</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>270</v>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>270</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -9939,19 +10205,25 @@
         <v>0</v>
       </c>
       <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
         <v>1</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="L44">
+      <c r="N44">
         <v>280</v>
       </c>
-      <c r="M44">
+      <c r="O44">
         <v>280</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -9981,19 +10253,25 @@
         <v>0</v>
       </c>
       <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
         <v>1</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="L45">
+      <c r="N45">
         <v>290</v>
       </c>
-      <c r="M45">
+      <c r="O45">
         <v>290</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -10023,19 +10301,25 @@
         <v>0</v>
       </c>
       <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
         <v>1</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="L46">
+      <c r="N46">
         <v>300</v>
       </c>
-      <c r="M46">
+      <c r="O46">
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:15" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -10067,17 +10351,23 @@
       <c r="J47" s="5">
         <v>0</v>
       </c>
-      <c r="K47" s="6" t="s">
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>0</v>
+      </c>
+      <c r="M47" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="L47" s="5">
+      <c r="N47" s="5">
         <v>9999</v>
       </c>
-      <c r="M47" s="5">
+      <c r="O47" s="5">
         <v>9999</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -10107,19 +10397,25 @@
         <v>0</v>
       </c>
       <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
         <v>1</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>310</v>
       </c>
-      <c r="M48">
+      <c r="O48">
         <v>310</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -10149,19 +10445,25 @@
         <v>0</v>
       </c>
       <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
         <v>1</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="L49">
+      <c r="N49">
         <v>320</v>
       </c>
-      <c r="M49">
+      <c r="O49">
         <v>320</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -10191,19 +10493,25 @@
         <v>0</v>
       </c>
       <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
         <v>1</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="L50">
+      <c r="N50">
         <v>330</v>
       </c>
-      <c r="M50">
+      <c r="O50">
         <v>330</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -10233,19 +10541,25 @@
         <v>0</v>
       </c>
       <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
         <v>1</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="M51" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="L51">
+      <c r="N51">
         <v>340</v>
       </c>
-      <c r="M51">
+      <c r="O51">
         <v>340</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -10275,19 +10589,25 @@
         <v>0</v>
       </c>
       <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
         <v>1</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="L52">
+      <c r="N52">
         <v>350</v>
       </c>
-      <c r="M52">
+      <c r="O52">
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -10317,19 +10637,25 @@
         <v>0</v>
       </c>
       <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
         <v>1</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="L53">
+      <c r="N53">
         <v>360</v>
       </c>
-      <c r="M53">
+      <c r="O53">
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -10359,19 +10685,25 @@
         <v>0</v>
       </c>
       <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
         <v>1</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="M54" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="L54">
+      <c r="N54">
         <v>370</v>
       </c>
-      <c r="M54">
+      <c r="O54">
         <v>370</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -10401,19 +10733,25 @@
         <v>0</v>
       </c>
       <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
         <v>1</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="L55">
+      <c r="N55">
         <v>380</v>
       </c>
-      <c r="M55">
+      <c r="O55">
         <v>380</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -10443,19 +10781,25 @@
         <v>0</v>
       </c>
       <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
         <v>1</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="L56">
+      <c r="N56">
         <v>390</v>
       </c>
-      <c r="M56">
+      <c r="O56">
         <v>390</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:15" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="9">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -10485,19 +10829,25 @@
         <v>0</v>
       </c>
       <c r="J57" s="9">
+        <v>0</v>
+      </c>
+      <c r="K57" s="9">
+        <v>0</v>
+      </c>
+      <c r="L57" s="9">
         <v>1</v>
       </c>
-      <c r="K57" s="10" t="s">
+      <c r="M57" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="L57" s="9">
+      <c r="N57" s="9">
         <v>400</v>
       </c>
-      <c r="M57" s="9">
+      <c r="O57" s="9">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -10527,19 +10877,25 @@
         <v>0</v>
       </c>
       <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
         <v>1</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="L58">
+      <c r="N58">
         <v>410</v>
       </c>
-      <c r="M58">
+      <c r="O58">
         <v>410</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -10569,19 +10925,25 @@
         <v>0</v>
       </c>
       <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
         <v>1</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="M59" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L59">
+      <c r="N59">
         <v>500</v>
       </c>
-      <c r="M59">
+      <c r="O59">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -10611,19 +10973,25 @@
         <v>0</v>
       </c>
       <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
         <v>1</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="L60">
+      <c r="N60">
         <v>510</v>
       </c>
-      <c r="M60">
+      <c r="O60">
         <v>510</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -10653,19 +11021,25 @@
         <v>0</v>
       </c>
       <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
         <v>1</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="M61" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="L61">
+      <c r="N61">
         <v>520</v>
       </c>
-      <c r="M61">
+      <c r="O61">
         <v>520</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -10695,19 +11069,25 @@
         <v>0</v>
       </c>
       <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
         <v>1</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="M62" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="L62">
+      <c r="N62">
         <v>530</v>
       </c>
-      <c r="M62">
+      <c r="O62">
         <v>530</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -10737,19 +11117,25 @@
         <v>0</v>
       </c>
       <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
         <v>1</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="M63" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="L63">
+      <c r="N63">
         <v>540</v>
       </c>
-      <c r="M63">
+      <c r="O63">
         <v>540</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -10779,19 +11165,25 @@
         <v>0</v>
       </c>
       <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
         <v>1</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="M64" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="L64">
+      <c r="N64">
         <v>550</v>
       </c>
-      <c r="M64">
+      <c r="O64">
         <v>550</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -10821,19 +11213,25 @@
         <v>0</v>
       </c>
       <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
         <v>1</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="M65" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="L65">
+      <c r="N65">
         <v>560</v>
       </c>
-      <c r="M65">
+      <c r="O65">
         <v>560</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -10863,19 +11261,25 @@
         <v>0</v>
       </c>
       <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
         <v>1</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="M66" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="L66">
+      <c r="N66">
         <v>570</v>
       </c>
-      <c r="M66">
+      <c r="O66">
         <v>570</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -10905,19 +11309,25 @@
         <v>0</v>
       </c>
       <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
         <v>1</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="M67" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="L67">
+      <c r="N67">
         <v>580</v>
       </c>
-      <c r="M67">
+      <c r="O67">
         <v>580</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -10947,19 +11357,25 @@
         <v>0</v>
       </c>
       <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
         <v>1</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="L68">
+      <c r="N68">
         <v>590</v>
       </c>
-      <c r="M68">
+      <c r="O68">
         <v>590</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:15" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="7">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -10991,17 +11407,23 @@
       <c r="J69" s="7">
         <v>0</v>
       </c>
-      <c r="K69" s="8" t="s">
+      <c r="K69" s="7">
+        <v>0</v>
+      </c>
+      <c r="L69" s="7">
+        <v>0</v>
+      </c>
+      <c r="M69" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="L69" s="7">
+      <c r="N69" s="7">
         <v>600</v>
       </c>
-      <c r="M69" s="7">
+      <c r="O69" s="7">
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>68</v>
@@ -11031,19 +11453,25 @@
         <v>0</v>
       </c>
       <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
         <v>1</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="M70" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="L70">
+      <c r="N70">
         <v>610</v>
       </c>
-      <c r="M70">
+      <c r="O70">
         <v>610</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:15" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="7">
         <f t="shared" si="0"/>
         <v>69</v>
@@ -11075,17 +11503,23 @@
       <c r="J71" s="7">
         <v>0</v>
       </c>
-      <c r="K71" s="8" t="s">
+      <c r="K71" s="7">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7">
+        <v>0</v>
+      </c>
+      <c r="M71" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="L71" s="7">
+      <c r="N71" s="7">
         <v>620</v>
       </c>
-      <c r="M71" s="7">
+      <c r="O71" s="7">
         <v>620</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72">
         <f t="shared" si="0"/>
         <v>70</v>
@@ -11115,19 +11549,25 @@
         <v>0</v>
       </c>
       <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
         <v>1</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="M72" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="L72">
+      <c r="N72">
         <v>700</v>
       </c>
-      <c r="M72">
+      <c r="O72">
         <v>700</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73">
         <f t="shared" si="0"/>
         <v>71</v>
@@ -11157,19 +11597,25 @@
         <v>0</v>
       </c>
       <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
         <v>1</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="M73" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="L73">
+      <c r="N73">
         <v>710</v>
       </c>
-      <c r="M73">
+      <c r="O73">
         <v>710</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74">
         <f t="shared" si="0"/>
         <v>72</v>
@@ -11199,19 +11645,25 @@
         <v>0</v>
       </c>
       <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
         <v>1</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="M74" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="L74">
+      <c r="N74">
         <v>720</v>
       </c>
-      <c r="M74">
+      <c r="O74">
         <v>720</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>73</v>
@@ -11241,19 +11693,25 @@
         <v>0</v>
       </c>
       <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
         <v>1</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="M75" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L75">
+      <c r="N75">
         <v>730</v>
       </c>
-      <c r="M75">
+      <c r="O75">
         <v>730</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>74</v>
@@ -11283,19 +11741,25 @@
         <v>0</v>
       </c>
       <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
         <v>1</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="M76" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="L76">
+      <c r="N76">
         <v>740</v>
       </c>
-      <c r="M76">
+      <c r="O76">
         <v>740</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>75</v>
@@ -11325,19 +11789,25 @@
         <v>0</v>
       </c>
       <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
         <v>1</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="M77" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="L77">
+      <c r="N77">
         <v>750</v>
       </c>
-      <c r="M77">
+      <c r="O77">
         <v>750</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>76</v>
@@ -11367,19 +11837,25 @@
         <v>0</v>
       </c>
       <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
         <v>1</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="L78">
+      <c r="N78">
         <v>760</v>
       </c>
-      <c r="M78">
+      <c r="O78">
         <v>760</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79">
         <f t="shared" si="0"/>
         <v>77</v>
@@ -11409,19 +11885,25 @@
         <v>0</v>
       </c>
       <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
         <v>1</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="L79">
+      <c r="N79">
         <v>770</v>
       </c>
-      <c r="M79">
+      <c r="O79">
         <v>770</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80">
         <f t="shared" si="0"/>
         <v>78</v>
@@ -11451,19 +11933,25 @@
         <v>0</v>
       </c>
       <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
         <v>1</v>
       </c>
-      <c r="K80" s="2" t="s">
+      <c r="M80" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="L80">
+      <c r="N80">
         <v>780</v>
       </c>
-      <c r="M80">
+      <c r="O80">
         <v>780</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:15" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="7">
         <f t="shared" si="0"/>
         <v>79</v>
@@ -11495,17 +11983,23 @@
       <c r="J81" s="7">
         <v>0</v>
       </c>
-      <c r="K81" s="8" t="s">
+      <c r="K81" s="7">
+        <v>0</v>
+      </c>
+      <c r="L81" s="7">
+        <v>0</v>
+      </c>
+      <c r="M81" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="L81" s="7">
+      <c r="N81" s="7">
         <v>790</v>
       </c>
-      <c r="M81" s="7">
+      <c r="O81" s="7">
         <v>790</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:15" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="11">
         <f t="shared" si="0"/>
         <v>80</v>
@@ -11537,17 +12031,23 @@
       <c r="J82" s="11">
         <v>0</v>
       </c>
-      <c r="K82" s="12" t="s">
+      <c r="K82" s="11">
+        <v>0</v>
+      </c>
+      <c r="L82" s="11">
+        <v>0</v>
+      </c>
+      <c r="M82" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="L82" s="11">
+      <c r="N82" s="11">
         <v>9999</v>
       </c>
-      <c r="M82" s="11">
+      <c r="O82" s="11">
         <v>9999</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83">
         <f t="shared" si="0"/>
         <v>81</v>
@@ -11577,19 +12077,25 @@
         <v>0</v>
       </c>
       <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
         <v>1</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="M83" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="L83">
+      <c r="N83">
         <v>2000</v>
       </c>
-      <c r="M83">
+      <c r="O83">
         <v>2000</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84">
         <f t="shared" si="0"/>
         <v>82</v>
@@ -11619,19 +12125,25 @@
         <v>0</v>
       </c>
       <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
         <v>1</v>
       </c>
-      <c r="K84" s="2" t="s">
+      <c r="M84" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="L84">
+      <c r="N84">
         <v>2100</v>
       </c>
-      <c r="M84">
+      <c r="O84">
         <v>2100</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85">
         <f t="shared" si="0"/>
         <v>83</v>
@@ -11661,19 +12173,25 @@
         <v>0</v>
       </c>
       <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
         <v>1</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="M85" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="L85">
+      <c r="N85">
         <v>2200</v>
       </c>
-      <c r="M85">
+      <c r="O85">
         <v>2200</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86">
         <f t="shared" si="0"/>
         <v>84</v>
@@ -11703,19 +12221,25 @@
         <v>0</v>
       </c>
       <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
         <v>1</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="M86" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="L86">
+      <c r="N86">
         <v>2300</v>
       </c>
-      <c r="M86">
+      <c r="O86">
         <v>2300</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87">
         <f t="shared" si="0"/>
         <v>85</v>
@@ -11745,19 +12269,25 @@
         <v>0</v>
       </c>
       <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
         <v>1</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="M87" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="L87">
+      <c r="N87">
         <v>2400</v>
       </c>
-      <c r="M87">
+      <c r="O87">
         <v>2400</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88">
         <f t="shared" si="0"/>
         <v>86</v>
@@ -11789,17 +12319,23 @@
       <c r="J88">
         <v>0</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="L88">
+      <c r="N88">
         <v>5000</v>
       </c>
-      <c r="M88">
+      <c r="O88">
         <v>5000</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89">
         <f t="shared" si="0"/>
         <v>87</v>
@@ -11831,17 +12367,23 @@
       <c r="J89">
         <v>0</v>
       </c>
-      <c r="K89" s="2" t="s">
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="L89">
+      <c r="N89">
         <v>5000</v>
       </c>
-      <c r="M89">
+      <c r="O89">
         <v>5000</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90">
         <f t="shared" si="0"/>
         <v>88</v>
@@ -11873,17 +12415,23 @@
       <c r="J90">
         <v>0</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L90">
+      <c r="N90">
         <v>5000</v>
       </c>
-      <c r="M90">
+      <c r="O90">
         <v>5000</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91">
         <f t="shared" si="0"/>
         <v>89</v>
@@ -11915,17 +12463,23 @@
       <c r="J91">
         <v>0</v>
       </c>
-      <c r="K91" s="2" t="s">
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="L91">
+      <c r="N91">
         <v>5000</v>
       </c>
-      <c r="M91">
+      <c r="O91">
         <v>5000</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92">
         <f t="shared" si="0"/>
         <v>90</v>
@@ -11957,17 +12511,23 @@
       <c r="J92">
         <v>0</v>
       </c>
-      <c r="K92" s="2" t="s">
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="L92">
+      <c r="N92">
         <v>5000</v>
       </c>
-      <c r="M92">
+      <c r="O92">
         <v>5000</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93">
         <f t="shared" si="0"/>
         <v>91</v>
@@ -11999,17 +12559,23 @@
       <c r="J93">
         <v>0</v>
       </c>
-      <c r="K93" s="2" t="s">
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="L93">
+      <c r="N93">
         <v>5000</v>
       </c>
-      <c r="M93">
+      <c r="O93">
         <v>5000</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94">
         <f t="shared" si="0"/>
         <v>92</v>
@@ -12041,17 +12607,23 @@
       <c r="J94">
         <v>0</v>
       </c>
-      <c r="K94" s="2" t="s">
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="L94">
+      <c r="N94">
         <v>5000</v>
       </c>
-      <c r="M94">
+      <c r="O94">
         <v>5000</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95">
         <f t="shared" si="0"/>
         <v>93</v>
@@ -12083,17 +12655,23 @@
       <c r="J95">
         <v>0</v>
       </c>
-      <c r="K95" s="2" t="s">
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="L95">
+      <c r="N95">
         <v>5000</v>
       </c>
-      <c r="M95">
+      <c r="O95">
         <v>5000</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96">
         <f t="shared" si="0"/>
         <v>94</v>
@@ -12125,17 +12703,23 @@
       <c r="J96">
         <v>0</v>
       </c>
-      <c r="K96" s="2" t="s">
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L96">
+      <c r="N96">
         <v>5000</v>
       </c>
-      <c r="M96">
+      <c r="O96">
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97">
         <f t="shared" si="0"/>
         <v>95</v>
@@ -12167,17 +12751,23 @@
       <c r="J97">
         <v>0</v>
       </c>
-      <c r="K97" s="2" t="s">
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="L97">
+      <c r="N97">
         <v>5000</v>
       </c>
-      <c r="M97">
+      <c r="O97">
         <v>5000</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98">
         <f t="shared" si="0"/>
         <v>96</v>
@@ -12209,17 +12799,23 @@
       <c r="J98">
         <v>0</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L98">
+      <c r="N98">
         <v>5000</v>
       </c>
-      <c r="M98">
+      <c r="O98">
         <v>5000</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99">
         <f t="shared" si="0"/>
         <v>97</v>
@@ -12251,17 +12847,23 @@
       <c r="J99">
         <v>0</v>
       </c>
-      <c r="K99" s="2" t="s">
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L99">
+      <c r="N99">
         <v>5000</v>
       </c>
-      <c r="M99">
+      <c r="O99">
         <v>5000</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100">
         <f t="shared" si="0"/>
         <v>98</v>
@@ -12293,17 +12895,23 @@
       <c r="J100">
         <v>0</v>
       </c>
-      <c r="K100" s="2" t="s">
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L100">
+      <c r="N100">
         <v>5000</v>
       </c>
-      <c r="M100">
+      <c r="O100">
         <v>5000</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101">
         <f t="shared" si="0"/>
         <v>99</v>
@@ -12335,17 +12943,23 @@
       <c r="J101">
         <v>0</v>
       </c>
-      <c r="K101" s="2" t="s">
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L101">
+      <c r="N101">
         <v>5000</v>
       </c>
-      <c r="M101">
+      <c r="O101">
         <v>5000</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102">
         <f t="shared" si="0"/>
         <v>100</v>
@@ -12377,17 +12991,23 @@
       <c r="J102">
         <v>0</v>
       </c>
-      <c r="K102" s="2" t="s">
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="L102">
+      <c r="N102">
         <v>5000</v>
       </c>
-      <c r="M102">
+      <c r="O102">
         <v>5000</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103">
         <f t="shared" si="0"/>
         <v>101</v>
@@ -12419,17 +13039,23 @@
       <c r="J103">
         <v>0</v>
       </c>
-      <c r="K103" s="2" t="s">
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="L103">
+      <c r="N103">
         <v>5000</v>
       </c>
-      <c r="M103">
+      <c r="O103">
         <v>5000</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104">
         <f t="shared" si="0"/>
         <v>102</v>
@@ -12461,17 +13087,23 @@
       <c r="J104">
         <v>0</v>
       </c>
-      <c r="K104" s="2" t="s">
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L104">
+      <c r="N104">
         <v>5000</v>
       </c>
-      <c r="M104">
+      <c r="O104">
         <v>5000</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105">
         <f t="shared" si="0"/>
         <v>103</v>
@@ -12503,17 +13135,23 @@
       <c r="J105">
         <v>0</v>
       </c>
-      <c r="K105" s="2" t="s">
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L105">
+      <c r="N105">
         <v>5000</v>
       </c>
-      <c r="M105">
+      <c r="O105">
         <v>5000</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -12545,17 +13183,23 @@
       <c r="J106">
         <v>0</v>
       </c>
-      <c r="K106" s="2" t="s">
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="L106">
+      <c r="N106">
         <v>5000</v>
       </c>
-      <c r="M106">
+      <c r="O106">
         <v>5000</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107">
         <f t="shared" si="0"/>
         <v>105</v>
@@ -12587,17 +13231,23 @@
       <c r="J107">
         <v>0</v>
       </c>
-      <c r="K107" s="2" t="s">
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="L107">
+      <c r="N107">
         <v>5000</v>
       </c>
-      <c r="M107">
+      <c r="O107">
         <v>5000</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -12629,17 +13279,23 @@
       <c r="J108">
         <v>0</v>
       </c>
-      <c r="K108" s="2" t="s">
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L108">
+      <c r="N108">
         <v>5000</v>
       </c>
-      <c r="M108">
+      <c r="O108">
         <v>5000</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109">
         <f t="shared" si="0"/>
         <v>107</v>
@@ -12671,17 +13327,23 @@
       <c r="J109">
         <v>0</v>
       </c>
-      <c r="K109" s="2" t="s">
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="L109">
+      <c r="N109">
         <v>5000</v>
       </c>
-      <c r="M109">
+      <c r="O109">
         <v>5000</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110">
         <f t="shared" si="0"/>
         <v>108</v>
@@ -12713,17 +13375,23 @@
       <c r="J110">
         <v>0</v>
       </c>
-      <c r="K110" s="2" t="s">
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L110">
+      <c r="N110">
         <v>5000</v>
       </c>
-      <c r="M110">
+      <c r="O110">
         <v>5000</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -12755,17 +13423,23 @@
       <c r="J111">
         <v>0</v>
       </c>
-      <c r="K111" s="2" t="s">
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L111">
+      <c r="N111">
         <v>5000</v>
       </c>
-      <c r="M111">
+      <c r="O111">
         <v>5000</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -12797,17 +13471,23 @@
       <c r="J112">
         <v>0</v>
       </c>
-      <c r="K112" s="2" t="s">
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="L112">
+      <c r="N112">
         <v>5000</v>
       </c>
-      <c r="M112">
+      <c r="O112">
         <v>5000</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -12839,17 +13519,23 @@
       <c r="J113">
         <v>0</v>
       </c>
-      <c r="K113" s="2" t="s">
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L113">
+      <c r="N113">
         <v>5000</v>
       </c>
-      <c r="M113">
+      <c r="O113">
         <v>5000</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -12881,17 +13567,23 @@
       <c r="J114">
         <v>0</v>
       </c>
-      <c r="K114" s="2" t="s">
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="L114">
+      <c r="N114">
         <v>5000</v>
       </c>
-      <c r="M114">
+      <c r="O114">
         <v>5000</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115">
         <f t="shared" si="0"/>
         <v>113</v>
@@ -12923,17 +13615,23 @@
       <c r="J115">
         <v>0</v>
       </c>
-      <c r="K115" s="2" t="s">
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="L115">
+      <c r="N115">
         <v>5000</v>
       </c>
-      <c r="M115">
+      <c r="O115">
         <v>5000</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116">
         <f t="shared" si="0"/>
         <v>114</v>
@@ -12965,17 +13663,23 @@
       <c r="J116">
         <v>0</v>
       </c>
-      <c r="K116" s="2" t="s">
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L116">
+      <c r="N116">
         <v>5000</v>
       </c>
-      <c r="M116">
+      <c r="O116">
         <v>5000</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -13007,17 +13711,23 @@
       <c r="J117">
         <v>0</v>
       </c>
-      <c r="K117" s="2" t="s">
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L117">
+      <c r="N117">
         <v>5000</v>
       </c>
-      <c r="M117">
+      <c r="O117">
         <v>5000</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118">
         <f t="shared" si="0"/>
         <v>116</v>
@@ -13049,17 +13759,23 @@
       <c r="J118">
         <v>0</v>
       </c>
-      <c r="K118" s="2" t="s">
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="L118">
+      <c r="N118">
         <v>5000</v>
       </c>
-      <c r="M118">
+      <c r="O118">
         <v>5000</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119">
         <f t="shared" si="0"/>
         <v>117</v>
@@ -13091,17 +13807,23 @@
       <c r="J119">
         <v>0</v>
       </c>
-      <c r="K119" s="2" t="s">
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L119">
+      <c r="N119">
         <v>5000</v>
       </c>
-      <c r="M119">
+      <c r="O119">
         <v>5000</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120">
         <f t="shared" si="0"/>
         <v>118</v>
@@ -13133,17 +13855,23 @@
       <c r="J120">
         <v>0</v>
       </c>
-      <c r="K120" s="2" t="s">
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="L120">
+      <c r="N120">
         <v>5000</v>
       </c>
-      <c r="M120">
+      <c r="O120">
         <v>5000</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121">
         <f t="shared" si="0"/>
         <v>119</v>
@@ -13175,17 +13903,23 @@
       <c r="J121">
         <v>0</v>
       </c>
-      <c r="K121" s="2" t="s">
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="L121">
+      <c r="N121">
         <v>5000</v>
       </c>
-      <c r="M121">
+      <c r="O121">
         <v>5000</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122">
         <f t="shared" si="0"/>
         <v>120</v>
@@ -13217,17 +13951,23 @@
       <c r="J122">
         <v>0</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="L122">
+      <c r="N122">
         <v>5000</v>
       </c>
-      <c r="M122">
+      <c r="O122">
         <v>5000</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123">
         <f t="shared" si="0"/>
         <v>121</v>
@@ -13259,17 +13999,23 @@
       <c r="J123">
         <v>0</v>
       </c>
-      <c r="K123" s="2" t="s">
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="L123">
+      <c r="N123">
         <v>5000</v>
       </c>
-      <c r="M123">
+      <c r="O123">
         <v>5000</v>
       </c>
     </row>
-    <row r="124" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="13">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -13301,17 +14047,23 @@
       <c r="J124" s="13">
         <v>0</v>
       </c>
-      <c r="K124" s="14" t="s">
+      <c r="K124" s="13">
+        <v>0</v>
+      </c>
+      <c r="L124" s="13">
+        <v>0</v>
+      </c>
+      <c r="M124" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L124" s="13">
+      <c r="N124" s="13">
         <v>5000</v>
       </c>
-      <c r="M124" s="13">
+      <c r="O124" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="125" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="13">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -13343,17 +14095,23 @@
       <c r="J125" s="13">
         <v>0</v>
       </c>
-      <c r="K125" s="14" t="s">
+      <c r="K125" s="13">
+        <v>0</v>
+      </c>
+      <c r="L125" s="13">
+        <v>0</v>
+      </c>
+      <c r="M125" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L125" s="13">
+      <c r="N125" s="13">
         <v>5000</v>
       </c>
-      <c r="M125" s="13">
+      <c r="O125" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="126" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="13">
         <f t="shared" si="0"/>
         <v>124</v>
@@ -13385,17 +14143,23 @@
       <c r="J126" s="13">
         <v>0</v>
       </c>
-      <c r="K126" s="14" t="s">
+      <c r="K126" s="13">
+        <v>0</v>
+      </c>
+      <c r="L126" s="13">
+        <v>0</v>
+      </c>
+      <c r="M126" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="L126" s="13">
+      <c r="N126" s="13">
         <v>5000</v>
       </c>
-      <c r="M126" s="13">
+      <c r="O126" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -13427,17 +14191,23 @@
       <c r="J127">
         <v>0</v>
       </c>
-      <c r="K127" s="2" t="s">
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="L127">
+      <c r="N127">
         <v>5000</v>
       </c>
-      <c r="M127">
+      <c r="O127">
         <v>5000</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -13469,17 +14239,23 @@
       <c r="J128">
         <v>0</v>
       </c>
-      <c r="K128" s="2" t="s">
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="L128">
+      <c r="N128">
         <v>5000</v>
       </c>
-      <c r="M128">
+      <c r="O128">
         <v>5000</v>
       </c>
     </row>
-    <row r="129" spans="1:13" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="13">
         <f t="shared" si="0"/>
         <v>127</v>
@@ -13511,17 +14287,23 @@
       <c r="J129" s="13">
         <v>0</v>
       </c>
-      <c r="K129" s="14" t="s">
+      <c r="K129" s="13">
+        <v>0</v>
+      </c>
+      <c r="L129" s="13">
+        <v>0</v>
+      </c>
+      <c r="M129" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="L129" s="13">
+      <c r="N129" s="13">
         <v>5000</v>
       </c>
-      <c r="M129" s="13">
+      <c r="O129" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -13553,17 +14335,23 @@
       <c r="J130">
         <v>0</v>
       </c>
-      <c r="K130" s="2" t="s">
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="L130">
+      <c r="N130">
         <v>5000</v>
       </c>
-      <c r="M130">
+      <c r="O130">
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131">
         <f>ROW()-2</f>
         <v>129</v>
@@ -13595,17 +14383,23 @@
       <c r="J131">
         <v>0</v>
       </c>
-      <c r="K131" t="s">
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" t="s">
         <v>444</v>
       </c>
-      <c r="L131">
+      <c r="N131">
         <v>9999</v>
       </c>
-      <c r="M131">
+      <c r="O131">
         <v>9999</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>10000</v>
       </c>
@@ -13634,15 +14428,21 @@
         <v>0</v>
       </c>
       <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
         <v>1</v>
       </c>
-      <c r="K132" s="2" t="s">
+      <c r="M132" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="L132">
+      <c r="N132">
         <v>9000</v>
       </c>
-      <c r="M132">
+      <c r="O132">
         <v>9000</v>
       </c>
     </row>
@@ -13655,7 +14455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94BD5E9F-9099-4495-A12D-C6B76FFF933E}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -13665,14 +14465,14 @@
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="7.75" customWidth="1"/>
     <col min="7" max="7" width="4.625" customWidth="1"/>
-    <col min="8" max="9" width="7.5" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="11" max="11" width="26.75" customWidth="1"/>
-    <col min="12" max="12" width="9.875" customWidth="1"/>
-    <col min="13" max="13" width="10.125" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="10.375" customWidth="1"/>
+    <col min="13" max="13" width="26.75" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
+    <col min="15" max="15" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -13701,19 +14501,25 @@
         <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f t="shared" ref="A2:A15" si="0">ROW()-2</f>
         <v>0</v>
@@ -13743,19 +14549,25 @@
         <v>1</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>102</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>9999</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>9999</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -13787,17 +14599,23 @@
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
         <v>81</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>9999</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>9999</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -13827,19 +14645,25 @@
         <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>81</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>9999</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>9999</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -13869,19 +14693,25 @@
         <v>1</v>
       </c>
       <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>81</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>9999</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>9999</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -13911,19 +14741,25 @@
         <v>1</v>
       </c>
       <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>81</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>9999</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>9999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -13950,22 +14786,28 @@
         <v>0</v>
       </c>
       <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>82</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>9999</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>9999</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -13992,22 +14834,28 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
+        <v>101</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
         <v>82</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>9999</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>9999</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -14034,22 +14882,28 @@
         <v>0</v>
       </c>
       <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>102</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>1</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>82</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>9999</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>9999</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -14076,22 +14930,28 @@
         <v>0</v>
       </c>
       <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>103</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>82</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>9999</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>9999</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -14118,22 +14978,28 @@
         <v>0</v>
       </c>
       <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>104</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>1</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>82</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>9999</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>9999</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -14160,22 +15026,28 @@
         <v>0</v>
       </c>
       <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>105</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>82</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>9999</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>9999</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -14202,22 +15074,28 @@
         <v>0</v>
       </c>
       <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>106</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>1</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>82</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>9999</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>9999</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -14244,22 +15122,28 @@
         <v>0</v>
       </c>
       <c r="I14" s="4">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4">
+        <v>107</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
         <v>1</v>
       </c>
-      <c r="J14" s="4">
-        <v>1</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="M14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="L14" s="4">
+      <c r="N14" s="4">
         <v>9999</v>
       </c>
-      <c r="M14" s="4">
+      <c r="O14" s="4">
         <v>9999</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -14286,18 +15170,24 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>1</v>
       </c>
-      <c r="K15" t="s">
+      <c r="M15" t="s">
         <v>70</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>9999</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>9999</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F03584-EB1F-49EC-98B8-A1FAE7492D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA1FCA3-17DF-4955-B4E9-303F3CBB3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2070" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -1390,44 +1390,6 @@
     </rPh>
     <rPh sb="399" eb="400">
       <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【クッキーのレシピ＜上級＞】
-☆全てのクッキーのための本☆
-・チーズクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;クリームチーズ&lt;/color&gt;
-・はちみつクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;はちみつ&lt;/color&gt;をかけて焼く。
-・ほしのクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;スターチップシュガー&lt;/color&gt;をトッピング！
-それぞれ仕上げで入れてみると.. おいしいクッキーが出来上がるよ！
-【コラム】
-・お店のキラキラトッピング5種類とさくらの花びらで、クッキーが作れるよ。
-【コラム２　やばいクッキー】
-・クッキーの仕上げに、へんな草やむらさキノコを入れると..　。
-</t>
-    <rPh sb="10" eb="12">
-      <t>ジョウキュウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="257" eb="258">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="276" eb="277">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="286" eb="287">
-      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7629,6 +7591,47 @@
   </si>
   <si>
     <t>cos_Equip</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【クッキーのレシピ＜上級＞】
+☆全てのクッキーのための本☆
+・チーズクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;クリームチーズ&lt;/color&gt;
+・はちみつクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;はちみつ&lt;/color&gt;をかけて焼く。
+・ほしのクッキー　・・・　クッキーの砂糖を&lt;color=#BA9535FF&gt;スターチップシュガー&lt;/color&gt;に変えると・・。
+・ラベンダークッキー　・・・　クッキーの砂糖を&lt;color=#BA9535FF&gt;ラベンダーシュガー&lt;/color&gt;に変えると・・。
+【コラム】
+・お店のキラキラトッピング5種類で、クッキーが作れるよ。
+【コラム２　やばいクッキー】
+・クッキーの仕上げに、へんな草やむらさキノコを入れると..　。
+</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウキュウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="166" eb="168">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="205" eb="206">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="289" eb="290">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="310" eb="311">
+      <t>ツク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8141,10 +8144,10 @@
         <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8246,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8390,7 +8393,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -8411,7 +8414,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8438,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -8582,7 +8585,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N10">
         <v>3070</v>
@@ -8630,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>179</v>
+        <v>492</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -8648,10 +8651,10 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E12">
         <v>500</v>
@@ -8678,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N12">
         <v>3090</v>
@@ -8696,10 +8699,10 @@
         <v>172</v>
       </c>
       <c r="C13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" t="s">
         <v>184</v>
-      </c>
-      <c r="D13" t="s">
-        <v>185</v>
       </c>
       <c r="E13">
         <v>500</v>
@@ -8726,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N13">
         <v>3100</v>
@@ -8744,10 +8747,10 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -8774,7 +8777,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -8792,10 +8795,10 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -8822,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -8840,10 +8843,10 @@
         <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D16" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E16">
         <v>500</v>
@@ -8870,7 +8873,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N16">
         <v>3130</v>
@@ -8888,10 +8891,10 @@
         <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -8918,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9158,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N22">
         <v>20</v>
@@ -9206,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N23">
         <v>30</v>
@@ -9302,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N25">
         <v>50</v>
@@ -9494,7 +9497,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N29">
         <v>90</v>
@@ -9686,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N33">
         <v>130</v>
@@ -9701,13 +9704,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C34" t="s">
+        <v>454</v>
+      </c>
+      <c r="D34" t="s">
         <v>455</v>
-      </c>
-      <c r="D34" t="s">
-        <v>456</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9734,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N34">
         <v>150</v>
@@ -10166,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N43">
         <v>270</v>
@@ -10214,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N44">
         <v>280</v>
@@ -10229,13 +10232,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -10262,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N45">
         <v>290</v>
@@ -10277,13 +10280,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -10310,7 +10313,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N46">
         <v>300</v>
@@ -10325,13 +10328,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E47" s="5">
         <v>500</v>
@@ -10358,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N47" s="5">
         <v>9999</v>
@@ -10373,13 +10376,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -10406,7 +10409,7 @@
         <v>1</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N48">
         <v>310</v>
@@ -10421,13 +10424,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -10454,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N49">
         <v>320</v>
@@ -10469,13 +10472,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10502,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N50">
         <v>330</v>
@@ -10517,13 +10520,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D51" t="s">
         <v>208</v>
-      </c>
-      <c r="D51" t="s">
-        <v>209</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10550,7 +10553,7 @@
         <v>1</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N51">
         <v>340</v>
@@ -10565,13 +10568,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C52" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10598,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N52">
         <v>350</v>
@@ -10613,13 +10616,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -10646,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N53">
         <v>360</v>
@@ -10661,13 +10664,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C54" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D54" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -10694,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N54">
         <v>370</v>
@@ -10709,13 +10712,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C55" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D55" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -10742,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N55">
         <v>380</v>
@@ -10757,13 +10760,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -10790,7 +10793,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N56">
         <v>390</v>
@@ -10805,13 +10808,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C57" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="E57" s="9">
         <v>500</v>
@@ -10838,7 +10841,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N57" s="9">
         <v>400</v>
@@ -10853,13 +10856,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -10886,7 +10889,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N58">
         <v>410</v>
@@ -10901,13 +10904,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -10934,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N59">
         <v>500</v>
@@ -10949,13 +10952,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -10982,7 +10985,7 @@
         <v>1</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N60">
         <v>510</v>
@@ -10997,13 +11000,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C61" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -11030,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N61">
         <v>520</v>
@@ -11045,13 +11048,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C62" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -11078,7 +11081,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N62">
         <v>530</v>
@@ -11093,13 +11096,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D63" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -11126,7 +11129,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N63">
         <v>540</v>
@@ -11141,13 +11144,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C64" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D64" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11174,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N64">
         <v>550</v>
@@ -11189,13 +11192,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E65">
         <v>500</v>
@@ -11222,7 +11225,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N65">
         <v>560</v>
@@ -11237,13 +11240,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D66" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -11270,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N66">
         <v>570</v>
@@ -11285,13 +11288,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C67" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E67">
         <v>500</v>
@@ -11318,7 +11321,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N67">
         <v>580</v>
@@ -11333,13 +11336,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -11366,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N68">
         <v>590</v>
@@ -11381,13 +11384,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E69" s="7">
         <v>500</v>
@@ -11414,7 +11417,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N69" s="7">
         <v>600</v>
@@ -11429,13 +11432,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D70" t="s">
         <v>237</v>
-      </c>
-      <c r="D70" t="s">
-        <v>238</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -11462,7 +11465,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N70">
         <v>610</v>
@@ -11477,13 +11480,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E71" s="7">
         <v>500</v>
@@ -11510,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N71" s="7">
         <v>620</v>
@@ -11525,13 +11528,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C72" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D72" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -11558,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N72">
         <v>700</v>
@@ -11573,13 +11576,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E73">
         <v>500</v>
@@ -11606,7 +11609,7 @@
         <v>1</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N73">
         <v>710</v>
@@ -11621,13 +11624,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -11654,7 +11657,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N74">
         <v>720</v>
@@ -11669,13 +11672,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C75" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D75" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -11702,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N75">
         <v>730</v>
@@ -11717,13 +11720,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76" t="s">
         <v>245</v>
-      </c>
-      <c r="D76" t="s">
-        <v>246</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -11750,7 +11753,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N76">
         <v>740</v>
@@ -11765,13 +11768,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C77" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D77" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -11798,7 +11801,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N77">
         <v>750</v>
@@ -11813,13 +11816,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C78" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -11846,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N78">
         <v>760</v>
@@ -11861,13 +11864,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C79" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D79" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E79">
         <v>500</v>
@@ -11894,7 +11897,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N79">
         <v>770</v>
@@ -11909,13 +11912,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C80" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D80" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -11942,7 +11945,7 @@
         <v>1</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N80">
         <v>780</v>
@@ -11957,13 +11960,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E81" s="7">
         <v>500</v>
@@ -11990,7 +11993,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N81" s="7">
         <v>790</v>
@@ -12005,13 +12008,13 @@
         <v>80</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E82" s="11">
         <v>500</v>
@@ -12038,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N82" s="11">
         <v>9999</v>
@@ -12053,13 +12056,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C83" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D83" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E83">
         <v>500</v>
@@ -12086,7 +12089,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N83">
         <v>2000</v>
@@ -12101,13 +12104,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C84" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D84" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12134,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N84">
         <v>2100</v>
@@ -12149,13 +12152,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C85" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D85" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -12182,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N85">
         <v>2200</v>
@@ -12197,13 +12200,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C86" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12230,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N86">
         <v>2300</v>
@@ -12245,13 +12248,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C87" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D87" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12278,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N87">
         <v>2400</v>
@@ -12293,13 +12296,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C88" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D88" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12326,7 +12329,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N88">
         <v>5000</v>
@@ -12341,13 +12344,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C89" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D89" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12374,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N89">
         <v>5000</v>
@@ -12389,13 +12392,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C90" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D90" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12422,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N90">
         <v>5000</v>
@@ -12437,13 +12440,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C91" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D91" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12470,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12485,13 +12488,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C92" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12518,7 +12521,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12533,13 +12536,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C93" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D93" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12566,7 +12569,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12581,13 +12584,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C94" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D94" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12614,7 +12617,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12629,13 +12632,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C95" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D95" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -12662,7 +12665,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -12677,13 +12680,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C96" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D96" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12710,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -12725,13 +12728,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C97" t="s">
+        <v>282</v>
+      </c>
+      <c r="D97" t="s">
         <v>283</v>
-      </c>
-      <c r="D97" t="s">
-        <v>284</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -12758,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -12773,13 +12776,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C98" t="s">
+        <v>322</v>
+      </c>
+      <c r="D98" t="s">
         <v>323</v>
-      </c>
-      <c r="D98" t="s">
-        <v>324</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12806,7 +12809,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -12821,13 +12824,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C99" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D99" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12854,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -12869,13 +12872,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C100" t="s">
+        <v>315</v>
+      </c>
+      <c r="D100" t="s">
         <v>316</v>
-      </c>
-      <c r="D100" t="s">
-        <v>317</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -12902,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -12917,13 +12920,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C101" t="s">
+        <v>328</v>
+      </c>
+      <c r="D101" t="s">
         <v>329</v>
-      </c>
-      <c r="D101" t="s">
-        <v>330</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12950,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -12965,13 +12968,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D102" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -12998,7 +13001,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13013,13 +13016,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13046,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13061,13 +13064,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C104" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D104" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13094,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13109,13 +13112,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C105" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D105" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13142,7 +13145,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13157,13 +13160,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C106" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D106" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13190,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13205,13 +13208,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C107" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D107" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13238,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13253,13 +13256,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C108" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D108" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13286,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13301,13 +13304,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C109" t="s">
+        <v>285</v>
+      </c>
+      <c r="D109" t="s">
         <v>286</v>
-      </c>
-      <c r="D109" t="s">
-        <v>287</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13334,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13349,13 +13352,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C110" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D110" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13382,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13397,13 +13400,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C111" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D111" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13430,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13445,13 +13448,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C112" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D112" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13478,7 +13481,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13493,13 +13496,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C113" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D113" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13526,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13541,13 +13544,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C114" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D114" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13574,7 +13577,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13589,13 +13592,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C115" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D115" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13622,7 +13625,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13637,13 +13640,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C116" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D116" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -13670,7 +13673,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -13685,13 +13688,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C117" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D117" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -13718,7 +13721,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -13733,13 +13736,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C118" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D118" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -13766,7 +13769,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -13781,13 +13784,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C119" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D119" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -13814,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -13829,13 +13832,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s">
+        <v>317</v>
+      </c>
+      <c r="D120" t="s">
         <v>318</v>
-      </c>
-      <c r="D120" t="s">
-        <v>319</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -13862,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -13877,13 +13880,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C121" t="s">
+        <v>310</v>
+      </c>
+      <c r="D121" t="s">
         <v>311</v>
-      </c>
-      <c r="D121" t="s">
-        <v>312</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -13910,7 +13913,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -13925,13 +13928,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C122" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D122" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -13958,7 +13961,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -13973,13 +13976,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C123" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D123" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14006,7 +14009,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14021,13 +14024,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E124" s="13">
         <v>500</v>
@@ -14054,7 +14057,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N124" s="13">
         <v>5000</v>
@@ -14069,13 +14072,13 @@
         <v>123</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E125" s="13">
         <v>500</v>
@@ -14102,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N125" s="13">
         <v>5000</v>
@@ -14117,13 +14120,13 @@
         <v>124</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E126" s="13">
         <v>500</v>
@@ -14150,7 +14153,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N126" s="13">
         <v>5000</v>
@@ -14165,13 +14168,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C127" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D127" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14198,7 +14201,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14213,13 +14216,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C128" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D128" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14246,7 +14249,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14261,13 +14264,13 @@
         <v>127</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E129" s="13">
         <v>500</v>
@@ -14294,7 +14297,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N129" s="13">
         <v>5000</v>
@@ -14309,13 +14312,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C130" t="s">
+        <v>312</v>
+      </c>
+      <c r="D130" t="s">
         <v>313</v>
-      </c>
-      <c r="D130" t="s">
-        <v>314</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14342,7 +14345,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14357,13 +14360,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C131" t="s">
+        <v>441</v>
+      </c>
+      <c r="D131" t="s">
         <v>442</v>
-      </c>
-      <c r="D131" t="s">
-        <v>443</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -14390,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N131">
         <v>9999</v>
@@ -14501,10 +14504,10 @@
         <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15104,10 +15107,10 @@
         <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA1FCA3-17DF-4955-B4E9-303F3CBB3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C231A98-9445-435E-A0E6-12F2B1B0C429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3570" yWindow="1020" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="497">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7632,6 +7632,32 @@
     <rPh sb="310" eb="311">
       <t>ツク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>house_for_noisette_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ふたりのおうちのレシピメモ】
+ヒカリがいうには、
+&lt;color=#BA9535FF&gt;くまさんチョコレートのおにいさんといもうと&lt;/color&gt;を、
+おかしのおうちに、&lt;color=#FF5CA1FF&gt;一緒に&lt;/color&gt;のせると、
+すごいお菓子ができる.. かもしれない。</t>
+    <rPh sb="104" eb="106">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ふたりのおうちのレシピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/memo</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7740,7 +7766,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7782,6 +7808,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8098,7 +8130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8164,7 +8196,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A130" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A131" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -12002,100 +12034,100 @@
         <v>790</v>
       </c>
     </row>
-    <row r="82" spans="1:15" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="11">
+    <row r="82" spans="1:15" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="15">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B82" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="E82" s="11">
+      <c r="B82" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="E82" s="15">
         <v>500</v>
       </c>
-      <c r="F82" s="11">
+      <c r="F82" s="15">
         <v>150</v>
       </c>
-      <c r="G82" s="11">
-        <v>0</v>
-      </c>
-      <c r="H82" s="11">
-        <v>0</v>
-      </c>
-      <c r="I82" s="11">
-        <v>0</v>
-      </c>
-      <c r="J82" s="11">
-        <v>0</v>
-      </c>
-      <c r="K82" s="11">
-        <v>0</v>
-      </c>
-      <c r="L82" s="11">
-        <v>0</v>
-      </c>
-      <c r="M82" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="N82" s="11">
+      <c r="G82" s="15">
+        <v>0</v>
+      </c>
+      <c r="H82" s="15">
+        <v>1</v>
+      </c>
+      <c r="I82" s="15">
+        <v>0</v>
+      </c>
+      <c r="J82" s="15">
+        <v>0</v>
+      </c>
+      <c r="K82" s="15">
+        <v>0</v>
+      </c>
+      <c r="L82" s="15">
+        <v>1</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="N82" s="15">
         <v>9999</v>
       </c>
-      <c r="O82" s="11">
-        <v>9999</v>
+      <c r="O82" s="15">
+        <v>800</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83">
+    <row r="83" spans="1:15" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="11">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="B83" t="s">
-        <v>433</v>
-      </c>
-      <c r="C83" t="s">
-        <v>291</v>
-      </c>
-      <c r="D83" t="s">
-        <v>309</v>
-      </c>
-      <c r="E83">
+      <c r="B83" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="E83" s="11">
         <v>500</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="11">
         <v>150</v>
       </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
-      <c r="H83">
-        <v>1</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
-      <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>1</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N83">
-        <v>2000</v>
-      </c>
-      <c r="O83">
-        <v>2000</v>
+      <c r="G83" s="11">
+        <v>0</v>
+      </c>
+      <c r="H83" s="11">
+        <v>0</v>
+      </c>
+      <c r="I83" s="11">
+        <v>0</v>
+      </c>
+      <c r="J83" s="11">
+        <v>0</v>
+      </c>
+      <c r="K83" s="11">
+        <v>0</v>
+      </c>
+      <c r="L83" s="11">
+        <v>0</v>
+      </c>
+      <c r="M83" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="N83" s="11">
+        <v>9999</v>
+      </c>
+      <c r="O83" s="11">
+        <v>9999</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12104,13 +12136,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C84" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D84" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12137,13 +12169,13 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>445</v>
+        <v>292</v>
       </c>
       <c r="N84">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="O84">
-        <v>2100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12152,13 +12184,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C85" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D85" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -12185,13 +12217,13 @@
         <v>1</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N85">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="O85">
-        <v>2200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12200,13 +12232,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D86" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12233,13 +12265,13 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N86">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="O86">
-        <v>2300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12248,13 +12280,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D87" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12281,13 +12313,13 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N87">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="O87">
-        <v>2400</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12296,13 +12328,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="D88" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12314,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -12326,16 +12358,16 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>277</v>
+        <v>448</v>
       </c>
       <c r="N88">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="O88">
-        <v>5000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12347,10 +12379,10 @@
         <v>374</v>
       </c>
       <c r="C89" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="D89" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12377,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>479</v>
+        <v>277</v>
       </c>
       <c r="N89">
         <v>5000</v>
@@ -12395,10 +12427,10 @@
         <v>374</v>
       </c>
       <c r="C90" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="D90" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12425,7 +12457,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="N90">
         <v>5000</v>
@@ -12443,10 +12475,10 @@
         <v>374</v>
       </c>
       <c r="C91" t="s">
-        <v>464</v>
+        <v>333</v>
       </c>
       <c r="D91" t="s">
-        <v>463</v>
+        <v>332</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12473,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12491,10 +12523,10 @@
         <v>374</v>
       </c>
       <c r="C92" t="s">
-        <v>335</v>
+        <v>464</v>
       </c>
       <c r="D92" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12521,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>429</v>
+        <v>472</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12539,10 +12571,10 @@
         <v>374</v>
       </c>
       <c r="C93" t="s">
-        <v>449</v>
+        <v>335</v>
       </c>
       <c r="D93" t="s">
-        <v>474</v>
+        <v>334</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12569,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12587,10 +12619,10 @@
         <v>374</v>
       </c>
       <c r="C94" t="s">
-        <v>372</v>
+        <v>449</v>
       </c>
       <c r="D94" t="s">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12617,7 +12649,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>421</v>
+        <v>475</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12635,10 +12667,10 @@
         <v>374</v>
       </c>
       <c r="C95" t="s">
-        <v>280</v>
+        <v>372</v>
       </c>
       <c r="D95" t="s">
-        <v>278</v>
+        <v>371</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -12665,7 +12697,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -12683,10 +12715,10 @@
         <v>374</v>
       </c>
       <c r="C96" t="s">
-        <v>432</v>
+        <v>280</v>
       </c>
       <c r="D96" t="s">
-        <v>431</v>
+        <v>278</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12713,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>473</v>
+        <v>425</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -12731,10 +12763,10 @@
         <v>374</v>
       </c>
       <c r="C97" t="s">
-        <v>282</v>
+        <v>432</v>
       </c>
       <c r="D97" t="s">
-        <v>283</v>
+        <v>431</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -12761,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -12779,10 +12811,10 @@
         <v>374</v>
       </c>
       <c r="C98" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="D98" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12809,7 +12841,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -12827,10 +12859,10 @@
         <v>374</v>
       </c>
       <c r="C99" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D99" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12875,10 +12907,10 @@
         <v>374</v>
       </c>
       <c r="C100" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D100" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -12923,10 +12955,10 @@
         <v>374</v>
       </c>
       <c r="C101" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D101" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12971,10 +13003,10 @@
         <v>374</v>
       </c>
       <c r="C102" t="s">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="D102" t="s">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13001,7 +13033,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13019,10 +13051,10 @@
         <v>374</v>
       </c>
       <c r="C103" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="D103" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13049,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>422</v>
+        <v>478</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13067,10 +13099,10 @@
         <v>374</v>
       </c>
       <c r="C104" t="s">
-        <v>440</v>
+        <v>331</v>
       </c>
       <c r="D104" t="s">
-        <v>439</v>
+        <v>330</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13097,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13115,10 +13147,10 @@
         <v>374</v>
       </c>
       <c r="C105" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="D105" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13163,10 +13195,10 @@
         <v>374</v>
       </c>
       <c r="C106" t="s">
-        <v>338</v>
+        <v>470</v>
       </c>
       <c r="D106" t="s">
-        <v>336</v>
+        <v>469</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13193,7 +13225,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>427</v>
+        <v>473</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13211,10 +13243,10 @@
         <v>374</v>
       </c>
       <c r="C107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D107" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13241,7 +13273,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13259,10 +13291,10 @@
         <v>374</v>
       </c>
       <c r="C108" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D108" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13289,7 +13321,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>473</v>
+        <v>425</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13307,10 +13339,10 @@
         <v>374</v>
       </c>
       <c r="C109" t="s">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="D109" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13337,7 +13369,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>424</v>
+        <v>473</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13355,10 +13387,10 @@
         <v>374</v>
       </c>
       <c r="C110" t="s">
-        <v>342</v>
+        <v>285</v>
       </c>
       <c r="D110" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13385,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>473</v>
+        <v>424</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13403,10 +13435,10 @@
         <v>374</v>
       </c>
       <c r="C111" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D111" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13451,10 +13483,10 @@
         <v>374</v>
       </c>
       <c r="C112" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D112" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13481,7 +13513,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13499,10 +13531,10 @@
         <v>374</v>
       </c>
       <c r="C113" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D113" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13529,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13547,10 +13579,10 @@
         <v>374</v>
       </c>
       <c r="C114" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D114" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13577,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13595,10 +13627,10 @@
         <v>374</v>
       </c>
       <c r="C115" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D115" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13643,10 +13675,10 @@
         <v>374</v>
       </c>
       <c r="C116" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D116" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -13673,7 +13705,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -13691,10 +13723,10 @@
         <v>374</v>
       </c>
       <c r="C117" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D117" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -13739,10 +13771,10 @@
         <v>374</v>
       </c>
       <c r="C118" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D118" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -13769,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>426</v>
+        <v>473</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -13787,10 +13819,10 @@
         <v>374</v>
       </c>
       <c r="C119" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D119" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -13817,7 +13849,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -13835,10 +13867,10 @@
         <v>374</v>
       </c>
       <c r="C120" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
       <c r="D120" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -13865,7 +13897,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -13883,10 +13915,10 @@
         <v>374</v>
       </c>
       <c r="C121" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D121" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -13913,7 +13945,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -13931,10 +13963,10 @@
         <v>374</v>
       </c>
       <c r="C122" t="s">
-        <v>467</v>
+        <v>310</v>
       </c>
       <c r="D122" t="s">
-        <v>465</v>
+        <v>311</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -13961,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -13979,10 +14011,10 @@
         <v>374</v>
       </c>
       <c r="C123" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D123" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14009,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14018,51 +14050,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="124" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="13">
+    <row r="124" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" t="s">
         <v>374</v>
       </c>
-      <c r="C124" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="E124" s="13">
+      <c r="C124" t="s">
+        <v>468</v>
+      </c>
+      <c r="D124" t="s">
+        <v>466</v>
+      </c>
+      <c r="E124">
         <v>500</v>
       </c>
-      <c r="F124" s="13">
+      <c r="F124">
         <v>150</v>
       </c>
-      <c r="G124" s="13">
-        <v>0</v>
-      </c>
-      <c r="H124" s="13">
-        <v>0</v>
-      </c>
-      <c r="I124" s="13">
-        <v>0</v>
-      </c>
-      <c r="J124" s="13">
-        <v>0</v>
-      </c>
-      <c r="K124" s="13">
-        <v>0</v>
-      </c>
-      <c r="L124" s="13">
-        <v>0</v>
-      </c>
-      <c r="M124" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="N124" s="13">
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="N124">
         <v>5000</v>
       </c>
-      <c r="O124" s="13">
+      <c r="O124">
         <v>5000</v>
       </c>
     </row>
@@ -14075,10 +14107,10 @@
         <v>374</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E125" s="13">
         <v>500</v>
@@ -14123,10 +14155,10 @@
         <v>374</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E126" s="13">
         <v>500</v>
@@ -14162,51 +14194,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127">
+    <row r="127" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="13">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="C127" t="s">
-        <v>366</v>
-      </c>
-      <c r="D127" t="s">
-        <v>365</v>
-      </c>
-      <c r="E127">
+      <c r="C127" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E127" s="13">
         <v>500</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="13">
         <v>150</v>
       </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="N127">
+      <c r="G127" s="13">
+        <v>0</v>
+      </c>
+      <c r="H127" s="13">
+        <v>0</v>
+      </c>
+      <c r="I127" s="13">
+        <v>0</v>
+      </c>
+      <c r="J127" s="13">
+        <v>0</v>
+      </c>
+      <c r="K127" s="13">
+        <v>0</v>
+      </c>
+      <c r="L127" s="13">
+        <v>0</v>
+      </c>
+      <c r="M127" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="N127" s="13">
         <v>5000</v>
       </c>
-      <c r="O127">
+      <c r="O127" s="13">
         <v>5000</v>
       </c>
     </row>
@@ -14219,10 +14251,10 @@
         <v>374</v>
       </c>
       <c r="C128" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D128" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14249,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>284</v>
+        <v>428</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14258,194 +14290,242 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="129" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="13">
+    <row r="129" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" t="s">
         <v>374</v>
       </c>
-      <c r="C129" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="E129" s="13">
+      <c r="C129" t="s">
+        <v>368</v>
+      </c>
+      <c r="D129" t="s">
+        <v>367</v>
+      </c>
+      <c r="E129">
         <v>500</v>
       </c>
-      <c r="F129" s="13">
+      <c r="F129">
         <v>150</v>
       </c>
-      <c r="G129" s="13">
-        <v>0</v>
-      </c>
-      <c r="H129" s="13">
-        <v>0</v>
-      </c>
-      <c r="I129" s="13">
-        <v>0</v>
-      </c>
-      <c r="J129" s="13">
-        <v>0</v>
-      </c>
-      <c r="K129" s="13">
-        <v>0</v>
-      </c>
-      <c r="L129" s="13">
-        <v>0</v>
-      </c>
-      <c r="M129" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="N129" s="13">
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="N129">
         <v>5000</v>
       </c>
-      <c r="O129" s="13">
+      <c r="O129">
         <v>5000</v>
       </c>
     </row>
-    <row r="130" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130">
+    <row r="130" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="13">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="E130" s="13">
+        <v>500</v>
+      </c>
+      <c r="F130" s="13">
+        <v>150</v>
+      </c>
+      <c r="G130" s="13">
+        <v>0</v>
+      </c>
+      <c r="H130" s="13">
+        <v>0</v>
+      </c>
+      <c r="I130" s="13">
+        <v>0</v>
+      </c>
+      <c r="J130" s="13">
+        <v>0</v>
+      </c>
+      <c r="K130" s="13">
+        <v>0</v>
+      </c>
+      <c r="L130" s="13">
+        <v>0</v>
+      </c>
+      <c r="M130" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="N130" s="13">
+        <v>5000</v>
+      </c>
+      <c r="O130" s="13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <f t="shared" si="0"/>
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>374</v>
+      </c>
+      <c r="C131" t="s">
         <v>312</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D131" t="s">
         <v>313</v>
       </c>
-      <c r="E130">
+      <c r="E131">
         <v>500</v>
       </c>
-      <c r="F130">
+      <c r="F131">
         <v>150</v>
       </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" s="2" t="s">
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="N130">
+      <c r="N131">
         <v>5000</v>
       </c>
-      <c r="O130">
+      <c r="O131">
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131">
+    <row r="132" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132">
         <f>ROW()-2</f>
-        <v>129</v>
-      </c>
-      <c r="B131" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" t="s">
         <v>444</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C132" t="s">
         <v>441</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D132" t="s">
         <v>442</v>
       </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-      <c r="F131">
-        <v>0</v>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
         <v>1</v>
       </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="s">
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" t="s">
         <v>443</v>
       </c>
-      <c r="N131">
+      <c r="N132">
         <v>9999</v>
       </c>
-      <c r="O131">
+      <c r="O132">
         <v>9999</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132">
+    <row r="133" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A133">
         <v>10000</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B133" t="s">
         <v>169</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C133" t="s">
         <v>173</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D133" t="s">
         <v>174</v>
       </c>
-      <c r="E132">
+      <c r="E133">
         <v>500</v>
       </c>
-      <c r="F132">
+      <c r="F133">
         <v>150</v>
       </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
         <v>1</v>
       </c>
-      <c r="M132" s="2" t="s">
+      <c r="M133" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="N132">
+      <c r="N133">
         <v>9000</v>
       </c>
-      <c r="O132">
+      <c r="O133">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C231A98-9445-435E-A0E6-12F2B1B0C429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00ADFF5F-EA54-4E79-8B68-0F6FB529B977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="1020" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -544,23 +544,6 @@
   </si>
   <si>
     <t>recipibook_6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【カリカリサクサク　ラスクのレシピ】
-&lt;color=#BA9535FF&gt;バゲット &lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;ナイフ&lt;/color&gt;で薄くスライスする。
-&lt;color=#BA9535FF&gt;砂糖 &lt;/color&gt;をまぶして、出来上がり！
-バゲット　：　砂糖　＝　&lt;color=#BA9535FF&gt;１　：　２&lt;/color&gt;
-</t>
-    <rPh sb="81" eb="82">
-      <t>ウス</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="126" eb="129">
-      <t>デキア</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3363,30 +3346,6 @@
   </si>
   <si>
     <t>eden_recipi_01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【エデンのレシピのかけら】
-エデンの作り方について書かれたレシピのようだ。
-古い文字でかかれており、読めない・・。</t>
-    <rPh sb="19" eb="20">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>フル</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ヨ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7658,6 +7617,61 @@
   </si>
   <si>
     <t>Items/memo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+アマクサから手描きのコピーをもらった。
+古い文字でかかれており、読めない・・。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>テガ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>フル</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【カリカリサクサク　ラスクのレシピ】
+&lt;color=#BA9535FF&gt;バゲット &lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;ナイフ&lt;/color&gt;で薄くスライスする。
+&lt;color=#BA9535FF&gt;砂糖 &lt;/color&gt;をまぶして、出来上がり！
+バゲット　：　砂糖　＝　&lt;color=#BA9535FF&gt;１　：　２&lt;/color&gt;
+ナイフを持ってくるの忘れてしまったかも。
+どこかで売ってるかなぁ・・？</t>
+    <rPh sb="81" eb="82">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="126" eb="129">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="182" eb="183">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="188" eb="189">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="204" eb="205">
+      <t>ウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7766,7 +7780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7808,12 +7822,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8173,13 +8181,13 @@
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8200,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -8248,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -8281,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8296,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -8344,7 +8352,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -8392,7 +8400,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -8425,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -8440,13 +8448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8473,7 +8481,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -8488,7 +8496,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
         <v>62</v>
@@ -8521,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N8">
         <v>3020</v>
@@ -8536,13 +8544,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E9">
         <v>500</v>
@@ -8569,7 +8577,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N9">
         <v>3050</v>
@@ -8584,13 +8592,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10">
         <v>500</v>
@@ -8617,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N10">
         <v>3070</v>
@@ -8632,13 +8640,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" t="s">
         <v>170</v>
-      </c>
-      <c r="D11" t="s">
-        <v>171</v>
       </c>
       <c r="E11">
         <v>500</v>
@@ -8665,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -8680,13 +8688,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E12">
         <v>500</v>
@@ -8713,7 +8721,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N12">
         <v>3090</v>
@@ -8728,13 +8736,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" t="s">
         <v>183</v>
-      </c>
-      <c r="D13" t="s">
-        <v>184</v>
       </c>
       <c r="E13">
         <v>500</v>
@@ -8761,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N13">
         <v>3100</v>
@@ -8776,13 +8784,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -8809,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -8824,13 +8832,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D15" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -8857,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -8872,13 +8880,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D16" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E16">
         <v>500</v>
@@ -8905,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="N16">
         <v>3130</v>
@@ -8920,13 +8928,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D17" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -8953,7 +8961,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -8968,7 +8976,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
         <v>61</v>
@@ -9001,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>3010</v>
@@ -9064,7 +9072,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
         <v>72</v>
@@ -9097,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N20">
         <v>3040</v>
@@ -9112,13 +9120,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
         <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>94</v>
       </c>
       <c r="E21">
         <v>500</v>
@@ -9145,7 +9153,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N21">
         <v>3060</v>
@@ -9166,7 +9174,7 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>500</v>
@@ -9193,7 +9201,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N22">
         <v>20</v>
@@ -9241,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N23">
         <v>30</v>
@@ -9262,7 +9270,7 @@
         <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24">
         <v>500</v>
@@ -9289,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>73</v>
+        <v>496</v>
       </c>
       <c r="N24">
         <v>40</v>
@@ -9304,13 +9312,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" t="s">
         <v>161</v>
-      </c>
-      <c r="C25" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" t="s">
-        <v>162</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -9337,7 +9345,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N25">
         <v>50</v>
@@ -9385,7 +9393,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N26">
         <v>60</v>
@@ -9433,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N27">
         <v>70</v>
@@ -9481,7 +9489,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N28">
         <v>80</v>
@@ -9502,7 +9510,7 @@
         <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -9529,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N29">
         <v>90</v>
@@ -9688,13 +9696,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33">
         <v>500</v>
@@ -9721,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N33">
         <v>130</v>
@@ -9736,13 +9744,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C34" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D34" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9769,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N34">
         <v>150</v>
@@ -9784,13 +9792,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -9817,7 +9825,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N35">
         <v>140</v>
@@ -9832,7 +9840,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -9865,7 +9873,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N36">
         <v>200</v>
@@ -9880,13 +9888,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E37">
         <v>500</v>
@@ -9913,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N37">
         <v>210</v>
@@ -9928,13 +9936,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E38">
         <v>500</v>
@@ -9961,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N38">
         <v>220</v>
@@ -9976,13 +9984,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -10009,7 +10017,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N39">
         <v>230</v>
@@ -10024,13 +10032,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -10057,7 +10065,7 @@
         <v>1</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N40">
         <v>240</v>
@@ -10072,13 +10080,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -10105,7 +10113,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N41">
         <v>250</v>
@@ -10153,7 +10161,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N42">
         <v>260</v>
@@ -10168,13 +10176,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" t="s">
         <v>164</v>
-      </c>
-      <c r="D43" t="s">
-        <v>165</v>
       </c>
       <c r="E43">
         <v>500</v>
@@ -10201,7 +10209,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="N43">
         <v>270</v>
@@ -10216,13 +10224,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -10249,7 +10257,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N44">
         <v>280</v>
@@ -10264,13 +10272,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -10297,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N45">
         <v>290</v>
@@ -10312,13 +10320,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -10345,7 +10353,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N46">
         <v>300</v>
@@ -10360,13 +10368,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E47" s="5">
         <v>500</v>
@@ -10393,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N47" s="5">
         <v>9999</v>
@@ -10408,13 +10416,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -10441,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N48">
         <v>310</v>
@@ -10456,13 +10464,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C49" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D49" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -10489,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N49">
         <v>320</v>
@@ -10504,13 +10512,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10537,7 +10545,7 @@
         <v>1</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N50">
         <v>330</v>
@@ -10552,13 +10560,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C51" t="s">
+        <v>206</v>
+      </c>
+      <c r="D51" t="s">
         <v>207</v>
-      </c>
-      <c r="D51" t="s">
-        <v>208</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10585,7 +10593,7 @@
         <v>1</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N51">
         <v>340</v>
@@ -10600,13 +10608,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10633,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N52">
         <v>350</v>
@@ -10648,13 +10656,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -10681,7 +10689,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N53">
         <v>360</v>
@@ -10696,13 +10704,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C54" t="s">
+        <v>296</v>
+      </c>
+      <c r="D54" t="s">
         <v>298</v>
-      </c>
-      <c r="D54" t="s">
-        <v>300</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -10729,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N54">
         <v>370</v>
@@ -10744,13 +10752,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C55" t="s">
+        <v>297</v>
+      </c>
+      <c r="D55" t="s">
         <v>299</v>
-      </c>
-      <c r="D55" t="s">
-        <v>301</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -10777,7 +10785,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="N55">
         <v>380</v>
@@ -10792,13 +10800,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -10825,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N56">
         <v>390</v>
@@ -10840,13 +10848,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C57" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="E57" s="9">
         <v>500</v>
@@ -10873,7 +10881,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N57" s="9">
         <v>400</v>
@@ -10888,13 +10896,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -10921,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N58">
         <v>410</v>
@@ -10936,13 +10944,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -10969,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N59">
         <v>500</v>
@@ -10984,13 +10992,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -11017,7 +11025,7 @@
         <v>1</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N60">
         <v>510</v>
@@ -11032,13 +11040,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -11065,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N61">
         <v>520</v>
@@ -11080,13 +11088,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -11113,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N62">
         <v>530</v>
@@ -11128,13 +11136,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -11161,7 +11169,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N63">
         <v>540</v>
@@ -11176,13 +11184,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C64" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D64" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11209,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N64">
         <v>550</v>
@@ -11224,13 +11232,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E65">
         <v>500</v>
@@ -11257,7 +11265,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N65">
         <v>560</v>
@@ -11272,13 +11280,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C66" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -11305,7 +11313,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N66">
         <v>570</v>
@@ -11320,13 +11328,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E67">
         <v>500</v>
@@ -11353,7 +11361,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N67">
         <v>580</v>
@@ -11368,13 +11376,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -11401,7 +11409,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N68">
         <v>590</v>
@@ -11416,13 +11424,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E69" s="7">
         <v>500</v>
@@ -11449,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N69" s="7">
         <v>600</v>
@@ -11464,13 +11472,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C70" t="s">
+        <v>235</v>
+      </c>
+      <c r="D70" t="s">
         <v>236</v>
-      </c>
-      <c r="D70" t="s">
-        <v>237</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -11497,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N70">
         <v>610</v>
@@ -11512,13 +11520,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E71" s="7">
         <v>500</v>
@@ -11545,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="N71" s="7">
         <v>620</v>
@@ -11560,13 +11568,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C72" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D72" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -11593,7 +11601,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N72">
         <v>700</v>
@@ -11608,13 +11616,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D73" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E73">
         <v>500</v>
@@ -11641,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N73">
         <v>710</v>
@@ -11656,13 +11664,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -11689,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N74">
         <v>720</v>
@@ -11704,13 +11712,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C75" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D75" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -11737,7 +11745,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N75">
         <v>730</v>
@@ -11752,13 +11760,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C76" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" t="s">
         <v>244</v>
-      </c>
-      <c r="D76" t="s">
-        <v>245</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -11785,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N76">
         <v>740</v>
@@ -11800,13 +11808,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C77" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -11833,7 +11841,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N77">
         <v>750</v>
@@ -11848,13 +11856,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D78" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -11881,7 +11889,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N78">
         <v>760</v>
@@ -11896,13 +11904,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C79" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D79" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E79">
         <v>500</v>
@@ -11929,7 +11937,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N79">
         <v>770</v>
@@ -11944,13 +11952,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C80" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D80" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -11977,7 +11985,7 @@
         <v>1</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N80">
         <v>780</v>
@@ -11992,13 +12000,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E81" s="7">
         <v>500</v>
@@ -12025,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N81" s="7">
         <v>790</v>
@@ -12034,51 +12042,51 @@
         <v>790</v>
       </c>
     </row>
-    <row r="82" spans="1:15" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="15">
+    <row r="82" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="C82" s="15" t="s">
+      <c r="B82" t="s">
+        <v>494</v>
+      </c>
+      <c r="C82" t="s">
+        <v>491</v>
+      </c>
+      <c r="D82" t="s">
         <v>493</v>
       </c>
-      <c r="D82" s="15" t="s">
-        <v>495</v>
-      </c>
-      <c r="E82" s="15">
+      <c r="E82">
         <v>500</v>
       </c>
-      <c r="F82" s="15">
+      <c r="F82">
         <v>150</v>
       </c>
-      <c r="G82" s="15">
-        <v>0</v>
-      </c>
-      <c r="H82" s="15">
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
         <v>1</v>
       </c>
-      <c r="I82" s="15">
-        <v>0</v>
-      </c>
-      <c r="J82" s="15">
-        <v>0</v>
-      </c>
-      <c r="K82" s="15">
-        <v>0</v>
-      </c>
-      <c r="L82" s="15">
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
         <v>1</v>
       </c>
-      <c r="M82" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="N82" s="15">
+      <c r="M82" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="N82">
         <v>9999</v>
       </c>
-      <c r="O82" s="15">
+      <c r="O82">
         <v>800</v>
       </c>
     </row>
@@ -12088,13 +12096,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E83" s="11">
         <v>500</v>
@@ -12121,7 +12129,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N83" s="11">
         <v>9999</v>
@@ -12136,13 +12144,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D84" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12169,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>292</v>
+        <v>495</v>
       </c>
       <c r="N84">
         <v>2000</v>
@@ -12184,13 +12192,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C85" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D85" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E85">
         <v>500</v>
@@ -12217,7 +12225,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N85">
         <v>2100</v>
@@ -12232,13 +12240,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C86" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12265,7 +12273,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N86">
         <v>2200</v>
@@ -12280,13 +12288,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C87" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D87" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12313,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N87">
         <v>2300</v>
@@ -12328,13 +12336,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C88" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D88" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12361,7 +12369,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N88">
         <v>2400</v>
@@ -12376,13 +12384,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D89" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12409,7 +12417,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N89">
         <v>5000</v>
@@ -12424,13 +12432,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C90" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D90" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12457,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="N90">
         <v>5000</v>
@@ -12472,13 +12480,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C91" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D91" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12505,7 +12513,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12520,13 +12528,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D92" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12553,7 +12561,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12568,13 +12576,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D93" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12601,7 +12609,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12616,13 +12624,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D94" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12649,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12664,13 +12672,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D95" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -12697,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -12712,13 +12720,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D96" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12745,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -12760,13 +12768,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C97" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D97" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -12793,7 +12801,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -12808,13 +12816,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C98" t="s">
+        <v>281</v>
+      </c>
+      <c r="D98" t="s">
         <v>282</v>
-      </c>
-      <c r="D98" t="s">
-        <v>283</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12841,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -12856,13 +12864,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C99" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D99" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12889,7 +12897,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -12904,13 +12912,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C100" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D100" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -12937,7 +12945,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -12952,13 +12960,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C101" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D101" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -12985,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13000,13 +13008,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C102" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D102" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13033,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13048,13 +13056,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C103" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D103" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13081,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13096,13 +13104,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C104" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D104" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13129,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13144,13 +13152,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C105" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D105" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13177,7 +13185,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13192,13 +13200,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C106" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D106" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13225,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13240,13 +13248,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C107" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D107" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13273,7 +13281,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13288,13 +13296,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C108" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D108" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13321,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13336,13 +13344,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C109" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D109" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13369,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13384,13 +13392,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C110" t="s">
+        <v>284</v>
+      </c>
+      <c r="D110" t="s">
         <v>285</v>
-      </c>
-      <c r="D110" t="s">
-        <v>286</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13417,7 +13425,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13432,13 +13440,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C111" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D111" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13465,7 +13473,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13480,13 +13488,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C112" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D112" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13513,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13528,13 +13536,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D113" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13561,7 +13569,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13576,13 +13584,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C114" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D114" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13609,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13624,13 +13632,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C115" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D115" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13657,7 +13665,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13672,13 +13680,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C116" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D116" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -13705,7 +13713,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -13720,13 +13728,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C117" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D117" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -13753,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -13768,13 +13776,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C118" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D118" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -13801,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -13816,13 +13824,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D119" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -13849,7 +13857,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -13864,13 +13872,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C120" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D120" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -13897,7 +13905,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -13912,13 +13920,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C121" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D121" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -13945,7 +13953,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -13960,13 +13968,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C122" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D122" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -13993,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14008,13 +14016,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C123" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D123" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14041,7 +14049,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14056,13 +14064,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C124" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D124" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14089,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14104,13 +14112,13 @@
         <v>123</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E125" s="13">
         <v>500</v>
@@ -14137,7 +14145,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N125" s="13">
         <v>5000</v>
@@ -14152,13 +14160,13 @@
         <v>124</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E126" s="13">
         <v>500</v>
@@ -14185,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N126" s="13">
         <v>5000</v>
@@ -14200,13 +14208,13 @@
         <v>125</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E127" s="13">
         <v>500</v>
@@ -14233,7 +14241,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N127" s="13">
         <v>5000</v>
@@ -14248,13 +14256,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C128" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D128" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14281,7 +14289,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14296,13 +14304,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C129" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D129" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14329,7 +14337,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14344,13 +14352,13 @@
         <v>128</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E130" s="13">
         <v>500</v>
@@ -14377,7 +14385,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N130" s="13">
         <v>5000</v>
@@ -14392,13 +14400,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C131" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -14425,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14440,13 +14448,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C132" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D132" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -14473,7 +14481,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N132">
         <v>9999</v>
@@ -14487,13 +14495,13 @@
         <v>10000</v>
       </c>
       <c r="B133" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C133" t="s">
+        <v>172</v>
+      </c>
+      <c r="D133" t="s">
         <v>173</v>
-      </c>
-      <c r="D133" t="s">
-        <v>174</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14520,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N133">
         <v>9000</v>
@@ -14581,13 +14589,13 @@
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -14608,13 +14616,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -14641,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N2">
         <v>9999</v>
@@ -14656,13 +14664,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -14689,7 +14697,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -14704,13 +14712,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -14737,7 +14745,7 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N4">
         <v>9999</v>
@@ -14752,13 +14760,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -14785,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N5">
         <v>9999</v>
@@ -14800,13 +14808,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -14833,7 +14841,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N6">
         <v>9999</v>
@@ -14848,13 +14856,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -14881,7 +14889,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N7">
         <v>9999</v>
@@ -14896,13 +14904,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -14929,7 +14937,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8">
         <v>9999</v>
@@ -14944,13 +14952,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -14977,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N9">
         <v>9999</v>
@@ -14992,13 +15000,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -15025,7 +15033,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N10">
         <v>9999</v>
@@ -15040,13 +15048,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" t="s">
         <v>145</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -15073,7 +15081,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N11">
         <v>9999</v>
@@ -15088,13 +15096,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -15121,7 +15129,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N12">
         <v>9999</v>
@@ -15136,13 +15144,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -15169,7 +15177,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N13">
         <v>9999</v>
@@ -15184,13 +15192,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -15217,7 +15225,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N14" s="4">
         <v>9999</v>
@@ -15238,7 +15246,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00ADFF5F-EA54-4E79-8B68-0F6FB529B977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11811FE0-1108-42A1-A968-C571070F27CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2805" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -7716,7 +7716,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7765,6 +7765,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -7780,7 +7786,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7822,6 +7828,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8874,51 +8886,51 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16">
+    <row r="16" spans="1:15" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="15">
         <v>500</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="15">
         <v>150</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="G16" s="15">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15">
         <v>1</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="15">
         <v>3130</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="15">
         <v>3130</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11811FE0-1108-42A1-A968-C571070F27CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA537F2-D7FD-417C-88B1-77B953A78A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2295" yWindow="825" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="508">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7672,6 +7672,53 @@
     <rPh sb="204" eb="205">
       <t>ウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Icon/CostumeIcon_6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Icon/CostumeIcon_7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Icon/CostumeIcon_8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクのうさぎワンピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パティシエ服</t>
+    <rPh sb="5" eb="6">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラベンダーワンピース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LavenderDress_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PinkUsagi_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patissier_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パティシエハット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PatissierHat_Acce</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -14558,7 +14605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94BD5E9F-9099-4495-A12D-C6B76FFF933E}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -14624,7 +14671,7 @@
     </row>
     <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A15" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A19" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -14868,13 +14915,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>497</v>
+      </c>
+      <c r="C7" t="s">
+        <v>503</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -14889,10 +14936,10 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -14901,7 +14948,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N7">
         <v>9999</v>
@@ -14916,13 +14963,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>498</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -14937,19 +14984,19 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N8">
         <v>9999</v>
@@ -14964,13 +15011,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>499</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>505</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>501</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -14985,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -14997,7 +15044,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N9">
         <v>9999</v>
@@ -15012,13 +15059,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
+        <v>105</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -15036,7 +15083,7 @@
         <v>2</v>
       </c>
       <c r="J10">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -15054,51 +15101,51 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:15" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="13">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
+      <c r="B11" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
         <v>2</v>
       </c>
-      <c r="J11">
-        <v>104</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="J11" s="13">
+        <v>101</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="13">
         <v>9999</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="13">
         <v>9999</v>
       </c>
     </row>
@@ -15108,13 +15155,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -15132,7 +15179,7 @@
         <v>2</v>
       </c>
       <c r="J12">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -15156,13 +15203,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -15180,7 +15227,7 @@
         <v>2</v>
       </c>
       <c r="J13">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -15198,51 +15245,51 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4">
+      <c r="B14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>2</v>
       </c>
-      <c r="J14" s="4">
-        <v>107</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="J14">
+        <v>104</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>1</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" t="s">
         <v>81</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14">
         <v>9999</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O14">
         <v>9999</v>
       </c>
     </row>
@@ -15252,13 +15299,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -15273,10 +15320,10 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -15285,12 +15332,204 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="N15">
         <v>9999</v>
       </c>
       <c r="O15">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>106</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16">
+        <v>9999</v>
+      </c>
+      <c r="O16">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>2</v>
+      </c>
+      <c r="J17" s="4">
+        <v>107</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N17" s="4">
+        <v>9999</v>
+      </c>
+      <c r="O17" s="4">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4">
+        <v>108</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N18" s="4">
+        <v>9999</v>
+      </c>
+      <c r="O18" s="4">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>70</v>
+      </c>
+      <c r="N19">
+        <v>9999</v>
+      </c>
+      <c r="O19">
         <v>9999</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA537F2-D7FD-417C-88B1-77B953A78A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F3D289-30C9-4F49-A354-28A7522233F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="825" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F3D289-30C9-4F49-A354-28A7522233F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7723E10F-F300-43E5-8C7E-9CD09CD9732B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1650" yWindow="960" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7723E10F-F300-43E5-8C7E-9CD09CD9732B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D152E9-8A10-4AD8-97AA-AF2C5753C726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="960" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3045" yWindow="1230" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="510">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7691,34 +7691,42 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パティシエ服</t>
-    <rPh sb="5" eb="6">
+    <t>ラベンダーワンピース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LavenderDress_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PinkUsagi_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patissier_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パティシエハット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PatissierHat_Acce</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコミントのパティシエ服</t>
+    <rPh sb="12" eb="13">
       <t>フク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ラベンダーワンピース</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LavenderDress_Costume</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PinkUsagi_Costume</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Patissier_Costume</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パティシエハット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PatissierHat_Acce</t>
+    <t>Icon/AcceIcon_7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Icon/AcceIcon_8</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7763,7 +7771,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7773,12 +7781,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7847,6 +7849,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -7877,11 +7882,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8933,51 +8935,51 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="15">
+    <row r="16" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="14">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <v>500</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <v>150</v>
       </c>
-      <c r="G16" s="15">
-        <v>0</v>
-      </c>
-      <c r="H16" s="15">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
-        <v>0</v>
-      </c>
-      <c r="J16" s="15">
-        <v>0</v>
-      </c>
-      <c r="K16" s="15">
-        <v>0</v>
-      </c>
-      <c r="L16" s="15">
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14">
+        <v>0</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14">
+        <v>0</v>
+      </c>
+      <c r="L16" s="14">
         <v>1</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M16" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="14">
         <v>3130</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="14">
         <v>3130</v>
       </c>
     </row>
@@ -10421,51 +10423,51 @@
         <v>300</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="5">
+    <row r="47" spans="1:15" s="4" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="4">
         <v>500</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="4">
         <v>150</v>
       </c>
-      <c r="G47" s="5">
-        <v>0</v>
-      </c>
-      <c r="H47" s="5">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5">
-        <v>0</v>
-      </c>
-      <c r="J47" s="5">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5">
-        <v>0</v>
-      </c>
-      <c r="L47" s="5">
-        <v>0</v>
-      </c>
-      <c r="M47" s="6" t="s">
+      <c r="G47" s="4">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>0</v>
+      </c>
+      <c r="M47" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="N47" s="5">
+      <c r="N47" s="4">
         <v>9999</v>
       </c>
-      <c r="O47" s="5">
+      <c r="O47" s="4">
         <v>9999</v>
       </c>
     </row>
@@ -10901,51 +10903,51 @@
         <v>390</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="9">
+    <row r="57" spans="1:15" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="8">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="8">
         <v>500</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="8">
         <v>150</v>
       </c>
-      <c r="G57" s="9">
-        <v>0</v>
-      </c>
-      <c r="H57" s="9">
-        <v>0</v>
-      </c>
-      <c r="I57" s="9">
-        <v>0</v>
-      </c>
-      <c r="J57" s="9">
-        <v>0</v>
-      </c>
-      <c r="K57" s="9">
-        <v>0</v>
-      </c>
-      <c r="L57" s="9">
+      <c r="G57" s="8">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8">
         <v>1</v>
       </c>
-      <c r="M57" s="10" t="s">
+      <c r="M57" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="N57" s="9">
+      <c r="N57" s="8">
         <v>400</v>
       </c>
-      <c r="O57" s="9">
+      <c r="O57" s="8">
         <v>400</v>
       </c>
     </row>
@@ -11477,51 +11479,51 @@
         <v>590</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="7">
+    <row r="69" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="6">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="6">
         <v>500</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="6">
         <v>150</v>
       </c>
-      <c r="G69" s="7">
-        <v>0</v>
-      </c>
-      <c r="H69" s="7">
-        <v>0</v>
-      </c>
-      <c r="I69" s="7">
-        <v>0</v>
-      </c>
-      <c r="J69" s="7">
-        <v>0</v>
-      </c>
-      <c r="K69" s="7">
-        <v>0</v>
-      </c>
-      <c r="L69" s="7">
-        <v>0</v>
-      </c>
-      <c r="M69" s="8" t="s">
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6">
+        <v>0</v>
+      </c>
+      <c r="K69" s="6">
+        <v>0</v>
+      </c>
+      <c r="L69" s="6">
+        <v>0</v>
+      </c>
+      <c r="M69" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="N69" s="7">
+      <c r="N69" s="6">
         <v>600</v>
       </c>
-      <c r="O69" s="7">
+      <c r="O69" s="6">
         <v>600</v>
       </c>
     </row>
@@ -11573,51 +11575,51 @@
         <v>610</v>
       </c>
     </row>
-    <row r="71" spans="1:15" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="7">
+    <row r="71" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="6">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="6">
         <v>500</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="6">
         <v>150</v>
       </c>
-      <c r="G71" s="7">
-        <v>0</v>
-      </c>
-      <c r="H71" s="7">
-        <v>0</v>
-      </c>
-      <c r="I71" s="7">
-        <v>0</v>
-      </c>
-      <c r="J71" s="7">
-        <v>0</v>
-      </c>
-      <c r="K71" s="7">
-        <v>0</v>
-      </c>
-      <c r="L71" s="7">
-        <v>0</v>
-      </c>
-      <c r="M71" s="8" t="s">
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6">
+        <v>0</v>
+      </c>
+      <c r="I71" s="6">
+        <v>0</v>
+      </c>
+      <c r="J71" s="6">
+        <v>0</v>
+      </c>
+      <c r="K71" s="6">
+        <v>0</v>
+      </c>
+      <c r="L71" s="6">
+        <v>0</v>
+      </c>
+      <c r="M71" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="6">
         <v>620</v>
       </c>
-      <c r="O71" s="7">
+      <c r="O71" s="6">
         <v>620</v>
       </c>
     </row>
@@ -12053,51 +12055,51 @@
         <v>780</v>
       </c>
     </row>
-    <row r="81" spans="1:15" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="7">
+    <row r="81" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="6">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="E81" s="7">
+      <c r="E81" s="6">
         <v>500</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="6">
         <v>150</v>
       </c>
-      <c r="G81" s="7">
-        <v>0</v>
-      </c>
-      <c r="H81" s="7">
-        <v>0</v>
-      </c>
-      <c r="I81" s="7">
-        <v>0</v>
-      </c>
-      <c r="J81" s="7">
-        <v>0</v>
-      </c>
-      <c r="K81" s="7">
-        <v>0</v>
-      </c>
-      <c r="L81" s="7">
-        <v>0</v>
-      </c>
-      <c r="M81" s="8" t="s">
+      <c r="G81" s="6">
+        <v>0</v>
+      </c>
+      <c r="H81" s="6">
+        <v>0</v>
+      </c>
+      <c r="I81" s="6">
+        <v>0</v>
+      </c>
+      <c r="J81" s="6">
+        <v>0</v>
+      </c>
+      <c r="K81" s="6">
+        <v>0</v>
+      </c>
+      <c r="L81" s="6">
+        <v>0</v>
+      </c>
+      <c r="M81" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="N81" s="7">
+      <c r="N81" s="6">
         <v>790</v>
       </c>
-      <c r="O81" s="7">
+      <c r="O81" s="6">
         <v>790</v>
       </c>
     </row>
@@ -12149,51 +12151,51 @@
         <v>800</v>
       </c>
     </row>
-    <row r="83" spans="1:15" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="11">
+    <row r="83" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="10">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="10">
         <v>500</v>
       </c>
-      <c r="F83" s="11">
+      <c r="F83" s="10">
         <v>150</v>
       </c>
-      <c r="G83" s="11">
-        <v>0</v>
-      </c>
-      <c r="H83" s="11">
-        <v>0</v>
-      </c>
-      <c r="I83" s="11">
-        <v>0</v>
-      </c>
-      <c r="J83" s="11">
-        <v>0</v>
-      </c>
-      <c r="K83" s="11">
-        <v>0</v>
-      </c>
-      <c r="L83" s="11">
-        <v>0</v>
-      </c>
-      <c r="M83" s="12" t="s">
+      <c r="G83" s="10">
+        <v>0</v>
+      </c>
+      <c r="H83" s="10">
+        <v>0</v>
+      </c>
+      <c r="I83" s="10">
+        <v>0</v>
+      </c>
+      <c r="J83" s="10">
+        <v>0</v>
+      </c>
+      <c r="K83" s="10">
+        <v>0</v>
+      </c>
+      <c r="L83" s="10">
+        <v>0</v>
+      </c>
+      <c r="M83" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="N83" s="11">
+      <c r="N83" s="10">
         <v>9999</v>
       </c>
-      <c r="O83" s="11">
+      <c r="O83" s="10">
         <v>9999</v>
       </c>
     </row>
@@ -14165,147 +14167,147 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="125" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="13">
+    <row r="125" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="12">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C125" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="D125" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="E125" s="13">
+      <c r="E125" s="12">
         <v>500</v>
       </c>
-      <c r="F125" s="13">
+      <c r="F125" s="12">
         <v>150</v>
       </c>
-      <c r="G125" s="13">
-        <v>0</v>
-      </c>
-      <c r="H125" s="13">
-        <v>0</v>
-      </c>
-      <c r="I125" s="13">
-        <v>0</v>
-      </c>
-      <c r="J125" s="13">
-        <v>0</v>
-      </c>
-      <c r="K125" s="13">
-        <v>0</v>
-      </c>
-      <c r="L125" s="13">
-        <v>0</v>
-      </c>
-      <c r="M125" s="14" t="s">
+      <c r="G125" s="12">
+        <v>0</v>
+      </c>
+      <c r="H125" s="12">
+        <v>0</v>
+      </c>
+      <c r="I125" s="12">
+        <v>0</v>
+      </c>
+      <c r="J125" s="12">
+        <v>0</v>
+      </c>
+      <c r="K125" s="12">
+        <v>0</v>
+      </c>
+      <c r="L125" s="12">
+        <v>0</v>
+      </c>
+      <c r="M125" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N125" s="13">
+      <c r="N125" s="12">
         <v>5000</v>
       </c>
-      <c r="O125" s="13">
+      <c r="O125" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="126" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="13">
+    <row r="126" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="12">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="E126" s="13">
+      <c r="E126" s="12">
         <v>500</v>
       </c>
-      <c r="F126" s="13">
+      <c r="F126" s="12">
         <v>150</v>
       </c>
-      <c r="G126" s="13">
-        <v>0</v>
-      </c>
-      <c r="H126" s="13">
-        <v>0</v>
-      </c>
-      <c r="I126" s="13">
-        <v>0</v>
-      </c>
-      <c r="J126" s="13">
-        <v>0</v>
-      </c>
-      <c r="K126" s="13">
-        <v>0</v>
-      </c>
-      <c r="L126" s="13">
-        <v>0</v>
-      </c>
-      <c r="M126" s="14" t="s">
+      <c r="G126" s="12">
+        <v>0</v>
+      </c>
+      <c r="H126" s="12">
+        <v>0</v>
+      </c>
+      <c r="I126" s="12">
+        <v>0</v>
+      </c>
+      <c r="J126" s="12">
+        <v>0</v>
+      </c>
+      <c r="K126" s="12">
+        <v>0</v>
+      </c>
+      <c r="L126" s="12">
+        <v>0</v>
+      </c>
+      <c r="M126" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N126" s="13">
+      <c r="N126" s="12">
         <v>5000</v>
       </c>
-      <c r="O126" s="13">
+      <c r="O126" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="13">
+    <row r="127" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="12">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="D127" s="13" t="s">
+      <c r="D127" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="E127" s="13">
+      <c r="E127" s="12">
         <v>500</v>
       </c>
-      <c r="F127" s="13">
+      <c r="F127" s="12">
         <v>150</v>
       </c>
-      <c r="G127" s="13">
-        <v>0</v>
-      </c>
-      <c r="H127" s="13">
-        <v>0</v>
-      </c>
-      <c r="I127" s="13">
-        <v>0</v>
-      </c>
-      <c r="J127" s="13">
-        <v>0</v>
-      </c>
-      <c r="K127" s="13">
-        <v>0</v>
-      </c>
-      <c r="L127" s="13">
-        <v>0</v>
-      </c>
-      <c r="M127" s="14" t="s">
+      <c r="G127" s="12">
+        <v>0</v>
+      </c>
+      <c r="H127" s="12">
+        <v>0</v>
+      </c>
+      <c r="I127" s="12">
+        <v>0</v>
+      </c>
+      <c r="J127" s="12">
+        <v>0</v>
+      </c>
+      <c r="K127" s="12">
+        <v>0</v>
+      </c>
+      <c r="L127" s="12">
+        <v>0</v>
+      </c>
+      <c r="M127" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N127" s="13">
+      <c r="N127" s="12">
         <v>5000</v>
       </c>
-      <c r="O127" s="13">
+      <c r="O127" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -14405,51 +14407,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="130" spans="1:15" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="13">
+    <row r="130" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="12">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="B130" s="13" t="s">
+      <c r="B130" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C130" s="13" t="s">
+      <c r="C130" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="E130" s="13">
+      <c r="E130" s="12">
         <v>500</v>
       </c>
-      <c r="F130" s="13">
+      <c r="F130" s="12">
         <v>150</v>
       </c>
-      <c r="G130" s="13">
-        <v>0</v>
-      </c>
-      <c r="H130" s="13">
-        <v>0</v>
-      </c>
-      <c r="I130" s="13">
-        <v>0</v>
-      </c>
-      <c r="J130" s="13">
-        <v>0</v>
-      </c>
-      <c r="K130" s="13">
-        <v>0</v>
-      </c>
-      <c r="L130" s="13">
-        <v>0</v>
-      </c>
-      <c r="M130" s="14" t="s">
+      <c r="G130" s="12">
+        <v>0</v>
+      </c>
+      <c r="H130" s="12">
+        <v>0</v>
+      </c>
+      <c r="I130" s="12">
+        <v>0</v>
+      </c>
+      <c r="J130" s="12">
+        <v>0</v>
+      </c>
+      <c r="K130" s="12">
+        <v>0</v>
+      </c>
+      <c r="L130" s="12">
+        <v>0</v>
+      </c>
+      <c r="M130" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="N130" s="13">
+      <c r="N130" s="12">
         <v>5000</v>
       </c>
-      <c r="O130" s="13">
+      <c r="O130" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -14918,10 +14920,10 @@
         <v>497</v>
       </c>
       <c r="C7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -14966,7 +14968,7 @@
         <v>498</v>
       </c>
       <c r="C8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D8" t="s">
         <v>500</v>
@@ -15014,10 +15016,10 @@
         <v>499</v>
       </c>
       <c r="C9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -15101,51 +15103,51 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="13">
+    <row r="11" spans="1:15" s="12" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="12">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13">
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
         <v>2</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <v>101</v>
       </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13" t="s">
+      <c r="K11" s="12">
+        <v>0</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="12">
         <v>9999</v>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="12">
         <v>9999</v>
       </c>
     </row>
@@ -15389,99 +15391,99 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+    <row r="17" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="E17" s="16">
+        <v>0</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16">
         <v>2</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="16">
         <v>107</v>
       </c>
-      <c r="K17" s="4">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
+      <c r="K17" s="16">
+        <v>0</v>
+      </c>
+      <c r="L17" s="16">
         <v>1</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N17" s="16">
         <v>9999</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O17" s="16">
         <v>9999</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+    <row r="18" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="16">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4">
+      <c r="D18" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
         <v>2</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="16">
         <v>108</v>
       </c>
-      <c r="K18" s="4">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4">
+      <c r="K18" s="16">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16">
         <v>1</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N18" s="16">
         <v>9999</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18" s="16">
         <v>9999</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D152E9-8A10-4AD8-97AA-AF2C5753C726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A249490-EDA4-4466-BD56-63C409FF2B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1230" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1725" yWindow="1230" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -7835,7 +7835,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7881,9 +7881,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15391,99 +15388,99 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="16">
+    <row r="17" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" t="s">
         <v>508</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" t="s">
         <v>198</v>
       </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
-        <v>0</v>
-      </c>
-      <c r="G17" s="16">
-        <v>0</v>
-      </c>
-      <c r="H17" s="16">
-        <v>0</v>
-      </c>
-      <c r="I17" s="16">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>2</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17">
         <v>107</v>
       </c>
-      <c r="K17" s="16">
-        <v>0</v>
-      </c>
-      <c r="L17" s="16">
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>1</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M17" t="s">
         <v>81</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17">
         <v>9999</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17">
         <v>9999</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="16">
+    <row r="18" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" t="s">
         <v>509</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" t="s">
         <v>506</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" t="s">
         <v>505</v>
       </c>
-      <c r="E18" s="16">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16">
-        <v>0</v>
-      </c>
-      <c r="G18" s="16">
-        <v>0</v>
-      </c>
-      <c r="H18" s="16">
-        <v>0</v>
-      </c>
-      <c r="I18" s="16">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>2</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18">
         <v>108</v>
       </c>
-      <c r="K18" s="16">
-        <v>0</v>
-      </c>
-      <c r="L18" s="16">
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>1</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M18" t="s">
         <v>81</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18">
         <v>9999</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18">
         <v>9999</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A249490-EDA4-4466-BD56-63C409FF2B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C53DF6-2EA3-4CD5-AECB-9329C45E3A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="1230" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1560" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -7086,13 +7086,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ルミエールエピファニアの賞品</t>
-    <rPh sb="12" eb="14">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>最初から覚えてる</t>
     <rPh sb="0" eb="2">
       <t>サイショ</t>
@@ -7727,6 +7720,13 @@
   </si>
   <si>
     <t>Icon/AcceIcon_8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターパネルで取得</t>
+    <rPh sb="7" eb="9">
+      <t>シュトク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8242,10 +8242,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8731,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -8875,7 +8875,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -8923,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -8941,10 +8941,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -8971,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -8989,10 +8989,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9019,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9355,7 +9355,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N24">
         <v>40</v>
@@ -10267,7 +10267,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N43">
         <v>270</v>
@@ -12106,13 +12106,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C82" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D82" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12139,7 +12139,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N82">
         <v>9999</v>
@@ -12235,7 +12235,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N84">
         <v>2000</v>
@@ -12523,7 +12523,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N90">
         <v>5000</v>
@@ -12571,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12619,7 +12619,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12688,7 +12688,7 @@
         <v>447</v>
       </c>
       <c r="D94" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12715,7 +12715,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12859,7 +12859,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -12907,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -12955,7 +12955,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13051,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13099,7 +13099,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13147,7 +13147,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13243,7 +13243,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13291,7 +13291,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13531,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13579,7 +13579,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13627,7 +13627,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13723,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13771,7 +13771,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -13819,7 +13819,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -13963,7 +13963,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14011,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14107,7 +14107,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14155,7 +14155,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14650,10 +14650,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -14914,13 +14914,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -14962,13 +14962,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -15010,13 +15010,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -15394,7 +15394,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C17" t="s">
         <v>197</v>
@@ -15442,13 +15442,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C53DF6-2EA3-4CD5-AECB-9329C45E3A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456B8101-5A5A-4164-ACA1-15DD322E324B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1875" yWindow="765" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="522">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -5444,13 +5444,6 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>カナラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ぬねと友達になったらもらえる</t>
-    <rPh sb="3" eb="5">
-      <t>トモダチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7726,6 +7719,154 @@
     <t>スターパネルで取得</t>
     <rPh sb="7" eb="9">
       <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_timemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時魔法解禁の本　エメラルショップ</t>
+    <rPh sb="0" eb="1">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイキン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_windmagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_firemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_icemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風魔法解禁の本　ぬねちゃんからもらう</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイキン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風の魔術書へ移行した</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火魔法解禁の本　＃なし</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイキン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷魔法解禁の本　＃なし</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイキン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8196,7 +8337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8242,10 +8383,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8262,7 +8403,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A131" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A135" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -8347,7 +8488,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8731,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -8845,10 +8986,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -8875,7 +9016,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -8893,10 +9034,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -8923,7 +9064,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -8941,10 +9082,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -8971,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -8989,10 +9130,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9019,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9307,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N23">
         <v>30</v>
@@ -9355,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N24">
         <v>40</v>
@@ -9787,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N33">
         <v>130</v>
@@ -9802,13 +9943,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C34" t="s">
+        <v>451</v>
+      </c>
+      <c r="D34" t="s">
         <v>452</v>
-      </c>
-      <c r="D34" t="s">
-        <v>453</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -9835,7 +9976,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N34">
         <v>150</v>
@@ -10267,7 +10408,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N43">
         <v>270</v>
@@ -10507,7 +10648,7 @@
         <v>1</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N48">
         <v>310</v>
@@ -10795,7 +10936,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N54">
         <v>370</v>
@@ -10843,7 +10984,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N55">
         <v>380</v>
@@ -10891,7 +11032,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N56">
         <v>390</v>
@@ -12106,13 +12247,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C82" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D82" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12139,7 +12280,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N82">
         <v>9999</v>
@@ -12202,7 +12343,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C84" t="s">
         <v>290</v>
@@ -12235,7 +12376,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N84">
         <v>2000</v>
@@ -12250,7 +12391,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C85" t="s">
         <v>291</v>
@@ -12283,7 +12424,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N85">
         <v>2100</v>
@@ -12298,7 +12439,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C86" t="s">
         <v>292</v>
@@ -12331,7 +12472,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N86">
         <v>2200</v>
@@ -12346,7 +12487,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C87" t="s">
         <v>293</v>
@@ -12379,7 +12520,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N87">
         <v>2300</v>
@@ -12394,7 +12535,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C88" t="s">
         <v>294</v>
@@ -12427,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N88">
         <v>2400</v>
@@ -12493,10 +12634,10 @@
         <v>372</v>
       </c>
       <c r="C90" t="s">
-        <v>289</v>
+        <v>516</v>
       </c>
       <c r="D90" t="s">
-        <v>288</v>
+        <v>515</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12523,7 +12664,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>476</v>
+        <v>520</v>
       </c>
       <c r="N90">
         <v>5000</v>
@@ -12541,10 +12682,10 @@
         <v>372</v>
       </c>
       <c r="C91" t="s">
-        <v>331</v>
+        <v>517</v>
       </c>
       <c r="D91" t="s">
-        <v>330</v>
+        <v>514</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12571,7 +12712,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12589,10 +12730,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>462</v>
+        <v>513</v>
       </c>
       <c r="D92" t="s">
-        <v>461</v>
+        <v>512</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12619,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12637,10 +12778,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>333</v>
+        <v>510</v>
       </c>
       <c r="D93" t="s">
-        <v>332</v>
+        <v>509</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12667,7 +12808,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>427</v>
+        <v>511</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12685,10 +12826,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>447</v>
+        <v>289</v>
       </c>
       <c r="D94" t="s">
-        <v>471</v>
+        <v>288</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12715,7 +12856,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12733,10 +12874,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="D95" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -12763,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>419</v>
+        <v>469</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -12781,10 +12922,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>279</v>
+        <v>461</v>
       </c>
       <c r="D96" t="s">
-        <v>277</v>
+        <v>460</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12811,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>423</v>
+        <v>508</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -12829,10 +12970,10 @@
         <v>372</v>
       </c>
       <c r="C97" t="s">
-        <v>430</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s">
-        <v>429</v>
+        <v>332</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -12859,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -12877,10 +13018,10 @@
         <v>372</v>
       </c>
       <c r="C98" t="s">
-        <v>281</v>
+        <v>446</v>
       </c>
       <c r="D98" t="s">
-        <v>282</v>
+        <v>470</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -12907,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -12925,10 +13066,10 @@
         <v>372</v>
       </c>
       <c r="C99" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="D99" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -12955,7 +13096,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -12973,10 +13114,10 @@
         <v>372</v>
       </c>
       <c r="C100" t="s">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="D100" t="s">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13003,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13021,10 +13162,10 @@
         <v>372</v>
       </c>
       <c r="C101" t="s">
-        <v>313</v>
+        <v>429</v>
       </c>
       <c r="D101" t="s">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13051,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13069,10 +13210,10 @@
         <v>372</v>
       </c>
       <c r="C102" t="s">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="D102" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13099,7 +13240,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13117,10 +13258,10 @@
         <v>372</v>
       </c>
       <c r="C103" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="D103" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13147,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13165,10 +13306,10 @@
         <v>372</v>
       </c>
       <c r="C104" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D104" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13195,7 +13336,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>420</v>
+        <v>469</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13213,10 +13354,10 @@
         <v>372</v>
       </c>
       <c r="C105" t="s">
-        <v>438</v>
+        <v>313</v>
       </c>
       <c r="D105" t="s">
-        <v>437</v>
+        <v>314</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13243,7 +13384,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13261,10 +13402,10 @@
         <v>372</v>
       </c>
       <c r="C106" t="s">
-        <v>468</v>
+        <v>326</v>
       </c>
       <c r="D106" t="s">
-        <v>467</v>
+        <v>327</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13291,7 +13432,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13309,10 +13450,10 @@
         <v>372</v>
       </c>
       <c r="C107" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="D107" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13339,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>425</v>
+        <v>474</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13357,10 +13498,10 @@
         <v>372</v>
       </c>
       <c r="C108" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D108" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13387,7 +13528,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13405,10 +13546,10 @@
         <v>372</v>
       </c>
       <c r="C109" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13435,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13453,10 +13594,10 @@
         <v>372</v>
       </c>
       <c r="C110" t="s">
-        <v>284</v>
+        <v>467</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>466</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13483,7 +13624,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>422</v>
+        <v>469</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13501,10 +13642,10 @@
         <v>372</v>
       </c>
       <c r="C111" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D111" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13531,7 +13672,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13549,10 +13690,10 @@
         <v>372</v>
       </c>
       <c r="C112" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D112" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13579,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13597,10 +13738,10 @@
         <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="D113" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13627,7 +13768,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13645,10 +13786,10 @@
         <v>372</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
+        <v>284</v>
       </c>
       <c r="D114" t="s">
-        <v>343</v>
+        <v>285</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13675,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>470</v>
+        <v>519</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13693,10 +13834,10 @@
         <v>372</v>
       </c>
       <c r="C115" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D115" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13723,7 +13864,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13741,10 +13882,10 @@
         <v>372</v>
       </c>
       <c r="C116" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D116" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -13771,7 +13912,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -13789,10 +13930,10 @@
         <v>372</v>
       </c>
       <c r="C117" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D117" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -13819,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -13837,10 +13978,10 @@
         <v>372</v>
       </c>
       <c r="C118" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D118" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -13867,7 +14008,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -13885,10 +14026,10 @@
         <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D119" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -13915,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -13933,10 +14074,10 @@
         <v>372</v>
       </c>
       <c r="C120" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D120" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -13963,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -13981,10 +14122,10 @@
         <v>372</v>
       </c>
       <c r="C121" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="D121" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14011,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14029,10 +14170,10 @@
         <v>372</v>
       </c>
       <c r="C122" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="D122" t="s">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14059,7 +14200,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14077,10 +14218,10 @@
         <v>372</v>
       </c>
       <c r="C123" t="s">
-        <v>465</v>
+        <v>356</v>
       </c>
       <c r="D123" t="s">
-        <v>463</v>
+        <v>353</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14107,7 +14248,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14125,10 +14266,10 @@
         <v>372</v>
       </c>
       <c r="C124" t="s">
-        <v>466</v>
+        <v>357</v>
       </c>
       <c r="D124" t="s">
-        <v>464</v>
+        <v>354</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14155,7 +14296,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14164,147 +14305,147 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="125" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="12">
+    <row r="125" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B125" t="s">
         <v>372</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E125" s="12">
+      <c r="C125" t="s">
+        <v>315</v>
+      </c>
+      <c r="D125" t="s">
+        <v>316</v>
+      </c>
+      <c r="E125">
         <v>500</v>
       </c>
-      <c r="F125" s="12">
+      <c r="F125">
         <v>150</v>
       </c>
-      <c r="G125" s="12">
-        <v>0</v>
-      </c>
-      <c r="H125" s="12">
-        <v>0</v>
-      </c>
-      <c r="I125" s="12">
-        <v>0</v>
-      </c>
-      <c r="J125" s="12">
-        <v>0</v>
-      </c>
-      <c r="K125" s="12">
-        <v>0</v>
-      </c>
-      <c r="L125" s="12">
-        <v>0</v>
-      </c>
-      <c r="M125" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N125" s="12">
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="N125">
         <v>5000</v>
       </c>
-      <c r="O125" s="12">
+      <c r="O125">
         <v>5000</v>
       </c>
     </row>
-    <row r="126" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="12">
+    <row r="126" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="B126" t="s">
         <v>372</v>
       </c>
-      <c r="C126" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="D126" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E126" s="12">
+      <c r="C126" t="s">
+        <v>308</v>
+      </c>
+      <c r="D126" t="s">
+        <v>309</v>
+      </c>
+      <c r="E126">
         <v>500</v>
       </c>
-      <c r="F126" s="12">
+      <c r="F126">
         <v>150</v>
       </c>
-      <c r="G126" s="12">
-        <v>0</v>
-      </c>
-      <c r="H126" s="12">
-        <v>0</v>
-      </c>
-      <c r="I126" s="12">
-        <v>0</v>
-      </c>
-      <c r="J126" s="12">
-        <v>0</v>
-      </c>
-      <c r="K126" s="12">
-        <v>0</v>
-      </c>
-      <c r="L126" s="12">
-        <v>0</v>
-      </c>
-      <c r="M126" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N126" s="12">
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="N126">
         <v>5000</v>
       </c>
-      <c r="O126" s="12">
+      <c r="O126">
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="12">
+    <row r="127" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" t="s">
         <v>372</v>
       </c>
-      <c r="C127" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E127" s="12">
+      <c r="C127" t="s">
+        <v>464</v>
+      </c>
+      <c r="D127" t="s">
+        <v>462</v>
+      </c>
+      <c r="E127">
         <v>500</v>
       </c>
-      <c r="F127" s="12">
+      <c r="F127">
         <v>150</v>
       </c>
-      <c r="G127" s="12">
-        <v>0</v>
-      </c>
-      <c r="H127" s="12">
-        <v>0</v>
-      </c>
-      <c r="I127" s="12">
-        <v>0</v>
-      </c>
-      <c r="J127" s="12">
-        <v>0</v>
-      </c>
-      <c r="K127" s="12">
-        <v>0</v>
-      </c>
-      <c r="L127" s="12">
-        <v>0</v>
-      </c>
-      <c r="M127" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N127" s="12">
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="N127">
         <v>5000</v>
       </c>
-      <c r="O127" s="12">
+      <c r="O127">
         <v>5000</v>
       </c>
     </row>
@@ -14317,10 +14458,10 @@
         <v>372</v>
       </c>
       <c r="C128" t="s">
-        <v>364</v>
+        <v>465</v>
       </c>
       <c r="D128" t="s">
-        <v>363</v>
+        <v>463</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14347,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>426</v>
+        <v>469</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14356,51 +14497,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129">
+    <row r="129" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="12">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C129" t="s">
-        <v>366</v>
-      </c>
-      <c r="D129" t="s">
-        <v>365</v>
-      </c>
-      <c r="E129">
+      <c r="C129" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E129" s="12">
         <v>500</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="12">
         <v>150</v>
       </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" s="2" t="s">
+      <c r="G129" s="12">
+        <v>0</v>
+      </c>
+      <c r="H129" s="12">
+        <v>0</v>
+      </c>
+      <c r="I129" s="12">
+        <v>0</v>
+      </c>
+      <c r="J129" s="12">
+        <v>0</v>
+      </c>
+      <c r="K129" s="12">
+        <v>0</v>
+      </c>
+      <c r="L129" s="12">
+        <v>0</v>
+      </c>
+      <c r="M129" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N129">
+      <c r="N129" s="12">
         <v>5000</v>
       </c>
-      <c r="O129">
+      <c r="O129" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -14413,10 +14554,10 @@
         <v>372</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E130" s="12">
         <v>500</v>
@@ -14443,7 +14584,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="13" t="s">
-        <v>428</v>
+        <v>283</v>
       </c>
       <c r="N130" s="12">
         <v>5000</v>
@@ -14452,79 +14593,79 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131">
+    <row r="131" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="12">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C131" t="s">
-        <v>310</v>
-      </c>
-      <c r="D131" t="s">
-        <v>311</v>
-      </c>
-      <c r="E131">
+      <c r="C131" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E131" s="12">
         <v>500</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="12">
         <v>150</v>
       </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="N131">
+      <c r="G131" s="12">
+        <v>0</v>
+      </c>
+      <c r="H131" s="12">
+        <v>0</v>
+      </c>
+      <c r="I131" s="12">
+        <v>0</v>
+      </c>
+      <c r="J131" s="12">
+        <v>0</v>
+      </c>
+      <c r="K131" s="12">
+        <v>0</v>
+      </c>
+      <c r="L131" s="12">
+        <v>0</v>
+      </c>
+      <c r="M131" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="N131" s="12">
         <v>5000</v>
       </c>
-      <c r="O131">
+      <c r="O131" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>442</v>
+        <v>372</v>
       </c>
       <c r="C132" t="s">
-        <v>439</v>
+        <v>364</v>
       </c>
       <c r="D132" t="s">
-        <v>440</v>
+        <v>363</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G132">
         <v>0</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -14538,28 +14679,29 @@
       <c r="L132">
         <v>0</v>
       </c>
-      <c r="M132" t="s">
-        <v>441</v>
+      <c r="M132" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="N132">
-        <v>9999</v>
+        <v>5000</v>
       </c>
       <c r="O132">
-        <v>9999</v>
+        <v>5000</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133">
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>168</v>
+        <v>372</v>
       </c>
       <c r="C133" t="s">
-        <v>172</v>
+        <v>366</v>
       </c>
       <c r="D133" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14583,15 +14725,206 @@
         <v>0</v>
       </c>
       <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N133">
+        <v>5000</v>
+      </c>
+      <c r="O133">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="12">
+        <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E134" s="12">
+        <v>500</v>
+      </c>
+      <c r="F134" s="12">
+        <v>150</v>
+      </c>
+      <c r="G134" s="12">
+        <v>0</v>
+      </c>
+      <c r="H134" s="12">
+        <v>0</v>
+      </c>
+      <c r="I134" s="12">
+        <v>0</v>
+      </c>
+      <c r="J134" s="12">
+        <v>0</v>
+      </c>
+      <c r="K134" s="12">
+        <v>0</v>
+      </c>
+      <c r="L134" s="12">
+        <v>0</v>
+      </c>
+      <c r="M134" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="N134" s="12">
+        <v>5000</v>
+      </c>
+      <c r="O134" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>372</v>
+      </c>
+      <c r="C135" t="s">
+        <v>310</v>
+      </c>
+      <c r="D135" t="s">
+        <v>311</v>
+      </c>
+      <c r="E135">
+        <v>500</v>
+      </c>
+      <c r="F135">
+        <v>150</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="N135">
+        <v>5000</v>
+      </c>
+      <c r="O135">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <f>ROW()-2</f>
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>441</v>
+      </c>
+      <c r="C136" t="s">
+        <v>438</v>
+      </c>
+      <c r="D136" t="s">
+        <v>439</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
         <v>1</v>
       </c>
-      <c r="M133" s="2" t="s">
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" t="s">
+        <v>440</v>
+      </c>
+      <c r="N136">
+        <v>9999</v>
+      </c>
+      <c r="O136">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137">
+        <v>10000</v>
+      </c>
+      <c r="B137" t="s">
+        <v>168</v>
+      </c>
+      <c r="C137" t="s">
+        <v>172</v>
+      </c>
+      <c r="D137" t="s">
+        <v>173</v>
+      </c>
+      <c r="E137">
+        <v>500</v>
+      </c>
+      <c r="F137">
+        <v>150</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="N133">
+      <c r="N137">
         <v>9000</v>
       </c>
-      <c r="O133">
+      <c r="O137">
         <v>9000</v>
       </c>
     </row>
@@ -14650,10 +14983,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -14914,13 +15247,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -14962,13 +15295,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -15010,13 +15343,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -15394,7 +15727,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C17" t="s">
         <v>197</v>
@@ -15442,13 +15775,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D18" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456B8101-5A5A-4164-ACA1-15DD322E324B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF54D1F5-7966-42EC-AF09-E6A89C3ED22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="765" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2340" yWindow="585" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="525">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7867,6 +7867,30 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_chocolatemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコレートの教本</t>
+    <rPh sb="7" eb="9">
+      <t>キョウホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏お店で売ってる</t>
+    <rPh sb="0" eb="1">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8337,7 +8361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8403,7 +8427,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A135" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A136" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -12634,10 +12658,10 @@
         <v>372</v>
       </c>
       <c r="C90" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D90" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12664,7 +12688,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="N90">
         <v>5000</v>
@@ -12682,10 +12706,10 @@
         <v>372</v>
       </c>
       <c r="C91" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D91" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12712,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12730,10 +12754,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D92" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12760,7 +12784,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12778,10 +12802,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D93" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12808,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12826,10 +12850,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>289</v>
+        <v>510</v>
       </c>
       <c r="D94" t="s">
-        <v>288</v>
+        <v>509</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12856,7 +12880,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12874,10 +12898,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="D95" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -12904,7 +12928,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -12922,10 +12946,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>461</v>
+        <v>331</v>
       </c>
       <c r="D96" t="s">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12952,7 +12976,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -12970,10 +12994,10 @@
         <v>372</v>
       </c>
       <c r="C97" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="D97" t="s">
-        <v>332</v>
+        <v>460</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -13000,7 +13024,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>426</v>
+        <v>508</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13018,10 +13042,10 @@
         <v>372</v>
       </c>
       <c r="C98" t="s">
-        <v>446</v>
+        <v>333</v>
       </c>
       <c r="D98" t="s">
-        <v>470</v>
+        <v>332</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13048,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13066,10 +13090,10 @@
         <v>372</v>
       </c>
       <c r="C99" t="s">
-        <v>370</v>
+        <v>446</v>
       </c>
       <c r="D99" t="s">
-        <v>369</v>
+        <v>470</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13096,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>419</v>
+        <v>471</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13114,10 +13138,10 @@
         <v>372</v>
       </c>
       <c r="C100" t="s">
-        <v>279</v>
+        <v>370</v>
       </c>
       <c r="D100" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13144,7 +13168,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13162,10 +13186,10 @@
         <v>372</v>
       </c>
       <c r="C101" t="s">
-        <v>429</v>
+        <v>279</v>
       </c>
       <c r="D101" t="s">
-        <v>428</v>
+        <v>277</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13192,7 +13216,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13210,10 +13234,10 @@
         <v>372</v>
       </c>
       <c r="C102" t="s">
-        <v>281</v>
+        <v>429</v>
       </c>
       <c r="D102" t="s">
-        <v>282</v>
+        <v>428</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13240,7 +13264,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13258,10 +13282,10 @@
         <v>372</v>
       </c>
       <c r="C103" t="s">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="D103" t="s">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13288,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13306,10 +13330,10 @@
         <v>372</v>
       </c>
       <c r="C104" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D104" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13354,10 +13378,10 @@
         <v>372</v>
       </c>
       <c r="C105" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D105" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13402,10 +13426,10 @@
         <v>372</v>
       </c>
       <c r="C106" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D106" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13450,10 +13474,10 @@
         <v>372</v>
       </c>
       <c r="C107" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="D107" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13480,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13498,10 +13522,10 @@
         <v>372</v>
       </c>
       <c r="C108" t="s">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="D108" t="s">
-        <v>328</v>
+        <v>286</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13528,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>420</v>
+        <v>474</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13546,10 +13570,10 @@
         <v>372</v>
       </c>
       <c r="C109" t="s">
-        <v>437</v>
+        <v>329</v>
       </c>
       <c r="D109" t="s">
-        <v>436</v>
+        <v>328</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13576,7 +13600,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>469</v>
+        <v>420</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13594,10 +13618,10 @@
         <v>372</v>
       </c>
       <c r="C110" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="D110" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13642,10 +13666,10 @@
         <v>372</v>
       </c>
       <c r="C111" t="s">
-        <v>336</v>
+        <v>467</v>
       </c>
       <c r="D111" t="s">
-        <v>334</v>
+        <v>466</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13672,7 +13696,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13690,10 +13714,10 @@
         <v>372</v>
       </c>
       <c r="C112" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D112" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13720,7 +13744,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13738,10 +13762,10 @@
         <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D113" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13768,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13786,10 +13810,10 @@
         <v>372</v>
       </c>
       <c r="C114" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="D114" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13816,7 +13840,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>519</v>
+        <v>469</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13834,10 +13858,10 @@
         <v>372</v>
       </c>
       <c r="C115" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="D115" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13864,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>469</v>
+        <v>519</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13882,10 +13906,10 @@
         <v>372</v>
       </c>
       <c r="C116" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D116" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -13930,10 +13954,10 @@
         <v>372</v>
       </c>
       <c r="C117" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D117" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -13960,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -13978,10 +14002,10 @@
         <v>372</v>
       </c>
       <c r="C118" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D118" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14008,7 +14032,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14026,10 +14050,10 @@
         <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D119" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14074,10 +14098,10 @@
         <v>372</v>
       </c>
       <c r="C120" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D120" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14104,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14122,10 +14146,10 @@
         <v>372</v>
       </c>
       <c r="C121" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D121" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14152,7 +14176,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14170,10 +14194,10 @@
         <v>372</v>
       </c>
       <c r="C122" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D122" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14218,10 +14242,10 @@
         <v>372</v>
       </c>
       <c r="C123" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D123" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14248,7 +14272,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14266,10 +14290,10 @@
         <v>372</v>
       </c>
       <c r="C124" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D124" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14296,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>469</v>
+        <v>423</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14314,10 +14338,10 @@
         <v>372</v>
       </c>
       <c r="C125" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="D125" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14344,7 +14368,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14362,10 +14386,10 @@
         <v>372</v>
       </c>
       <c r="C126" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D126" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14392,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>421</v>
+        <v>474</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14410,10 +14434,10 @@
         <v>372</v>
       </c>
       <c r="C127" t="s">
-        <v>464</v>
+        <v>308</v>
       </c>
       <c r="D127" t="s">
-        <v>462</v>
+        <v>309</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14440,7 +14464,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14458,10 +14482,10 @@
         <v>372</v>
       </c>
       <c r="C128" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D128" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14488,7 +14512,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14497,51 +14521,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="129" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="12">
+    <row r="129" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A129">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" t="s">
         <v>372</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E129" s="12">
+      <c r="C129" t="s">
+        <v>465</v>
+      </c>
+      <c r="D129" t="s">
+        <v>463</v>
+      </c>
+      <c r="E129">
         <v>500</v>
       </c>
-      <c r="F129" s="12">
+      <c r="F129">
         <v>150</v>
       </c>
-      <c r="G129" s="12">
-        <v>0</v>
-      </c>
-      <c r="H129" s="12">
-        <v>0</v>
-      </c>
-      <c r="I129" s="12">
-        <v>0</v>
-      </c>
-      <c r="J129" s="12">
-        <v>0</v>
-      </c>
-      <c r="K129" s="12">
-        <v>0</v>
-      </c>
-      <c r="L129" s="12">
-        <v>0</v>
-      </c>
-      <c r="M129" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N129" s="12">
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N129">
         <v>5000</v>
       </c>
-      <c r="O129" s="12">
+      <c r="O129">
         <v>5000</v>
       </c>
     </row>
@@ -14554,10 +14578,10 @@
         <v>372</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E130" s="12">
         <v>500</v>
@@ -14602,10 +14626,10 @@
         <v>372</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E131" s="12">
         <v>500</v>
@@ -14641,51 +14665,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132">
+    <row r="132" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="12">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C132" t="s">
-        <v>364</v>
-      </c>
-      <c r="D132" t="s">
-        <v>363</v>
-      </c>
-      <c r="E132">
+      <c r="C132" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E132" s="12">
         <v>500</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="12">
         <v>150</v>
       </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="N132">
+      <c r="G132" s="12">
+        <v>0</v>
+      </c>
+      <c r="H132" s="12">
+        <v>0</v>
+      </c>
+      <c r="I132" s="12">
+        <v>0</v>
+      </c>
+      <c r="J132" s="12">
+        <v>0</v>
+      </c>
+      <c r="K132" s="12">
+        <v>0</v>
+      </c>
+      <c r="L132" s="12">
+        <v>0</v>
+      </c>
+      <c r="M132" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="N132" s="12">
         <v>5000</v>
       </c>
-      <c r="O132">
+      <c r="O132" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -14698,10 +14722,10 @@
         <v>372</v>
       </c>
       <c r="C133" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D133" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14728,7 +14752,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14737,194 +14761,242 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="12">
+    <row r="134" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="D134" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E134" s="12">
+      <c r="C134" t="s">
+        <v>366</v>
+      </c>
+      <c r="D134" t="s">
+        <v>365</v>
+      </c>
+      <c r="E134">
         <v>500</v>
       </c>
-      <c r="F134" s="12">
+      <c r="F134">
         <v>150</v>
       </c>
-      <c r="G134" s="12">
-        <v>0</v>
-      </c>
-      <c r="H134" s="12">
-        <v>0</v>
-      </c>
-      <c r="I134" s="12">
-        <v>0</v>
-      </c>
-      <c r="J134" s="12">
-        <v>0</v>
-      </c>
-      <c r="K134" s="12">
-        <v>0</v>
-      </c>
-      <c r="L134" s="12">
-        <v>0</v>
-      </c>
-      <c r="M134" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="N134" s="12">
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N134">
         <v>5000</v>
       </c>
-      <c r="O134" s="12">
+      <c r="O134">
         <v>5000</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135">
+    <row r="135" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="12">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E135" s="12">
+        <v>500</v>
+      </c>
+      <c r="F135" s="12">
+        <v>150</v>
+      </c>
+      <c r="G135" s="12">
+        <v>0</v>
+      </c>
+      <c r="H135" s="12">
+        <v>0</v>
+      </c>
+      <c r="I135" s="12">
+        <v>0</v>
+      </c>
+      <c r="J135" s="12">
+        <v>0</v>
+      </c>
+      <c r="K135" s="12">
+        <v>0</v>
+      </c>
+      <c r="L135" s="12">
+        <v>0</v>
+      </c>
+      <c r="M135" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="N135" s="12">
+        <v>5000</v>
+      </c>
+      <c r="O135" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <f t="shared" si="0"/>
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>372</v>
+      </c>
+      <c r="C136" t="s">
         <v>310</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D136" t="s">
         <v>311</v>
       </c>
-      <c r="E135">
+      <c r="E136">
         <v>500</v>
       </c>
-      <c r="F135">
+      <c r="F136">
         <v>150</v>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" s="2" t="s">
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="N135">
+      <c r="N136">
         <v>5000</v>
       </c>
-      <c r="O135">
+      <c r="O136">
         <v>5000</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136">
+    <row r="137" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137">
         <f>ROW()-2</f>
-        <v>134</v>
-      </c>
-      <c r="B136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" t="s">
         <v>441</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C137" t="s">
         <v>438</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D137" t="s">
         <v>439</v>
       </c>
-      <c r="E136">
-        <v>0</v>
-      </c>
-      <c r="F136">
-        <v>0</v>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
         <v>1</v>
       </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="s">
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="s">
         <v>440</v>
       </c>
-      <c r="N136">
+      <c r="N137">
         <v>9999</v>
       </c>
-      <c r="O136">
+      <c r="O137">
         <v>9999</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137">
+    <row r="138" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138">
         <v>10000</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B138" t="s">
         <v>168</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C138" t="s">
         <v>172</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D138" t="s">
         <v>173</v>
       </c>
-      <c r="E137">
+      <c r="E138">
         <v>500</v>
       </c>
-      <c r="F137">
+      <c r="F138">
         <v>150</v>
       </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
         <v>1</v>
       </c>
-      <c r="M137" s="2" t="s">
+      <c r="M138" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="N137">
+      <c r="N138">
         <v>9000</v>
       </c>
-      <c r="O137">
+      <c r="O138">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF54D1F5-7966-42EC-AF09-E6A89C3ED22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63E1F3F-2F5D-4419-B21E-920F54F5FE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="585" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2340" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="532">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -4572,63 +4572,6 @@
     </rPh>
     <rPh sb="233" eb="234">
       <t>タノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【ポテトの宝石箱のレシピ】
-ポテト好きにたまらない..
-ポテトの宝石箱のレシピです。
-作り方は簡単♪
-①じゃが、さつまいもに&lt;color=#BA9535FF&gt;塩&lt;/color&gt;をかけて、&lt;color=#FF5CA1FF&gt;「フライヤー」&lt;/color&gt;であげてしまいます。
-※注意：芋は、別々に揚げましょう。
-②それぞれの&lt;color=#BA9535FF&gt;フライドおいも&lt;/color&gt;をミックスし、その上に&lt;color=#BA9535FF&gt;バター&lt;/color&gt;をかけて、完成♪
-まさに・・！　大地の恵の味・・！
-芋同士のそれぞれの味わいを一つにまとめた、珠玉のお菓子です。</t>
-    <rPh sb="18" eb="19">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>ホウセキバコ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カンタン</t>
-    </rPh>
-    <rPh sb="81" eb="82">
-      <t>シオ</t>
-    </rPh>
-    <rPh sb="204" eb="205">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="251" eb="253">
-      <t>ダイチ</t>
-    </rPh>
-    <rPh sb="254" eb="255">
-      <t>メグミ</t>
-    </rPh>
-    <rPh sb="256" eb="257">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="261" eb="264">
-      <t>イモドウシ</t>
-    </rPh>
-    <rPh sb="270" eb="271">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="274" eb="275">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="282" eb="284">
-      <t>シュギョク</t>
-    </rPh>
-    <rPh sb="286" eb="288">
-      <t>カシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7584,20 +7527,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【ふたりのおうちのレシピメモ】
-ヒカリがいうには、
-&lt;color=#BA9535FF&gt;くまさんチョコレートのおにいさんといもうと&lt;/color&gt;を、
-おかしのおうちに、&lt;color=#FF5CA1FF&gt;一緒に&lt;/color&gt;のせると、
-すごいお菓子ができる.. かもしれない。</t>
-    <rPh sb="104" eb="106">
-      <t>イッショ</t>
-    </rPh>
-    <rPh sb="126" eb="128">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ふたりのおうちのレシピ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7891,6 +7820,165 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコバナナクレープのレシピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocobanana_crepe_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">シンプルなホイップクレープに&lt;color=#BA9535FF&gt;バナナ&lt;/color&gt;をトッピング。
+その上から、&lt;color=#BA9535FF&gt;チョコペン&lt;/color&gt;でチョコレートをトッピングすれば完成！！
+ミントを添えると、色合いともによく合います☆
+</t>
+    <rPh sb="53" eb="54">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>ソ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>イロア</t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/crepe_chocobanana</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ポテトの宝石箱のレシピ】
+ポテト好きにたまらない..
+ポテトの宝石箱のレシピです。
+作り方は簡単♪
+①じゃが、さつまいもに&lt;color=#BA9535FF&gt;塩&lt;/color&gt;をかけて、&lt;color=#FF5CA1FF&gt;「フライヤー」&lt;/color&gt;であげてしまいます。
+※注意：芋は、別々に揚げましょう。
+②それぞれの&lt;color=#BA9535FF&gt;フライドおいも&lt;/color&gt;をミックスし、その上に&lt;color=#BA9535FF&gt;バター&lt;/color&gt;をかけて、完成♪
+まさに・・！　北海、大地の恵の味・・！
+芋同士のそれぞれの味わいを一つにまとめた、珠玉のお菓子です。
+バターが効いておいしいです。ぜひお試しあれ☆</t>
+    <rPh sb="18" eb="19">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>ホウセキバコ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>シオ</t>
+    </rPh>
+    <rPh sb="204" eb="205">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="251" eb="253">
+      <t>ホッカイ</t>
+    </rPh>
+    <rPh sb="254" eb="256">
+      <t>ダイチ</t>
+    </rPh>
+    <rPh sb="257" eb="258">
+      <t>メグミ</t>
+    </rPh>
+    <rPh sb="259" eb="260">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="264" eb="267">
+      <t>イモドウシ</t>
+    </rPh>
+    <rPh sb="273" eb="274">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="277" eb="278">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="285" eb="287">
+      <t>シュギョク</t>
+    </rPh>
+    <rPh sb="289" eb="291">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="300" eb="301">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="313" eb="314">
+      <t>タメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フライドポテトのレシピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>potatefried_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ふたりのおうちのレシピメモ】
+ヒカリがいうには、
+&lt;color=#BA9535FF&gt;くまさんチョコレートのおにいさんといもうと&lt;/color&gt;を、
+おかしのおうちに、一緒にのせたいらしい・・。</t>
+    <rPh sb="87" eb="89">
+      <t>イッショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【フライドポテトのレシピ】
+とってもシンプルで、サクサクなフライドポテトの作り方。
+①&lt;color=#BA9535FF&gt;じゃがいも&lt;/color&gt;に&lt;color=#BA9535FF&gt;塩&lt;/color&gt;をまぶし、&lt;color=#FF5CA1FF&gt;フライヤー&lt;/color&gt;で揚げてみましょう。
+ほっくほっくでアツアツのフライドポテト♪
+子供も大人もみ～んな大好き！！
+そんなスナック感覚のおやつです！
+※じゃがいもの代わりに、さつまいもを揚げてもおいしいかも・・？</t>
+    <rPh sb="38" eb="39">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>シオ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="181" eb="183">
+      <t>ダイス</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="212" eb="213">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="223" eb="224">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7936,7 +8024,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7985,6 +8073,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -8000,7 +8094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8045,6 +8139,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8361,7 +8461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8407,10 +8507,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8427,7 +8527,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A136" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A138" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -8512,7 +8612,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8896,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9010,10 +9110,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9040,7 +9140,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9058,10 +9158,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9088,7 +9188,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9106,10 +9206,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -9136,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -9154,10 +9254,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9184,7 +9284,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9199,19 +9299,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>526</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>524</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>523</v>
       </c>
       <c r="E18">
         <v>500</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -9232,13 +9332,13 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>100</v>
+        <v>525</v>
       </c>
       <c r="N18">
-        <v>3010</v>
+        <v>3150</v>
       </c>
       <c r="O18">
-        <v>3010</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9247,19 +9347,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>500</v>
       </c>
       <c r="F19">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -9280,13 +9380,13 @@
         <v>1</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="O19">
-        <v>3030</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9295,19 +9395,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>500</v>
       </c>
       <c r="F20">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -9328,13 +9428,13 @@
         <v>1</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="N20">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="O20">
-        <v>3040</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9343,13 +9443,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>500</v>
@@ -9376,13 +9476,13 @@
         <v>1</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="N21">
-        <v>3060</v>
+        <v>3040</v>
       </c>
       <c r="O21">
-        <v>3060</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9391,19 +9491,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E22">
         <v>500</v>
       </c>
       <c r="F22">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -9424,13 +9524,13 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>199</v>
+        <v>94</v>
       </c>
       <c r="N22">
-        <v>20</v>
+        <v>3060</v>
       </c>
       <c r="O22">
-        <v>20</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9439,19 +9539,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="E23">
         <v>500</v>
       </c>
       <c r="F23">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -9472,13 +9572,13 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>468</v>
+        <v>199</v>
       </c>
       <c r="N23">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O23">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9487,19 +9587,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>500</v>
       </c>
       <c r="F24">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -9520,13 +9620,13 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="N24">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O24">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9535,13 +9635,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -9568,13 +9668,13 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>251</v>
+        <v>492</v>
       </c>
       <c r="N25">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O25">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9583,19 +9683,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="E26">
         <v>500</v>
       </c>
       <c r="F26">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -9616,13 +9716,13 @@
         <v>1</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="N26">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O26">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9631,13 +9731,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E27">
         <v>500</v>
@@ -9664,13 +9764,13 @@
         <v>1</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="N27">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O27">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9679,13 +9779,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>500</v>
@@ -9712,13 +9812,13 @@
         <v>1</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N28">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O28">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9727,13 +9827,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="E29">
         <v>500</v>
@@ -9760,13 +9860,13 @@
         <v>1</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>252</v>
+        <v>87</v>
       </c>
       <c r="N29">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O29">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9775,13 +9875,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="E30">
         <v>500</v>
@@ -9808,13 +9908,13 @@
         <v>1</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>67</v>
+        <v>252</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9823,13 +9923,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E31">
         <v>500</v>
@@ -9856,13 +9956,13 @@
         <v>1</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="N31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9871,13 +9971,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E32">
         <v>500</v>
@@ -9904,13 +10004,13 @@
         <v>1</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N32">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O32">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9919,13 +10019,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="E33">
         <v>500</v>
@@ -9952,13 +10052,13 @@
         <v>1</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>458</v>
+        <v>56</v>
       </c>
       <c r="N33">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O33">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9967,13 +10067,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>453</v>
+        <v>155</v>
       </c>
       <c r="C34" t="s">
-        <v>451</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>452</v>
+        <v>118</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -10000,13 +10100,13 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N34">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="O34">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10015,13 +10115,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>452</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>450</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>451</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10048,13 +10148,13 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>123</v>
+        <v>458</v>
       </c>
       <c r="N35">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="O35">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10063,13 +10163,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="E36">
         <v>500</v>
@@ -10096,13 +10196,13 @@
         <v>1</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="N36">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O36">
-        <v>200</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10111,13 +10211,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="E37">
         <v>500</v>
@@ -10144,13 +10244,13 @@
         <v>1</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N37">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="O37">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10159,13 +10259,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E38">
         <v>500</v>
@@ -10192,13 +10292,13 @@
         <v>1</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="N38">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="O38">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10207,13 +10307,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -10240,13 +10340,13 @@
         <v>1</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="N39">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="O39">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10255,13 +10355,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -10288,13 +10388,13 @@
         <v>1</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="N40">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O40">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10303,13 +10403,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -10336,13 +10436,13 @@
         <v>1</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N41">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O41">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10351,13 +10451,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="E42">
         <v>500</v>
@@ -10384,13 +10484,13 @@
         <v>1</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="N42">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="O42">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10399,13 +10499,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>163</v>
+        <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="E43">
         <v>500</v>
@@ -10432,13 +10532,13 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>485</v>
+        <v>159</v>
       </c>
       <c r="N43">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O43">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10447,13 +10547,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -10480,13 +10580,13 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>178</v>
+        <v>484</v>
       </c>
       <c r="N44">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="O44">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10495,13 +10595,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -10528,13 +10628,13 @@
         <v>1</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="N45">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="O45">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10543,13 +10643,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D46" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -10576,124 +10676,124 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N46">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="O46">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="4" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="4">
+    <row r="47" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" t="s">
         <v>193</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E47" s="4">
+      <c r="C47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47">
         <v>500</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47">
         <v>150</v>
       </c>
-      <c r="G47" s="4">
-        <v>0</v>
-      </c>
-      <c r="H47" s="4">
-        <v>0</v>
-      </c>
-      <c r="I47" s="4">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4">
-        <v>0</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="N47" s="4">
-        <v>9999</v>
-      </c>
-      <c r="O47" s="4">
-        <v>9999</v>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="N47">
+        <v>300</v>
+      </c>
+      <c r="O47">
+        <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48">
+    <row r="48" spans="1:15" s="4" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" t="s">
-        <v>373</v>
-      </c>
-      <c r="C48" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" t="s">
-        <v>195</v>
-      </c>
-      <c r="E48">
+      <c r="B48" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E48" s="4">
         <v>500</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="4">
         <v>150</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="N48">
-        <v>310</v>
-      </c>
-      <c r="O48">
-        <v>310</v>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="N48" s="4">
+        <v>9999</v>
+      </c>
+      <c r="O48" s="4">
+        <v>9999</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C49" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -10720,13 +10820,13 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>202</v>
+        <v>434</v>
       </c>
       <c r="N49">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="O49">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10735,13 +10835,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D50" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10768,13 +10868,13 @@
         <v>1</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N50">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="O50">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10783,13 +10883,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D51" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10816,13 +10916,13 @@
         <v>1</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>402</v>
+        <v>205</v>
       </c>
       <c r="N51">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="O51">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10831,13 +10931,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10864,13 +10964,13 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N52">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="O52">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10879,13 +10979,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -10912,13 +11012,13 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>317</v>
+        <v>403</v>
       </c>
       <c r="N53">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="O53">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10927,13 +11027,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C54" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -10960,13 +11060,13 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>447</v>
+        <v>317</v>
       </c>
       <c r="N54">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="O54">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10975,13 +11075,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -11008,13 +11108,13 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N55">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="O55">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11023,13 +11123,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C56" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D56" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -11056,109 +11156,109 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N56">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="O56">
-        <v>390</v>
+        <v>380</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="8">
+    <row r="57" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="E57" s="8">
+      <c r="B57" t="s">
+        <v>381</v>
+      </c>
+      <c r="C57" t="s">
+        <v>275</v>
+      </c>
+      <c r="D57" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57">
         <v>500</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57">
         <v>150</v>
       </c>
-      <c r="G57" s="8">
-        <v>0</v>
-      </c>
-      <c r="H57" s="8">
-        <v>0</v>
-      </c>
-      <c r="I57" s="8">
-        <v>0</v>
-      </c>
-      <c r="J57" s="8">
-        <v>0</v>
-      </c>
-      <c r="K57" s="8">
-        <v>0</v>
-      </c>
-      <c r="L57" s="8">
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
         <v>1</v>
       </c>
-      <c r="M57" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="N57" s="8">
-        <v>400</v>
-      </c>
-      <c r="O57" s="8">
-        <v>400</v>
+      <c r="M57" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="N57">
+        <v>390</v>
+      </c>
+      <c r="O57">
+        <v>390</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58">
+    <row r="58" spans="1:15" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="8">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" t="s">
-        <v>382</v>
-      </c>
-      <c r="C58" t="s">
-        <v>211</v>
-      </c>
-      <c r="D58" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58">
+      <c r="B58" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E58" s="8">
         <v>500</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="8">
         <v>150</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
+      <c r="G58" s="8">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>0</v>
+      </c>
+      <c r="I58" s="8">
+        <v>0</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
         <v>1</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="N58">
-        <v>410</v>
-      </c>
-      <c r="O58">
-        <v>410</v>
+      <c r="M58" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="N58" s="8">
+        <v>400</v>
+      </c>
+      <c r="O58" s="8">
+        <v>400</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11167,13 +11267,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C59" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D59" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -11200,13 +11300,13 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N59">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="O59">
-        <v>500</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11215,13 +11315,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D60" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -11248,13 +11348,13 @@
         <v>1</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="O60">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11263,13 +11363,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -11296,13 +11396,13 @@
         <v>1</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>404</v>
+        <v>254</v>
       </c>
       <c r="N61">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="O61">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11311,13 +11411,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -11344,13 +11444,13 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N62">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="O62">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11359,13 +11459,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>385</v>
       </c>
       <c r="C63" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D63" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -11392,61 +11492,61 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N63">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="O63">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64">
+    <row r="64" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="16">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" t="s">
-        <v>386</v>
-      </c>
-      <c r="C64" t="s">
-        <v>224</v>
-      </c>
-      <c r="D64" t="s">
-        <v>222</v>
-      </c>
-      <c r="E64">
+      <c r="B64" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E64" s="16">
         <v>500</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="16">
         <v>150</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
+      <c r="G64" s="16">
+        <v>0</v>
+      </c>
+      <c r="H64" s="16">
+        <v>0</v>
+      </c>
+      <c r="I64" s="16">
+        <v>0</v>
+      </c>
+      <c r="J64" s="16">
+        <v>0</v>
+      </c>
+      <c r="K64" s="16">
+        <v>0</v>
+      </c>
+      <c r="L64" s="16">
         <v>1</v>
       </c>
-      <c r="M64" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="N64">
-        <v>550</v>
-      </c>
-      <c r="O64">
-        <v>550</v>
+      <c r="M64" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="N64" s="16">
+        <v>535</v>
+      </c>
+      <c r="O64" s="16">
+        <v>535</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11455,13 +11555,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>387</v>
+        <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E65">
         <v>500</v>
@@ -11488,13 +11588,13 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>408</v>
+        <v>527</v>
       </c>
       <c r="N65">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="O65">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11503,13 +11603,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C66" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D66" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -11536,13 +11636,13 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="N66">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="O66">
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11551,13 +11651,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C67" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D67" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E67">
         <v>500</v>
@@ -11584,13 +11684,13 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>256</v>
+        <v>407</v>
       </c>
       <c r="N67">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="O67">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11599,13 +11699,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C68" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D68" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -11632,61 +11732,61 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>273</v>
+        <v>408</v>
       </c>
       <c r="N68">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="O68">
-        <v>590</v>
+        <v>570</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="6">
+    <row r="69" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E69" s="6">
+      <c r="B69" t="s">
+        <v>389</v>
+      </c>
+      <c r="C69" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" t="s">
+        <v>227</v>
+      </c>
+      <c r="E69">
         <v>500</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69">
         <v>150</v>
       </c>
-      <c r="G69" s="6">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6">
-        <v>0</v>
-      </c>
-      <c r="I69" s="6">
-        <v>0</v>
-      </c>
-      <c r="J69" s="6">
-        <v>0</v>
-      </c>
-      <c r="K69" s="6">
-        <v>0</v>
-      </c>
-      <c r="L69" s="6">
-        <v>0</v>
-      </c>
-      <c r="M69" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="N69" s="6">
-        <v>600</v>
-      </c>
-      <c r="O69" s="6">
-        <v>600</v>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="N69">
+        <v>580</v>
+      </c>
+      <c r="O69">
+        <v>580</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11695,13 +11795,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C70" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D70" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -11728,13 +11828,13 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>412</v>
+        <v>273</v>
       </c>
       <c r="N70">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="O70">
-        <v>610</v>
+        <v>590</v>
       </c>
     </row>
     <row r="71" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11746,10 +11846,10 @@
         <v>193</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="E71" s="6">
         <v>500</v>
@@ -11776,13 +11876,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="N71" s="6">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="O71" s="6">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11791,13 +11891,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C72" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D72" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -11824,61 +11924,61 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N72">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="O72">
-        <v>700</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73">
+    <row r="73" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="6">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="B73" t="s">
-        <v>392</v>
-      </c>
-      <c r="C73" t="s">
-        <v>260</v>
-      </c>
-      <c r="D73" t="s">
-        <v>259</v>
-      </c>
-      <c r="E73">
+      <c r="B73" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E73" s="6">
         <v>500</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="6">
         <v>150</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>1</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="N73">
-        <v>710</v>
-      </c>
-      <c r="O73">
-        <v>710</v>
+      <c r="G73" s="6">
+        <v>0</v>
+      </c>
+      <c r="H73" s="6">
+        <v>0</v>
+      </c>
+      <c r="I73" s="6">
+        <v>0</v>
+      </c>
+      <c r="J73" s="6">
+        <v>0</v>
+      </c>
+      <c r="K73" s="6">
+        <v>0</v>
+      </c>
+      <c r="L73" s="6">
+        <v>0</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="N73" s="6">
+        <v>620</v>
+      </c>
+      <c r="O73" s="6">
+        <v>620</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11887,13 +11987,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C74" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D74" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -11920,13 +12020,13 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="N74">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="O74">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11935,13 +12035,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C75" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D75" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -11968,13 +12068,13 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N75">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="O75">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -11983,13 +12083,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C76" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D76" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -12016,13 +12116,13 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="N76">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="O76">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12031,13 +12131,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C77" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D77" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -12064,13 +12164,13 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N77">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="O77">
-        <v>750</v>
+        <v>730</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12079,13 +12179,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C78" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -12112,13 +12212,13 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>253</v>
+        <v>416</v>
       </c>
       <c r="N78">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="O78">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12127,13 +12227,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C79" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D79" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E79">
         <v>500</v>
@@ -12160,13 +12260,13 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>263</v>
+        <v>417</v>
       </c>
       <c r="N79">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="O79">
-        <v>770</v>
+        <v>750</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12175,13 +12275,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C80" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D80" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -12208,61 +12308,61 @@
         <v>1</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>411</v>
+        <v>253</v>
       </c>
       <c r="N80">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="O80">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
-    <row r="81" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="6">
+    <row r="81" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E81" s="6">
+      <c r="B81" t="s">
+        <v>398</v>
+      </c>
+      <c r="C81" t="s">
+        <v>262</v>
+      </c>
+      <c r="D81" t="s">
+        <v>261</v>
+      </c>
+      <c r="E81">
         <v>500</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81">
         <v>150</v>
       </c>
-      <c r="G81" s="6">
-        <v>0</v>
-      </c>
-      <c r="H81" s="6">
-        <v>0</v>
-      </c>
-      <c r="I81" s="6">
-        <v>0</v>
-      </c>
-      <c r="J81" s="6">
-        <v>0</v>
-      </c>
-      <c r="K81" s="6">
-        <v>0</v>
-      </c>
-      <c r="L81" s="6">
-        <v>0</v>
-      </c>
-      <c r="M81" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="N81" s="6">
-        <v>790</v>
-      </c>
-      <c r="O81" s="6">
-        <v>790</v>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="N81">
+        <v>770</v>
+      </c>
+      <c r="O81">
+        <v>770</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12271,13 +12371,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>492</v>
+        <v>401</v>
       </c>
       <c r="C82" t="s">
-        <v>489</v>
+        <v>269</v>
       </c>
       <c r="D82" t="s">
-        <v>491</v>
+        <v>268</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12289,7 +12389,7 @@
         <v>0</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -12304,61 +12404,61 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="N82">
-        <v>9999</v>
+        <v>780</v>
       </c>
       <c r="O82">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
-    <row r="83" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="10">
+    <row r="83" spans="1:15" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="6">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="E83" s="10">
+      <c r="C83" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E83" s="6">
         <v>500</v>
       </c>
-      <c r="F83" s="10">
+      <c r="F83" s="6">
         <v>150</v>
       </c>
-      <c r="G83" s="10">
-        <v>0</v>
-      </c>
-      <c r="H83" s="10">
-        <v>0</v>
-      </c>
-      <c r="I83" s="10">
-        <v>0</v>
-      </c>
-      <c r="J83" s="10">
-        <v>0</v>
-      </c>
-      <c r="K83" s="10">
-        <v>0</v>
-      </c>
-      <c r="L83" s="10">
-        <v>0</v>
-      </c>
-      <c r="M83" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="N83" s="10">
-        <v>9999</v>
-      </c>
-      <c r="O83" s="10">
-        <v>9999</v>
+      <c r="G83" s="6">
+        <v>0</v>
+      </c>
+      <c r="H83" s="6">
+        <v>0</v>
+      </c>
+      <c r="I83" s="6">
+        <v>0</v>
+      </c>
+      <c r="J83" s="6">
+        <v>0</v>
+      </c>
+      <c r="K83" s="6">
+        <v>0</v>
+      </c>
+      <c r="L83" s="6">
+        <v>0</v>
+      </c>
+      <c r="M83" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="N83" s="6">
+        <v>790</v>
+      </c>
+      <c r="O83" s="6">
+        <v>790</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12367,13 +12467,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="C84" t="s">
-        <v>290</v>
+        <v>488</v>
       </c>
       <c r="D84" t="s">
-        <v>307</v>
+        <v>489</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12400,61 +12500,61 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="N84">
-        <v>2000</v>
+        <v>9999</v>
       </c>
       <c r="O84">
-        <v>2000</v>
+        <v>800</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85">
+    <row r="85" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="10">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B85" t="s">
-        <v>431</v>
-      </c>
-      <c r="C85" t="s">
-        <v>291</v>
-      </c>
-      <c r="D85" t="s">
-        <v>304</v>
-      </c>
-      <c r="E85">
+      <c r="B85" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E85" s="10">
         <v>500</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="10">
         <v>150</v>
       </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>1</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>1</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="N85">
-        <v>2100</v>
-      </c>
-      <c r="O85">
-        <v>2100</v>
+      <c r="G85" s="10">
+        <v>0</v>
+      </c>
+      <c r="H85" s="10">
+        <v>0</v>
+      </c>
+      <c r="I85" s="10">
+        <v>0</v>
+      </c>
+      <c r="J85" s="10">
+        <v>0</v>
+      </c>
+      <c r="K85" s="10">
+        <v>0</v>
+      </c>
+      <c r="L85" s="10">
+        <v>0</v>
+      </c>
+      <c r="M85" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="N85" s="10">
+        <v>9999</v>
+      </c>
+      <c r="O85" s="10">
+        <v>9999</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12463,13 +12563,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C86" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D86" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12496,13 +12596,13 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>443</v>
+        <v>491</v>
       </c>
       <c r="N86">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="O86">
-        <v>2200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12511,13 +12611,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C87" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D87" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12544,13 +12644,13 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="N87">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="O87">
-        <v>2300</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12559,13 +12659,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C88" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D88" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12592,13 +12692,13 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N88">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="O88">
-        <v>2400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12607,13 +12707,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="C89" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D89" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12625,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -12637,16 +12737,16 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>276</v>
+        <v>443</v>
       </c>
       <c r="N89">
-        <v>5000</v>
+        <v>2300</v>
       </c>
       <c r="O89">
-        <v>5000</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12655,13 +12755,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>372</v>
+        <v>433</v>
       </c>
       <c r="C90" t="s">
-        <v>522</v>
+        <v>294</v>
       </c>
       <c r="D90" t="s">
-        <v>523</v>
+        <v>312</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12673,7 +12773,7 @@
         <v>0</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -12685,16 +12785,16 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>524</v>
+        <v>444</v>
       </c>
       <c r="N90">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="O90">
-        <v>5000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -12706,10 +12806,10 @@
         <v>372</v>
       </c>
       <c r="C91" t="s">
-        <v>516</v>
+        <v>278</v>
       </c>
       <c r="D91" t="s">
-        <v>515</v>
+        <v>280</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12736,7 +12836,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>520</v>
+        <v>276</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12754,10 +12854,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D92" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12784,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12802,10 +12902,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
+        <v>514</v>
+      </c>
+      <c r="D93" t="s">
         <v>513</v>
-      </c>
-      <c r="D93" t="s">
-        <v>512</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12850,10 +12950,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D94" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12880,7 +12980,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12898,10 +12998,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>289</v>
+        <v>511</v>
       </c>
       <c r="D95" t="s">
-        <v>288</v>
+        <v>510</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -12928,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -12946,10 +13046,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>331</v>
+        <v>508</v>
       </c>
       <c r="D96" t="s">
-        <v>330</v>
+        <v>507</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -12976,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -12994,10 +13094,10 @@
         <v>372</v>
       </c>
       <c r="C97" t="s">
-        <v>461</v>
+        <v>289</v>
       </c>
       <c r="D97" t="s">
-        <v>460</v>
+        <v>288</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -13024,7 +13124,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13042,10 +13142,10 @@
         <v>372</v>
       </c>
       <c r="C98" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D98" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13072,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>426</v>
+        <v>468</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13090,10 +13190,10 @@
         <v>372</v>
       </c>
       <c r="C99" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D99" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13120,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>471</v>
+        <v>506</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13138,10 +13238,10 @@
         <v>372</v>
       </c>
       <c r="C100" t="s">
-        <v>370</v>
+        <v>333</v>
       </c>
       <c r="D100" t="s">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13168,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13186,10 +13286,10 @@
         <v>372</v>
       </c>
       <c r="C101" t="s">
-        <v>279</v>
+        <v>445</v>
       </c>
       <c r="D101" t="s">
-        <v>277</v>
+        <v>469</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13216,7 +13316,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13234,10 +13334,10 @@
         <v>372</v>
       </c>
       <c r="C102" t="s">
-        <v>429</v>
+        <v>370</v>
       </c>
       <c r="D102" t="s">
-        <v>428</v>
+        <v>369</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13264,7 +13364,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>469</v>
+        <v>418</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13282,10 +13382,10 @@
         <v>372</v>
       </c>
       <c r="C103" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D103" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13312,7 +13412,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13330,10 +13430,10 @@
         <v>372</v>
       </c>
       <c r="C104" t="s">
-        <v>320</v>
+        <v>428</v>
       </c>
       <c r="D104" t="s">
-        <v>321</v>
+        <v>427</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13360,7 +13460,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13378,10 +13478,10 @@
         <v>372</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="D105" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13408,7 +13508,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13426,10 +13526,10 @@
         <v>372</v>
       </c>
       <c r="C106" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D106" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13456,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13474,10 +13574,10 @@
         <v>372</v>
       </c>
       <c r="C107" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D107" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13504,7 +13604,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13522,10 +13622,10 @@
         <v>372</v>
       </c>
       <c r="C108" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="D108" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13552,7 +13652,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13570,10 +13670,10 @@
         <v>372</v>
       </c>
       <c r="C109" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D109" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13600,7 +13700,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13618,10 +13718,10 @@
         <v>372</v>
       </c>
       <c r="C110" t="s">
-        <v>437</v>
+        <v>287</v>
       </c>
       <c r="D110" t="s">
-        <v>436</v>
+        <v>286</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13648,7 +13748,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13666,10 +13766,10 @@
         <v>372</v>
       </c>
       <c r="C111" t="s">
-        <v>467</v>
+        <v>329</v>
       </c>
       <c r="D111" t="s">
-        <v>466</v>
+        <v>328</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13696,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>469</v>
+        <v>419</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13714,10 +13814,10 @@
         <v>372</v>
       </c>
       <c r="C112" t="s">
-        <v>336</v>
+        <v>436</v>
       </c>
       <c r="D112" t="s">
-        <v>334</v>
+        <v>435</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13744,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13762,10 +13862,10 @@
         <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>337</v>
+        <v>466</v>
       </c>
       <c r="D113" t="s">
-        <v>335</v>
+        <v>465</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13792,7 +13892,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13810,10 +13910,10 @@
         <v>372</v>
       </c>
       <c r="C114" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D114" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13840,7 +13940,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>469</v>
+        <v>423</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13858,10 +13958,10 @@
         <v>372</v>
       </c>
       <c r="C115" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="D115" t="s">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13888,7 +13988,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>519</v>
+        <v>421</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13906,10 +14006,10 @@
         <v>372</v>
       </c>
       <c r="C116" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D116" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -13936,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -13954,10 +14054,10 @@
         <v>372</v>
       </c>
       <c r="C117" t="s">
-        <v>341</v>
+        <v>284</v>
       </c>
       <c r="D117" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -13984,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14002,10 +14102,10 @@
         <v>372</v>
       </c>
       <c r="C118" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D118" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14032,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14050,10 +14150,10 @@
         <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D119" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14080,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14098,10 +14198,10 @@
         <v>372</v>
       </c>
       <c r="C120" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D120" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14128,7 +14228,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14146,10 +14246,10 @@
         <v>372</v>
       </c>
       <c r="C121" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D121" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14176,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14194,10 +14294,10 @@
         <v>372</v>
       </c>
       <c r="C122" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D122" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14224,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14242,10 +14342,10 @@
         <v>372</v>
       </c>
       <c r="C123" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D123" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14272,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14290,10 +14390,10 @@
         <v>372</v>
       </c>
       <c r="C124" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D124" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14320,7 +14420,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14338,10 +14438,10 @@
         <v>372</v>
       </c>
       <c r="C125" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D125" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14368,7 +14468,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14386,10 +14486,10 @@
         <v>372</v>
       </c>
       <c r="C126" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="D126" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14416,7 +14516,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14434,10 +14534,10 @@
         <v>372</v>
       </c>
       <c r="C127" t="s">
-        <v>308</v>
+        <v>357</v>
       </c>
       <c r="D127" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14464,7 +14564,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14482,10 +14582,10 @@
         <v>372</v>
       </c>
       <c r="C128" t="s">
-        <v>464</v>
+        <v>315</v>
       </c>
       <c r="D128" t="s">
-        <v>462</v>
+        <v>316</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14530,10 +14630,10 @@
         <v>372</v>
       </c>
       <c r="C129" t="s">
-        <v>465</v>
+        <v>308</v>
       </c>
       <c r="D129" t="s">
-        <v>463</v>
+        <v>309</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14560,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>469</v>
+        <v>420</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14569,99 +14669,99 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="130" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="12">
+    <row r="130" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A130">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" t="s">
         <v>372</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E130" s="12">
+      <c r="C130" t="s">
+        <v>463</v>
+      </c>
+      <c r="D130" t="s">
+        <v>461</v>
+      </c>
+      <c r="E130">
         <v>500</v>
       </c>
-      <c r="F130" s="12">
+      <c r="F130">
         <v>150</v>
       </c>
-      <c r="G130" s="12">
-        <v>0</v>
-      </c>
-      <c r="H130" s="12">
-        <v>0</v>
-      </c>
-      <c r="I130" s="12">
-        <v>0</v>
-      </c>
-      <c r="J130" s="12">
-        <v>0</v>
-      </c>
-      <c r="K130" s="12">
-        <v>0</v>
-      </c>
-      <c r="L130" s="12">
-        <v>0</v>
-      </c>
-      <c r="M130" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N130" s="12">
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="N130">
         <v>5000</v>
       </c>
-      <c r="O130" s="12">
+      <c r="O130">
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="12">
+    <row r="131" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B131" t="s">
         <v>372</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E131" s="12">
+      <c r="C131" t="s">
+        <v>464</v>
+      </c>
+      <c r="D131" t="s">
+        <v>462</v>
+      </c>
+      <c r="E131">
         <v>500</v>
       </c>
-      <c r="F131" s="12">
+      <c r="F131">
         <v>150</v>
       </c>
-      <c r="G131" s="12">
-        <v>0</v>
-      </c>
-      <c r="H131" s="12">
-        <v>0</v>
-      </c>
-      <c r="I131" s="12">
-        <v>0</v>
-      </c>
-      <c r="J131" s="12">
-        <v>0</v>
-      </c>
-      <c r="K131" s="12">
-        <v>0</v>
-      </c>
-      <c r="L131" s="12">
-        <v>0</v>
-      </c>
-      <c r="M131" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N131" s="12">
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="N131">
         <v>5000</v>
       </c>
-      <c r="O131" s="12">
+      <c r="O131">
         <v>5000</v>
       </c>
     </row>
@@ -14674,10 +14774,10 @@
         <v>372</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E132" s="12">
         <v>500</v>
@@ -14713,147 +14813,147 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133">
+    <row r="133" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="12">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C133" t="s">
-        <v>364</v>
-      </c>
-      <c r="D133" t="s">
-        <v>363</v>
-      </c>
-      <c r="E133">
+      <c r="C133" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="E133" s="12">
         <v>500</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="12">
         <v>150</v>
       </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="N133">
+      <c r="G133" s="12">
+        <v>0</v>
+      </c>
+      <c r="H133" s="12">
+        <v>0</v>
+      </c>
+      <c r="I133" s="12">
+        <v>0</v>
+      </c>
+      <c r="J133" s="12">
+        <v>0</v>
+      </c>
+      <c r="K133" s="12">
+        <v>0</v>
+      </c>
+      <c r="L133" s="12">
+        <v>0</v>
+      </c>
+      <c r="M133" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="N133" s="12">
         <v>5000</v>
       </c>
-      <c r="O133">
+      <c r="O133" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134">
+    <row r="134" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="12">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C134" t="s">
-        <v>366</v>
-      </c>
-      <c r="D134" t="s">
-        <v>365</v>
-      </c>
-      <c r="E134">
+      <c r="C134" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E134" s="12">
         <v>500</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="12">
         <v>150</v>
       </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" s="2" t="s">
+      <c r="G134" s="12">
+        <v>0</v>
+      </c>
+      <c r="H134" s="12">
+        <v>0</v>
+      </c>
+      <c r="I134" s="12">
+        <v>0</v>
+      </c>
+      <c r="J134" s="12">
+        <v>0</v>
+      </c>
+      <c r="K134" s="12">
+        <v>0</v>
+      </c>
+      <c r="L134" s="12">
+        <v>0</v>
+      </c>
+      <c r="M134" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N134">
+      <c r="N134" s="12">
         <v>5000</v>
       </c>
-      <c r="O134">
+      <c r="O134" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="135" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="12">
+    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" t="s">
         <v>372</v>
       </c>
-      <c r="C135" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E135" s="12">
+      <c r="C135" t="s">
+        <v>364</v>
+      </c>
+      <c r="D135" t="s">
+        <v>363</v>
+      </c>
+      <c r="E135">
         <v>500</v>
       </c>
-      <c r="F135" s="12">
+      <c r="F135">
         <v>150</v>
       </c>
-      <c r="G135" s="12">
-        <v>0</v>
-      </c>
-      <c r="H135" s="12">
-        <v>0</v>
-      </c>
-      <c r="I135" s="12">
-        <v>0</v>
-      </c>
-      <c r="J135" s="12">
-        <v>0</v>
-      </c>
-      <c r="K135" s="12">
-        <v>0</v>
-      </c>
-      <c r="L135" s="12">
-        <v>0</v>
-      </c>
-      <c r="M135" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="N135" s="12">
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="N135">
         <v>5000</v>
       </c>
-      <c r="O135" s="12">
+      <c r="O135">
         <v>5000</v>
       </c>
     </row>
@@ -14866,10 +14966,10 @@
         <v>372</v>
       </c>
       <c r="C136" t="s">
-        <v>310</v>
+        <v>366</v>
       </c>
       <c r="D136" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -14896,7 +14996,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>421</v>
+        <v>283</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -14905,66 +15005,67 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137">
-        <f>ROW()-2</f>
+    <row r="137" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="12">
+        <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="B137" t="s">
-        <v>441</v>
-      </c>
-      <c r="C137" t="s">
-        <v>438</v>
-      </c>
-      <c r="D137" t="s">
-        <v>439</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-      <c r="F137">
-        <v>0</v>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>1</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="s">
-        <v>440</v>
-      </c>
-      <c r="N137">
-        <v>9999</v>
-      </c>
-      <c r="O137">
-        <v>9999</v>
+      <c r="B137" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E137" s="12">
+        <v>500</v>
+      </c>
+      <c r="F137" s="12">
+        <v>150</v>
+      </c>
+      <c r="G137" s="12">
+        <v>0</v>
+      </c>
+      <c r="H137" s="12">
+        <v>0</v>
+      </c>
+      <c r="I137" s="12">
+        <v>0</v>
+      </c>
+      <c r="J137" s="12">
+        <v>0</v>
+      </c>
+      <c r="K137" s="12">
+        <v>0</v>
+      </c>
+      <c r="L137" s="12">
+        <v>0</v>
+      </c>
+      <c r="M137" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="N137" s="12">
+        <v>5000</v>
+      </c>
+      <c r="O137" s="12">
+        <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138">
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>168</v>
+        <v>372</v>
       </c>
       <c r="C138" t="s">
-        <v>172</v>
+        <v>310</v>
       </c>
       <c r="D138" t="s">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="E138">
         <v>500</v>
@@ -14988,15 +15089,110 @@
         <v>0</v>
       </c>
       <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="N138">
+        <v>5000</v>
+      </c>
+      <c r="O138">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A139">
+        <f>ROW()-2</f>
+        <v>137</v>
+      </c>
+      <c r="B139" t="s">
+        <v>440</v>
+      </c>
+      <c r="C139" t="s">
+        <v>437</v>
+      </c>
+      <c r="D139" t="s">
+        <v>438</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
         <v>1</v>
       </c>
-      <c r="M138" s="2" t="s">
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="s">
+        <v>439</v>
+      </c>
+      <c r="N139">
+        <v>9999</v>
+      </c>
+      <c r="O139">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140">
+        <v>10000</v>
+      </c>
+      <c r="B140" t="s">
+        <v>168</v>
+      </c>
+      <c r="C140" t="s">
+        <v>172</v>
+      </c>
+      <c r="D140" t="s">
+        <v>173</v>
+      </c>
+      <c r="E140">
+        <v>500</v>
+      </c>
+      <c r="F140">
+        <v>150</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>1</v>
+      </c>
+      <c r="M140" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="N138">
+      <c r="N140">
         <v>9000</v>
       </c>
-      <c r="O138">
+      <c r="O140">
         <v>9000</v>
       </c>
     </row>
@@ -15055,10 +15251,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15319,13 +15515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -15367,13 +15563,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>494</v>
+      </c>
+      <c r="C8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" t="s">
         <v>496</v>
-      </c>
-      <c r="C8" t="s">
-        <v>501</v>
-      </c>
-      <c r="D8" t="s">
-        <v>498</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -15415,13 +15611,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -15799,7 +15995,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C17" t="s">
         <v>197</v>
@@ -15847,13 +16043,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C18" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D18" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63E1F3F-2F5D-4419-B21E-920F54F5FE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BE2FCD-1782-4460-AD8F-1E16E9590603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="533">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7652,19 +7652,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>時の魔術書</t>
-    <rPh sb="0" eb="1">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マジュツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mg_timemagic_book</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7685,46 +7672,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>風の魔術書</t>
-    <rPh sb="0" eb="1">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マジュツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mg_windmagic_book</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>氷の魔術書</t>
-    <rPh sb="0" eb="1">
-      <t>コオリ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マジュツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>火の魔術書</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マジュツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7943,9 +7891,65 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>時魔法の書</t>
+    <rPh sb="0" eb="1">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風魔法の書</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷魔法の書</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火魔法の書</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/potate_chips</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>【フライドポテトのレシピ】
 とってもシンプルで、サクサクなフライドポテトの作り方。
-①&lt;color=#BA9535FF&gt;じゃがいも&lt;/color&gt;に&lt;color=#BA9535FF&gt;塩&lt;/color&gt;をまぶし、&lt;color=#FF5CA1FF&gt;フライヤー&lt;/color&gt;で揚げてみましょう。
+・&lt;color=#BA9535FF&gt;じゃがいも&lt;/color&gt;に&lt;color=#BA9535FF&gt;塩&lt;/color&gt;をまぶし、&lt;color=#FF5CA1FF&gt;フライヤー&lt;/color&gt;で揚げてみましょう。
 ほっくほっくでアツアツのフライドポテト♪
 子供も大人もみ～んな大好き！！
 そんなスナック感覚のおやつです！
@@ -8024,7 +8028,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8070,12 +8074,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8141,10 +8139,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9299,13 +9297,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C18" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D18" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9332,7 +9330,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -11507,13 +11505,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>385</v>
+        <v>531</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E64" s="16">
         <v>500</v>
@@ -11540,7 +11538,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="17" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N64" s="16">
         <v>535</v>
@@ -11588,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -12500,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12854,10 +12852,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D92" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12884,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12902,10 +12900,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D93" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12932,7 +12930,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12950,10 +12948,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D94" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12980,7 +12978,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -12998,10 +12996,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D95" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13028,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13046,10 +13044,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D96" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13076,7 +13074,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -14084,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="N117">
         <v>5000</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BE2FCD-1782-4460-AD8F-1E16E9590603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D54B979-F63B-4DB6-BB70-B9841BA8165B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -7891,58 +7891,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>時魔法の書</t>
-    <rPh sb="0" eb="1">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>風魔法の書</t>
-    <rPh sb="0" eb="1">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>氷魔法の書</t>
-    <rPh sb="0" eb="1">
-      <t>コオリ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>火魔法の書</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Items/potate_chips</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7983,6 +7931,49 @@
     </rPh>
     <rPh sb="223" eb="224">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8092,7 +8083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8137,12 +8128,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11499,51 +11484,51 @@
         <v>530</v>
       </c>
     </row>
-    <row r="64" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="16">
+    <row r="64" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="C64" s="16" t="s">
+      <c r="B64" t="s">
+        <v>527</v>
+      </c>
+      <c r="C64" t="s">
         <v>525</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" t="s">
         <v>524</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64">
         <v>500</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64">
         <v>150</v>
       </c>
-      <c r="G64" s="16">
-        <v>0</v>
-      </c>
-      <c r="H64" s="16">
-        <v>0</v>
-      </c>
-      <c r="I64" s="16">
-        <v>0</v>
-      </c>
-      <c r="J64" s="16">
-        <v>0</v>
-      </c>
-      <c r="K64" s="16">
-        <v>0</v>
-      </c>
-      <c r="L64" s="16">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
         <v>1</v>
       </c>
-      <c r="M64" s="17" t="s">
-        <v>532</v>
-      </c>
-      <c r="N64" s="16">
+      <c r="M64" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="N64">
         <v>535</v>
       </c>
-      <c r="O64" s="16">
+      <c r="O64">
         <v>535</v>
       </c>
     </row>
@@ -12903,7 +12888,7 @@
         <v>510</v>
       </c>
       <c r="D93" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12951,7 +12936,7 @@
         <v>511</v>
       </c>
       <c r="D94" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12999,7 +12984,7 @@
         <v>509</v>
       </c>
       <c r="D95" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13047,7 +13032,7 @@
         <v>507</v>
       </c>
       <c r="D96" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E96">
         <v>500</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D54B979-F63B-4DB6-BB70-B9841BA8165B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EAFBE4-1207-4177-8F06-336FEB34F770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2430" yWindow="1140" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="542">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7977,6 +7977,54 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>mg_parfect_princess_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エピクレイシスの本</t>
+    <rPh sb="8" eb="9">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_epiclesis_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラトリアの本</t>
+    <rPh sb="5" eb="6">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_latria_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_three_stars_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スリー・スターズの本</t>
+    <rPh sb="9" eb="10">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーフェクト・プリン・プリンセスの本</t>
+    <rPh sb="17" eb="18">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -8019,7 +8067,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8068,6 +8116,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -8083,7 +8137,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8128,6 +8182,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8444,7 +8504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O140"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8510,7 +8570,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A138" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A142" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -14748,243 +14808,243 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="12">
+    <row r="132" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="16">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="B132" s="12" t="s">
+      <c r="B132" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E132" s="12">
+      <c r="C132" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="D132" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="E132" s="16">
         <v>500</v>
       </c>
-      <c r="F132" s="12">
+      <c r="F132" s="16">
         <v>150</v>
       </c>
-      <c r="G132" s="12">
-        <v>0</v>
-      </c>
-      <c r="H132" s="12">
-        <v>0</v>
-      </c>
-      <c r="I132" s="12">
-        <v>0</v>
-      </c>
-      <c r="J132" s="12">
-        <v>0</v>
-      </c>
-      <c r="K132" s="12">
-        <v>0</v>
-      </c>
-      <c r="L132" s="12">
-        <v>0</v>
-      </c>
-      <c r="M132" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N132" s="12">
+      <c r="G132" s="16">
+        <v>0</v>
+      </c>
+      <c r="H132" s="16">
+        <v>0</v>
+      </c>
+      <c r="I132" s="16">
+        <v>0</v>
+      </c>
+      <c r="J132" s="16">
+        <v>0</v>
+      </c>
+      <c r="K132" s="16">
+        <v>0</v>
+      </c>
+      <c r="L132" s="16">
+        <v>0</v>
+      </c>
+      <c r="M132" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="N132" s="16">
         <v>5000</v>
       </c>
-      <c r="O132" s="12">
+      <c r="O132" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="133" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="12">
+    <row r="133" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="16">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="B133" s="12" t="s">
+      <c r="B133" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E133" s="12">
+      <c r="C133" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="E133" s="16">
         <v>500</v>
       </c>
-      <c r="F133" s="12">
+      <c r="F133" s="16">
         <v>150</v>
       </c>
-      <c r="G133" s="12">
-        <v>0</v>
-      </c>
-      <c r="H133" s="12">
-        <v>0</v>
-      </c>
-      <c r="I133" s="12">
-        <v>0</v>
-      </c>
-      <c r="J133" s="12">
-        <v>0</v>
-      </c>
-      <c r="K133" s="12">
-        <v>0</v>
-      </c>
-      <c r="L133" s="12">
-        <v>0</v>
-      </c>
-      <c r="M133" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N133" s="12">
+      <c r="G133" s="16">
+        <v>0</v>
+      </c>
+      <c r="H133" s="16">
+        <v>0</v>
+      </c>
+      <c r="I133" s="16">
+        <v>0</v>
+      </c>
+      <c r="J133" s="16">
+        <v>0</v>
+      </c>
+      <c r="K133" s="16">
+        <v>0</v>
+      </c>
+      <c r="L133" s="16">
+        <v>0</v>
+      </c>
+      <c r="M133" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="N133" s="16">
         <v>5000</v>
       </c>
-      <c r="O133" s="12">
+      <c r="O133" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="12">
+    <row r="134" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="16">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="D134" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E134" s="12">
+      <c r="C134" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="E134" s="16">
         <v>500</v>
       </c>
-      <c r="F134" s="12">
+      <c r="F134" s="16">
         <v>150</v>
       </c>
-      <c r="G134" s="12">
-        <v>0</v>
-      </c>
-      <c r="H134" s="12">
-        <v>0</v>
-      </c>
-      <c r="I134" s="12">
-        <v>0</v>
-      </c>
-      <c r="J134" s="12">
-        <v>0</v>
-      </c>
-      <c r="K134" s="12">
-        <v>0</v>
-      </c>
-      <c r="L134" s="12">
-        <v>0</v>
-      </c>
-      <c r="M134" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N134" s="12">
+      <c r="G134" s="16">
+        <v>0</v>
+      </c>
+      <c r="H134" s="16">
+        <v>0</v>
+      </c>
+      <c r="I134" s="16">
+        <v>0</v>
+      </c>
+      <c r="J134" s="16">
+        <v>0</v>
+      </c>
+      <c r="K134" s="16">
+        <v>0</v>
+      </c>
+      <c r="L134" s="16">
+        <v>0</v>
+      </c>
+      <c r="M134" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="N134" s="16">
         <v>5000</v>
       </c>
-      <c r="O134" s="12">
+      <c r="O134" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135">
+    <row r="135" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="16">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C135" t="s">
-        <v>364</v>
-      </c>
-      <c r="D135" t="s">
-        <v>363</v>
-      </c>
-      <c r="E135">
+      <c r="C135" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="D135" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="E135" s="16">
         <v>500</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="16">
         <v>150</v>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="N135">
+      <c r="G135" s="16">
+        <v>0</v>
+      </c>
+      <c r="H135" s="16">
+        <v>0</v>
+      </c>
+      <c r="I135" s="16">
+        <v>0</v>
+      </c>
+      <c r="J135" s="16">
+        <v>0</v>
+      </c>
+      <c r="K135" s="16">
+        <v>0</v>
+      </c>
+      <c r="L135" s="16">
+        <v>0</v>
+      </c>
+      <c r="M135" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="N135" s="16">
         <v>5000</v>
       </c>
-      <c r="O135">
+      <c r="O135" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136">
+    <row r="136" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="12">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C136" t="s">
-        <v>366</v>
-      </c>
-      <c r="D136" t="s">
-        <v>365</v>
-      </c>
-      <c r="E136">
+      <c r="C136" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E136" s="12">
         <v>500</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="12">
         <v>150</v>
       </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" s="2" t="s">
+      <c r="G136" s="12">
+        <v>0</v>
+      </c>
+      <c r="H136" s="12">
+        <v>0</v>
+      </c>
+      <c r="I136" s="12">
+        <v>0</v>
+      </c>
+      <c r="J136" s="12">
+        <v>0</v>
+      </c>
+      <c r="K136" s="12">
+        <v>0</v>
+      </c>
+      <c r="L136" s="12">
+        <v>0</v>
+      </c>
+      <c r="M136" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N136">
+      <c r="N136" s="12">
         <v>5000</v>
       </c>
-      <c r="O136">
+      <c r="O136" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -14997,10 +15057,10 @@
         <v>372</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E137" s="12">
         <v>500</v>
@@ -15027,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="13" t="s">
-        <v>426</v>
+        <v>283</v>
       </c>
       <c r="N137" s="12">
         <v>5000</v>
@@ -15036,79 +15096,79 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138">
+    <row r="138" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="12">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C138" t="s">
-        <v>310</v>
-      </c>
-      <c r="D138" t="s">
-        <v>311</v>
-      </c>
-      <c r="E138">
+      <c r="C138" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E138" s="12">
         <v>500</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="12">
         <v>150</v>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="N138">
+      <c r="G138" s="12">
+        <v>0</v>
+      </c>
+      <c r="H138" s="12">
+        <v>0</v>
+      </c>
+      <c r="I138" s="12">
+        <v>0</v>
+      </c>
+      <c r="J138" s="12">
+        <v>0</v>
+      </c>
+      <c r="K138" s="12">
+        <v>0</v>
+      </c>
+      <c r="L138" s="12">
+        <v>0</v>
+      </c>
+      <c r="M138" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="N138" s="12">
         <v>5000</v>
       </c>
-      <c r="O138">
+      <c r="O138" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>440</v>
+        <v>372</v>
       </c>
       <c r="C139" t="s">
-        <v>437</v>
+        <v>364</v>
       </c>
       <c r="D139" t="s">
-        <v>438</v>
+        <v>363</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G139">
         <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -15122,28 +15182,29 @@
       <c r="L139">
         <v>0</v>
       </c>
-      <c r="M139" t="s">
-        <v>439</v>
+      <c r="M139" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="N139">
-        <v>9999</v>
+        <v>5000</v>
       </c>
       <c r="O139">
-        <v>9999</v>
+        <v>5000</v>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140">
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>168</v>
+        <v>372</v>
       </c>
       <c r="C140" t="s">
-        <v>172</v>
+        <v>366</v>
       </c>
       <c r="D140" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="E140">
         <v>500</v>
@@ -15167,15 +15228,206 @@
         <v>0</v>
       </c>
       <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N140">
+        <v>5000</v>
+      </c>
+      <c r="O140">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="12">
+        <f t="shared" si="0"/>
+        <v>139</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E141" s="12">
+        <v>500</v>
+      </c>
+      <c r="F141" s="12">
+        <v>150</v>
+      </c>
+      <c r="G141" s="12">
+        <v>0</v>
+      </c>
+      <c r="H141" s="12">
+        <v>0</v>
+      </c>
+      <c r="I141" s="12">
+        <v>0</v>
+      </c>
+      <c r="J141" s="12">
+        <v>0</v>
+      </c>
+      <c r="K141" s="12">
+        <v>0</v>
+      </c>
+      <c r="L141" s="12">
+        <v>0</v>
+      </c>
+      <c r="M141" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="N141" s="12">
+        <v>5000</v>
+      </c>
+      <c r="O141" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="B142" t="s">
+        <v>372</v>
+      </c>
+      <c r="C142" t="s">
+        <v>310</v>
+      </c>
+      <c r="D142" t="s">
+        <v>311</v>
+      </c>
+      <c r="E142">
+        <v>500</v>
+      </c>
+      <c r="F142">
+        <v>150</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="N142">
+        <v>5000</v>
+      </c>
+      <c r="O142">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A143">
+        <f>ROW()-2</f>
+        <v>141</v>
+      </c>
+      <c r="B143" t="s">
+        <v>440</v>
+      </c>
+      <c r="C143" t="s">
+        <v>437</v>
+      </c>
+      <c r="D143" t="s">
+        <v>438</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
         <v>1</v>
       </c>
-      <c r="M140" s="2" t="s">
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143" t="s">
+        <v>439</v>
+      </c>
+      <c r="N143">
+        <v>9999</v>
+      </c>
+      <c r="O143">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A144">
+        <v>10000</v>
+      </c>
+      <c r="B144" t="s">
+        <v>168</v>
+      </c>
+      <c r="C144" t="s">
+        <v>172</v>
+      </c>
+      <c r="D144" t="s">
+        <v>173</v>
+      </c>
+      <c r="E144">
+        <v>500</v>
+      </c>
+      <c r="F144">
+        <v>150</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="N140">
+      <c r="N144">
         <v>9000</v>
       </c>
-      <c r="O140">
+      <c r="O144">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EAFBE4-1207-4177-8F06-336FEB34F770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236A4092-0E21-45E0-854B-CB51CC3E9857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1140" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2700" yWindow="1035" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -5497,60 +5497,6 @@
   </si>
   <si>
     <t>Items/eden_recipi_5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【ブラックチョコレートのレシピ】
-①&lt;color=#BA9535FF&gt;カカオ豆&lt;/color&gt;　→　ローストする。　魔法&lt;color=#FF5CA1FF&gt;「豆焼き」&lt;/color&gt;を使う
-カカオニブができる。
-②&lt;color=#BA9535FF&gt;カカオニブ&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;をまぜる。
-&lt;color=#FF5CA1FF&gt;すりばち&lt;/color&gt;で、豆をつぶしながらまぜる。
-③溶けたカカオ＜カカオマス＞　→　&lt;color=#FF5CA1FF&gt;魔法「テンパリング」&lt;/color&gt;
-50°　→　26°　→　31°
-各温度は、超えてはいけない
-④液体チョコレート　→　&lt;color=#FF5CA1FF&gt;魔法ふりーじんぐ&lt;/color&gt; or &lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;
-ブラックチョコレート完成！
-ほろ苦くて甘い♪　カカオがよく効いた絶品のお菓子でございます。
-</t>
-    <rPh sb="39" eb="40">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>マメヤ</t>
-    </rPh>
-    <rPh sb="92" eb="93">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="204" eb="205">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="252" eb="254">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="256" eb="257">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="288" eb="291">
-      <t>カクオンド</t>
-    </rPh>
-    <rPh sb="310" eb="311">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="332" eb="334">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="394" eb="396">
-      <t>ヒムロ</t>
-    </rPh>
-    <rPh sb="408" eb="410">
-      <t>カンセイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8019,8 +7965,77 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パーフェクト・プリン・プリンセスの本</t>
-    <rPh sb="17" eb="18">
+    <t xml:space="preserve">【ブラックチョコレートのレシピ】
+①&lt;color=#BA9535FF&gt;カカオ豆&lt;/color&gt;　→　ローストする。　魔法&lt;color=#FF5CA1FF&gt;「豆焼き」&lt;/color&gt;を使う
+カカオニブができる。
+②&lt;color=#BA9535FF&gt;カカオニブ&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;をまぜる。
+&lt;color=#FF5CA1FF&gt;すりばち&lt;/color&gt;で、豆をつぶしながらまぜる。
+③溶けたカカオ＜カカオマス＞　→　&lt;color=#FF5CA1FF&gt;魔法「テンパリング」&lt;/color&gt;
+50°　→　26°　→　31°
+各温度は、超えてはいけない
+④液体チョコレート　→　&lt;color=#FF5CA1FF&gt;魔法ふりーじんぐ&lt;/color&gt; or &lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;
+ブラックチョコレート完成！
+ほろ苦くて甘い♪　カカオがよく効いた絶品のお菓子でございます。
+■コラム「チョコレート・ヴィントホーゼ」
+液体のチョコレートに、&lt;color=#FF5CA1FF&gt;ツイスターの魔法&lt;/color&gt;をかけると..
+「チョコレートヴィントホーゼ」とよばれる渦巻きのチョコの形ができるというウワサです。
+</t>
+    <rPh sb="39" eb="40">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>マメヤ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="204" eb="205">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="252" eb="254">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="256" eb="257">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="288" eb="291">
+      <t>カクオンド</t>
+    </rPh>
+    <rPh sb="310" eb="311">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="332" eb="334">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="394" eb="396">
+      <t>ヒムロ</t>
+    </rPh>
+    <rPh sb="408" eb="410">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="452" eb="454">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="486" eb="488">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="524" eb="526">
+      <t>ウズマキ</t>
+    </rPh>
+    <rPh sb="532" eb="533">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーフェクト・プリンセスの本</t>
+    <rPh sb="13" eb="14">
       <t>ホン</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -8550,10 +8565,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8655,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -9039,7 +9054,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9153,10 +9168,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9183,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9201,10 +9216,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9231,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9249,10 +9264,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -9279,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -9297,10 +9312,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9327,7 +9342,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9342,13 +9357,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C18" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D18" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9375,7 +9390,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9663,7 +9678,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9711,7 +9726,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10143,7 +10158,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10158,13 +10173,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C35" t="s">
+        <v>449</v>
+      </c>
+      <c r="D35" t="s">
         <v>450</v>
-      </c>
-      <c r="D35" t="s">
-        <v>451</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10191,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10623,7 +10638,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10863,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>434</v>
+        <v>540</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -11151,7 +11166,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11199,7 +11214,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11247,7 +11262,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11550,13 +11565,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C64" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D64" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11583,7 +11598,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11631,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -12510,13 +12525,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C84" t="s">
+        <v>487</v>
+      </c>
+      <c r="D84" t="s">
         <v>488</v>
-      </c>
-      <c r="D84" t="s">
-        <v>489</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12543,7 +12558,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12639,7 +12654,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12687,7 +12702,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12735,7 +12750,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12783,7 +12798,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12831,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12897,10 +12912,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
+        <v>515</v>
+      </c>
+      <c r="D92" t="s">
         <v>516</v>
-      </c>
-      <c r="D92" t="s">
-        <v>517</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12927,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12945,10 +12960,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D93" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12975,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12993,10 +13008,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D94" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13023,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13041,10 +13056,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D95" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13071,7 +13086,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13089,10 +13104,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D96" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13119,7 +13134,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13167,7 +13182,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13215,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13233,10 +13248,10 @@
         <v>372</v>
       </c>
       <c r="C99" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D99" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13263,7 +13278,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13329,10 +13344,10 @@
         <v>372</v>
       </c>
       <c r="C101" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D101" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13359,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13503,7 +13518,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13551,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13599,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13647,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13695,7 +13710,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13743,7 +13758,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13791,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13857,10 +13872,10 @@
         <v>372</v>
       </c>
       <c r="C112" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D112" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13887,7 +13902,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13905,10 +13920,10 @@
         <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D113" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13935,7 +13950,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -14079,7 +14094,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14127,7 +14142,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14175,7 +14190,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14223,7 +14238,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14271,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14319,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14367,7 +14382,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14415,7 +14430,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14463,7 +14478,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14511,7 +14526,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14607,7 +14622,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14655,7 +14670,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14721,10 +14736,10 @@
         <v>372</v>
       </c>
       <c r="C130" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D130" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14751,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14769,10 +14784,10 @@
         <v>372</v>
       </c>
       <c r="C131" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D131" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -14799,7 +14814,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14817,7 +14832,7 @@
         <v>372</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D132" s="16" t="s">
         <v>541</v>
@@ -14847,7 +14862,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N132" s="16">
         <v>5000</v>
@@ -14865,10 +14880,10 @@
         <v>372</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E133" s="16">
         <v>500</v>
@@ -14895,7 +14910,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N133" s="16">
         <v>5000</v>
@@ -14913,10 +14928,10 @@
         <v>372</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E134" s="16">
         <v>500</v>
@@ -14943,7 +14958,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N134" s="16">
         <v>5000</v>
@@ -14961,10 +14976,10 @@
         <v>372</v>
       </c>
       <c r="C135" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D135" s="16" t="s">
         <v>539</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>540</v>
       </c>
       <c r="E135" s="16">
         <v>500</v>
@@ -14991,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N135" s="16">
         <v>5000</v>
@@ -15342,13 +15357,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C143" t="s">
+        <v>436</v>
+      </c>
+      <c r="D143" t="s">
         <v>437</v>
-      </c>
-      <c r="D143" t="s">
-        <v>438</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -15375,7 +15390,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N143">
         <v>9999</v>
@@ -15486,10 +15501,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15750,13 +15765,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -15798,13 +15813,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -15846,13 +15861,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16230,7 +16245,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C17" t="s">
         <v>197</v>
@@ -16278,13 +16293,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236A4092-0E21-45E0-854B-CB51CC3E9857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45FEC86-7C63-40D7-8696-23B2CD9E9595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="1035" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1875" yWindow="1200" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="550">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7946,10 +7946,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>まだ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mg_latria_book</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -8037,6 +8033,72 @@
     <t>パーフェクト・プリンセスの本</t>
     <rPh sb="13" eb="14">
       <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナイトバロンの本</t>
+    <rPh sb="7" eb="8">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クレッセント・ムーンの本</t>
+    <rPh sb="11" eb="12">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトニング・グレープの本</t>
+    <rPh sb="12" eb="13">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夢見るサファイアの本</t>
+    <rPh sb="9" eb="10">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_night_barron_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_crescent_moon_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_lightning_grape_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_dreamy_sapphire_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだ(本入手いれてない。他、習得等の登録はOK）</t>
+    <rPh sb="3" eb="4">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウシュ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8133,7 +8195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8519,7 +8581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8585,7 +8647,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A142" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A146" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -10878,7 +10940,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -14835,7 +14897,7 @@
         <v>532</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E132" s="16">
         <v>500</v>
@@ -14862,7 +14924,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="N132" s="16">
         <v>5000</v>
@@ -14910,7 +14972,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="17" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="N133" s="16">
         <v>5000</v>
@@ -14928,7 +14990,7 @@
         <v>372</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D134" s="16" t="s">
         <v>535</v>
@@ -14958,7 +15020,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="17" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="N134" s="16">
         <v>5000</v>
@@ -14976,10 +15038,10 @@
         <v>372</v>
       </c>
       <c r="C135" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="D135" s="16" t="s">
         <v>538</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>539</v>
       </c>
       <c r="E135" s="16">
         <v>500</v>
@@ -15006,7 +15068,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="N135" s="16">
         <v>5000</v>
@@ -15015,243 +15077,243 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="136" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="12">
+    <row r="136" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="16">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="B136" s="12" t="s">
+      <c r="B136" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C136" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E136" s="12">
+      <c r="C136" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="E136" s="16">
         <v>500</v>
       </c>
-      <c r="F136" s="12">
+      <c r="F136" s="16">
         <v>150</v>
       </c>
-      <c r="G136" s="12">
-        <v>0</v>
-      </c>
-      <c r="H136" s="12">
-        <v>0</v>
-      </c>
-      <c r="I136" s="12">
-        <v>0</v>
-      </c>
-      <c r="J136" s="12">
-        <v>0</v>
-      </c>
-      <c r="K136" s="12">
-        <v>0</v>
-      </c>
-      <c r="L136" s="12">
-        <v>0</v>
-      </c>
-      <c r="M136" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N136" s="12">
+      <c r="G136" s="16">
+        <v>0</v>
+      </c>
+      <c r="H136" s="16">
+        <v>0</v>
+      </c>
+      <c r="I136" s="16">
+        <v>0</v>
+      </c>
+      <c r="J136" s="16">
+        <v>0</v>
+      </c>
+      <c r="K136" s="16">
+        <v>0</v>
+      </c>
+      <c r="L136" s="16">
+        <v>0</v>
+      </c>
+      <c r="M136" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="N136" s="16">
         <v>5000</v>
       </c>
-      <c r="O136" s="12">
+      <c r="O136" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="137" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="12">
+    <row r="137" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="16">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="B137" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C137" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="D137" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E137" s="12">
+      <c r="C137" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D137" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="E137" s="16">
         <v>500</v>
       </c>
-      <c r="F137" s="12">
+      <c r="F137" s="16">
         <v>150</v>
       </c>
-      <c r="G137" s="12">
-        <v>0</v>
-      </c>
-      <c r="H137" s="12">
-        <v>0</v>
-      </c>
-      <c r="I137" s="12">
-        <v>0</v>
-      </c>
-      <c r="J137" s="12">
-        <v>0</v>
-      </c>
-      <c r="K137" s="12">
-        <v>0</v>
-      </c>
-      <c r="L137" s="12">
-        <v>0</v>
-      </c>
-      <c r="M137" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N137" s="12">
+      <c r="G137" s="16">
+        <v>0</v>
+      </c>
+      <c r="H137" s="16">
+        <v>0</v>
+      </c>
+      <c r="I137" s="16">
+        <v>0</v>
+      </c>
+      <c r="J137" s="16">
+        <v>0</v>
+      </c>
+      <c r="K137" s="16">
+        <v>0</v>
+      </c>
+      <c r="L137" s="16">
+        <v>0</v>
+      </c>
+      <c r="M137" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="N137" s="16">
         <v>5000</v>
       </c>
-      <c r="O137" s="12">
+      <c r="O137" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="12">
+    <row r="138" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="16">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" s="12" t="s">
+      <c r="B138" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C138" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="D138" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E138" s="12">
+      <c r="C138" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="D138" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="E138" s="16">
         <v>500</v>
       </c>
-      <c r="F138" s="12">
+      <c r="F138" s="16">
         <v>150</v>
       </c>
-      <c r="G138" s="12">
-        <v>0</v>
-      </c>
-      <c r="H138" s="12">
-        <v>0</v>
-      </c>
-      <c r="I138" s="12">
-        <v>0</v>
-      </c>
-      <c r="J138" s="12">
-        <v>0</v>
-      </c>
-      <c r="K138" s="12">
-        <v>0</v>
-      </c>
-      <c r="L138" s="12">
-        <v>0</v>
-      </c>
-      <c r="M138" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N138" s="12">
+      <c r="G138" s="16">
+        <v>0</v>
+      </c>
+      <c r="H138" s="16">
+        <v>0</v>
+      </c>
+      <c r="I138" s="16">
+        <v>0</v>
+      </c>
+      <c r="J138" s="16">
+        <v>0</v>
+      </c>
+      <c r="K138" s="16">
+        <v>0</v>
+      </c>
+      <c r="L138" s="16">
+        <v>0</v>
+      </c>
+      <c r="M138" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="N138" s="16">
         <v>5000</v>
       </c>
-      <c r="O138" s="12">
+      <c r="O138" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139">
+    <row r="139" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="16">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C139" t="s">
-        <v>364</v>
-      </c>
-      <c r="D139" t="s">
-        <v>363</v>
-      </c>
-      <c r="E139">
+      <c r="C139" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="E139" s="16">
         <v>500</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="16">
         <v>150</v>
       </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="N139">
+      <c r="G139" s="16">
+        <v>0</v>
+      </c>
+      <c r="H139" s="16">
+        <v>0</v>
+      </c>
+      <c r="I139" s="16">
+        <v>0</v>
+      </c>
+      <c r="J139" s="16">
+        <v>0</v>
+      </c>
+      <c r="K139" s="16">
+        <v>0</v>
+      </c>
+      <c r="L139" s="16">
+        <v>0</v>
+      </c>
+      <c r="M139" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="N139" s="16">
         <v>5000</v>
       </c>
-      <c r="O139">
+      <c r="O139" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140">
+    <row r="140" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="12">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C140" t="s">
-        <v>366</v>
-      </c>
-      <c r="D140" t="s">
-        <v>365</v>
-      </c>
-      <c r="E140">
+      <c r="C140" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E140" s="12">
         <v>500</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="12">
         <v>150</v>
       </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" s="2" t="s">
+      <c r="G140" s="12">
+        <v>0</v>
+      </c>
+      <c r="H140" s="12">
+        <v>0</v>
+      </c>
+      <c r="I140" s="12">
+        <v>0</v>
+      </c>
+      <c r="J140" s="12">
+        <v>0</v>
+      </c>
+      <c r="K140" s="12">
+        <v>0</v>
+      </c>
+      <c r="L140" s="12">
+        <v>0</v>
+      </c>
+      <c r="M140" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="N140">
+      <c r="N140" s="12">
         <v>5000</v>
       </c>
-      <c r="O140">
+      <c r="O140" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -15264,10 +15326,10 @@
         <v>372</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E141" s="12">
         <v>500</v>
@@ -15294,7 +15356,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="13" t="s">
-        <v>426</v>
+        <v>283</v>
       </c>
       <c r="N141" s="12">
         <v>5000</v>
@@ -15303,79 +15365,79 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142">
+    <row r="142" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="12">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C142" t="s">
-        <v>310</v>
-      </c>
-      <c r="D142" t="s">
-        <v>311</v>
-      </c>
-      <c r="E142">
+      <c r="C142" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E142" s="12">
         <v>500</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="12">
         <v>150</v>
       </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="N142">
+      <c r="G142" s="12">
+        <v>0</v>
+      </c>
+      <c r="H142" s="12">
+        <v>0</v>
+      </c>
+      <c r="I142" s="12">
+        <v>0</v>
+      </c>
+      <c r="J142" s="12">
+        <v>0</v>
+      </c>
+      <c r="K142" s="12">
+        <v>0</v>
+      </c>
+      <c r="L142" s="12">
+        <v>0</v>
+      </c>
+      <c r="M142" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="N142" s="12">
         <v>5000</v>
       </c>
-      <c r="O142">
+      <c r="O142" s="12">
         <v>5000</v>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>439</v>
+        <v>372</v>
       </c>
       <c r="C143" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="D143" t="s">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G143">
         <v>0</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -15389,28 +15451,29 @@
       <c r="L143">
         <v>0</v>
       </c>
-      <c r="M143" t="s">
-        <v>438</v>
+      <c r="M143" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="N143">
-        <v>9999</v>
+        <v>5000</v>
       </c>
       <c r="O143">
-        <v>9999</v>
+        <v>5000</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144">
-        <v>10000</v>
+        <f t="shared" si="0"/>
+        <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>168</v>
+        <v>372</v>
       </c>
       <c r="C144" t="s">
-        <v>172</v>
+        <v>366</v>
       </c>
       <c r="D144" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15434,15 +15497,206 @@
         <v>0</v>
       </c>
       <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N144">
+        <v>5000</v>
+      </c>
+      <c r="O144">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="12">
+        <f t="shared" si="0"/>
+        <v>143</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E145" s="12">
+        <v>500</v>
+      </c>
+      <c r="F145" s="12">
+        <v>150</v>
+      </c>
+      <c r="G145" s="12">
+        <v>0</v>
+      </c>
+      <c r="H145" s="12">
+        <v>0</v>
+      </c>
+      <c r="I145" s="12">
+        <v>0</v>
+      </c>
+      <c r="J145" s="12">
+        <v>0</v>
+      </c>
+      <c r="K145" s="12">
+        <v>0</v>
+      </c>
+      <c r="L145" s="12">
+        <v>0</v>
+      </c>
+      <c r="M145" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="N145" s="12">
+        <v>5000</v>
+      </c>
+      <c r="O145" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146">
+        <f t="shared" si="0"/>
+        <v>144</v>
+      </c>
+      <c r="B146" t="s">
+        <v>372</v>
+      </c>
+      <c r="C146" t="s">
+        <v>310</v>
+      </c>
+      <c r="D146" t="s">
+        <v>311</v>
+      </c>
+      <c r="E146">
+        <v>500</v>
+      </c>
+      <c r="F146">
+        <v>150</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="N146">
+        <v>5000</v>
+      </c>
+      <c r="O146">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <f>ROW()-2</f>
+        <v>145</v>
+      </c>
+      <c r="B147" t="s">
+        <v>439</v>
+      </c>
+      <c r="C147" t="s">
+        <v>436</v>
+      </c>
+      <c r="D147" t="s">
+        <v>437</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
         <v>1</v>
       </c>
-      <c r="M144" s="2" t="s">
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147" t="s">
+        <v>438</v>
+      </c>
+      <c r="N147">
+        <v>9999</v>
+      </c>
+      <c r="O147">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <v>10000</v>
+      </c>
+      <c r="B148" t="s">
+        <v>168</v>
+      </c>
+      <c r="C148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D148" t="s">
+        <v>173</v>
+      </c>
+      <c r="E148">
+        <v>500</v>
+      </c>
+      <c r="F148">
+        <v>150</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="N144">
+      <c r="N148">
         <v>9000</v>
       </c>
-      <c r="O144">
+      <c r="O148">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45FEC86-7C63-40D7-8696-23B2CD9E9595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7EE9F2-38B6-4E6E-995F-C98FC7715768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="1200" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2745" yWindow="1035" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="552">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7598,26 +7598,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>mg_timemagic_book</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>時魔法解禁の本　エメラルショップ</t>
-    <rPh sb="0" eb="1">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カイキン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mg_windmagic_book</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7887,16 +7867,6 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>マジュツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>時の魔術書</t>
-    <rPh sb="0" eb="1">
-      <t>トキ</t>
     </rPh>
     <rPh sb="4" eb="5">
       <t>ショ</t>
@@ -8100,6 +8070,47 @@
     <rPh sb="18" eb="20">
       <t>トウロク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_starmagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星の魔術書</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星魔法解禁の本　エメラルショップ</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイキン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンティマンの本</t>
+    <rPh sb="7" eb="8">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_santiman_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8581,7 +8592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8647,7 +8658,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A146" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A147" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -9419,13 +9430,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C18" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D18" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9452,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -10940,7 +10951,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -11627,13 +11638,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D64" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11660,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11708,7 +11719,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -12620,7 +12631,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12974,10 +12985,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D92" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -13004,7 +13015,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -13022,10 +13033,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D93" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -13052,7 +13063,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -13070,10 +13081,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D94" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13100,7 +13111,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13118,10 +13129,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D95" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13148,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13166,10 +13177,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="D96" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13196,7 +13207,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>507</v>
+        <v>549</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -14204,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14837,51 +14848,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131">
+    <row r="131" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="16">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="16">
         <v>500</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="16">
         <v>150</v>
       </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="N131">
+      <c r="G131" s="16">
+        <v>0</v>
+      </c>
+      <c r="H131" s="16">
+        <v>0</v>
+      </c>
+      <c r="I131" s="16">
+        <v>0</v>
+      </c>
+      <c r="J131" s="16">
+        <v>0</v>
+      </c>
+      <c r="K131" s="16">
+        <v>0</v>
+      </c>
+      <c r="L131" s="16">
+        <v>0</v>
+      </c>
+      <c r="M131" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="N131" s="16">
         <v>5000</v>
       </c>
-      <c r="O131">
+      <c r="O131" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -14894,10 +14905,10 @@
         <v>372</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="E132" s="16">
         <v>500</v>
@@ -14924,7 +14935,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N132" s="16">
         <v>5000</v>
@@ -14933,147 +14944,147 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="133" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="16">
+    <row r="133" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A133">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="B133" s="16" t="s">
+      <c r="B133" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="D133" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="E133" s="16">
+      <c r="C133" t="s">
+        <v>529</v>
+      </c>
+      <c r="D133" t="s">
+        <v>537</v>
+      </c>
+      <c r="E133">
         <v>500</v>
       </c>
-      <c r="F133" s="16">
+      <c r="F133">
         <v>150</v>
       </c>
-      <c r="G133" s="16">
-        <v>0</v>
-      </c>
-      <c r="H133" s="16">
-        <v>0</v>
-      </c>
-      <c r="I133" s="16">
-        <v>0</v>
-      </c>
-      <c r="J133" s="16">
-        <v>0</v>
-      </c>
-      <c r="K133" s="16">
-        <v>0</v>
-      </c>
-      <c r="L133" s="16">
-        <v>0</v>
-      </c>
-      <c r="M133" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="N133" s="16">
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N133">
         <v>5000</v>
       </c>
-      <c r="O133" s="16">
+      <c r="O133">
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="16">
+    <row r="134" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B134" s="16" t="s">
+      <c r="B134" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="16" t="s">
-        <v>536</v>
-      </c>
-      <c r="D134" s="16" t="s">
-        <v>535</v>
-      </c>
-      <c r="E134" s="16">
+      <c r="C134" t="s">
+        <v>531</v>
+      </c>
+      <c r="D134" t="s">
+        <v>530</v>
+      </c>
+      <c r="E134">
         <v>500</v>
       </c>
-      <c r="F134" s="16">
+      <c r="F134">
         <v>150</v>
       </c>
-      <c r="G134" s="16">
-        <v>0</v>
-      </c>
-      <c r="H134" s="16">
-        <v>0</v>
-      </c>
-      <c r="I134" s="16">
-        <v>0</v>
-      </c>
-      <c r="J134" s="16">
-        <v>0</v>
-      </c>
-      <c r="K134" s="16">
-        <v>0</v>
-      </c>
-      <c r="L134" s="16">
-        <v>0</v>
-      </c>
-      <c r="M134" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="N134" s="16">
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N134">
         <v>5000</v>
       </c>
-      <c r="O134" s="16">
+      <c r="O134">
         <v>5000</v>
       </c>
     </row>
-    <row r="135" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="16">
+    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B135" s="16" t="s">
+      <c r="B135" t="s">
         <v>372</v>
       </c>
-      <c r="C135" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>538</v>
-      </c>
-      <c r="E135" s="16">
+      <c r="C135" t="s">
+        <v>533</v>
+      </c>
+      <c r="D135" t="s">
+        <v>532</v>
+      </c>
+      <c r="E135">
         <v>500</v>
       </c>
-      <c r="F135" s="16">
+      <c r="F135">
         <v>150</v>
       </c>
-      <c r="G135" s="16">
-        <v>0</v>
-      </c>
-      <c r="H135" s="16">
-        <v>0</v>
-      </c>
-      <c r="I135" s="16">
-        <v>0</v>
-      </c>
-      <c r="J135" s="16">
-        <v>0</v>
-      </c>
-      <c r="K135" s="16">
-        <v>0</v>
-      </c>
-      <c r="L135" s="16">
-        <v>0</v>
-      </c>
-      <c r="M135" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="N135" s="16">
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N135">
         <v>5000</v>
       </c>
-      <c r="O135" s="16">
+      <c r="O135">
         <v>5000</v>
       </c>
     </row>
@@ -15086,10 +15097,10 @@
         <v>372</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E136" s="16">
         <v>500</v>
@@ -15116,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="17" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N136" s="16">
         <v>5000</v>
@@ -15125,99 +15136,99 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="137" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="16">
+    <row r="137" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" t="s">
         <v>372</v>
       </c>
-      <c r="C137" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="D137" s="16" t="s">
+      <c r="C137" t="s">
         <v>542</v>
       </c>
-      <c r="E137" s="16">
+      <c r="D137" t="s">
+        <v>538</v>
+      </c>
+      <c r="E137">
         <v>500</v>
       </c>
-      <c r="F137" s="16">
+      <c r="F137">
         <v>150</v>
       </c>
-      <c r="G137" s="16">
-        <v>0</v>
-      </c>
-      <c r="H137" s="16">
-        <v>0</v>
-      </c>
-      <c r="I137" s="16">
-        <v>0</v>
-      </c>
-      <c r="J137" s="16">
-        <v>0</v>
-      </c>
-      <c r="K137" s="16">
-        <v>0</v>
-      </c>
-      <c r="L137" s="16">
-        <v>0</v>
-      </c>
-      <c r="M137" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="N137" s="16">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N137">
         <v>5000</v>
       </c>
-      <c r="O137" s="16">
+      <c r="O137">
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="16">
+    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" s="16" t="s">
+      <c r="B138" t="s">
         <v>372</v>
       </c>
-      <c r="C138" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="D138" s="16" t="s">
+      <c r="C138" t="s">
         <v>543</v>
       </c>
-      <c r="E138" s="16">
+      <c r="D138" t="s">
+        <v>539</v>
+      </c>
+      <c r="E138">
         <v>500</v>
       </c>
-      <c r="F138" s="16">
+      <c r="F138">
         <v>150</v>
       </c>
-      <c r="G138" s="16">
-        <v>0</v>
-      </c>
-      <c r="H138" s="16">
-        <v>0</v>
-      </c>
-      <c r="I138" s="16">
-        <v>0</v>
-      </c>
-      <c r="J138" s="16">
-        <v>0</v>
-      </c>
-      <c r="K138" s="16">
-        <v>0</v>
-      </c>
-      <c r="L138" s="16">
-        <v>0</v>
-      </c>
-      <c r="M138" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="N138" s="16">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N138">
         <v>5000</v>
       </c>
-      <c r="O138" s="16">
+      <c r="O138">
         <v>5000</v>
       </c>
     </row>
@@ -15230,10 +15241,10 @@
         <v>372</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E139" s="16">
         <v>500</v>
@@ -15260,7 +15271,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="17" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N139" s="16">
         <v>5000</v>
@@ -15269,51 +15280,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="12">
+    <row r="140" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="16">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C140" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="D140" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E140" s="12">
+      <c r="C140" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="E140" s="16">
         <v>500</v>
       </c>
-      <c r="F140" s="12">
+      <c r="F140" s="16">
         <v>150</v>
       </c>
-      <c r="G140" s="12">
-        <v>0</v>
-      </c>
-      <c r="H140" s="12">
-        <v>0</v>
-      </c>
-      <c r="I140" s="12">
-        <v>0</v>
-      </c>
-      <c r="J140" s="12">
-        <v>0</v>
-      </c>
-      <c r="K140" s="12">
-        <v>0</v>
-      </c>
-      <c r="L140" s="12">
-        <v>0</v>
-      </c>
-      <c r="M140" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="N140" s="12">
+      <c r="G140" s="16">
+        <v>0</v>
+      </c>
+      <c r="H140" s="16">
+        <v>0</v>
+      </c>
+      <c r="I140" s="16">
+        <v>0</v>
+      </c>
+      <c r="J140" s="16">
+        <v>0</v>
+      </c>
+      <c r="K140" s="16">
+        <v>0</v>
+      </c>
+      <c r="L140" s="16">
+        <v>0</v>
+      </c>
+      <c r="M140" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="N140" s="16">
         <v>5000</v>
       </c>
-      <c r="O140" s="12">
+      <c r="O140" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -15326,10 +15337,10 @@
         <v>372</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E141" s="12">
         <v>500</v>
@@ -15374,10 +15385,10 @@
         <v>372</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E142" s="12">
         <v>500</v>
@@ -15413,51 +15424,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143">
+    <row r="143" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="12">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C143" t="s">
-        <v>364</v>
-      </c>
-      <c r="D143" t="s">
-        <v>363</v>
-      </c>
-      <c r="E143">
+      <c r="C143" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E143" s="12">
         <v>500</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="12">
         <v>150</v>
       </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="N143">
+      <c r="G143" s="12">
+        <v>0</v>
+      </c>
+      <c r="H143" s="12">
+        <v>0</v>
+      </c>
+      <c r="I143" s="12">
+        <v>0</v>
+      </c>
+      <c r="J143" s="12">
+        <v>0</v>
+      </c>
+      <c r="K143" s="12">
+        <v>0</v>
+      </c>
+      <c r="L143" s="12">
+        <v>0</v>
+      </c>
+      <c r="M143" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="N143" s="12">
         <v>5000</v>
       </c>
-      <c r="O143">
+      <c r="O143" s="12">
         <v>5000</v>
       </c>
     </row>
@@ -15470,10 +15481,10 @@
         <v>372</v>
       </c>
       <c r="C144" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D144" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15500,7 +15511,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>283</v>
+        <v>424</v>
       </c>
       <c r="N144">
         <v>5000</v>
@@ -15509,194 +15520,242 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="145" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="12">
+    <row r="145" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A145">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-      <c r="B145" s="12" t="s">
+      <c r="B145" t="s">
         <v>372</v>
       </c>
-      <c r="C145" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="D145" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E145" s="12">
+      <c r="C145" t="s">
+        <v>366</v>
+      </c>
+      <c r="D145" t="s">
+        <v>365</v>
+      </c>
+      <c r="E145">
         <v>500</v>
       </c>
-      <c r="F145" s="12">
+      <c r="F145">
         <v>150</v>
       </c>
-      <c r="G145" s="12">
-        <v>0</v>
-      </c>
-      <c r="H145" s="12">
-        <v>0</v>
-      </c>
-      <c r="I145" s="12">
-        <v>0</v>
-      </c>
-      <c r="J145" s="12">
-        <v>0</v>
-      </c>
-      <c r="K145" s="12">
-        <v>0</v>
-      </c>
-      <c r="L145" s="12">
-        <v>0</v>
-      </c>
-      <c r="M145" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="N145" s="12">
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="N145">
         <v>5000</v>
       </c>
-      <c r="O145" s="12">
+      <c r="O145">
         <v>5000</v>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146">
+    <row r="146" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="12">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E146" s="12">
+        <v>500</v>
+      </c>
+      <c r="F146" s="12">
+        <v>150</v>
+      </c>
+      <c r="G146" s="12">
+        <v>0</v>
+      </c>
+      <c r="H146" s="12">
+        <v>0</v>
+      </c>
+      <c r="I146" s="12">
+        <v>0</v>
+      </c>
+      <c r="J146" s="12">
+        <v>0</v>
+      </c>
+      <c r="K146" s="12">
+        <v>0</v>
+      </c>
+      <c r="L146" s="12">
+        <v>0</v>
+      </c>
+      <c r="M146" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="N146" s="12">
+        <v>5000</v>
+      </c>
+      <c r="O146" s="12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <f t="shared" si="0"/>
+        <v>145</v>
+      </c>
+      <c r="B147" t="s">
+        <v>372</v>
+      </c>
+      <c r="C147" t="s">
         <v>310</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D147" t="s">
         <v>311</v>
       </c>
-      <c r="E146">
+      <c r="E147">
         <v>500</v>
       </c>
-      <c r="F146">
+      <c r="F147">
         <v>150</v>
       </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146" s="2" t="s">
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="N146">
+      <c r="N147">
         <v>5000</v>
       </c>
-      <c r="O146">
+      <c r="O147">
         <v>5000</v>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147">
+    <row r="148" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A148">
         <f>ROW()-2</f>
-        <v>145</v>
-      </c>
-      <c r="B147" t="s">
+        <v>146</v>
+      </c>
+      <c r="B148" t="s">
         <v>439</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C148" t="s">
         <v>436</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D148" t="s">
         <v>437</v>
       </c>
-      <c r="E147">
-        <v>0</v>
-      </c>
-      <c r="F147">
-        <v>0</v>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
         <v>1</v>
       </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147" t="s">
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148" t="s">
         <v>438</v>
       </c>
-      <c r="N147">
+      <c r="N148">
         <v>9999</v>
       </c>
-      <c r="O147">
+      <c r="O148">
         <v>9999</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148">
+    <row r="149" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A149">
         <v>10000</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B149" t="s">
         <v>168</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C149" t="s">
         <v>172</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D149" t="s">
         <v>173</v>
       </c>
-      <c r="E148">
+      <c r="E149">
         <v>500</v>
       </c>
-      <c r="F148">
+      <c r="F149">
         <v>150</v>
       </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
         <v>1</v>
       </c>
-      <c r="M148" s="2" t="s">
+      <c r="M149" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="N148">
+      <c r="N149">
         <v>9000</v>
       </c>
-      <c r="O148">
+      <c r="O149">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7EE9F2-38B6-4E6E-995F-C98FC7715768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41AD506-CA63-44AD-9555-5BA5607CBE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="1035" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2580" yWindow="825" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="553">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -8111,6 +8111,13 @@
   </si>
   <si>
     <t>mg_santiman_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春のおかし大祭典の賞品</t>
+    <rPh sb="9" eb="11">
+      <t>ショウヒン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -14983,7 +14990,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>469</v>
+        <v>552</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14992,99 +14999,99 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134">
+    <row r="134" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="16">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="16" t="s">
         <v>531</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="16">
         <v>500</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="16">
         <v>150</v>
       </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" s="2" t="s">
+      <c r="G134" s="16">
+        <v>0</v>
+      </c>
+      <c r="H134" s="16">
+        <v>0</v>
+      </c>
+      <c r="I134" s="16">
+        <v>0</v>
+      </c>
+      <c r="J134" s="16">
+        <v>0</v>
+      </c>
+      <c r="K134" s="16">
+        <v>0</v>
+      </c>
+      <c r="L134" s="16">
+        <v>0</v>
+      </c>
+      <c r="M134" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="N134">
+      <c r="N134" s="16">
         <v>5000</v>
       </c>
-      <c r="O134">
+      <c r="O134" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135">
+    <row r="135" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="16">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="16" t="s">
         <v>533</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="16" t="s">
         <v>532</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="16">
         <v>500</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="16">
         <v>150</v>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" s="2" t="s">
+      <c r="G135" s="16">
+        <v>0</v>
+      </c>
+      <c r="H135" s="16">
+        <v>0</v>
+      </c>
+      <c r="I135" s="16">
+        <v>0</v>
+      </c>
+      <c r="J135" s="16">
+        <v>0</v>
+      </c>
+      <c r="K135" s="16">
+        <v>0</v>
+      </c>
+      <c r="L135" s="16">
+        <v>0</v>
+      </c>
+      <c r="M135" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="N135">
+      <c r="N135" s="16">
         <v>5000</v>
       </c>
-      <c r="O135">
+      <c r="O135" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -15136,99 +15143,99 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137">
+    <row r="137" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="16">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="16">
         <v>500</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="16">
         <v>150</v>
       </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" s="2" t="s">
+      <c r="G137" s="16">
+        <v>0</v>
+      </c>
+      <c r="H137" s="16">
+        <v>0</v>
+      </c>
+      <c r="I137" s="16">
+        <v>0</v>
+      </c>
+      <c r="J137" s="16">
+        <v>0</v>
+      </c>
+      <c r="K137" s="16">
+        <v>0</v>
+      </c>
+      <c r="L137" s="16">
+        <v>0</v>
+      </c>
+      <c r="M137" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="N137">
+      <c r="N137" s="16">
         <v>5000</v>
       </c>
-      <c r="O137">
+      <c r="O137" s="16">
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138">
+    <row r="138" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="16">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="16" t="s">
         <v>539</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="16">
         <v>500</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="16">
         <v>150</v>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" s="2" t="s">
+      <c r="G138" s="16">
+        <v>0</v>
+      </c>
+      <c r="H138" s="16">
+        <v>0</v>
+      </c>
+      <c r="I138" s="16">
+        <v>0</v>
+      </c>
+      <c r="J138" s="16">
+        <v>0</v>
+      </c>
+      <c r="K138" s="16">
+        <v>0</v>
+      </c>
+      <c r="L138" s="16">
+        <v>0</v>
+      </c>
+      <c r="M138" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="N138">
+      <c r="N138" s="16">
         <v>5000</v>
       </c>
-      <c r="O138">
+      <c r="O138" s="16">
         <v>5000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41AD506-CA63-44AD-9555-5BA5607CBE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB068B-1B44-4D5F-A7DF-4CD5FA9E079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="825" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1545" yWindow="1260" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -5533,326 +5533,6 @@
   </si>
   <si>
     <t>Items/memo_white</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【エデンのレシピのかけら】
-エデンの作り方について書かれたレシピのようだ。
-- 太陽のレシピ -
-ケーキ生地のつくりかた
-i. はくりきこ　×　ココアパウダー
-ii. たまご　×　さとう　×　バターを混ぜ、アパレイユを作る
-iii. &lt;color=#BA9535FF&gt;ブラックロータスポーション&lt;/color&gt;
-iの粉生地とiiのアパレイユに、iiiブラックロータスポーションを入れ、３つを混ぜる。
-→　出来上がった生地を、&lt;color=#FF5CA1FF&gt;ウィンドミキサー&lt;/color&gt;でよく混ぜて、焼き上げる。
-ブラックロータスココアケーキ（生地）の完成。</t>
-    <rPh sb="19" eb="20">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>タイヨウ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="104" eb="105">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="113" eb="114">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="164" eb="167">
-      <t>コナキジ</t>
-    </rPh>
-    <rPh sb="195" eb="196">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="201" eb="202">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="209" eb="212">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="215" eb="217">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="255" eb="256">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="259" eb="260">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="261" eb="262">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="282" eb="284">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="286" eb="288">
-      <t>カンセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【エデンのレシピのかけら】
-エデンの作り方について書かれたレシピのようだ。
-- 星のレシピ -
-クリームの作り方
-太陽と月のしずくをまぜたクリーム
-i. 作りたてクリームを事前に作っておく
-ii. クリームに、&lt;color=#BA9535FF&gt;太陽の実&lt;/color&gt;と&lt;color=#BA9535FF&gt;月の実&lt;/color&gt;を同時に入れ、混ぜ合わせる。
-夢見のクリームの完成
-＜太陽の実は、さわやかですっぱいオレンジ色の果実＞
-＜月の実は、銀色に輝く寒い場所でしか採れない果実＞</t>
-    <rPh sb="19" eb="20">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>タイヨウ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="81" eb="82">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="127" eb="129">
-      <t>タイヨウ</t>
-    </rPh>
-    <rPh sb="130" eb="131">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="157" eb="158">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="159" eb="160">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>ドウジ</t>
-    </rPh>
-    <rPh sb="172" eb="173">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="175" eb="176">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="177" eb="178">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="184" eb="186">
-      <t>ユメミ</t>
-    </rPh>
-    <rPh sb="192" eb="194">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="197" eb="199">
-      <t>タイヨウ</t>
-    </rPh>
-    <rPh sb="200" eb="201">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="216" eb="217">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="218" eb="220">
-      <t>カジツ</t>
-    </rPh>
-    <rPh sb="223" eb="224">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="225" eb="226">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="228" eb="230">
-      <t>ギンイロ</t>
-    </rPh>
-    <rPh sb="231" eb="232">
-      <t>カガヤ</t>
-    </rPh>
-    <rPh sb="233" eb="234">
-      <t>サム</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="240" eb="241">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="244" eb="246">
-      <t>カジツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【エデンのレシピのかけら】
-エデンの作り方について書かれたレシピのようだ。
-- 月のレシピ -
-トッピング方法のレシピ
-ケーキ全体にクリームをぬったあと、最後の仕上げに&lt;color=#BA9535FF&gt;２つの果物&lt;/color&gt;を同時にのせる。
-・&lt;color=#BA9535FF&gt;スカーレットベリー&lt;/color&gt;
-・&lt;color=#BA9535FF&gt;ジェムナッツ&lt;/color&gt;
-仕上げに、もりだくさんのせること。
-また、同時にトッピングすること。</t>
-    <rPh sb="19" eb="20">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>クダモノ</t>
-    </rPh>
-    <rPh sb="118" eb="120">
-      <t>ドウジ</t>
-    </rPh>
-    <rPh sb="197" eb="199">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="218" eb="220">
-      <t>ドウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【エデンのレシピのかけら】
-エデンの作り方について書かれたレシピのようだ。
-- ハートのレシピ -
-エデンの手順のレシピ
-完成までの手順がかかれている。
-◆事前に、スポンジ生地を&lt;color=#FF5CA1FF&gt;スライサー&lt;/color&gt;で３つに分ける。
-◆i. 一段目　スライスしたスポンジ生地に、&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;と、&lt;color=#BA9535FF&gt;白いクリーム&lt;/color&gt;を塗る。
-◆ii. 二段目　スライスしたスポンジ生地に、&lt;color=#BA9535FF&gt;レインボーベリー&lt;/color&gt;と、&lt;color=#BA9535FF&gt;白いクリーム&lt;/color&gt;を塗る。
-◆iii. iとiiの生地、さらにスポンジ生地でふたをし、&lt;color=#BA9535FF&gt;三段重ね&lt;/color&gt;にする。
-そのあと、全体を&lt;color=#BA9535FF&gt;夢見クリーム&lt;/color&gt;できれいに塗り仕上げる。
-※クリームは、絞り袋に入れず、直接ぬってよい。
-◆iiii. 月のレシ.. どおりに、２種類の果実をふんだんに.. トッピング。
-◆.. （かすれて読みづらい）
-しあげ.. に.. &lt;color=#FF5CA1FF&gt;ハートの魔法&lt;/color&gt;を.. 
-◆.. .. ま.. げつ.. の夜.. たべ.. ..と。</t>
-    <rPh sb="19" eb="20">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="202" eb="203">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="217" eb="218">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="227" eb="230">
-      <t>ニダンメ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="297" eb="298">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="312" eb="313">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="328" eb="330">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="338" eb="340">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="363" eb="366">
-      <t>サンダンガサ</t>
-    </rPh>
-    <rPh sb="386" eb="388">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="406" eb="408">
-      <t>ユメミ</t>
-    </rPh>
-    <rPh sb="425" eb="426">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="427" eb="429">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="440" eb="441">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="442" eb="443">
-      <t>ブクロ</t>
-    </rPh>
-    <rPh sb="444" eb="445">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="448" eb="450">
-      <t>チョクセツ</t>
-    </rPh>
-    <rPh sb="465" eb="466">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="478" eb="480">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="481" eb="483">
-      <t>カジツ</t>
-    </rPh>
-    <rPh sb="509" eb="510">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="547" eb="549">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="580" eb="581">
-      <t>ヨル</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8117,6 +7797,237 @@
     <t>春のおかし大祭典の賞品</t>
     <rPh sb="9" eb="11">
       <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- 太陽のレシピ -
+ケーキ生地のつくりかた
+i. はくりきこ　×　ココアパウダー
+ii. たまご　×　さとう　×　バターを混ぜ、アパレイユを作る
+iii. &lt;color=#BA9535FF&gt;ブラックロータスポーション&lt;/color&gt;
+i + ii + iiiをまぜて.. 
+&lt;color=#FF5CA1FF&gt;ウィンドミキサー&lt;/color&gt;の絵が描かれている。
+ブラックロータスココアケーキ（生地）の完成。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="218" eb="219">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="242" eb="244">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- 星のレシピ -
+クリームの作り方
+太陽と月のしずくをまぜたクリーム
+i. 作りたてクリームを事前に作っておく
+ii. &lt;color=#BA9535FF&gt;太陽の実&lt;/color&gt;と&lt;color=#BA9535FF&gt;月の実&lt;/color&gt;を同時にクリームに入れ、混ぜ合わせる。
+夢見のクリームの完成
+太陽の実とは.. オレンジのこと？
+月の実とは.. なにも描かれていないようだ。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="124" eb="125">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="151" eb="152">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="163" eb="165">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="171" eb="172">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="174" eb="175">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="183" eb="185">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="191" eb="193">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- 月のレシピ -
+トッピング方法のレシピ
+ケーキ全体にクリームをぬったあとの状態の絵が描かれている。
+仕上げに、&lt;color=#FDFF80FF&gt;２つの果物&lt;/color&gt;を同時にのせるようだ。
+・&lt;color=#BA9535FF&gt;スカーレットベリー&lt;/color&gt;
+・&lt;color=#BA9535FF&gt;ジェムナッツ&lt;/color&gt;
+仕上げに、もりだくさんのせる.. とかいている。
+※注意書き：　&lt;color=#FDFF80FF&gt;同時に&lt;/color&gt;トッピングすること。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エデンのレシピのかけら】
+エデンの作り方について書かれたレシピのようだ。
+- ハートのレシピ -
+エデンの制作の流れがかかれている。
+◆事前に、スポンジ生地を&lt;color=#FF5CA1FF&gt;スライサー&lt;/color&gt;で３つに分ける。
+◆i. 一段目　スライスしたスポンジ生地に、&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;と、&lt;color=#BA9535FF&gt;白いクリーム&lt;/color&gt;を塗る。
+◆ii. 二段目　スライスしたスポンジ生地に、&lt;color=#BA9535FF&gt;レインボーベリー&lt;/color&gt;と、&lt;color=#BA9535FF&gt;白いクリーム&lt;/color&gt;を塗る。
+◆iii. iとiiの生地、さらにスポンジ生地でふたをし、&lt;color=#BA9535FF&gt;三段重ね&lt;/color&gt;にする。
+そのあと、全体を&lt;color=#BA9535FF&gt;夢見クリーム&lt;/color&gt;できれいに塗り仕上げる。
+※クリームは、絞り袋に入れず、直接ぬって良さそうだ。
+◆iiii. 月のレシ.. どおりに、２種類の果実をふんだんに.. トッピング。
+◆.. （かすれて読みづらい）
+.. &lt;color=#FF5CA1FF&gt;ハートの魔法&lt;/color&gt;？
+◆.. .. ま.. げつ.. の夜.. たべる.. と？
+手順は、これ以降かすれて読めなくなっている。</t>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="192" eb="193">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="207" eb="208">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="217" eb="220">
+      <t>ニダンメ</t>
+    </rPh>
+    <rPh sb="231" eb="233">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="287" eb="288">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="302" eb="303">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="318" eb="320">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="328" eb="330">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="353" eb="356">
+      <t>サンダンガサ</t>
+    </rPh>
+    <rPh sb="376" eb="378">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="396" eb="398">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="415" eb="416">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="417" eb="419">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="458" eb="459">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="471" eb="473">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="474" eb="476">
+      <t>カジツ</t>
+    </rPh>
+    <rPh sb="502" eb="503">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="533" eb="535">
+      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8645,10 +8556,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8750,7 +8661,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -9134,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9248,10 +9159,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D14" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9278,7 +9189,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9296,10 +9207,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D15" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9326,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9344,10 +9255,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -9374,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -9392,10 +9303,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D17" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9422,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9437,13 +9348,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C18" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D18" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9470,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9758,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9806,7 +9717,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10238,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10253,13 +10164,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C35" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D35" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10286,7 +10197,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10718,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10958,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -11246,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11294,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11342,7 +11253,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11645,13 +11556,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C64" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D64" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11678,7 +11589,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11726,7 +11637,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -12605,13 +12516,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C84" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D84" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12638,7 +12549,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12734,7 +12645,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12782,7 +12693,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>440</v>
+        <v>549</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12830,7 +12741,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>441</v>
+        <v>550</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12878,7 +12789,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>442</v>
+        <v>551</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12926,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>443</v>
+        <v>552</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12992,10 +12903,10 @@
         <v>372</v>
       </c>
       <c r="C92" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D92" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -13022,7 +12933,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -13040,10 +12951,10 @@
         <v>372</v>
       </c>
       <c r="C93" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D93" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -13070,7 +12981,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -13088,10 +12999,10 @@
         <v>372</v>
       </c>
       <c r="C94" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D94" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13118,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13136,10 +13047,10 @@
         <v>372</v>
       </c>
       <c r="C95" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D95" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13166,7 +13077,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13184,10 +13095,10 @@
         <v>372</v>
       </c>
       <c r="C96" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D96" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13214,7 +13125,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13262,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13310,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13328,10 +13239,10 @@
         <v>372</v>
       </c>
       <c r="C99" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D99" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13358,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13424,10 +13335,10 @@
         <v>372</v>
       </c>
       <c r="C101" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D101" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13454,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13598,7 +13509,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13646,7 +13557,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13694,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13742,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13790,7 +13701,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13838,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13886,7 +13797,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13982,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -14000,10 +13911,10 @@
         <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D113" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -14030,7 +13941,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -14174,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14222,7 +14133,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14270,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14318,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14366,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14414,7 +14325,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14462,7 +14373,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14510,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14558,7 +14469,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14606,7 +14517,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14702,7 +14613,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14750,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14816,10 +14727,10 @@
         <v>372</v>
       </c>
       <c r="C130" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D130" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14846,7 +14757,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14864,10 +14775,10 @@
         <v>372</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E131" s="16">
         <v>500</v>
@@ -14894,7 +14805,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="17" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N131" s="16">
         <v>5000</v>
@@ -14912,10 +14823,10 @@
         <v>372</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E132" s="16">
         <v>500</v>
@@ -14942,7 +14853,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N132" s="16">
         <v>5000</v>
@@ -14960,10 +14871,10 @@
         <v>372</v>
       </c>
       <c r="C133" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D133" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14990,7 +14901,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -15008,10 +14919,10 @@
         <v>372</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E134" s="16">
         <v>500</v>
@@ -15038,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="17" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N134" s="16">
         <v>5000</v>
@@ -15056,10 +14967,10 @@
         <v>372</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E135" s="16">
         <v>500</v>
@@ -15086,7 +14997,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N135" s="16">
         <v>5000</v>
@@ -15104,10 +15015,10 @@
         <v>372</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E136" s="16">
         <v>500</v>
@@ -15134,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="17" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N136" s="16">
         <v>5000</v>
@@ -15152,10 +15063,10 @@
         <v>372</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E137" s="16">
         <v>500</v>
@@ -15182,7 +15093,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="17" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N137" s="16">
         <v>5000</v>
@@ -15200,10 +15111,10 @@
         <v>372</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E138" s="16">
         <v>500</v>
@@ -15230,7 +15141,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="17" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N138" s="16">
         <v>5000</v>
@@ -15248,10 +15159,10 @@
         <v>372</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E139" s="16">
         <v>500</v>
@@ -15278,7 +15189,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="17" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N139" s="16">
         <v>5000</v>
@@ -15296,10 +15207,10 @@
         <v>372</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E140" s="16">
         <v>500</v>
@@ -15326,7 +15237,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="17" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N140" s="16">
         <v>5000</v>
@@ -15821,10 +15732,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -16085,13 +15996,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>488</v>
+      </c>
+      <c r="C7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D7" t="s">
         <v>492</v>
-      </c>
-      <c r="C7" t="s">
-        <v>497</v>
-      </c>
-      <c r="D7" t="s">
-        <v>496</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16133,13 +16044,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D8" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16181,13 +16092,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C9" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D9" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16565,7 +16476,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C17" t="s">
         <v>197</v>
@@ -16613,13 +16524,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C18" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D18" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB068B-1B44-4D5F-A7DF-4CD5FA9E079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8447DEAE-F313-4C09-BBC3-1E9EA5FEB37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="1260" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="556">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -3456,13 +3456,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>エデンのレシピ＜絵柄＞</t>
-    <rPh sb="8" eb="10">
-      <t>エガラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mg_aromapotion_book</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -5412,13 +5405,6 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マジックパティスリーの賞品</t>
-    <rPh sb="11" eb="13">
-      <t>ショウヒン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7358,26 +7344,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>チョコレートの教本</t>
-    <rPh sb="7" eb="9">
-      <t>キョウホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>夏お店で売ってる</t>
-    <rPh sb="0" eb="1">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>チョコバナナクレープのレシピ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7794,13 +7760,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>春のおかし大祭典の賞品</t>
-    <rPh sb="9" eb="11">
-      <t>ショウヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【エデンのレシピのかけら】
 エデンの作り方について書かれたレシピのようだ。
 - 太陽のレシピ -
@@ -8028,6 +7987,65 @@
     </rPh>
     <rPh sb="533" eb="535">
       <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコレートの魔術書</t>
+    <rPh sb="7" eb="9">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひんやりお菓子コンテストの賞品</t>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディオショコラチャンピオンシップの賞品</t>
+    <rPh sb="17" eb="19">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エデンのレシピのメモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジックパティスリーの賞品（2位）</t>
+    <rPh sb="11" eb="13">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジックパティスリーの賞品（1位）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春のおかし大祭典の賞品（2位）</t>
+    <rPh sb="9" eb="11">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンチェルティーノ・イン・ブルーの賞品</t>
+    <rPh sb="17" eb="19">
+      <t>ショウヒン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8143,7 +8161,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8194,6 +8212,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8556,10 +8580,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8661,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8826,7 +8850,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8853,7 +8877,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -9045,7 +9069,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9159,10 +9183,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D14" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9189,7 +9213,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9207,10 +9231,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9237,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9255,10 +9279,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -9285,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -9303,10 +9327,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D17" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9333,7 +9357,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9348,13 +9372,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C18" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D18" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9381,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9669,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9717,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10149,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10164,13 +10188,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C35" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D35" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10197,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10629,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10821,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N48" s="4">
         <v>9999</v>
@@ -10836,7 +10860,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C49" t="s">
         <v>196</v>
@@ -10869,7 +10893,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10884,7 +10908,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C50" t="s">
         <v>201</v>
@@ -10932,7 +10956,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C51" t="s">
         <v>204</v>
@@ -10980,7 +11004,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C52" t="s">
         <v>206</v>
@@ -11013,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11028,7 +11052,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s">
         <v>266</v>
@@ -11061,7 +11085,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N53">
         <v>350</v>
@@ -11076,7 +11100,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C54" t="s">
         <v>267</v>
@@ -11109,7 +11133,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11124,7 +11148,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C55" t="s">
         <v>296</v>
@@ -11157,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11172,7 +11196,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C56" t="s">
         <v>297</v>
@@ -11205,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11220,7 +11244,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C57" t="s">
         <v>275</v>
@@ -11253,7 +11277,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11316,7 +11340,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C59" t="s">
         <v>211</v>
@@ -11364,7 +11388,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C60" t="s">
         <v>213</v>
@@ -11412,7 +11436,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C61" t="s">
         <v>215</v>
@@ -11460,7 +11484,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C62" t="s">
         <v>218</v>
@@ -11493,7 +11517,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N62">
         <v>520</v>
@@ -11508,7 +11532,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C63" t="s">
         <v>219</v>
@@ -11541,7 +11565,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N63">
         <v>530</v>
@@ -11556,13 +11580,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C64" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D64" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11589,7 +11613,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11637,7 +11661,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -11652,7 +11676,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C66" t="s">
         <v>224</v>
@@ -11685,7 +11709,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N66">
         <v>550</v>
@@ -11700,7 +11724,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C67" t="s">
         <v>225</v>
@@ -11733,7 +11757,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N67">
         <v>560</v>
@@ -11748,7 +11772,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C68" t="s">
         <v>229</v>
@@ -11781,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N68">
         <v>570</v>
@@ -11796,7 +11820,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C69" t="s">
         <v>228</v>
@@ -11844,7 +11868,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C70" t="s">
         <v>231</v>
@@ -11940,7 +11964,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C72" t="s">
         <v>235</v>
@@ -11973,7 +11997,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N72">
         <v>610</v>
@@ -12036,7 +12060,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C74" t="s">
         <v>238</v>
@@ -12069,7 +12093,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N74">
         <v>700</v>
@@ -12084,7 +12108,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C75" t="s">
         <v>260</v>
@@ -12117,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N75">
         <v>710</v>
@@ -12132,7 +12156,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C76" t="s">
         <v>240</v>
@@ -12165,7 +12189,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N76">
         <v>720</v>
@@ -12180,7 +12204,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C77" t="s">
         <v>242</v>
@@ -12213,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N77">
         <v>730</v>
@@ -12228,7 +12252,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C78" t="s">
         <v>243</v>
@@ -12261,7 +12285,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N78">
         <v>740</v>
@@ -12276,7 +12300,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C79" t="s">
         <v>250</v>
@@ -12309,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N79">
         <v>750</v>
@@ -12324,7 +12348,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C80" t="s">
         <v>246</v>
@@ -12372,7 +12396,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C81" t="s">
         <v>262</v>
@@ -12420,7 +12444,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C82" t="s">
         <v>269</v>
@@ -12453,7 +12477,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N82">
         <v>780</v>
@@ -12516,13 +12540,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C84" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D84" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12549,7 +12573,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12612,13 +12636,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C86" t="s">
         <v>290</v>
       </c>
       <c r="D86" t="s">
-        <v>307</v>
+        <v>551</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12645,7 +12669,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12660,7 +12684,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C87" t="s">
         <v>291</v>
@@ -12693,7 +12717,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12708,7 +12732,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C88" t="s">
         <v>292</v>
@@ -12741,7 +12765,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12756,7 +12780,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C89" t="s">
         <v>293</v>
@@ -12789,7 +12813,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12804,13 +12828,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C90" t="s">
         <v>294</v>
       </c>
       <c r="D90" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12837,7 +12861,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12852,7 +12876,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C91" t="s">
         <v>278</v>
@@ -12900,13 +12924,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C92" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D92" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12933,7 +12957,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12948,13 +12972,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C93" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D93" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12981,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12996,13 +13020,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C94" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D94" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13029,7 +13053,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13044,13 +13068,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C95" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D95" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13077,7 +13101,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13092,13 +13116,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C96" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D96" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13125,7 +13149,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13140,7 +13164,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C97" t="s">
         <v>289</v>
@@ -13173,7 +13197,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13188,13 +13212,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C98" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13221,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13236,13 +13260,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C99" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D99" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13269,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13284,13 +13308,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C100" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D100" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13317,7 +13341,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13332,13 +13356,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C101" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D101" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13365,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13380,13 +13404,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C102" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13413,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13428,7 +13452,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C103" t="s">
         <v>279</v>
@@ -13461,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13476,13 +13500,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C104" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D104" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13509,7 +13533,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13524,7 +13548,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C105" t="s">
         <v>281</v>
@@ -13557,7 +13581,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13572,13 +13596,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C106" t="s">
+        <v>319</v>
+      </c>
+      <c r="D106" t="s">
         <v>320</v>
-      </c>
-      <c r="D106" t="s">
-        <v>321</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13605,7 +13629,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13620,13 +13644,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C107" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D107" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13653,7 +13677,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13668,13 +13692,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C108" t="s">
+        <v>312</v>
+      </c>
+      <c r="D108" t="s">
         <v>313</v>
-      </c>
-      <c r="D108" t="s">
-        <v>314</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13701,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13716,13 +13740,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C109" t="s">
+        <v>325</v>
+      </c>
+      <c r="D109" t="s">
         <v>326</v>
-      </c>
-      <c r="D109" t="s">
-        <v>327</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13749,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13764,7 +13788,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C110" t="s">
         <v>287</v>
@@ -13797,7 +13821,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13812,13 +13836,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D111" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13845,7 +13869,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13860,13 +13884,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C112" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D112" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13893,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13908,13 +13932,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C113" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D113" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13941,7 +13965,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13956,13 +13980,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C114" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D114" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13989,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -14004,13 +14028,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C115" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D115" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -14037,7 +14061,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -14052,13 +14076,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C116" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D116" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -14085,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14100,7 +14124,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C117" t="s">
         <v>284</v>
@@ -14133,7 +14157,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14148,13 +14172,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D118" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14181,7 +14205,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14196,13 +14220,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C119" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14229,7 +14253,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14244,13 +14268,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C120" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14277,7 +14301,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14292,13 +14316,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C121" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D121" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14325,7 +14349,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14340,13 +14364,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C122" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D122" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14373,7 +14397,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14388,13 +14412,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C123" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D123" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14421,7 +14445,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14436,13 +14460,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C124" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D124" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14469,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14484,13 +14508,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C125" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D125" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14517,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14532,13 +14556,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C126" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D126" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14565,7 +14589,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>422</v>
+        <v>552</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14580,13 +14604,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C127" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D127" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14613,7 +14637,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14628,13 +14652,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C128" t="s">
+        <v>314</v>
+      </c>
+      <c r="D128" t="s">
         <v>315</v>
-      </c>
-      <c r="D128" t="s">
-        <v>316</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14661,7 +14685,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14676,13 +14700,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C129" t="s">
+        <v>307</v>
+      </c>
+      <c r="D129" t="s">
         <v>308</v>
-      </c>
-      <c r="D129" t="s">
-        <v>309</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14709,7 +14733,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14724,13 +14748,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C130" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D130" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14757,7 +14781,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14772,13 +14796,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E131" s="16">
         <v>500</v>
@@ -14805,7 +14829,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="17" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N131" s="16">
         <v>5000</v>
@@ -14820,13 +14844,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E132" s="16">
         <v>500</v>
@@ -14853,7 +14877,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N132" s="16">
         <v>5000</v>
@@ -14868,13 +14892,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D133" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14901,7 +14925,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14910,51 +14934,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="16">
+    <row r="134" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A134">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="B134" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="16" t="s">
-        <v>527</v>
-      </c>
-      <c r="D134" s="16" t="s">
-        <v>526</v>
-      </c>
-      <c r="E134" s="16">
+      <c r="B134" t="s">
+        <v>371</v>
+      </c>
+      <c r="C134" t="s">
+        <v>523</v>
+      </c>
+      <c r="D134" t="s">
+        <v>522</v>
+      </c>
+      <c r="E134">
         <v>500</v>
       </c>
-      <c r="F134" s="16">
+      <c r="F134">
         <v>150</v>
       </c>
-      <c r="G134" s="16">
-        <v>0</v>
-      </c>
-      <c r="H134" s="16">
-        <v>0</v>
-      </c>
-      <c r="I134" s="16">
-        <v>0</v>
-      </c>
-      <c r="J134" s="16">
-        <v>0</v>
-      </c>
-      <c r="K134" s="16">
-        <v>0</v>
-      </c>
-      <c r="L134" s="16">
-        <v>0</v>
-      </c>
-      <c r="M134" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="N134" s="16">
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="N134">
         <v>5000</v>
       </c>
-      <c r="O134" s="16">
+      <c r="O134">
         <v>5000</v>
       </c>
     </row>
@@ -14964,13 +14988,13 @@
         <v>133</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E135" s="16">
         <v>500</v>
@@ -14997,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N135" s="16">
         <v>5000</v>
@@ -15006,51 +15030,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="136" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="16">
+    <row r="136" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="B136" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="E136" s="16">
+      <c r="B136" t="s">
+        <v>371</v>
+      </c>
+      <c r="C136" t="s">
+        <v>526</v>
+      </c>
+      <c r="D136" t="s">
+        <v>527</v>
+      </c>
+      <c r="E136">
         <v>500</v>
       </c>
-      <c r="F136" s="16">
+      <c r="F136">
         <v>150</v>
       </c>
-      <c r="G136" s="16">
-        <v>0</v>
-      </c>
-      <c r="H136" s="16">
-        <v>0</v>
-      </c>
-      <c r="I136" s="16">
-        <v>0</v>
-      </c>
-      <c r="J136" s="16">
-        <v>0</v>
-      </c>
-      <c r="K136" s="16">
-        <v>0</v>
-      </c>
-      <c r="L136" s="16">
-        <v>0</v>
-      </c>
-      <c r="M136" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="N136" s="16">
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="N136">
         <v>5000</v>
       </c>
-      <c r="O136" s="16">
+      <c r="O136">
         <v>5000</v>
       </c>
     </row>
@@ -15060,13 +15084,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E137" s="16">
         <v>500</v>
@@ -15093,7 +15117,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="17" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N137" s="16">
         <v>5000</v>
@@ -15102,51 +15126,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="16">
+    <row r="138" spans="1:15" s="18" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="18">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="D138" s="16" t="s">
+      <c r="B138" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C138" s="18" t="s">
         <v>535</v>
       </c>
-      <c r="E138" s="16">
+      <c r="D138" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="E138" s="18">
         <v>500</v>
       </c>
-      <c r="F138" s="16">
+      <c r="F138" s="18">
         <v>150</v>
       </c>
-      <c r="G138" s="16">
-        <v>0</v>
-      </c>
-      <c r="H138" s="16">
-        <v>0</v>
-      </c>
-      <c r="I138" s="16">
-        <v>0</v>
-      </c>
-      <c r="J138" s="16">
-        <v>0</v>
-      </c>
-      <c r="K138" s="16">
-        <v>0</v>
-      </c>
-      <c r="L138" s="16">
-        <v>0</v>
-      </c>
-      <c r="M138" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="N138" s="16">
+      <c r="G138" s="18">
+        <v>0</v>
+      </c>
+      <c r="H138" s="18">
+        <v>0</v>
+      </c>
+      <c r="I138" s="18">
+        <v>0</v>
+      </c>
+      <c r="J138" s="18">
+        <v>0</v>
+      </c>
+      <c r="K138" s="18">
+        <v>0</v>
+      </c>
+      <c r="L138" s="18">
+        <v>0</v>
+      </c>
+      <c r="M138" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="N138" s="18">
         <v>5000</v>
       </c>
-      <c r="O138" s="16">
+      <c r="O138" s="18">
         <v>5000</v>
       </c>
     </row>
@@ -15156,13 +15180,13 @@
         <v>137</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E139" s="16">
         <v>500</v>
@@ -15189,7 +15213,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="17" t="s">
-        <v>542</v>
+        <v>463</v>
       </c>
       <c r="N139" s="16">
         <v>5000</v>
@@ -15204,13 +15228,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E140" s="16">
         <v>500</v>
@@ -15237,7 +15261,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="17" t="s">
-        <v>542</v>
+        <v>463</v>
       </c>
       <c r="N140" s="16">
         <v>5000</v>
@@ -15252,13 +15276,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E141" s="12">
         <v>500</v>
@@ -15300,13 +15324,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E142" s="12">
         <v>500</v>
@@ -15348,13 +15372,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E143" s="12">
         <v>500</v>
@@ -15396,13 +15420,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C144" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D144" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15429,7 +15453,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N144">
         <v>5000</v>
@@ -15444,13 +15468,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C145" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D145" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -15492,13 +15516,13 @@
         <v>144</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E146" s="12">
         <v>500</v>
@@ -15525,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N146" s="12">
         <v>5000</v>
@@ -15540,13 +15564,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C147" t="s">
+        <v>309</v>
+      </c>
+      <c r="D147" t="s">
         <v>310</v>
-      </c>
-      <c r="D147" t="s">
-        <v>311</v>
       </c>
       <c r="E147">
         <v>500</v>
@@ -15573,7 +15597,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N147">
         <v>5000</v>
@@ -15588,13 +15612,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C148" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D148" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -15621,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N148">
         <v>9999</v>
@@ -15732,10 +15756,10 @@
         <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15996,13 +16020,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16044,13 +16068,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>487</v>
+      </c>
+      <c r="C8" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" t="s">
         <v>489</v>
-      </c>
-      <c r="C8" t="s">
-        <v>494</v>
-      </c>
-      <c r="D8" t="s">
-        <v>491</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16092,13 +16116,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D9" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16476,7 +16500,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C17" t="s">
         <v>197</v>
@@ -16524,13 +16548,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C18" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D18" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8447DEAE-F313-4C09-BBC3-1E9EA5FEB37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA06695-B9CA-4BBD-911E-889669E2F6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -779,29 +779,6 @@
     <t>ジュースのしぼり方</t>
     <rPh sb="8" eb="9">
       <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">☆ジュースのしぼり方
-①まずは、&lt;color=#BA9535FF&gt;くだもの&lt;/color&gt;を集めましょう。
-②&lt;color=#FF5CA1FF&gt;魔法のジュースミキサー&lt;/color&gt;に、&lt;color=#BA9535FF&gt;くだもの&lt;/color&gt;を入れ、スイッチポン！
-あっという間に、おいしいジュースの出来上がり！
-</t>
-    <rPh sb="9" eb="10">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="142" eb="143">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="154" eb="157">
-      <t>デキア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8046,6 +8023,31 @@
     <t>コンチェルティーノ・イン・ブルーの賞品</t>
     <rPh sb="17" eb="19">
       <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>☆ジュースのしぼり方
+①まずは、&lt;color=#BA9535FF&gt;くだもの&lt;/color&gt;を集めましょう。
+②&lt;color=#FF5CA1FF&gt;魔法のジュースミキサー&lt;/color&gt;に、&lt;color=#BA9535FF&gt;くだもの&lt;/color&gt;を入れ、スイッチポン！
+あっという間に、おいしいジュースの出来上がり！
+なお、ジュースに使う果物は、
+入れれば入れた分だけ、濃縮されておいしくなります。
+目安としては、&lt;color=#BA9535FF&gt;5個&lt;/color&gt;以上は入れたほうが良いでしょう。</t>
+    <rPh sb="9" eb="10">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="142" eb="143">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="154" eb="157">
+      <t>デキア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8161,7 +8163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8212,12 +8214,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8577,13 +8573,13 @@
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8685,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8829,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -8850,7 +8846,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8877,7 +8873,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -8946,7 +8942,7 @@
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9">
         <v>500</v>
@@ -8973,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N9">
         <v>3050</v>
@@ -8991,10 +8987,10 @@
         <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E10">
         <v>500</v>
@@ -9021,7 +9017,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N10">
         <v>3070</v>
@@ -9036,13 +9032,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" t="s">
         <v>169</v>
-      </c>
-      <c r="D11" t="s">
-        <v>170</v>
       </c>
       <c r="E11">
         <v>500</v>
@@ -9069,7 +9065,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9084,13 +9080,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12">
         <v>500</v>
@@ -9117,7 +9113,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N12">
         <v>3090</v>
@@ -9132,13 +9128,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" t="s">
         <v>182</v>
-      </c>
-      <c r="D13" t="s">
-        <v>183</v>
       </c>
       <c r="E13">
         <v>500</v>
@@ -9165,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N13">
         <v>3100</v>
@@ -9183,10 +9179,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9213,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9231,10 +9227,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9261,7 +9257,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9279,10 +9275,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E16" s="14">
         <v>500</v>
@@ -9309,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N16" s="14">
         <v>3130</v>
@@ -9327,10 +9323,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9357,7 +9353,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9372,13 +9368,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9405,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9420,7 +9416,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
         <v>61</v>
@@ -9453,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N19">
         <v>3010</v>
@@ -9516,7 +9512,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
         <v>72</v>
@@ -9549,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N21">
         <v>3040</v>
@@ -9564,7 +9560,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
         <v>92</v>
@@ -9597,7 +9593,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>94</v>
+        <v>555</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -9645,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N23">
         <v>20</v>
@@ -9693,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9714,7 +9710,7 @@
         <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E25">
         <v>500</v>
@@ -9741,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -9756,13 +9752,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" t="s">
         <v>160</v>
-      </c>
-      <c r="C26" t="s">
-        <v>162</v>
-      </c>
-      <c r="D26" t="s">
-        <v>161</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -9789,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N26">
         <v>50</v>
@@ -9954,7 +9950,7 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E30">
         <v>500</v>
@@ -9981,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N30">
         <v>90</v>
@@ -10140,13 +10136,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E34">
         <v>500</v>
@@ -10173,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10188,13 +10184,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C35" t="s">
+        <v>442</v>
+      </c>
+      <c r="D35" t="s">
         <v>443</v>
-      </c>
-      <c r="D35" t="s">
-        <v>444</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10221,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10236,13 +10232,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E36">
         <v>500</v>
@@ -10269,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N36">
         <v>140</v>
@@ -10284,7 +10280,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -10317,7 +10313,7 @@
         <v>1</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N37">
         <v>200</v>
@@ -10332,13 +10328,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E38">
         <v>500</v>
@@ -10365,7 +10361,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N38">
         <v>210</v>
@@ -10380,13 +10376,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E39">
         <v>500</v>
@@ -10413,7 +10409,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N39">
         <v>220</v>
@@ -10428,13 +10424,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E40">
         <v>500</v>
@@ -10461,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N40">
         <v>230</v>
@@ -10476,13 +10472,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E41">
         <v>500</v>
@@ -10509,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N41">
         <v>240</v>
@@ -10524,13 +10520,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E42">
         <v>500</v>
@@ -10557,7 +10553,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N42">
         <v>250</v>
@@ -10605,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N43">
         <v>260</v>
@@ -10620,13 +10616,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" t="s">
         <v>163</v>
-      </c>
-      <c r="D44" t="s">
-        <v>164</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -10653,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10668,13 +10664,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -10701,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N45">
         <v>280</v>
@@ -10716,13 +10712,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -10749,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N46">
         <v>290</v>
@@ -10764,13 +10760,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E47">
         <v>500</v>
@@ -10797,7 +10793,7 @@
         <v>1</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N47">
         <v>300</v>
@@ -10812,13 +10808,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E48" s="4">
         <v>500</v>
@@ -10845,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N48" s="4">
         <v>9999</v>
@@ -10860,13 +10856,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D49" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -10893,7 +10889,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10908,13 +10904,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10941,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N50">
         <v>320</v>
@@ -10956,13 +10952,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10989,7 +10985,7 @@
         <v>1</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N51">
         <v>330</v>
@@ -11004,13 +11000,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C52" t="s">
+        <v>205</v>
+      </c>
+      <c r="D52" t="s">
         <v>206</v>
-      </c>
-      <c r="D52" t="s">
-        <v>207</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -11037,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11052,13 +11048,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -11085,7 +11081,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N53">
         <v>350</v>
@@ -11100,13 +11096,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -11133,7 +11129,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11148,13 +11144,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C55" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D55" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -11181,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11196,13 +11192,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D56" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -11229,7 +11225,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11244,13 +11240,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C57" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -11277,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11292,13 +11288,13 @@
         <v>56</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>209</v>
       </c>
       <c r="E58" s="8">
         <v>500</v>
@@ -11325,7 +11321,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N58" s="8">
         <v>400</v>
@@ -11340,13 +11336,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -11373,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11388,13 +11384,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C60" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -11421,7 +11417,7 @@
         <v>1</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N60">
         <v>500</v>
@@ -11436,13 +11432,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -11469,7 +11465,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N61">
         <v>510</v>
@@ -11484,13 +11480,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -11517,7 +11513,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N62">
         <v>520</v>
@@ -11532,13 +11528,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C63" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -11565,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N63">
         <v>530</v>
@@ -11580,13 +11576,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C64" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D64" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11613,7 +11609,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11628,13 +11624,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E65">
         <v>500</v>
@@ -11661,7 +11657,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -11676,13 +11672,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D66" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -11709,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N66">
         <v>550</v>
@@ -11724,13 +11720,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E67">
         <v>500</v>
@@ -11757,7 +11753,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N67">
         <v>560</v>
@@ -11772,13 +11768,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -11805,7 +11801,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N68">
         <v>570</v>
@@ -11820,13 +11816,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D69" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E69">
         <v>500</v>
@@ -11853,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N69">
         <v>580</v>
@@ -11868,13 +11864,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -11901,7 +11897,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N70">
         <v>590</v>
@@ -11916,13 +11912,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E71" s="6">
         <v>500</v>
@@ -11949,7 +11945,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N71" s="6">
         <v>600</v>
@@ -11964,13 +11960,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C72" t="s">
+        <v>234</v>
+      </c>
+      <c r="D72" t="s">
         <v>235</v>
-      </c>
-      <c r="D72" t="s">
-        <v>236</v>
       </c>
       <c r="E72">
         <v>500</v>
@@ -11997,7 +11993,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N72">
         <v>610</v>
@@ -12012,13 +12008,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E73" s="6">
         <v>500</v>
@@ -12045,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N73" s="6">
         <v>620</v>
@@ -12060,13 +12056,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -12093,7 +12089,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N74">
         <v>700</v>
@@ -12108,13 +12104,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C75" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -12141,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N75">
         <v>710</v>
@@ -12156,13 +12152,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C76" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D76" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -12189,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N76">
         <v>720</v>
@@ -12204,13 +12200,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D77" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -12237,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N77">
         <v>730</v>
@@ -12252,13 +12248,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C78" t="s">
+        <v>242</v>
+      </c>
+      <c r="D78" t="s">
         <v>243</v>
-      </c>
-      <c r="D78" t="s">
-        <v>244</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -12285,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N78">
         <v>740</v>
@@ -12300,13 +12296,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C79" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D79" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E79">
         <v>500</v>
@@ -12333,7 +12329,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N79">
         <v>750</v>
@@ -12348,13 +12344,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C80" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D80" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -12381,7 +12377,7 @@
         <v>1</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N80">
         <v>760</v>
@@ -12396,13 +12392,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C81" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E81">
         <v>500</v>
@@ -12429,7 +12425,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N81">
         <v>770</v>
@@ -12444,13 +12440,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C82" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12477,7 +12473,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N82">
         <v>780</v>
@@ -12492,13 +12488,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E83" s="6">
         <v>500</v>
@@ -12525,7 +12521,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N83" s="6">
         <v>790</v>
@@ -12540,13 +12536,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C84" t="s">
+        <v>480</v>
+      </c>
+      <c r="D84" t="s">
         <v>481</v>
-      </c>
-      <c r="D84" t="s">
-        <v>482</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12573,7 +12569,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12588,13 +12584,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E85" s="10">
         <v>500</v>
@@ -12621,7 +12617,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N85" s="10">
         <v>9999</v>
@@ -12636,13 +12632,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C86" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D86" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12669,7 +12665,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12684,13 +12680,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C87" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12717,7 +12713,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12732,13 +12728,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C88" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D88" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12765,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12780,13 +12776,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C89" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D89" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12813,7 +12809,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12828,13 +12824,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D90" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12861,7 +12857,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12876,13 +12872,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C91" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D91" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12909,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12924,13 +12920,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C92" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D92" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12957,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12972,13 +12968,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C93" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D93" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -13005,7 +13001,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -13020,13 +13016,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C94" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D94" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13053,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13068,13 +13064,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C95" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D95" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13101,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13116,13 +13112,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C96" t="s">
+        <v>538</v>
+      </c>
+      <c r="D96" t="s">
         <v>539</v>
-      </c>
-      <c r="D96" t="s">
-        <v>540</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13149,7 +13145,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13164,13 +13160,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C97" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D97" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -13197,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13212,13 +13208,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D98" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13245,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13260,13 +13256,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C99" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D99" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13293,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13308,13 +13304,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C100" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13341,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13356,13 +13352,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C101" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D101" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13389,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13404,13 +13400,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C102" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D102" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13437,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13452,13 +13448,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C103" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13485,7 +13481,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13500,13 +13496,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C104" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D104" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13533,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13548,13 +13544,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C105" t="s">
+        <v>280</v>
+      </c>
+      <c r="D105" t="s">
         <v>281</v>
-      </c>
-      <c r="D105" t="s">
-        <v>282</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13581,7 +13577,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13596,13 +13592,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C106" t="s">
+        <v>318</v>
+      </c>
+      <c r="D106" t="s">
         <v>319</v>
-      </c>
-      <c r="D106" t="s">
-        <v>320</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13629,7 +13625,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13644,13 +13640,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C107" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D107" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13677,7 +13673,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13692,13 +13688,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C108" t="s">
+        <v>311</v>
+      </c>
+      <c r="D108" t="s">
         <v>312</v>
-      </c>
-      <c r="D108" t="s">
-        <v>313</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13725,7 +13721,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13740,13 +13736,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C109" t="s">
+        <v>324</v>
+      </c>
+      <c r="D109" t="s">
         <v>325</v>
-      </c>
-      <c r="D109" t="s">
-        <v>326</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13773,7 +13769,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13788,13 +13784,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C110" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D110" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13821,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13836,13 +13832,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C111" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D111" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13869,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13884,13 +13880,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C112" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D112" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13917,7 +13913,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13932,13 +13928,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C113" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D113" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13965,7 +13961,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13980,13 +13976,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C114" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -14013,7 +14009,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -14028,13 +14024,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C115" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D115" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -14061,7 +14057,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -14076,13 +14072,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C116" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D116" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -14109,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14124,13 +14120,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C117" t="s">
+        <v>283</v>
+      </c>
+      <c r="D117" t="s">
         <v>284</v>
-      </c>
-      <c r="D117" t="s">
-        <v>285</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -14157,7 +14153,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14172,13 +14168,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C118" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D118" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14205,7 +14201,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14220,13 +14216,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C119" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D119" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14253,7 +14249,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14268,13 +14264,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C120" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D120" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14301,7 +14297,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14316,13 +14312,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C121" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D121" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14349,7 +14345,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14364,13 +14360,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C122" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D122" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14397,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14412,13 +14408,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C123" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14445,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14460,13 +14456,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C124" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D124" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14493,7 +14489,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14508,13 +14504,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C125" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D125" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14541,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14556,13 +14552,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C126" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D126" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14589,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14604,13 +14600,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C127" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D127" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14637,7 +14633,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14652,13 +14648,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C128" t="s">
+        <v>313</v>
+      </c>
+      <c r="D128" t="s">
         <v>314</v>
-      </c>
-      <c r="D128" t="s">
-        <v>315</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14685,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14700,13 +14696,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C129" t="s">
+        <v>306</v>
+      </c>
+      <c r="D129" t="s">
         <v>307</v>
-      </c>
-      <c r="D129" t="s">
-        <v>308</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14733,7 +14729,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14748,13 +14744,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C130" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D130" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14781,7 +14777,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14796,13 +14792,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E131" s="16">
         <v>500</v>
@@ -14829,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N131" s="16">
         <v>5000</v>
@@ -14844,13 +14840,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E132" s="16">
         <v>500</v>
@@ -14877,7 +14873,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N132" s="16">
         <v>5000</v>
@@ -14892,13 +14888,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C133" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D133" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14925,7 +14921,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14940,13 +14936,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C134" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D134" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14973,7 +14969,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14988,13 +14984,13 @@
         <v>133</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E135" s="16">
         <v>500</v>
@@ -15021,7 +15017,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N135" s="16">
         <v>5000</v>
@@ -15036,13 +15032,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C136" t="s">
+        <v>525</v>
+      </c>
+      <c r="D136" t="s">
         <v>526</v>
-      </c>
-      <c r="D136" t="s">
-        <v>527</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -15069,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -15084,13 +15080,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E137" s="16">
         <v>500</v>
@@ -15117,7 +15113,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N137" s="16">
         <v>5000</v>
@@ -15126,51 +15122,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="18" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="18">
+    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="C138" s="18" t="s">
-        <v>535</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>531</v>
-      </c>
-      <c r="E138" s="18">
+      <c r="B138" t="s">
+        <v>370</v>
+      </c>
+      <c r="C138" t="s">
+        <v>534</v>
+      </c>
+      <c r="D138" t="s">
+        <v>530</v>
+      </c>
+      <c r="E138">
         <v>500</v>
       </c>
-      <c r="F138" s="18">
+      <c r="F138">
         <v>150</v>
       </c>
-      <c r="G138" s="18">
-        <v>0</v>
-      </c>
-      <c r="H138" s="18">
-        <v>0</v>
-      </c>
-      <c r="I138" s="18">
-        <v>0</v>
-      </c>
-      <c r="J138" s="18">
-        <v>0</v>
-      </c>
-      <c r="K138" s="18">
-        <v>0</v>
-      </c>
-      <c r="L138" s="18">
-        <v>0</v>
-      </c>
-      <c r="M138" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="N138" s="18">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="N138">
         <v>5000</v>
       </c>
-      <c r="O138" s="18">
+      <c r="O138">
         <v>5000</v>
       </c>
     </row>
@@ -15180,13 +15176,13 @@
         <v>137</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E139" s="16">
         <v>500</v>
@@ -15213,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N139" s="16">
         <v>5000</v>
@@ -15228,13 +15224,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E140" s="16">
         <v>500</v>
@@ -15261,7 +15257,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N140" s="16">
         <v>5000</v>
@@ -15276,13 +15272,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E141" s="12">
         <v>500</v>
@@ -15309,7 +15305,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N141" s="12">
         <v>5000</v>
@@ -15324,13 +15320,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E142" s="12">
         <v>500</v>
@@ -15357,7 +15353,7 @@
         <v>0</v>
       </c>
       <c r="M142" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N142" s="12">
         <v>5000</v>
@@ -15372,13 +15368,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E143" s="12">
         <v>500</v>
@@ -15405,7 +15401,7 @@
         <v>0</v>
       </c>
       <c r="M143" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N143" s="12">
         <v>5000</v>
@@ -15420,13 +15416,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C144" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D144" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15453,7 +15449,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N144">
         <v>5000</v>
@@ -15468,13 +15464,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C145" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D145" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -15501,7 +15497,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N145">
         <v>5000</v>
@@ -15516,13 +15512,13 @@
         <v>144</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E146" s="12">
         <v>500</v>
@@ -15549,7 +15545,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N146" s="12">
         <v>5000</v>
@@ -15564,13 +15560,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C147" t="s">
+        <v>308</v>
+      </c>
+      <c r="D147" t="s">
         <v>309</v>
-      </c>
-      <c r="D147" t="s">
-        <v>310</v>
       </c>
       <c r="E147">
         <v>500</v>
@@ -15597,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N147">
         <v>5000</v>
@@ -15612,13 +15608,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C148" t="s">
+        <v>433</v>
+      </c>
+      <c r="D148" t="s">
         <v>434</v>
-      </c>
-      <c r="D148" t="s">
-        <v>435</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -15645,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N148">
         <v>9999</v>
@@ -15659,13 +15655,13 @@
         <v>10000</v>
       </c>
       <c r="B149" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C149" t="s">
+        <v>171</v>
+      </c>
+      <c r="D149" t="s">
         <v>172</v>
-      </c>
-      <c r="D149" t="s">
-        <v>173</v>
       </c>
       <c r="E149">
         <v>500</v>
@@ -15692,7 +15688,7 @@
         <v>1</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N149">
         <v>9000</v>
@@ -15753,13 +15749,13 @@
         <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15780,7 +15776,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
@@ -15813,7 +15809,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N2">
         <v>9999</v>
@@ -15828,13 +15824,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -15876,13 +15872,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -15924,13 +15920,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
         <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -15972,13 +15968,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -16020,13 +16016,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16068,13 +16064,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16116,13 +16112,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16164,7 +16160,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>76</v>
@@ -16212,7 +16208,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>77</v>
@@ -16260,13 +16256,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -16308,7 +16304,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
         <v>85</v>
@@ -16356,13 +16352,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" t="s">
         <v>144</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -16404,13 +16400,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -16452,13 +16448,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -16500,13 +16496,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" t="s">
         <v>197</v>
-      </c>
-      <c r="D17" t="s">
-        <v>198</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -16548,13 +16544,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D18" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA06695-B9CA-4BBD-911E-889669E2F6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF384FAF-4326-478B-B386-661AABC3E3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2550" yWindow="1335" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="557">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -2810,225 +2810,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">【お城ケーキ　ファンタジアのレシピ】
-難易度：高
-とってもかわいいお城のケーキ♪
-でも、実は2段重ねのケーキをベースに、作れますよ。
-作るのが大変なお菓子ですが、ぜひ挑戦してみてくださいね。
-以下の事前準備が必要です。作れない場合は、先に作れるようにしましょう。
-事前準備：
-・生クリームといちご・ラズベリー
-・液体チョコレート
-・スポンジケーキ＜スライス＞
-・ロールクッキーとコンフィズリー
-・魔法「ウィンドクラウン」の習得
-【作り方】
-①２つのケーキ土台を作りましょう♪
-・一段目
-&lt;color=#BA9535FF&gt;スポンジケーキ（スライスしたもの）&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;ピンク色のクリーム&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;
-・二段目
-&lt;color=#BA9535FF&gt;スポンジケーキ（スライスしたもの）&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;ピンク色のクリーム&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;ラズベリー&lt;/color&gt;
-クリームはホイップでなく、作りたてクリームをそのまま塗ります。
-土台が出来上がったら、&lt;color=#FF5CA1FF&gt;２つをのせます&lt;/color&gt;。
-②&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;魔法「ウィンドクラウン」&lt;/color&gt;で王冠の形のチョコレートにする。冷やすのを忘れない。
-③お城の柱の部分を作る。
-&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;に三角形の&lt;color=#BA9535FF&gt;コンフィズリー&lt;/color&gt;をのせる。2個作る。
-④　①＋②＋③で、材料を組み合わせて完成☆
-【さらに仕上げ】
-このままだと見た目が少しシンプルなので、
-トッピングに、
-&lt;color=#BA9535FF&gt;・お花を散らす
-・人形の兵隊をのせる
-・光る砂糖を散りばめる&lt;/color&gt;
-など工夫すると、
-すっごくかわいくなりますよ～♪
-ぜひお試しくださいね。
-パステルカラーで夢気分♪
-お姫様気分で召し上がってね♪
-</t>
-    <rPh sb="2" eb="3">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ジツ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ダンカサ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>タイヘン</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>チョウセン</t>
-    </rPh>
-    <rPh sb="97" eb="99">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="100" eb="104">
-      <t>ジゼンジュンビ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="110" eb="111">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="118" eb="119">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="120" eb="121">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="135" eb="139">
-      <t>ジゼンジュンビ</t>
-    </rPh>
-    <rPh sb="142" eb="143">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="159" eb="161">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="219" eb="220">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="221" eb="222">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="231" eb="233">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="234" eb="235">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="490" eb="491">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="503" eb="504">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="509" eb="511">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="512" eb="515">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="573" eb="575">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="608" eb="610">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="629" eb="631">
-      <t>オウカン</t>
-    </rPh>
-    <rPh sb="632" eb="633">
-      <t>カタチ</t>
-    </rPh>
-    <rPh sb="644" eb="645">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="649" eb="650">
-      <t>ワス</t>
-    </rPh>
-    <rPh sb="658" eb="659">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="660" eb="661">
-      <t>ハシラ</t>
-    </rPh>
-    <rPh sb="662" eb="664">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="665" eb="666">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="702" eb="705">
-      <t>サンカクケイ</t>
-    </rPh>
-    <rPh sb="744" eb="745">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="745" eb="746">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="759" eb="761">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="762" eb="763">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="764" eb="765">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="768" eb="770">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="777" eb="779">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="788" eb="789">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="790" eb="791">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="792" eb="793">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="832" eb="833">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="834" eb="835">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="839" eb="841">
-      <t>ニンギョウ</t>
-    </rPh>
-    <rPh sb="842" eb="844">
-      <t>ヘイタイ</t>
-    </rPh>
-    <rPh sb="850" eb="851">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="852" eb="854">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="855" eb="856">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="871" eb="873">
-      <t>クフウ</t>
-    </rPh>
-    <rPh sb="898" eb="899">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="916" eb="919">
-      <t>ユメキブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ロールクッキーのレシピ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4253,126 +4034,6 @@
   </si>
   <si>
     <t>Items/patipati_soda</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【チーズケーキのレシピ】
-難易度・・　中～高　ぐらい
-少し手順が複雑ですが、がんばって作ってみてくださいね！
-事前準備：ビスケットを焼けるようにしておく
-チーズケーキは、①底の生地（タルト生地）と②上のクリームの生地の二つを合わせて作ります。
-①底の生地・・・&lt;color=#BA9535FF&gt;ビスケット&lt;/color&gt;を細かく砕き、&lt;color=#BA9535FF&gt;バター&lt;/color&gt;を混ぜて、型作って焼けば完成♪
-②クリームの生地・・・
-1. &lt;color=#BA9535FF&gt;クリームチーズ、砂糖、卵黄&lt;/color&gt;を混ぜ合わせます。
-2. できた生地に、さらに、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;と&lt;color=#BA9535FF&gt;レモン&lt;/color&gt;を加えます。
-3. 2の生地に&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;を入れ、&lt;color=#FF5CA1FF&gt;ウィンドミキサー&lt;/color&gt;でふんわり混ぜます。
-①に②を足して、焼き上げれば完成！！
-ふんわり濃厚なチーズケーキを召し上がれ♪</t>
-    <rPh sb="14" eb="17">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="58" eb="62">
-      <t>ジゼンジュンビ</t>
-    </rPh>
-    <rPh sb="69" eb="70">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="90" eb="91">
-      <t>ソコ</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="103" eb="104">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="113" eb="114">
-      <t>フタ</t>
-    </rPh>
-    <rPh sb="116" eb="117">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="120" eb="121">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="128" eb="129">
-      <t>ソコ</t>
-    </rPh>
-    <rPh sb="130" eb="132">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="166" eb="167">
-      <t>コマ</t>
-    </rPh>
-    <rPh sb="169" eb="170">
-      <t>クダ</t>
-    </rPh>
-    <rPh sb="201" eb="202">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="223" eb="225">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="257" eb="259">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="260" eb="262">
-      <t>ランオウ</t>
-    </rPh>
-    <rPh sb="271" eb="272">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="273" eb="274">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="287" eb="289">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="312" eb="313">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="355" eb="356">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="367" eb="369">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="387" eb="390">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="399" eb="400">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="440" eb="441">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="451" eb="452">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="455" eb="456">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="457" eb="458">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="461" eb="463">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="471" eb="473">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="481" eb="482">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="483" eb="484">
-      <t>ア</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8051,6 +7712,350 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>【チーズケーキのレシピ】
+難易度・・　中～高　ぐらい
+少し手順が複雑ですが、がんばって作ってみてくださいね！
+事前準備：ビスケットを焼けるようにしておく
+チーズケーキは、①底の生地（タルト生地）と②上のクリームの生地の二つを合わせて作ります。
+①底の生地・・・&lt;color=#BA9535FF&gt;ビスケット&lt;/color&gt;、&lt;color=#BA9535FF&gt;バター&lt;/color&gt;を混ぜて、型作って焼けば完成♪
+②クリームの生地・・・
+1. &lt;color=#BA9535FF&gt;クリームチーズ、砂糖、卵黄&lt;/color&gt;を混ぜ合わせます。
+2. できた生地に、さらに、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;と&lt;color=#BA9535FF&gt;レモン&lt;/color&gt;を加えます。
+3. 2の生地に&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;を入れ、&lt;color=#FF5CA1FF&gt;ウィンドミキサー&lt;/color&gt;でふんわり混ぜます。
+①タルト生地に、②チーズケーキの生地を足して、焼き上げれば完成！！
+ふんわり濃厚なチーズケーキを召し上がれ♪</t>
+    <rPh sb="14" eb="17">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="58" eb="62">
+      <t>ジゼンジュンビ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ソコ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="120" eb="121">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>ソコ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="195" eb="196">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="217" eb="219">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="251" eb="253">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="254" eb="256">
+      <t>ランオウ</t>
+    </rPh>
+    <rPh sb="265" eb="266">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="267" eb="268">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="281" eb="283">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="306" eb="307">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="349" eb="350">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="361" eb="363">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="381" eb="384">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="393" eb="394">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="434" eb="435">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="445" eb="447">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="457" eb="459">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="460" eb="461">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="464" eb="465">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="466" eb="467">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="470" eb="472">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="480" eb="482">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="490" eb="491">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="492" eb="493">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/fantasian</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【お城ケーキ　ファンタジアのレシピ】
+難易度：高
+とってもかわいいお城のケーキ♪
+でも、実は2段重ねのケーキをベースに、作れますよ。
+作るのが大変なお菓子ですが、ぜひ挑戦してみてくださいね。
+以下の事前準備が必要です。作れない場合は、先に作れるようにしましょう。
+事前準備：
+・生クリームといちご・ラズベリー
+・液体チョコレート
+・スポンジケーキ＜スライス＞
+・ロールクッキーとコンフィズリー
+・魔法「ウィンドクラウン」の習得
+【作り方】
+①２つのケーキ土台を作りましょう♪
+・一段目
+&lt;color=#BA9535FF&gt;スポンジケーキ（スライスしたもの）&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;ピンク色のクリーム&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;いちご&lt;/color&gt;
+・二段目
+&lt;color=#BA9535FF&gt;スポンジケーキ（スライスしたもの）&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;ピンク色のクリーム&lt;/color&gt;　＋　&lt;color=#BA9535FF&gt;ラズベリー&lt;/color&gt;
+クリームはホイップでなく、作りたてクリームをそのまま塗ります。
+土台が出来上がったら、&lt;color=#FF5CA1FF&gt;２つをのせます&lt;/color&gt;。
+②&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;魔法「ウィンドクラウン」&lt;/color&gt;で王冠の形のチョコレートにする。冷やすのを忘れない。
+③お城の柱の部分を作る。
+&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;に三角形の&lt;color=#BA9535FF&gt;コンフィズリー&lt;/color&gt;をのせる。2個作る。
+④　①＋②＋③で、材料を組み合わせて完成☆
+【さらに仕上げ】
+このままだと見た目が少しシンプルなので、
+トッピングに、
+&lt;color=#BA9535FF&gt;・お花を散らす
+・光る砂糖を散りばめる
+・キラキラの光りで演出する&lt;/color&gt;
+など
+工夫すると、
+すっごくかわいくなりますよ～♪
+ぜひお試しくださいね。
+パステルカラーで夢気分♪
+お姫様気分で召し上がってね♪
+</t>
+    <rPh sb="2" eb="3">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ダンカサ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>タイヘン</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>チョウセン</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="100" eb="104">
+      <t>ジゼンジュンビ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="118" eb="119">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="120" eb="121">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="135" eb="139">
+      <t>ジゼンジュンビ</t>
+    </rPh>
+    <rPh sb="142" eb="143">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="219" eb="220">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="221" eb="222">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="231" eb="233">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="234" eb="235">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="490" eb="491">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="503" eb="504">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="509" eb="511">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="512" eb="515">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="573" eb="575">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="608" eb="610">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="629" eb="631">
+      <t>オウカン</t>
+    </rPh>
+    <rPh sb="632" eb="633">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="644" eb="645">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="649" eb="650">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="658" eb="659">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="660" eb="661">
+      <t>ハシラ</t>
+    </rPh>
+    <rPh sb="662" eb="664">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="665" eb="666">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="702" eb="705">
+      <t>サンカクケイ</t>
+    </rPh>
+    <rPh sb="744" eb="745">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="745" eb="746">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="759" eb="761">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="762" eb="763">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="764" eb="765">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="768" eb="770">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="777" eb="779">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="788" eb="789">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="790" eb="791">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="792" eb="793">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="832" eb="833">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="834" eb="835">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="839" eb="840">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="841" eb="843">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="844" eb="845">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="856" eb="857">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="859" eb="861">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="876" eb="878">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="903" eb="904">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="921" eb="924">
+      <t>ユメキブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -8093,7 +8098,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8115,12 +8120,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8210,10 +8209,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8576,10 +8575,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8681,7 +8680,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8846,7 +8845,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8873,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -9065,7 +9064,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9179,10 +9178,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9209,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9227,10 +9226,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9257,7 +9256,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9266,51 +9265,51 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14">
+    <row r="16" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="12">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>467</v>
-      </c>
-      <c r="E16" s="14">
+      <c r="C16" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E16" s="12">
         <v>500</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <v>150</v>
       </c>
-      <c r="G16" s="14">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14">
-        <v>0</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0</v>
-      </c>
-      <c r="K16" s="14">
-        <v>0</v>
-      </c>
-      <c r="L16" s="14">
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
         <v>1</v>
       </c>
-      <c r="M16" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="N16" s="14">
+      <c r="M16" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="N16" s="12">
         <v>3130</v>
       </c>
-      <c r="O16" s="14">
+      <c r="O16" s="12">
         <v>3130</v>
       </c>
     </row>
@@ -9323,10 +9322,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9353,7 +9352,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9368,13 +9367,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D18" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9401,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9593,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -9689,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9737,7 +9736,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10169,7 +10168,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10184,13 +10183,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C35" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D35" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10217,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10649,7 +10648,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10841,7 +10840,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N48" s="4">
         <v>9999</v>
@@ -10856,7 +10855,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C49" t="s">
         <v>195</v>
@@ -10889,7 +10888,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10904,7 +10903,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C50" t="s">
         <v>200</v>
@@ -10952,7 +10951,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C51" t="s">
         <v>203</v>
@@ -11000,7 +10999,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C52" t="s">
         <v>205</v>
@@ -11033,7 +11032,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11048,13 +11047,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -11081,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="N53">
         <v>350</v>
@@ -11096,13 +11095,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -11129,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11144,13 +11143,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -11177,7 +11176,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11192,13 +11191,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -11225,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11240,13 +11239,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -11273,7 +11272,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11282,51 +11281,51 @@
         <v>390</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="8">
+    <row r="58" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="16">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="C58" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="16">
         <v>500</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="16">
         <v>150</v>
       </c>
-      <c r="G58" s="8">
-        <v>0</v>
-      </c>
-      <c r="H58" s="8">
-        <v>0</v>
-      </c>
-      <c r="I58" s="8">
-        <v>0</v>
-      </c>
-      <c r="J58" s="8">
-        <v>0</v>
-      </c>
-      <c r="K58" s="8">
-        <v>0</v>
-      </c>
-      <c r="L58" s="8">
+      <c r="G58" s="16">
+        <v>0</v>
+      </c>
+      <c r="H58" s="16">
+        <v>0</v>
+      </c>
+      <c r="I58" s="16">
+        <v>0</v>
+      </c>
+      <c r="J58" s="16">
+        <v>0</v>
+      </c>
+      <c r="K58" s="16">
+        <v>0</v>
+      </c>
+      <c r="L58" s="16">
         <v>1</v>
       </c>
-      <c r="M58" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="N58" s="8">
+      <c r="M58" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="N58" s="16">
         <v>400</v>
       </c>
-      <c r="O58" s="8">
+      <c r="O58" s="16">
         <v>400</v>
       </c>
     </row>
@@ -11336,7 +11335,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C59" t="s">
         <v>210</v>
@@ -11384,7 +11383,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C60" t="s">
         <v>212</v>
@@ -11432,7 +11431,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C61" t="s">
         <v>214</v>
@@ -11480,7 +11479,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C62" t="s">
         <v>217</v>
@@ -11513,7 +11512,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N62">
         <v>520</v>
@@ -11528,7 +11527,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C63" t="s">
         <v>218</v>
@@ -11561,7 +11560,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N63">
         <v>530</v>
@@ -11576,13 +11575,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C64" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D64" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11609,7 +11608,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11657,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -11672,7 +11671,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C66" t="s">
         <v>223</v>
@@ -11705,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N66">
         <v>550</v>
@@ -11720,7 +11719,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C67" t="s">
         <v>224</v>
@@ -11753,7 +11752,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N67">
         <v>560</v>
@@ -11768,7 +11767,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C68" t="s">
         <v>228</v>
@@ -11801,7 +11800,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N68">
         <v>570</v>
@@ -11816,7 +11815,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C69" t="s">
         <v>227</v>
@@ -11864,7 +11863,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C70" t="s">
         <v>230</v>
@@ -11897,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N70">
         <v>590</v>
@@ -11960,7 +11959,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s">
         <v>234</v>
@@ -11993,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N72">
         <v>610</v>
@@ -12011,10 +12010,10 @@
         <v>192</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E73" s="6">
         <v>500</v>
@@ -12041,7 +12040,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N73" s="6">
         <v>620</v>
@@ -12056,7 +12055,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C74" t="s">
         <v>237</v>
@@ -12089,7 +12088,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N74">
         <v>700</v>
@@ -12104,13 +12103,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D75" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -12137,7 +12136,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N75">
         <v>710</v>
@@ -12152,7 +12151,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C76" t="s">
         <v>239</v>
@@ -12185,7 +12184,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N76">
         <v>720</v>
@@ -12200,7 +12199,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C77" t="s">
         <v>241</v>
@@ -12233,7 +12232,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N77">
         <v>730</v>
@@ -12248,7 +12247,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C78" t="s">
         <v>242</v>
@@ -12281,7 +12280,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N78">
         <v>740</v>
@@ -12296,7 +12295,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C79" t="s">
         <v>249</v>
@@ -12329,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N79">
         <v>750</v>
@@ -12344,7 +12343,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C80" t="s">
         <v>245</v>
@@ -12392,13 +12391,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E81">
         <v>500</v>
@@ -12425,7 +12424,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N81">
         <v>770</v>
@@ -12440,13 +12439,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12473,7 +12472,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N82">
         <v>780</v>
@@ -12491,10 +12490,10 @@
         <v>192</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E83" s="6">
         <v>500</v>
@@ -12521,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N83" s="6">
         <v>790</v>
@@ -12536,13 +12535,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C84" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D84" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12569,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12578,51 +12577,51 @@
         <v>800</v>
       </c>
     </row>
-    <row r="85" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="10">
+    <row r="85" spans="1:15" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="8">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="E85" s="10">
+      <c r="C85" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="E85" s="8">
         <v>500</v>
       </c>
-      <c r="F85" s="10">
+      <c r="F85" s="8">
         <v>150</v>
       </c>
-      <c r="G85" s="10">
-        <v>0</v>
-      </c>
-      <c r="H85" s="10">
-        <v>0</v>
-      </c>
-      <c r="I85" s="10">
-        <v>0</v>
-      </c>
-      <c r="J85" s="10">
-        <v>0</v>
-      </c>
-      <c r="K85" s="10">
-        <v>0</v>
-      </c>
-      <c r="L85" s="10">
-        <v>0</v>
-      </c>
-      <c r="M85" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="N85" s="10">
+      <c r="G85" s="8">
+        <v>0</v>
+      </c>
+      <c r="H85" s="8">
+        <v>0</v>
+      </c>
+      <c r="I85" s="8">
+        <v>0</v>
+      </c>
+      <c r="J85" s="8">
+        <v>0</v>
+      </c>
+      <c r="K85" s="8">
+        <v>0</v>
+      </c>
+      <c r="L85" s="8">
+        <v>0</v>
+      </c>
+      <c r="M85" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="N85" s="8">
         <v>9999</v>
       </c>
-      <c r="O85" s="10">
+      <c r="O85" s="8">
         <v>9999</v>
       </c>
     </row>
@@ -12632,13 +12631,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C86" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D86" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12665,7 +12664,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12680,13 +12679,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C87" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D87" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12713,7 +12712,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12728,13 +12727,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C88" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D88" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12761,7 +12760,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12776,13 +12775,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C89" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D89" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12809,7 +12808,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12824,13 +12823,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C90" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D90" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12857,7 +12856,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12872,13 +12871,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D91" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12905,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12920,13 +12919,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C92" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D92" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12953,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12968,13 +12967,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C93" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D93" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -13001,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -13016,13 +13015,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C94" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D94" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13049,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13064,13 +13063,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C95" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D95" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13097,7 +13096,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13112,13 +13111,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C96" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D96" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13145,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13160,13 +13159,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C97" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D97" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -13193,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13208,13 +13207,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C98" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D98" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13241,7 +13240,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13256,13 +13255,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C99" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D99" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13289,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13304,13 +13303,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D100" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13337,7 +13336,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13352,13 +13351,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C101" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D101" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13385,7 +13384,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13400,13 +13399,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C102" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D102" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13433,7 +13432,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13448,13 +13447,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C103" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D103" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13481,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13496,13 +13495,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C104" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D104" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13529,7 +13528,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13544,13 +13543,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C105" t="s">
+        <v>279</v>
+      </c>
+      <c r="D105" t="s">
         <v>280</v>
-      </c>
-      <c r="D105" t="s">
-        <v>281</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13577,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13592,13 +13591,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C106" t="s">
+        <v>317</v>
+      </c>
+      <c r="D106" t="s">
         <v>318</v>
-      </c>
-      <c r="D106" t="s">
-        <v>319</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13625,7 +13624,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13640,13 +13639,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C107" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D107" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13673,7 +13672,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13688,13 +13687,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C108" t="s">
+        <v>310</v>
+      </c>
+      <c r="D108" t="s">
         <v>311</v>
-      </c>
-      <c r="D108" t="s">
-        <v>312</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13721,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13736,13 +13735,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C109" t="s">
+        <v>323</v>
+      </c>
+      <c r="D109" t="s">
         <v>324</v>
-      </c>
-      <c r="D109" t="s">
-        <v>325</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13769,7 +13768,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13784,13 +13783,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C110" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13817,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13832,13 +13831,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C111" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D111" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13865,7 +13864,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13880,13 +13879,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C112" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D112" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13913,7 +13912,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13928,13 +13927,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C113" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D113" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13961,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13976,13 +13975,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C114" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D114" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -14009,7 +14008,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -14024,13 +14023,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C115" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D115" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -14057,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -14072,13 +14071,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C116" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D116" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -14105,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14120,13 +14119,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C117" t="s">
+        <v>282</v>
+      </c>
+      <c r="D117" t="s">
         <v>283</v>
-      </c>
-      <c r="D117" t="s">
-        <v>284</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -14153,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14168,13 +14167,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C118" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D118" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14201,7 +14200,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14216,13 +14215,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D119" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14249,7 +14248,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14264,13 +14263,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D120" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14297,7 +14296,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14312,13 +14311,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C121" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D121" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14345,7 +14344,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14360,13 +14359,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C122" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D122" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14393,7 +14392,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14408,13 +14407,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D123" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14441,7 +14440,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14456,13 +14455,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C124" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D124" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14489,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14504,13 +14503,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C125" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D125" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14537,7 +14536,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14552,13 +14551,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C126" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D126" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14585,7 +14584,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14600,13 +14599,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C127" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D127" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14633,7 +14632,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14648,13 +14647,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C128" t="s">
+        <v>312</v>
+      </c>
+      <c r="D128" t="s">
         <v>313</v>
-      </c>
-      <c r="D128" t="s">
-        <v>314</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14681,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14696,13 +14695,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C129" t="s">
+        <v>305</v>
+      </c>
+      <c r="D129" t="s">
         <v>306</v>
-      </c>
-      <c r="D129" t="s">
-        <v>307</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14729,7 +14728,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14744,13 +14743,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C130" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D130" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14777,7 +14776,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14786,99 +14785,99 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="16">
+    <row r="131" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="14">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="B131" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="C131" s="16" t="s">
-        <v>456</v>
-      </c>
-      <c r="D131" s="16" t="s">
+      <c r="B131" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C131" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="E131" s="16">
+      <c r="D131" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="E131" s="14">
         <v>500</v>
       </c>
-      <c r="F131" s="16">
+      <c r="F131" s="14">
         <v>150</v>
       </c>
-      <c r="G131" s="16">
-        <v>0</v>
-      </c>
-      <c r="H131" s="16">
-        <v>0</v>
-      </c>
-      <c r="I131" s="16">
-        <v>0</v>
-      </c>
-      <c r="J131" s="16">
-        <v>0</v>
-      </c>
-      <c r="K131" s="16">
-        <v>0</v>
-      </c>
-      <c r="L131" s="16">
-        <v>0</v>
-      </c>
-      <c r="M131" s="17" t="s">
-        <v>537</v>
-      </c>
-      <c r="N131" s="16">
+      <c r="G131" s="14">
+        <v>0</v>
+      </c>
+      <c r="H131" s="14">
+        <v>0</v>
+      </c>
+      <c r="I131" s="14">
+        <v>0</v>
+      </c>
+      <c r="J131" s="14">
+        <v>0</v>
+      </c>
+      <c r="K131" s="14">
+        <v>0</v>
+      </c>
+      <c r="L131" s="14">
+        <v>0</v>
+      </c>
+      <c r="M131" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="N131" s="14">
         <v>5000</v>
       </c>
-      <c r="O131" s="16">
+      <c r="O131" s="14">
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="16">
+    <row r="132" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="14">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="B132" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="C132" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="D132" s="16" t="s">
-        <v>541</v>
-      </c>
-      <c r="E132" s="16">
+      <c r="B132" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C132" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="E132" s="14">
         <v>500</v>
       </c>
-      <c r="F132" s="16">
+      <c r="F132" s="14">
         <v>150</v>
       </c>
-      <c r="G132" s="16">
-        <v>0</v>
-      </c>
-      <c r="H132" s="16">
-        <v>0</v>
-      </c>
-      <c r="I132" s="16">
-        <v>0</v>
-      </c>
-      <c r="J132" s="16">
-        <v>0</v>
-      </c>
-      <c r="K132" s="16">
-        <v>0</v>
-      </c>
-      <c r="L132" s="16">
-        <v>0</v>
-      </c>
-      <c r="M132" s="17" t="s">
-        <v>537</v>
-      </c>
-      <c r="N132" s="16">
+      <c r="G132" s="14">
+        <v>0</v>
+      </c>
+      <c r="H132" s="14">
+        <v>0</v>
+      </c>
+      <c r="I132" s="14">
+        <v>0</v>
+      </c>
+      <c r="J132" s="14">
+        <v>0</v>
+      </c>
+      <c r="K132" s="14">
+        <v>0</v>
+      </c>
+      <c r="L132" s="14">
+        <v>0</v>
+      </c>
+      <c r="M132" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="N132" s="14">
         <v>5000</v>
       </c>
-      <c r="O132" s="16">
+      <c r="O132" s="14">
         <v>5000</v>
       </c>
     </row>
@@ -14888,13 +14887,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C133" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D133" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14921,7 +14920,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14936,13 +14935,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C134" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D134" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14969,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14984,13 +14983,13 @@
         <v>133</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E135" s="16">
         <v>500</v>
@@ -15017,7 +15016,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N135" s="16">
         <v>5000</v>
@@ -15026,51 +15025,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136">
+    <row r="136" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="16">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="B136" t="s">
-        <v>370</v>
-      </c>
-      <c r="C136" t="s">
-        <v>525</v>
-      </c>
-      <c r="D136" t="s">
-        <v>526</v>
-      </c>
-      <c r="E136">
+      <c r="B136" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="E136" s="16">
         <v>500</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="16">
         <v>150</v>
       </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="N136">
+      <c r="G136" s="16">
+        <v>0</v>
+      </c>
+      <c r="H136" s="16">
+        <v>0</v>
+      </c>
+      <c r="I136" s="16">
+        <v>0</v>
+      </c>
+      <c r="J136" s="16">
+        <v>0</v>
+      </c>
+      <c r="K136" s="16">
+        <v>0</v>
+      </c>
+      <c r="L136" s="16">
+        <v>0</v>
+      </c>
+      <c r="M136" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="N136" s="16">
         <v>5000</v>
       </c>
-      <c r="O136">
+      <c r="O136" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -15080,13 +15079,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E137" s="16">
         <v>500</v>
@@ -15113,7 +15112,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N137" s="16">
         <v>5000</v>
@@ -15122,51 +15121,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138">
+    <row r="138" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="16">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" t="s">
-        <v>370</v>
-      </c>
-      <c r="C138" t="s">
-        <v>534</v>
-      </c>
-      <c r="D138" t="s">
-        <v>530</v>
-      </c>
-      <c r="E138">
+      <c r="B138" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="D138" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E138" s="16">
         <v>500</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="16">
         <v>150</v>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="N138">
+      <c r="G138" s="16">
+        <v>0</v>
+      </c>
+      <c r="H138" s="16">
+        <v>0</v>
+      </c>
+      <c r="I138" s="16">
+        <v>0</v>
+      </c>
+      <c r="J138" s="16">
+        <v>0</v>
+      </c>
+      <c r="K138" s="16">
+        <v>0</v>
+      </c>
+      <c r="L138" s="16">
+        <v>0</v>
+      </c>
+      <c r="M138" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="N138" s="16">
         <v>5000</v>
       </c>
-      <c r="O138">
+      <c r="O138" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -15176,13 +15175,13 @@
         <v>137</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E139" s="16">
         <v>500</v>
@@ -15209,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N139" s="16">
         <v>5000</v>
@@ -15224,13 +15223,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E140" s="16">
         <v>500</v>
@@ -15257,7 +15256,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N140" s="16">
         <v>5000</v>
@@ -15266,147 +15265,147 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="141" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="12">
+    <row r="141" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="10">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="B141" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C141" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="D141" s="12" t="s">
+      <c r="B141" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C141" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="E141" s="12">
+      <c r="D141" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E141" s="10">
         <v>500</v>
       </c>
-      <c r="F141" s="12">
+      <c r="F141" s="10">
         <v>150</v>
       </c>
-      <c r="G141" s="12">
-        <v>0</v>
-      </c>
-      <c r="H141" s="12">
-        <v>0</v>
-      </c>
-      <c r="I141" s="12">
-        <v>0</v>
-      </c>
-      <c r="J141" s="12">
-        <v>0</v>
-      </c>
-      <c r="K141" s="12">
-        <v>0</v>
-      </c>
-      <c r="L141" s="12">
-        <v>0</v>
-      </c>
-      <c r="M141" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="N141" s="12">
+      <c r="G141" s="10">
+        <v>0</v>
+      </c>
+      <c r="H141" s="10">
+        <v>0</v>
+      </c>
+      <c r="I141" s="10">
+        <v>0</v>
+      </c>
+      <c r="J141" s="10">
+        <v>0</v>
+      </c>
+      <c r="K141" s="10">
+        <v>0</v>
+      </c>
+      <c r="L141" s="10">
+        <v>0</v>
+      </c>
+      <c r="M141" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="N141" s="10">
         <v>5000</v>
       </c>
-      <c r="O141" s="12">
+      <c r="O141" s="10">
         <v>5000</v>
       </c>
     </row>
-    <row r="142" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="12">
+    <row r="142" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="10">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="B142" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C142" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="D142" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E142" s="12">
+      <c r="B142" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="E142" s="10">
         <v>500</v>
       </c>
-      <c r="F142" s="12">
+      <c r="F142" s="10">
         <v>150</v>
       </c>
-      <c r="G142" s="12">
-        <v>0</v>
-      </c>
-      <c r="H142" s="12">
-        <v>0</v>
-      </c>
-      <c r="I142" s="12">
-        <v>0</v>
-      </c>
-      <c r="J142" s="12">
-        <v>0</v>
-      </c>
-      <c r="K142" s="12">
-        <v>0</v>
-      </c>
-      <c r="L142" s="12">
-        <v>0</v>
-      </c>
-      <c r="M142" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="N142" s="12">
+      <c r="G142" s="10">
+        <v>0</v>
+      </c>
+      <c r="H142" s="10">
+        <v>0</v>
+      </c>
+      <c r="I142" s="10">
+        <v>0</v>
+      </c>
+      <c r="J142" s="10">
+        <v>0</v>
+      </c>
+      <c r="K142" s="10">
+        <v>0</v>
+      </c>
+      <c r="L142" s="10">
+        <v>0</v>
+      </c>
+      <c r="M142" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="N142" s="10">
         <v>5000</v>
       </c>
-      <c r="O142" s="12">
+      <c r="O142" s="10">
         <v>5000</v>
       </c>
     </row>
-    <row r="143" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="12">
+    <row r="143" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="10">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="B143" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C143" s="12" t="s">
+      <c r="B143" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="D143" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="E143" s="12">
+      <c r="C143" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="E143" s="10">
         <v>500</v>
       </c>
-      <c r="F143" s="12">
+      <c r="F143" s="10">
         <v>150</v>
       </c>
-      <c r="G143" s="12">
-        <v>0</v>
-      </c>
-      <c r="H143" s="12">
-        <v>0</v>
-      </c>
-      <c r="I143" s="12">
-        <v>0</v>
-      </c>
-      <c r="J143" s="12">
-        <v>0</v>
-      </c>
-      <c r="K143" s="12">
-        <v>0</v>
-      </c>
-      <c r="L143" s="12">
-        <v>0</v>
-      </c>
-      <c r="M143" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="N143" s="12">
+      <c r="G143" s="10">
+        <v>0</v>
+      </c>
+      <c r="H143" s="10">
+        <v>0</v>
+      </c>
+      <c r="I143" s="10">
+        <v>0</v>
+      </c>
+      <c r="J143" s="10">
+        <v>0</v>
+      </c>
+      <c r="K143" s="10">
+        <v>0</v>
+      </c>
+      <c r="L143" s="10">
+        <v>0</v>
+      </c>
+      <c r="M143" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="N143" s="10">
         <v>5000</v>
       </c>
-      <c r="O143" s="12">
+      <c r="O143" s="10">
         <v>5000</v>
       </c>
     </row>
@@ -15416,13 +15415,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C144" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D144" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15449,7 +15448,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N144">
         <v>5000</v>
@@ -15464,13 +15463,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C145" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D145" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -15497,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N145">
         <v>5000</v>
@@ -15506,51 +15505,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="146" spans="1:15" s="12" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="12">
+    <row r="146" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="10">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-      <c r="B146" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C146" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D146" s="12" t="s">
+      <c r="B146" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C146" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="E146" s="12">
+      <c r="D146" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E146" s="10">
         <v>500</v>
       </c>
-      <c r="F146" s="12">
+      <c r="F146" s="10">
         <v>150</v>
       </c>
-      <c r="G146" s="12">
-        <v>0</v>
-      </c>
-      <c r="H146" s="12">
-        <v>0</v>
-      </c>
-      <c r="I146" s="12">
-        <v>0</v>
-      </c>
-      <c r="J146" s="12">
-        <v>0</v>
-      </c>
-      <c r="K146" s="12">
-        <v>0</v>
-      </c>
-      <c r="L146" s="12">
-        <v>0</v>
-      </c>
-      <c r="M146" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="N146" s="12">
+      <c r="G146" s="10">
+        <v>0</v>
+      </c>
+      <c r="H146" s="10">
+        <v>0</v>
+      </c>
+      <c r="I146" s="10">
+        <v>0</v>
+      </c>
+      <c r="J146" s="10">
+        <v>0</v>
+      </c>
+      <c r="K146" s="10">
+        <v>0</v>
+      </c>
+      <c r="L146" s="10">
+        <v>0</v>
+      </c>
+      <c r="M146" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="N146" s="10">
         <v>5000</v>
       </c>
-      <c r="O146" s="12">
+      <c r="O146" s="10">
         <v>5000</v>
       </c>
     </row>
@@ -15560,13 +15559,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C147" t="s">
+        <v>307</v>
+      </c>
+      <c r="D147" t="s">
         <v>308</v>
-      </c>
-      <c r="D147" t="s">
-        <v>309</v>
       </c>
       <c r="E147">
         <v>500</v>
@@ -15593,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N147">
         <v>5000</v>
@@ -15608,13 +15607,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C148" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D148" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -15641,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="N148">
         <v>9999</v>
@@ -15752,10 +15751,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -16016,13 +16015,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16064,13 +16063,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>484</v>
+      </c>
+      <c r="C8" t="s">
+        <v>489</v>
+      </c>
+      <c r="D8" t="s">
         <v>486</v>
-      </c>
-      <c r="C8" t="s">
-        <v>491</v>
-      </c>
-      <c r="D8" t="s">
-        <v>488</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16112,13 +16111,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16202,51 +16201,51 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="12" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="12">
+    <row r="11" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="12">
-        <v>0</v>
-      </c>
-      <c r="F11" s="12">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12">
-        <v>0</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
         <v>2</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="10">
         <v>101</v>
       </c>
-      <c r="K11" s="12">
-        <v>0</v>
-      </c>
-      <c r="L11" s="12">
-        <v>0</v>
-      </c>
-      <c r="M11" s="12" t="s">
+      <c r="K11" s="10">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="10">
         <v>9999</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="10">
         <v>9999</v>
       </c>
     </row>
@@ -16496,7 +16495,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C17" t="s">
         <v>196</v>
@@ -16544,13 +16543,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C18" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D18" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF384FAF-4326-478B-B386-661AABC3E3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D9BE98-36EC-414C-9C92-BE6753EA03CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1335" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2310" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -2525,291 +2525,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【クッキーのお家　フォーゲットミーノットのレシピ】
-恋人への特別なお菓子「フォーゲットミーノット」のご紹介です。
-材料が多く大変ですが、ぜひ挑戦してみてくださいね！
-ざっくりと、
-A.壁
-B.ドアと窓
-C.屋根部分
-の3種類を作って、飾り付けていきましょう。
-A. 壁部分
-①&lt;color=#BA9535FF&gt;ビスケット×８&lt;/color&gt;と&lt;color=#BA9535FF&gt;ココアクッキー×４&lt;/color&gt;
-&lt;color=#BA9535FF&gt;ロールクッキー×２&lt;/color&gt;を準備する。
-※数は好きな数で良いですが、少ないと出来栄えが悪くなります。
-②&lt;color=#BA9535FF&gt;ビスケット&lt;/color&gt;と&lt;color=#BA9535FF&gt;ココアクッキー&lt;/color&gt;をれんがに見立て、組み合わせていきます。
-③できた壁部分の内側に、&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;を詰めましょう。屋根の支えになります。
-壁部分はこれで完成。
-B.ドアと窓
-①窓部分は、&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;に&lt;color=#FF5CA1FF&gt;「魔法ウィンドハート」&lt;/color&gt;をかけて、ハート型のチョコにします。
-2個作っておきましょう。
-※ちゃんと冷やして固めておきましょう。
-②ドアは、&lt;color=#BA9535FF&gt;ビスケット&lt;/color&gt;に、&lt;color=#BA9535FF&gt;チョコペン&lt;/color&gt;で模様を描きます。
-ドアと窓はこれで完了です。
-C. 屋根部分
-屋根は、チョコレートで作ります。
-①液体チョコレートに、&lt;color=#FF5CA1FF&gt;魔法「ウィンド板チョコ」&lt;/color&gt;で板チョコレートを2個作ります。
-②板チョコに、&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;を一個くっつけて、煙突にします。
-屋根の完成です。
-【組み立て】
-①&lt;color=#BA9535FF&gt;A壁部分&lt;/color&gt;に、&lt;color=#BA9535FF&gt;C屋根部分&lt;/color&gt;を先にくっつけます。
-②できた土台に、&lt;color=#BA9535FF&gt;Bのドアと窓&lt;/color&gt;をくっつけて、
-お菓子のおうち完成です！
-さらに仕上げに、
-・宝石キャンディを散りばめる
-・くまさんやうさぎさんを配置する
-・クリスタルシュガーやパウダーシュガーなどをふりかける
-など
-よりかわいく見せてあげてくださいね♪</t>
-    <rPh sb="7" eb="8">
-      <t>ウチ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>コイビト</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>タイヘン</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>チョウセン</t>
-    </rPh>
-    <rPh sb="94" eb="95">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>マド</t>
-    </rPh>
-    <rPh sb="105" eb="109">
-      <t>ヤネブブン</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="119" eb="120">
-      <t>カザ</t>
-    </rPh>
-    <rPh sb="121" eb="122">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="136" eb="137">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="137" eb="139">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="244" eb="246">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="251" eb="252">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="253" eb="254">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="256" eb="257">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="258" eb="259">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="264" eb="265">
-      <t>スク</t>
-    </rPh>
-    <rPh sb="268" eb="271">
-      <t>デキバ</t>
-    </rPh>
-    <rPh sb="273" eb="274">
-      <t>ワル</t>
-    </rPh>
-    <rPh sb="351" eb="353">
-      <t>ミタ</t>
-    </rPh>
-    <rPh sb="355" eb="356">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="357" eb="358">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="372" eb="373">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="373" eb="375">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="376" eb="378">
-      <t>ウチガワ</t>
-    </rPh>
-    <rPh sb="413" eb="414">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="420" eb="422">
-      <t>ヤネ</t>
-    </rPh>
-    <rPh sb="423" eb="424">
-      <t>ササ</t>
-    </rPh>
-    <rPh sb="433" eb="434">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="434" eb="436">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="440" eb="442">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="450" eb="451">
-      <t>マド</t>
-    </rPh>
-    <rPh sb="453" eb="456">
-      <t>マドブブン</t>
-    </rPh>
-    <rPh sb="475" eb="477">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="510" eb="512">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="536" eb="537">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="548" eb="549">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="549" eb="550">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="565" eb="566">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="569" eb="570">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="648" eb="650">
-      <t>モヨウ</t>
-    </rPh>
-    <rPh sb="651" eb="652">
-      <t>エガ</t>
-    </rPh>
-    <rPh sb="660" eb="661">
-      <t>マド</t>
-    </rPh>
-    <rPh sb="665" eb="667">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="675" eb="677">
-      <t>ヤネ</t>
-    </rPh>
-    <rPh sb="677" eb="679">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="680" eb="682">
-      <t>ヤネ</t>
-    </rPh>
-    <rPh sb="691" eb="692">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="698" eb="700">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="725" eb="727">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="732" eb="733">
-      <t>イタ</t>
-    </rPh>
-    <rPh sb="746" eb="747">
-      <t>イタ</t>
-    </rPh>
-    <rPh sb="755" eb="756">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="756" eb="757">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="763" eb="764">
-      <t>イタ</t>
-    </rPh>
-    <rPh sb="802" eb="804">
-      <t>イッコ</t>
-    </rPh>
-    <rPh sb="810" eb="812">
-      <t>エントツ</t>
-    </rPh>
-    <rPh sb="818" eb="820">
-      <t>ヤネ</t>
-    </rPh>
-    <rPh sb="821" eb="823">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="829" eb="830">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="831" eb="832">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="854" eb="855">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="855" eb="857">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="885" eb="887">
-      <t>ヤネ</t>
-    </rPh>
-    <rPh sb="887" eb="889">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="898" eb="899">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="912" eb="914">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="938" eb="939">
-      <t>マド</t>
-    </rPh>
-    <rPh sb="956" eb="958">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="962" eb="964">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="972" eb="974">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="979" eb="981">
-      <t>ホウセキ</t>
-    </rPh>
-    <rPh sb="987" eb="988">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="1005" eb="1007">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="1048" eb="1049">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ロールクッキーのレシピ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3261,289 +2976,6 @@
     <t>レインボーレインの本</t>
     <rPh sb="9" eb="10">
       <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【モンブランのレシピ】
-難易度・・　中～高　ぐらい
-少し難しいですが、順番に丁寧に作ってみてくださいね。
-先に、
-A. 土台の生地
-B. マロンクリーム
-を準備します。
-あとで仕上げていきましょう。
-また事前に、
-・くり
-・ホイップクリーム
-・メレンゲ
-・モンブラン用絞り袋
-も用意しましょう。
-A.
-※メレンゲの準備・・・&lt;color=#BA9535FF&gt;卵白&lt;/color&gt;に、&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を混ぜて、メレンゲを作ります。
-&lt;color=#FF5CA1FF&gt;泡だて器かウィンドミキサー&lt;/color&gt;を使うのを忘れずに！
-①クリーム生地・・・準備したメレンゲに、&lt;color=#BA9535FF&gt;薄力粉・アーモンドパウダー&lt;/color&gt;を混ぜて、土台の生地クリームを作ります。
-②できたクリーム生地を、&lt;color=#FF5CA1FF&gt;絞り袋&lt;/color&gt;に入れ、薄く円盤に絞ります。このとき、粉砂糖も振りかけておきましょう。
-焼き上げれば土台の完成です！
-B.
-①&lt;color=#BA9535FF&gt;水&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;にはり、&lt;color=#BA9535FF&gt;栗&lt;/color&gt;を入れて煮ます。柔らかくゆでた栗にします。
-②できたゆで栗に、&lt;color=#BA9535FF&gt;砂糖・ミルク&lt;/color&gt;を混ぜて、さらに煮詰めます。そのまま潰せば、マロンペーストが出来上がります。
-③マロンペーストに、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;を混ぜて、&lt;color=#FF5CA1FF&gt;泡だて器&lt;/color&gt;で混ぜます。とろり濃厚なマロンクリームの完成です♪
-④できたマロンクリームは、&lt;color=#FF5CA1FF&gt;モンブラン用の絞り袋&lt;/color&gt;に入れて準備します。
-【仕上げ】
-①Aで作った土台生地に、&lt;color=#BA9535FF&gt;ゆで栗&lt;/color&gt;を一粒のせ、&lt;color=#BA9535FF&gt;ホイップクリーム&lt;/color&gt;を周りに絞り、ドーム型にします。
-②その周りに、Bで準備した&lt;color=#BA9535FF&gt;マロンクリーム&lt;/color&gt;をたっぷりとかけていけば..
-マロンの風味が香るとってもおいしいモンブランの完成です♪
-秋の定番スイーツ、ぜひ作ってみてくださいね！
-</t>
-    <rPh sb="13" eb="16">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ムズカ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ジュンバン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>テイネイ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="137" eb="138">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="138" eb="139">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="140" eb="141">
-      <t>ブクロ</t>
-    </rPh>
-    <rPh sb="143" eb="145">
-      <t>ヨウイ</t>
-    </rPh>
-    <rPh sb="184" eb="186">
-      <t>ランパク</t>
-    </rPh>
-    <rPh sb="213" eb="215">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="224" eb="225">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="256" eb="257">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="259" eb="260">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="278" eb="279">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="282" eb="283">
-      <t>ワス</t>
-    </rPh>
-    <rPh sb="294" eb="296">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="299" eb="301">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="326" eb="329">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="348" eb="349">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="352" eb="354">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="355" eb="357">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="362" eb="363">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="377" eb="379">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="398" eb="399">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="400" eb="401">
-      <t>ブクロ</t>
-    </rPh>
-    <rPh sb="410" eb="411">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="413" eb="414">
-      <t>ウス</t>
-    </rPh>
-    <rPh sb="415" eb="417">
-      <t>エンバン</t>
-    </rPh>
-    <rPh sb="418" eb="419">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="428" eb="431">
-      <t>コナザトウ</t>
-    </rPh>
-    <rPh sb="432" eb="433">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="446" eb="447">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="448" eb="449">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="452" eb="454">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="455" eb="457">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="511" eb="512">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="541" eb="542">
-      <t>クリ</t>
-    </rPh>
-    <rPh sb="551" eb="552">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="554" eb="555">
-      <t>ニ</t>
-    </rPh>
-    <rPh sb="558" eb="559">
-      <t>ヤワ</t>
-    </rPh>
-    <rPh sb="565" eb="566">
-      <t>クリ</t>
-    </rPh>
-    <rPh sb="579" eb="580">
-      <t>クリ</t>
-    </rPh>
-    <rPh sb="599" eb="601">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="614" eb="615">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="621" eb="623">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="631" eb="632">
-      <t>ツブ</t>
-    </rPh>
-    <rPh sb="643" eb="646">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="680" eb="681">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="694" eb="695">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="715" eb="716">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="718" eb="719">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="728" eb="729">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="736" eb="738">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="747" eb="749">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="789" eb="790">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="791" eb="792">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="793" eb="794">
-      <t>ブクロ</t>
-    </rPh>
-    <rPh sb="803" eb="804">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="806" eb="808">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="815" eb="817">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="824" eb="825">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="827" eb="829">
-      <t>ドダイ</t>
-    </rPh>
-    <rPh sb="829" eb="831">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="852" eb="853">
-      <t>クリ</t>
-    </rPh>
-    <rPh sb="862" eb="864">
-      <t>ヒトツブ</t>
-    </rPh>
-    <rPh sb="901" eb="902">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="904" eb="905">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="910" eb="911">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="921" eb="922">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="927" eb="929">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="983" eb="985">
-      <t>フウミ</t>
-    </rPh>
-    <rPh sb="986" eb="987">
-      <t>カオル</t>
-    </rPh>
-    <rPh sb="1002" eb="1004">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1009" eb="1010">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="1011" eb="1013">
-      <t>テイバン</t>
-    </rPh>
-    <rPh sb="1020" eb="1021">
-      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5456,402 +4888,6 @@
     </rPh>
     <rPh sb="1116" eb="1117">
       <t>サイワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【オペラのレシピ】
-難易度・・　超高
-濃厚かつしっとりとした、まさに正統派なチョコレートケーキです。
-かなり手順が複雑で多いのですが、がんばってみてくださいね。
-◆必要器材
-四角いセルクル
-★メレンゲも作れるようになっておきましょう。
-★焦がしバターも使います。作り方を事前に覚えておきましょう。
-以下、
-A, スポンジ生地作り
-B. コーヒーシロップ
-C. コーヒーバタークリーム
-D. ガナッシュクリーム
-E. チョコレートソースグラサージュ
-の５つを先に準備します。
-全部できたら、最後に仕上げていきましょう。
-A. 生地作り
-※事前に、&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;とココアパウダーを混ぜておきます。
-また、&lt;color=#BA9535FF&gt;メレンゲ、焦がしバター&lt;/color&gt;も準備しておきましょう。
-①&lt;color=#BA9535FF&gt;砂糖、卵&lt;/color&gt;に、アーモンドパウダーを入れ、混ぜ合わせます。
-②①でできたアパレイユに、事前に用意した粉類とメレンゲを入れて、よく混ぜましょう。
-③&lt;color=#BA9535FF&gt;焦がしバター&lt;/color&gt;を最後に加えて混ぜます。
-焼き上げれば、オペラケーキ生地が完成です。
-B. コーヒーシロップ
-&lt;color=#BA9535FF&gt;水・砂糖・コーヒーパウダー&lt;/color&gt;を加えて、煮詰めればコーヒーシロップができます。準備しておきます。
-C. コーヒーのバタークリーム
-①&lt;color=#BA9535FF&gt;卵黄&lt;/color&gt;に&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を混ぜます。＜アパレイユ黄身＞
-さらに、少量の&lt;color=#BA9535FF&gt;コーヒー&lt;/color&gt;を入れよく混ぜます。
-②ある程度混ざったら、&lt;color=#BA9535FF&gt;バター&lt;/color&gt;を入れて、よく混ぜます。
-香り高いコーヒークリームの完成です。
-D. ガナッシュクリーム
-①お鍋に、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;を入れ、&lt;color=#BA9535FF&gt;液体状のチョコレート&lt;/color&gt;を入れ、火にかけながら混ぜます。
-濃厚なガナッシュクリームの完成です。
-E. チョコレートソースグラサージュ
-ケーキに最後にかけるコーティング用のチョコソースを作っていきます。
-①&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;に、&lt;color=#BA9535FF&gt;砂糖・ココアパウダー&lt;/color&gt;を入れ、混ぜながら火にかけます。
-②&lt;color=#BA9535FF&gt;水・ゼラチン&lt;/color&gt;を加えて、さらに混ぜ合わせます。
-濃厚でとろりとした、真っ黒のチョコソースが完成です。
-【仕上げ】
-①Aで作ったケーキ生地を、&lt;color=#FF5CA1FF&gt;四角いセルクル&lt;/color&gt;でスライスし切り分けます。
-②生地に、&lt;color=#BA9535FF&gt;液体状チョコレート&lt;/color&gt;を塗ります。これが底生地になります。
-ここから上にどんどん生地・クリームを重ねていきます。
-③底生地に、&lt;color=#BA9535FF&gt;Bのコーヒーシロップ&lt;/color&gt;をぬって、味付けをし、その上に&lt;color=#BA9535FF&gt;コーヒーバタークリーム&lt;/color&gt;を塗り、層を作ります。
-④③の上に、スライスしたケーキ生地をのせます。
-⑤④の生地の表面に、&lt;color=#BA9535FF&gt;コーヒーシロップ&lt;/color&gt;をさらにつけ、その上に、&lt;color=#BA9535FF&gt;Dのガナッシュクリーム&lt;/color&gt;を塗っていきます。
-ソースは平坦にぬると、きれいになります。
-⑥⑤の生地の上に、さらに&lt;color=#BA9535FF&gt;コーヒーバタークリーム&lt;/color&gt;を塗ります。平に塗っていきます。
-⑦ベースは完成です。あとは、&lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;、もしくは&lt;color=#FF5CA1FF&gt;魔法「フリージング」&lt;/color&gt;で冷やしていきましょう。
-⑧最後に、真っ黒な&lt;color=#BA9535FF&gt;Eのチョコソースグラサージュ&lt;/color&gt;をかけてコーティングすれば..
-高貴なチョコケーキ「オペラ」完成です♪
-仕上げに、&lt;color=#BA9535FF&gt;「金箔」&lt;/color&gt;を一つまみのせると、王様も大喜びのリッチな仕上げになります。</t>
-    <rPh sb="11" eb="14">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="36" eb="39">
-      <t>セイトウハ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>キザイ</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>シカク</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="167" eb="168">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="233" eb="234">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="242" eb="244">
-      <t>ゼンブ</t>
-    </rPh>
-    <rPh sb="249" eb="251">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="252" eb="254">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="269" eb="271">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="271" eb="272">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="296" eb="299">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="316" eb="317">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="350" eb="351">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="365" eb="367">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="396" eb="398">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="420" eb="421">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="423" eb="424">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="425" eb="426">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="446" eb="448">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="449" eb="451">
-      <t>ヨウイ</t>
-    </rPh>
-    <rPh sb="453" eb="455">
-      <t>コナルイ</t>
-    </rPh>
-    <rPh sb="461" eb="462">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="467" eb="468">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="522" eb="523">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="524" eb="525">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="535" eb="537">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="538" eb="540">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="574" eb="575">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="576" eb="578">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="596" eb="597">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="600" eb="602">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="619" eb="621">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="664" eb="666">
-      <t>ランオウ</t>
-    </rPh>
-    <rPh sb="714" eb="716">
-      <t>キミ</t>
-    </rPh>
-    <rPh sb="722" eb="724">
-      <t>ショウリョウ</t>
-    </rPh>
-    <rPh sb="755" eb="756">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="759" eb="760">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="819" eb="820">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="821" eb="822">
-      <t>ダカ</t>
-    </rPh>
-    <rPh sb="854" eb="855">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="874" eb="875">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="888" eb="889">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="908" eb="911">
-      <t>エキタイジョウ</t>
-    </rPh>
-    <rPh sb="927" eb="928">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="930" eb="931">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="937" eb="938">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="944" eb="946">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="987" eb="989">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="999" eb="1000">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="1008" eb="1009">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="1036" eb="1037">
-      <t>ナマ</t>
-    </rPh>
-    <rPh sb="1068" eb="1070">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="1087" eb="1088">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="1090" eb="1091">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="1095" eb="1096">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="1122" eb="1123">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="1137" eb="1138">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="1144" eb="1145">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="1146" eb="1147">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="1154" eb="1156">
-      <t>ノウコウ</t>
-    </rPh>
-    <rPh sb="1164" eb="1165">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="1166" eb="1167">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="1175" eb="1177">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1183" eb="1185">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="1192" eb="1193">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="1198" eb="1200">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1219" eb="1221">
-      <t>シカク</t>
-    </rPh>
-    <rPh sb="1240" eb="1241">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="1242" eb="1243">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="1250" eb="1252">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1271" eb="1274">
-      <t>エキタイジョウ</t>
-    </rPh>
-    <rPh sb="1289" eb="1290">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1297" eb="1300">
-      <t>ソコキジ</t>
-    </rPh>
-    <rPh sb="1312" eb="1313">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1318" eb="1320">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1326" eb="1327">
-      <t>カサ</t>
-    </rPh>
-    <rPh sb="1337" eb="1340">
-      <t>ソコキジ</t>
-    </rPh>
-    <rPh sb="1382" eb="1384">
-      <t>アジツ</t>
-    </rPh>
-    <rPh sb="1390" eb="1391">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1444" eb="1445">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1456" eb="1458">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1469" eb="1471">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1472" eb="1474">
-      <t>ヒョウメン</t>
-    </rPh>
-    <rPh sb="1518" eb="1519">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1558" eb="1559">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1571" eb="1573">
-      <t>ヘイタン</t>
-    </rPh>
-    <rPh sb="1592" eb="1594">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1595" eb="1596">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1638" eb="1639">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1643" eb="1644">
-      <t>タイラ</t>
-    </rPh>
-    <rPh sb="1645" eb="1646">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="1660" eb="1662">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1686" eb="1688">
-      <t>ヒムロ</t>
-    </rPh>
-    <rPh sb="1718" eb="1720">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="1737" eb="1738">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="1751" eb="1753">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="1755" eb="1756">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="1757" eb="1758">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="1815" eb="1817">
-      <t>コウキ</t>
-    </rPh>
-    <rPh sb="1829" eb="1831">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1836" eb="1838">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="1859" eb="1861">
-      <t>キンパク</t>
-    </rPh>
-    <rPh sb="1871" eb="1872">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="1880" eb="1882">
-      <t>オウサマ</t>
-    </rPh>
-    <rPh sb="1883" eb="1885">
-      <t>オオヨロコ</t>
-    </rPh>
-    <rPh sb="1891" eb="1893">
-      <t>シア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6914,22 +5950,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>風魔法解禁の本　ぬねちゃんからもらう</t>
-    <rPh sb="0" eb="1">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カイキン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>風の魔術書へ移行した</t>
     <rPh sb="0" eb="1">
       <t>カゼ</t>
@@ -7660,16 +6680,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>マジックパティスリーの賞品（2位）</t>
-    <rPh sb="11" eb="13">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マジックパティスリーの賞品（1位）</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -7834,6 +6844,289 @@
   </si>
   <si>
     <t>Items/fantasian</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【モンブランのレシピ】
+難易度・・　中～高　ぐらい
+少し難しいですが、順番に丁寧に作ってみてくださいね。
+先に、
+A. 土台の生地
+B. マロンクリーム
+を準備します。
+あとで仕上げていきましょう。
+また事前に、
+・くり
+・ホイップクリーム
+・メレンゲ
+・モンブラン用絞り袋
+も用意しましょう。
+A.
+※メレンゲの準備・・・&lt;color=#BA9535FF&gt;卵白&lt;/color&gt;に、&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を混ぜて、メレンゲを作ります。
+&lt;color=#FF5CA1FF&gt;泡だて器かウィンドミキサー&lt;/color&gt;を使うのを忘れずに！
+①クリーム生地・・・準備したメレンゲに、&lt;color=#BA9535FF&gt;薄力粉・アーモンドパウダー&lt;/color&gt;を混ぜて、土台の生地クリームを作ります。
+②できたクリーム生地を、&lt;color=#FF5CA1FF&gt;絞り袋&lt;/color&gt;に入れ、薄く円盤に絞ります。このとき、粉砂糖も振りかけておきましょう。
+焼き上げれば土台の完成です！
+B.
+①&lt;color=#BA9535FF&gt;水&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;にはり、&lt;color=#BA9535FF&gt;栗&lt;/color&gt;を入れて煮ます。柔らかくゆでた栗にします。
+②できたゆで栗に、&lt;color=#BA9535FF&gt;砂糖・ミルク&lt;/color&gt;を混ぜて、さらに煮詰めます。そのまま潰せば、マロンペーストが出来上がります。
+③マロンペーストに、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;を混ぜて、&lt;color=#FF5CA1FF&gt;泡だて器&lt;/color&gt;で混ぜます。とろり濃厚なマロンクリームの完成です♪
+④できたマロンクリームは、&lt;color=#FF5CA1FF&gt;モンブラン用の絞り袋&lt;/color&gt;に入れて準備します。
+【仕上げ】
+①Aで作った土台生地に、&lt;color=#BA9535FF&gt;ゆで栗&lt;/color&gt;を一粒のせ、&lt;color=#BA9535FF&gt;作りたてクリーム&lt;/color&gt;を周りにコーティング、ドーム型にします。
+②その周りに、Bで準備した&lt;color=#BA9535FF&gt;マロンクリーム&lt;/color&gt;をたっぷりとかけていけば..
+マロンの風味が香るとってもおいしいモンブランの完成です♪
+秋の定番スイーツ、ぜひ作ってみてくださいね！
+</t>
+    <rPh sb="13" eb="16">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>テイネイ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="140" eb="141">
+      <t>ブクロ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>ランパク</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="224" eb="225">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="256" eb="257">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="259" eb="260">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="278" eb="279">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="282" eb="283">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="294" eb="296">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="326" eb="329">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="348" eb="349">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="352" eb="354">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="355" eb="357">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="362" eb="363">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="377" eb="379">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="398" eb="399">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="400" eb="401">
+      <t>ブクロ</t>
+    </rPh>
+    <rPh sb="410" eb="411">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="413" eb="414">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="415" eb="417">
+      <t>エンバン</t>
+    </rPh>
+    <rPh sb="418" eb="419">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="428" eb="431">
+      <t>コナザトウ</t>
+    </rPh>
+    <rPh sb="432" eb="433">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="446" eb="447">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="448" eb="449">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="452" eb="454">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="455" eb="457">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="511" eb="512">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="541" eb="542">
+      <t>クリ</t>
+    </rPh>
+    <rPh sb="551" eb="552">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="554" eb="555">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="558" eb="559">
+      <t>ヤワ</t>
+    </rPh>
+    <rPh sb="565" eb="566">
+      <t>クリ</t>
+    </rPh>
+    <rPh sb="579" eb="580">
+      <t>クリ</t>
+    </rPh>
+    <rPh sb="599" eb="601">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="614" eb="615">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="621" eb="623">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="631" eb="632">
+      <t>ツブ</t>
+    </rPh>
+    <rPh sb="643" eb="646">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="680" eb="681">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="694" eb="695">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="715" eb="716">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="718" eb="719">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="728" eb="729">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="736" eb="738">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="747" eb="749">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="789" eb="790">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="791" eb="792">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="793" eb="794">
+      <t>ブクロ</t>
+    </rPh>
+    <rPh sb="803" eb="804">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="806" eb="808">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="815" eb="817">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="824" eb="825">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="827" eb="829">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="829" eb="831">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="852" eb="853">
+      <t>クリ</t>
+    </rPh>
+    <rPh sb="862" eb="864">
+      <t>ヒトツブ</t>
+    </rPh>
+    <rPh sb="884" eb="885">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="901" eb="902">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="914" eb="915">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="925" eb="926">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="931" eb="933">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="987" eb="989">
+      <t>フウミ</t>
+    </rPh>
+    <rPh sb="990" eb="991">
+      <t>カオル</t>
+    </rPh>
+    <rPh sb="1006" eb="1008">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1013" eb="1014">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="1015" eb="1017">
+      <t>テイバン</t>
+    </rPh>
+    <rPh sb="1024" eb="1025">
+      <t>ツク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7859,7 +7152,7 @@
 土台が出来上がったら、&lt;color=#FF5CA1FF&gt;２つをのせます&lt;/color&gt;。
 ②&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;魔法「ウィンドクラウン」&lt;/color&gt;で王冠の形のチョコレートにする。冷やすのを忘れない。
 ③お城の柱の部分を作る。
-&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;に三角形の&lt;color=#BA9535FF&gt;コンフィズリー&lt;/color&gt;をのせる。2個作る。
+&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;に&lt;color=#BA9535FF&gt;コンフィズリー&lt;/color&gt;をのせる。
 ④　①＋②＋③で、材料を組み合わせて完成☆
 【さらに仕上げ】
 このままだと見た目が少しシンプルなので、
@@ -7991,68 +7284,731 @@
     <rPh sb="665" eb="666">
       <t>ツク</t>
     </rPh>
-    <rPh sb="702" eb="705">
-      <t>サンカクケイ</t>
-    </rPh>
-    <rPh sb="744" eb="745">
+    <rPh sb="750" eb="752">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="753" eb="754">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="755" eb="756">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="759" eb="761">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="768" eb="770">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="779" eb="780">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="781" eb="782">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="783" eb="784">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="823" eb="824">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="825" eb="826">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="830" eb="831">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="832" eb="834">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="835" eb="836">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="847" eb="848">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="850" eb="852">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="867" eb="869">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="894" eb="895">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="912" eb="915">
+      <t>ユメキブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【オペラのレシピ】
+難易度・・　超高
+濃厚かつしっとりとした、まさに正統派なチョコレートケーキです。
+かなり手順が複雑で多いのですが、がんばってみてくださいね。
+◆必要器材
+四角いセルクル
+★メレンゲも作れるようになっておきましょう。
+★焦がしバターも使います。作り方を事前に覚えておきましょう。
+以下、
+A, スポンジ生地作り
+B. コーヒーシロップ
+C. コーヒーバタークリーム
+D. ガナッシュクリーム
+E. チョコレートソースグラサージュ
+の５つを先に準備します。
+全部できたら、最後に仕上げていきましょう。
+A. 生地作り
+※事前に、&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;とココアパウダーを混ぜておきます。
+また、&lt;color=#BA9535FF&gt;メレンゲ、焦がしバター&lt;/color&gt;も準備しておきましょう。
+①&lt;color=#BA9535FF&gt;砂糖、卵&lt;/color&gt;に、&lt;color=#BA9535FF&gt;アーモンドプードル&lt;/color&gt;を入れ、混ぜ合わせます。
+②①でできたアパレイユに、事前に用意した粉類とメレンゲを入れて、よく混ぜましょう。
+③&lt;color=#BA9535FF&gt;焦がしバター&lt;/color&gt;を最後に加えて混ぜます。
+焼き上げれば、オペラケーキ生地が完成です。
+B. コーヒーシロップ
+&lt;color=#BA9535FF&gt;水・砂糖・コーヒーパウダー&lt;/color&gt;を加えて、煮詰めればコーヒーシロップができます。準備しておきます。
+C. コーヒーのバタークリーム
+①&lt;color=#BA9535FF&gt;卵黄&lt;/color&gt;に&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を混ぜます。＜アパレイユ黄身＞
+さらに、少量の&lt;color=#BA9535FF&gt;コーヒー&lt;/color&gt;を入れよく混ぜます。
+②ある程度混ざったら、&lt;color=#BA9535FF&gt;バター&lt;/color&gt;を入れて、よく混ぜます。
+香り高いコーヒークリームの完成です。
+D. ガナッシュクリーム
+①お鍋に、&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;を入れ、&lt;color=#BA9535FF&gt;液体状のチョコレート&lt;/color&gt;を入れ、火にかけながら混ぜます。
+濃厚なガナッシュクリームの完成です。
+E. チョコレートソースグラサージュ
+ケーキに最後にかけるコーティング用のチョコソースを作っていきます。
+①&lt;color=#BA9535FF&gt;生クリーム&lt;/color&gt;に、&lt;color=#BA9535FF&gt;砂糖・ココアパウダー&lt;/color&gt;を入れ、混ぜながら火にかけます。
+②&lt;color=#BA9535FF&gt;水・ゼラチン&lt;/color&gt;を加えて、さらに混ぜ合わせます。
+濃厚でとろりとした、真っ黒のチョコソースが完成です。
+【仕上げ】
+①Aで作ったケーキ生地を、&lt;color=#FF5CA1FF&gt;四角いセルクル&lt;/color&gt;でスライスし切り分けます。
+②生地に、&lt;color=#BA9535FF&gt;液体状チョコレート&lt;/color&gt;を塗ります。これが底生地になります。
+ここから上にどんどん生地・クリームを重ねていきます。
+③底生地に、&lt;color=#BA9535FF&gt;Bのコーヒーシロップ&lt;/color&gt;をぬって、味付けをし、その上に&lt;color=#BA9535FF&gt;コーヒーバタークリーム&lt;/color&gt;を塗り、層を作ります。
+④③の上に、スライスしたケーキ生地をのせます。
+⑤④の生地の表面に、&lt;color=#BA9535FF&gt;コーヒーシロップ&lt;/color&gt;をさらにつけ、その上に、&lt;color=#BA9535FF&gt;Dのガナッシュクリーム&lt;/color&gt;を塗っていきます。
+ソースは平坦にぬると、きれいになります。
+⑥⑤の生地の上に、さらに&lt;color=#BA9535FF&gt;コーヒーバタークリーム&lt;/color&gt;を塗ります。平に塗っていきます。
+⑦ベースは完成です。あとは、&lt;color=#FF5CA1FF&gt;氷室&lt;/color&gt;、もしくは&lt;color=#FF5CA1FF&gt;魔法「フリージング」&lt;/color&gt;で冷やしていきましょう。
+⑧最後に、真っ黒な&lt;color=#BA9535FF&gt;Eのチョコソースグラサージュ&lt;/color&gt;をかけてコーティングすれば..
+高貴なチョコケーキ「オペラ」完成です♪
+仕上げに、&lt;color=#BA9535FF&gt;「金箔」&lt;/color&gt;を一つまみのせると、王様も大喜びのリッチな仕上げになります。</t>
+    <rPh sb="11" eb="14">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>セイトウハ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>キザイ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="167" eb="168">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="233" eb="234">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="242" eb="244">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="249" eb="251">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="252" eb="254">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="269" eb="271">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="271" eb="272">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="296" eb="299">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="316" eb="317">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="350" eb="351">
       <t>コ</t>
     </rPh>
-    <rPh sb="745" eb="746">
+    <rPh sb="365" eb="367">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="396" eb="398">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="445" eb="446">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="448" eb="449">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="450" eb="451">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="471" eb="473">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="474" eb="476">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="478" eb="480">
+      <t>コナルイ</t>
+    </rPh>
+    <rPh sb="486" eb="487">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="492" eb="493">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="547" eb="548">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="549" eb="550">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="560" eb="562">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="563" eb="565">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="599" eb="600">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="601" eb="603">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="621" eb="622">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="625" eb="627">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="644" eb="646">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="689" eb="691">
+      <t>ランオウ</t>
+    </rPh>
+    <rPh sb="739" eb="741">
+      <t>キミ</t>
+    </rPh>
+    <rPh sb="747" eb="749">
+      <t>ショウリョウ</t>
+    </rPh>
+    <rPh sb="780" eb="781">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="784" eb="785">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="844" eb="845">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="846" eb="847">
+      <t>ダカ</t>
+    </rPh>
+    <rPh sb="879" eb="880">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="899" eb="900">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="913" eb="914">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="933" eb="936">
+      <t>エキタイジョウ</t>
+    </rPh>
+    <rPh sb="952" eb="953">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="955" eb="956">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="962" eb="963">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="969" eb="971">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="1012" eb="1014">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="1024" eb="1025">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1033" eb="1034">
       <t>ツク</t>
     </rPh>
-    <rPh sb="759" eb="761">
+    <rPh sb="1061" eb="1062">
+      <t>ナマ</t>
+    </rPh>
+    <rPh sb="1093" eb="1095">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="1112" eb="1113">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="1115" eb="1116">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1120" eb="1121">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1147" eb="1148">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="1162" eb="1163">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1169" eb="1170">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1171" eb="1172">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="1179" eb="1181">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="1189" eb="1190">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1191" eb="1192">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1200" eb="1202">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1208" eb="1210">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="1217" eb="1218">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="1223" eb="1225">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1244" eb="1246">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="1265" eb="1266">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="1267" eb="1268">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="1275" eb="1277">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1296" eb="1299">
+      <t>エキタイジョウ</t>
+    </rPh>
+    <rPh sb="1314" eb="1315">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1322" eb="1325">
+      <t>ソコキジ</t>
+    </rPh>
+    <rPh sb="1337" eb="1338">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1343" eb="1345">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1351" eb="1352">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="1362" eb="1365">
+      <t>ソコキジ</t>
+    </rPh>
+    <rPh sb="1407" eb="1409">
+      <t>アジツ</t>
+    </rPh>
+    <rPh sb="1415" eb="1416">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1469" eb="1470">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1481" eb="1483">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1494" eb="1496">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1497" eb="1499">
+      <t>ヒョウメン</t>
+    </rPh>
+    <rPh sb="1543" eb="1544">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1583" eb="1584">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1596" eb="1598">
+      <t>ヘイタン</t>
+    </rPh>
+    <rPh sb="1617" eb="1619">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1620" eb="1621">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1663" eb="1664">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1668" eb="1669">
+      <t>タイラ</t>
+    </rPh>
+    <rPh sb="1670" eb="1671">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1685" eb="1687">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1711" eb="1713">
+      <t>ヒムロ</t>
+    </rPh>
+    <rPh sb="1743" eb="1745">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="1762" eb="1763">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1776" eb="1778">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="1780" eb="1781">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="1782" eb="1783">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1840" eb="1842">
+      <t>コウキ</t>
+    </rPh>
+    <rPh sb="1854" eb="1856">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1861" eb="1863">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="1884" eb="1886">
+      <t>キンパク</t>
+    </rPh>
+    <rPh sb="1896" eb="1897">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="1905" eb="1907">
+      <t>オウサマ</t>
+    </rPh>
+    <rPh sb="1908" eb="1910">
+      <t>オオヨロコ</t>
+    </rPh>
+    <rPh sb="1916" eb="1918">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぬねちゃんから初対面で入手</t>
+    <rPh sb="7" eb="8">
+      <t>ハツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風魔法解禁の本　＃なし</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイキン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【クッキーのお家　フォーゲットミーノットのレシピ】
+恋人への特別なお菓子「フォーゲットミーノット」のご紹介です。
+材料が多く大変ですが、ぜひ挑戦してみてくださいね！
+ざっくりと、
+A.壁
+B.ドアと窓
+C.屋根部分
+の3種類を作って、飾り付けていきましょう。
+A. 壁部分
+①&lt;color=#BA9535FF&gt;ビスケット&lt;/color&gt;と&lt;color=#BA9535FF&gt;ココアクッキー&lt;/color&gt;
+&lt;color=#BA9535FF&gt;ロールクッキー&lt;/color&gt;を準備し、３つを組み合わせます。
+※数は好きな数で良いです。多く入れると、見栄えもおいしさもアップ！
+壁部分はこれで完成。
+B.ドアと窓
+①窓部分は、&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;に&lt;color=#FF5CA1FF&gt;「魔法ウィンドハート」&lt;/color&gt;をかけて、ハート型のチョコにします。
+※ちゃんと冷やして固めておきましょう。
+②ドアは、&lt;color=#BA9535FF&gt;ビスケット&lt;/color&gt;に、&lt;color=#BA9535FF&gt;チョコペン&lt;/color&gt;で模様を描きます。
+チョコペンは、&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;に&lt;color=#FF5CA1FF&gt;魔法「ウインドペンシル」&lt;/color&gt;でできます。
+ドアと窓はこれで完了です。
+C. 屋根部分
+屋根は、チョコレートで作ります。
+①液体チョコレートに、&lt;color=#FF5CA1FF&gt;魔法「ウィンド板チョコ」&lt;/color&gt;で板チョコレートを作ります。
+こちらも冷やしましょう。
+屋根の完成です。
+【組み立て】
+①Aの&lt;color=#BA9535FF&gt;壁と土台&lt;/color&gt;に、Bの&lt;color=#BA9535FF&gt;ドア&lt;/color&gt;、Cの&lt;color=#BA9535FF&gt;板チョコ&lt;/color&gt;を先にくっつけます。
+②最後に、仕上げで&lt;color=#BA9535FF&gt;チョコの窓&lt;/color&gt;をくっつけて、
+お菓子のおうち完成です！
+さらに仕上げに、
+・宝石キャンディを散りばめる
+・くまさんやうさぎさんを配置する
+・クリスタルシュガーやパウダーシュガーなどをふりかける
+など
+よりかわいく見せてあげてくださいね♪</t>
+    <rPh sb="7" eb="8">
+      <t>ウチ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コイビト</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
       <t>ザイリョウ</t>
     </rPh>
-    <rPh sb="762" eb="763">
+    <rPh sb="61" eb="62">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>タイヘン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>チョウセン</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>マド</t>
+    </rPh>
+    <rPh sb="105" eb="109">
+      <t>ヤネブブン</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="119" eb="120">
+      <t>カザ</t>
+    </rPh>
+    <rPh sb="121" eb="122">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="239" eb="241">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="246" eb="247">
       <t>ク</t>
     </rPh>
-    <rPh sb="764" eb="765">
+    <rPh sb="248" eb="249">
       <t>ア</t>
     </rPh>
-    <rPh sb="768" eb="770">
+    <rPh sb="256" eb="257">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="258" eb="259">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="261" eb="262">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="263" eb="264">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="268" eb="269">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="270" eb="271">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="275" eb="277">
+      <t>ミバ</t>
+    </rPh>
+    <rPh sb="290" eb="291">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="291" eb="293">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="297" eb="299">
       <t>カンセイ</t>
     </rPh>
-    <rPh sb="777" eb="779">
+    <rPh sb="307" eb="308">
+      <t>マド</t>
+    </rPh>
+    <rPh sb="311" eb="314">
+      <t>マドブブン</t>
+    </rPh>
+    <rPh sb="333" eb="335">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="368" eb="370">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="394" eb="395">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="410" eb="411">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="414" eb="415">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="494" eb="496">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="497" eb="498">
+      <t>エガ</t>
+    </rPh>
+    <rPh sb="561" eb="563">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="591" eb="592">
+      <t>マド</t>
+    </rPh>
+    <rPh sb="596" eb="598">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="606" eb="608">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="608" eb="610">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="612" eb="614">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="623" eb="624">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="630" eb="632">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="657" eb="659">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="664" eb="665">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="678" eb="679">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="686" eb="687">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="696" eb="697">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="705" eb="707">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="708" eb="710">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="716" eb="717">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="718" eb="719">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="743" eb="744">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="745" eb="747">
+      <t>ドダイ</t>
+    </rPh>
+    <rPh sb="819" eb="820">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="830" eb="832">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="834" eb="836">
       <t>シア</t>
     </rPh>
-    <rPh sb="788" eb="789">
+    <rPh sb="859" eb="860">
+      <t>マド</t>
+    </rPh>
+    <rPh sb="877" eb="879">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="883" eb="885">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="893" eb="895">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="900" eb="902">
+      <t>ホウセキ</t>
+    </rPh>
+    <rPh sb="908" eb="909">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="926" eb="928">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="969" eb="970">
       <t>ミ</t>
-    </rPh>
-    <rPh sb="790" eb="791">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="792" eb="793">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="832" eb="833">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="834" eb="835">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="839" eb="840">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="841" eb="843">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="844" eb="845">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="856" eb="857">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="859" eb="861">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="876" eb="878">
-      <t>クフウ</t>
-    </rPh>
-    <rPh sb="903" eb="904">
-      <t>タメ</t>
-    </rPh>
-    <rPh sb="921" eb="924">
-      <t>ユメキブン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8162,7 +8118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8207,12 +8163,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8575,10 +8525,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8680,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8845,7 +8795,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8872,7 +8822,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -9064,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9178,10 +9128,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D14" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9208,7 +9158,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9226,10 +9176,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9256,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9274,10 +9224,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E16" s="12">
         <v>500</v>
@@ -9304,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="N16" s="12">
         <v>3130</v>
@@ -9322,10 +9272,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9352,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9367,13 +9317,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C18" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D18" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9400,7 +9350,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9592,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -9688,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9736,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10168,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10183,13 +10133,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C35" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D35" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10216,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10648,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10840,7 +10790,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N48" s="4">
         <v>9999</v>
@@ -10855,7 +10805,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C49" t="s">
         <v>195</v>
@@ -10888,7 +10838,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10903,7 +10853,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C50" t="s">
         <v>200</v>
@@ -10951,7 +10901,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C51" t="s">
         <v>203</v>
@@ -10999,7 +10949,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C52" t="s">
         <v>205</v>
@@ -11032,7 +10982,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11047,13 +10997,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -11080,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N53">
         <v>350</v>
@@ -11095,13 +11045,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -11128,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>314</v>
+        <v>551</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11143,13 +11093,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D55" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -11176,7 +11126,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11191,13 +11141,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C56" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -11224,7 +11174,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>437</v>
+        <v>553</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11239,13 +11189,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -11272,7 +11222,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11281,51 +11231,51 @@
         <v>390</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="16">
+    <row r="58" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>555</v>
-      </c>
-      <c r="C58" s="16" t="s">
+      <c r="B58" t="s">
+        <v>550</v>
+      </c>
+      <c r="C58" t="s">
         <v>207</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D58" t="s">
         <v>208</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58">
         <v>500</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58">
         <v>150</v>
       </c>
-      <c r="G58" s="16">
-        <v>0</v>
-      </c>
-      <c r="H58" s="16">
-        <v>0</v>
-      </c>
-      <c r="I58" s="16">
-        <v>0</v>
-      </c>
-      <c r="J58" s="16">
-        <v>0</v>
-      </c>
-      <c r="K58" s="16">
-        <v>0</v>
-      </c>
-      <c r="L58" s="16">
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
         <v>1</v>
       </c>
-      <c r="M58" s="17" t="s">
-        <v>556</v>
-      </c>
-      <c r="N58" s="16">
+      <c r="M58" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="N58">
         <v>400</v>
       </c>
-      <c r="O58" s="16">
+      <c r="O58">
         <v>400</v>
       </c>
     </row>
@@ -11335,7 +11285,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C59" t="s">
         <v>210</v>
@@ -11368,7 +11318,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>256</v>
+        <v>556</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11383,7 +11333,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C60" t="s">
         <v>212</v>
@@ -11431,7 +11381,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C61" t="s">
         <v>214</v>
@@ -11479,7 +11429,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
         <v>217</v>
@@ -11512,7 +11462,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N62">
         <v>520</v>
@@ -11527,7 +11477,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C63" t="s">
         <v>218</v>
@@ -11560,7 +11510,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="N63">
         <v>530</v>
@@ -11575,13 +11525,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C64" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D64" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11608,7 +11558,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11656,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -11671,7 +11621,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C66" t="s">
         <v>223</v>
@@ -11704,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N66">
         <v>550</v>
@@ -11719,7 +11669,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C67" t="s">
         <v>224</v>
@@ -11752,7 +11702,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N67">
         <v>560</v>
@@ -11767,7 +11717,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C68" t="s">
         <v>228</v>
@@ -11800,7 +11750,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N68">
         <v>570</v>
@@ -11815,7 +11765,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C69" t="s">
         <v>227</v>
@@ -11863,7 +11813,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C70" t="s">
         <v>230</v>
@@ -11896,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N70">
         <v>590</v>
@@ -11959,7 +11909,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C72" t="s">
         <v>234</v>
@@ -11992,7 +11942,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N72">
         <v>610</v>
@@ -12010,10 +11960,10 @@
         <v>192</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E73" s="6">
         <v>500</v>
@@ -12040,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N73" s="6">
         <v>620</v>
@@ -12055,7 +12005,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C74" t="s">
         <v>237</v>
@@ -12088,7 +12038,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N74">
         <v>700</v>
@@ -12103,13 +12053,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C75" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D75" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -12136,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N75">
         <v>710</v>
@@ -12151,7 +12101,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C76" t="s">
         <v>239</v>
@@ -12184,7 +12134,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N76">
         <v>720</v>
@@ -12199,7 +12149,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C77" t="s">
         <v>241</v>
@@ -12232,7 +12182,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N77">
         <v>730</v>
@@ -12247,7 +12197,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C78" t="s">
         <v>242</v>
@@ -12280,7 +12230,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N78">
         <v>740</v>
@@ -12295,7 +12245,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C79" t="s">
         <v>249</v>
@@ -12328,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N79">
         <v>750</v>
@@ -12343,7 +12293,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C80" t="s">
         <v>245</v>
@@ -12391,13 +12341,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E81">
         <v>500</v>
@@ -12424,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N81">
         <v>770</v>
@@ -12439,13 +12389,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12472,7 +12422,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N82">
         <v>780</v>
@@ -12490,10 +12440,10 @@
         <v>192</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E83" s="6">
         <v>500</v>
@@ -12520,7 +12470,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N83" s="6">
         <v>790</v>
@@ -12535,13 +12485,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C84" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D84" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12568,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12586,10 +12536,10 @@
         <v>192</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E85" s="8">
         <v>500</v>
@@ -12616,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N85" s="8">
         <v>9999</v>
@@ -12631,13 +12581,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C86" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D86" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12664,7 +12614,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12679,13 +12629,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C87" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D87" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12712,7 +12662,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12727,13 +12677,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C88" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12760,7 +12710,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12775,13 +12725,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C89" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D89" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12808,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12823,13 +12773,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C90" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D90" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12856,7 +12806,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12871,13 +12821,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D91" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12904,7 +12854,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12919,13 +12869,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C92" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D92" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12952,7 +12902,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12967,13 +12917,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C93" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D93" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -13000,7 +12950,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -13015,13 +12965,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C94" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D94" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -13048,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13063,13 +13013,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C95" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D95" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13096,7 +13046,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>500</v>
+        <v>555</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13111,13 +13061,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C96" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D96" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13144,7 +13094,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13159,13 +13109,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C97" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D97" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -13192,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13207,13 +13157,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C98" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D98" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13240,7 +13190,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13255,13 +13205,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C99" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D99" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13288,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13303,13 +13253,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C100" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D100" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13336,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13351,13 +13301,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C101" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D101" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13384,7 +13334,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13399,13 +13349,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C102" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13432,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13447,13 +13397,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D103" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13480,7 +13430,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13495,13 +13445,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C104" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D104" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13528,7 +13478,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13543,13 +13493,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C105" t="s">
+        <v>278</v>
+      </c>
+      <c r="D105" t="s">
         <v>279</v>
-      </c>
-      <c r="D105" t="s">
-        <v>280</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13576,7 +13526,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13591,13 +13541,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C106" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D106" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13624,7 +13574,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13639,13 +13589,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C107" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13672,7 +13622,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13687,13 +13637,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C108" t="s">
+        <v>309</v>
+      </c>
+      <c r="D108" t="s">
         <v>310</v>
-      </c>
-      <c r="D108" t="s">
-        <v>311</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13720,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13735,13 +13685,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C109" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13768,7 +13718,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13783,13 +13733,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13816,7 +13766,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13831,13 +13781,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C111" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D111" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13864,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13879,13 +13829,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C112" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D112" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13912,7 +13862,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13927,13 +13877,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C113" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D113" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13960,7 +13910,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13975,13 +13925,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C114" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D114" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -14008,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -14023,13 +13973,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C115" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D115" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -14056,7 +14006,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -14071,13 +14021,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C116" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D116" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -14104,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14119,13 +14069,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C117" t="s">
+        <v>281</v>
+      </c>
+      <c r="D117" t="s">
         <v>282</v>
-      </c>
-      <c r="D117" t="s">
-        <v>283</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -14152,7 +14102,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14167,13 +14117,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C118" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D118" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14200,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14215,13 +14165,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C119" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D119" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14248,7 +14198,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14263,13 +14213,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C120" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D120" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14296,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14311,13 +14261,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C121" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D121" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14344,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14359,13 +14309,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C122" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D122" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14392,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14407,13 +14357,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C123" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D123" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14440,7 +14390,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14455,13 +14405,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C124" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D124" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14488,7 +14438,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14503,13 +14453,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C125" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D125" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14536,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14551,13 +14501,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C126" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D126" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14584,7 +14534,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>549</v>
+        <v>457</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14599,13 +14549,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C127" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D127" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14632,7 +14582,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14647,13 +14597,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C128" t="s">
+        <v>311</v>
+      </c>
+      <c r="D128" t="s">
         <v>312</v>
-      </c>
-      <c r="D128" t="s">
-        <v>313</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14680,7 +14630,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14695,13 +14645,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C129" t="s">
+        <v>304</v>
+      </c>
+      <c r="D129" t="s">
         <v>305</v>
-      </c>
-      <c r="D129" t="s">
-        <v>306</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14728,7 +14678,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14743,13 +14693,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D130" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14776,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14785,51 +14735,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="131" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="14">
+    <row r="131" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A131">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="B131" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="C131" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="D131" s="14" t="s">
-        <v>452</v>
-      </c>
-      <c r="E131" s="14">
+      <c r="B131" t="s">
+        <v>367</v>
+      </c>
+      <c r="C131" t="s">
+        <v>451</v>
+      </c>
+      <c r="D131" t="s">
+        <v>449</v>
+      </c>
+      <c r="E131">
         <v>500</v>
       </c>
-      <c r="F131" s="14">
+      <c r="F131">
         <v>150</v>
       </c>
-      <c r="G131" s="14">
-        <v>0</v>
-      </c>
-      <c r="H131" s="14">
-        <v>0</v>
-      </c>
-      <c r="I131" s="14">
-        <v>0</v>
-      </c>
-      <c r="J131" s="14">
-        <v>0</v>
-      </c>
-      <c r="K131" s="14">
-        <v>0</v>
-      </c>
-      <c r="L131" s="14">
-        <v>0</v>
-      </c>
-      <c r="M131" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="N131" s="14">
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="N131">
         <v>5000</v>
       </c>
-      <c r="O131" s="14">
+      <c r="O131">
         <v>5000</v>
       </c>
     </row>
@@ -14839,13 +14789,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E132" s="14">
         <v>500</v>
@@ -14872,7 +14822,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="15" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="N132" s="14">
         <v>5000</v>
@@ -14887,13 +14837,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C133" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D133" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14920,7 +14870,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14935,13 +14885,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C134" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D134" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14968,7 +14918,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14977,291 +14927,291 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="135" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="16">
+    <row r="135" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A135">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C135" s="16" t="s">
-        <v>522</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="E135" s="16">
+      <c r="B135" t="s">
+        <v>367</v>
+      </c>
+      <c r="C135" t="s">
+        <v>518</v>
+      </c>
+      <c r="D135" t="s">
+        <v>517</v>
+      </c>
+      <c r="E135">
         <v>500</v>
       </c>
-      <c r="F135" s="16">
+      <c r="F135">
         <v>150</v>
       </c>
-      <c r="G135" s="16">
-        <v>0</v>
-      </c>
-      <c r="H135" s="16">
-        <v>0</v>
-      </c>
-      <c r="I135" s="16">
-        <v>0</v>
-      </c>
-      <c r="J135" s="16">
-        <v>0</v>
-      </c>
-      <c r="K135" s="16">
-        <v>0</v>
-      </c>
-      <c r="L135" s="16">
-        <v>0</v>
-      </c>
-      <c r="M135" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="N135" s="16">
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="N135">
         <v>5000</v>
       </c>
-      <c r="O135" s="16">
+      <c r="O135">
         <v>5000</v>
       </c>
     </row>
-    <row r="136" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="16">
+    <row r="136" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="B136" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>524</v>
-      </c>
-      <c r="E136" s="16">
+      <c r="B136" t="s">
+        <v>367</v>
+      </c>
+      <c r="C136" t="s">
+        <v>519</v>
+      </c>
+      <c r="D136" t="s">
+        <v>520</v>
+      </c>
+      <c r="E136">
         <v>500</v>
       </c>
-      <c r="F136" s="16">
+      <c r="F136">
         <v>150</v>
       </c>
-      <c r="G136" s="16">
-        <v>0</v>
-      </c>
-      <c r="H136" s="16">
-        <v>0</v>
-      </c>
-      <c r="I136" s="16">
-        <v>0</v>
-      </c>
-      <c r="J136" s="16">
-        <v>0</v>
-      </c>
-      <c r="K136" s="16">
-        <v>0</v>
-      </c>
-      <c r="L136" s="16">
-        <v>0</v>
-      </c>
-      <c r="M136" s="17" t="s">
-        <v>547</v>
-      </c>
-      <c r="N136" s="16">
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="N136">
         <v>5000</v>
       </c>
-      <c r="O136" s="16">
+      <c r="O136">
         <v>5000</v>
       </c>
     </row>
-    <row r="137" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="16">
+    <row r="137" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="B137" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="D137" s="16" t="s">
+      <c r="B137" t="s">
+        <v>367</v>
+      </c>
+      <c r="C137" t="s">
         <v>527</v>
       </c>
-      <c r="E137" s="16">
+      <c r="D137" t="s">
+        <v>523</v>
+      </c>
+      <c r="E137">
         <v>500</v>
       </c>
-      <c r="F137" s="16">
+      <c r="F137">
         <v>150</v>
       </c>
-      <c r="G137" s="16">
-        <v>0</v>
-      </c>
-      <c r="H137" s="16">
-        <v>0</v>
-      </c>
-      <c r="I137" s="16">
-        <v>0</v>
-      </c>
-      <c r="J137" s="16">
-        <v>0</v>
-      </c>
-      <c r="K137" s="16">
-        <v>0</v>
-      </c>
-      <c r="L137" s="16">
-        <v>0</v>
-      </c>
-      <c r="M137" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="N137" s="16">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="N137">
         <v>5000</v>
       </c>
-      <c r="O137" s="16">
+      <c r="O137">
         <v>5000</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="16">
+    <row r="138" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="D138" s="16" t="s">
+      <c r="B138" t="s">
+        <v>367</v>
+      </c>
+      <c r="C138" t="s">
         <v>528</v>
       </c>
-      <c r="E138" s="16">
+      <c r="D138" t="s">
+        <v>524</v>
+      </c>
+      <c r="E138">
         <v>500</v>
       </c>
-      <c r="F138" s="16">
+      <c r="F138">
         <v>150</v>
       </c>
-      <c r="G138" s="16">
-        <v>0</v>
-      </c>
-      <c r="H138" s="16">
-        <v>0</v>
-      </c>
-      <c r="I138" s="16">
-        <v>0</v>
-      </c>
-      <c r="J138" s="16">
-        <v>0</v>
-      </c>
-      <c r="K138" s="16">
-        <v>0</v>
-      </c>
-      <c r="L138" s="16">
-        <v>0</v>
-      </c>
-      <c r="M138" s="17" t="s">
-        <v>552</v>
-      </c>
-      <c r="N138" s="16">
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="N138">
         <v>5000</v>
       </c>
-      <c r="O138" s="16">
+      <c r="O138">
         <v>5000</v>
       </c>
     </row>
-    <row r="139" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="16">
+    <row r="139" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A139">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-      <c r="B139" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="D139" s="16" t="s">
+      <c r="B139" t="s">
+        <v>367</v>
+      </c>
+      <c r="C139" t="s">
         <v>529</v>
       </c>
-      <c r="E139" s="16">
+      <c r="D139" t="s">
+        <v>525</v>
+      </c>
+      <c r="E139">
         <v>500</v>
       </c>
-      <c r="F139" s="16">
+      <c r="F139">
         <v>150</v>
       </c>
-      <c r="G139" s="16">
-        <v>0</v>
-      </c>
-      <c r="H139" s="16">
-        <v>0</v>
-      </c>
-      <c r="I139" s="16">
-        <v>0</v>
-      </c>
-      <c r="J139" s="16">
-        <v>0</v>
-      </c>
-      <c r="K139" s="16">
-        <v>0</v>
-      </c>
-      <c r="L139" s="16">
-        <v>0</v>
-      </c>
-      <c r="M139" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="N139" s="16">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="N139">
         <v>5000</v>
       </c>
-      <c r="O139" s="16">
+      <c r="O139">
         <v>5000</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="16">
+    <row r="140" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A140">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="B140" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="D140" s="16" t="s">
+      <c r="B140" t="s">
+        <v>367</v>
+      </c>
+      <c r="C140" t="s">
         <v>530</v>
       </c>
-      <c r="E140" s="16">
+      <c r="D140" t="s">
+        <v>526</v>
+      </c>
+      <c r="E140">
         <v>500</v>
       </c>
-      <c r="F140" s="16">
+      <c r="F140">
         <v>150</v>
       </c>
-      <c r="G140" s="16">
-        <v>0</v>
-      </c>
-      <c r="H140" s="16">
-        <v>0</v>
-      </c>
-      <c r="I140" s="16">
-        <v>0</v>
-      </c>
-      <c r="J140" s="16">
-        <v>0</v>
-      </c>
-      <c r="K140" s="16">
-        <v>0</v>
-      </c>
-      <c r="L140" s="16">
-        <v>0</v>
-      </c>
-      <c r="M140" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="N140" s="16">
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="N140">
         <v>5000</v>
       </c>
-      <c r="O140" s="16">
+      <c r="O140">
         <v>5000</v>
       </c>
     </row>
@@ -15271,13 +15221,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E141" s="10">
         <v>500</v>
@@ -15304,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N141" s="10">
         <v>5000</v>
@@ -15319,13 +15269,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E142" s="10">
         <v>500</v>
@@ -15352,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="M142" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N142" s="10">
         <v>5000</v>
@@ -15367,13 +15317,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E143" s="10">
         <v>500</v>
@@ -15400,7 +15350,7 @@
         <v>0</v>
       </c>
       <c r="M143" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N143" s="10">
         <v>5000</v>
@@ -15415,13 +15365,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C144" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D144" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15448,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N144">
         <v>5000</v>
@@ -15463,13 +15413,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C145" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D145" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -15496,7 +15446,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N145">
         <v>5000</v>
@@ -15511,13 +15461,13 @@
         <v>144</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E146" s="10">
         <v>500</v>
@@ -15544,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="11" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N146" s="10">
         <v>5000</v>
@@ -15559,13 +15509,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C147" t="s">
+        <v>306</v>
+      </c>
+      <c r="D147" t="s">
         <v>307</v>
-      </c>
-      <c r="D147" t="s">
-        <v>308</v>
       </c>
       <c r="E147">
         <v>500</v>
@@ -15592,7 +15542,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N147">
         <v>5000</v>
@@ -15607,13 +15557,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C148" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D148" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -15640,7 +15590,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N148">
         <v>9999</v>
@@ -15751,10 +15701,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -16015,13 +15965,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16063,13 +16013,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C8" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D8" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16111,13 +16061,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C9" t="s">
+        <v>487</v>
+      </c>
+      <c r="D9" t="s">
         <v>490</v>
-      </c>
-      <c r="D9" t="s">
-        <v>493</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16495,7 +16445,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C17" t="s">
         <v>196</v>
@@ -16543,13 +16493,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C18" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D18" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D9BE98-36EC-414C-9C92-BE6753EA03CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454A904F-B454-46DA-B324-B7C87F42565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="558">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -4596,532 +4596,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【ザッハトルテのレシピ】
-難易度・・　高
-つやつやの滑らかで、伝統的なチョコレートケーキです。
-以下、３つの生地を作り、あとで合わせて仕上げていきます。
-A. ザッハトルテ生地
-B. コーティングチョコ生地
-C. あんずジャム
-A.
-①チョコの生地・・・卵黄・砂糖に、バターを入れて混ぜ合わせます。
-できたバタークリームに、&lt;color=#BA9535FF&gt;溶けた液体のチョコレート&lt;/color&gt;をいれて混ぜます。
-チョコレートの生地ができます。
-②事前にメレンゲを作っておきます。・・・
-&lt;color=#BA9535FF&gt;卵白&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;泡だて器&lt;/color&gt;で角が立つまで、混ぜ合わせます。
-③先ほど作った、チョコ生地とメレンゲを混ぜ合わせ、そこに薄力粉を加えて、しっかり混ぜます。
-焼き上げれば、ザッハトルテ生地は完成です！！
-※170度で約40~50分。
-あとで、スライスして、他のソースをつけていきます。今は置いておきましょう。
-B. コーティング用チョコ生地＜ザッハトルテソース＞
-①&lt;color=#BA9535FF&gt;水&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;にかけ、水あめを先に作ります。
-②水あめに、液体チョコレートを混ぜ、お鍋にかけて、とろとろに煮詰めましょう。
-これで、とろりとしたチョコのコーティング生地の完成です。
-C. あんずジャムの作り方
-①&lt;color=#BA9535FF&gt;あんず&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;に入れて、とろとろと煮詰めていきます。
-とろりしたら、完成です。
-【完成まで】
-①Aで作った生地をスライスします。
-②スライスした生地の上面に、&lt;color=#BA9535FF&gt;あんずジャム&lt;/color&gt;を塗り、再度スライスしたザッハトルテ生地を上からかぶせます。
-③できあがったケーキベースに、あんずジャムを、全体的に塗ってコーティングします。
-※2時間ほど乾燥させます。
-④コーティングした生地に、上から&lt;color=#BA9535FF&gt;Bのチョコレート生地&lt;/color&gt;をかけて、コーティングします。
-きれいに全体がチョコでコーティングされたら、完成です♪
-なめらかなチョコの艶や光沢、そしてあんずの芳醇な香り.. それらの調和をお楽しみ頂ければ幸いです。</t>
-    <rPh sb="14" eb="17">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ナメ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="127" eb="129">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>ランオウ</t>
-    </rPh>
-    <rPh sb="135" eb="137">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="146" eb="147">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="148" eb="149">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="209" eb="210">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="223" eb="225">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="271" eb="273">
-      <t>ランパク</t>
-    </rPh>
-    <rPh sb="299" eb="301">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="340" eb="341">
-      <t>ツノ</t>
-    </rPh>
-    <rPh sb="342" eb="343">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="347" eb="348">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="349" eb="350">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="358" eb="359">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="361" eb="362">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="368" eb="370">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="376" eb="377">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="378" eb="379">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="385" eb="388">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="389" eb="390">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="397" eb="398">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="404" eb="405">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="406" eb="407">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="417" eb="419">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="420" eb="422">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="431" eb="432">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="433" eb="434">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="439" eb="440">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="454" eb="455">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="468" eb="469">
-      <t>イマ</t>
-    </rPh>
-    <rPh sb="470" eb="471">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="492" eb="493">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="496" eb="498">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="528" eb="529">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="555" eb="557">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="584" eb="585">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="597" eb="598">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="601" eb="602">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="603" eb="604">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="611" eb="612">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="616" eb="618">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="625" eb="626">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="629" eb="630">
-      <t>ナベ</t>
-    </rPh>
-    <rPh sb="640" eb="642">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="670" eb="672">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="673" eb="675">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="691" eb="692">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="693" eb="694">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="742" eb="744">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="782" eb="783">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="791" eb="793">
-      <t>ニツ</t>
-    </rPh>
-    <rPh sb="808" eb="810">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="816" eb="818">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="826" eb="827">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="829" eb="831">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="849" eb="851">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="852" eb="854">
-      <t>ジョウメン</t>
-    </rPh>
-    <rPh sb="888" eb="889">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="891" eb="893">
-      <t>サイド</t>
-    </rPh>
-    <rPh sb="942" eb="945">
-      <t>ゼンタイテキ</t>
-    </rPh>
-    <rPh sb="946" eb="947">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="962" eb="964">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="966" eb="968">
-      <t>カンソウ</t>
-    </rPh>
-    <rPh sb="984" eb="986">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="988" eb="989">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="1016" eb="1018">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="1047" eb="1049">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="1065" eb="1067">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="1081" eb="1082">
-      <t>ツヤ</t>
-    </rPh>
-    <rPh sb="1083" eb="1085">
-      <t>コウタク</t>
-    </rPh>
-    <rPh sb="1093" eb="1095">
-      <t>ホウジュン</t>
-    </rPh>
-    <rPh sb="1096" eb="1097">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="1105" eb="1107">
-      <t>チョウワ</t>
-    </rPh>
-    <rPh sb="1109" eb="1110">
-      <t>タノ</t>
-    </rPh>
-    <rPh sb="1112" eb="1113">
-      <t>イタダ</t>
-    </rPh>
-    <rPh sb="1116" eb="1117">
-      <t>サイワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【ブッシュドノエルのレシピ】
-難易度・・　中～高　ぐらい
-木を模した伝統的なケーキ菓子です。チョコレートやココアの風味が、森を思わせる・・
-森のケーキをお楽しみください。
-★魔法「ウィンドロール」を覚えておきましょう。
-★模様をつけるため、器材「フォーク」も買っておきましょう。
-下準備として、
-A. ココアケーキ生地
-B. チョコレートクリーム
-の２つを先に作ります。
-あとで、生地をまきまきしていきましょう♪
-【作り方】
-A. ココアケーキ生地
-①&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;と、&lt;color=#BA9535FF&gt;ココアパウダー&lt;/color&gt;を先に混ぜておきます。
-②アパレイユを作る・・・
- &lt;color=#BA9535FF&gt;砂糖、卵、バター&lt;/color&gt;を混ぜ、アパレイユを作ります。
-③アパレイユに先ほどの粉類をふるい入れ、ウィンドミキサーで混ぜます。焼き上げれば生地の完成です。
-※180度で10~12分ほど焼くといい感じです。
-B.チョコレートバタークリーム
-①卵黄に砂糖を混ぜます。＜アパレイユ黄身＞
-さらに、少量の液体状チョコレートを入れよく混ぜます。
-②ある程度混ざったら、バターを入れて、よく混ぜます。
-芳醇で味わい深いチョコレートバタークリームの完成です。
-【仕上げ】
-※Aの生地を事前にスライスします。
-①スライスした生地の片面に、Bのチョコレートクリームをぬっていきます。
-②できた生地に、魔法「ウィンドロール」をかけて、きれいに巻きましょう！
-③巻いたロール生地に、さらにBチョコレートクリームをぬります。このとき、「フォーク」を使って、木の模様をつけていきます。
-④上にマジパンで作ったお花や、動物などのトッピングでデコレーションして..
-ブッシュドノエル完成で～す♪
-まさに、木を模した伝統的で豪華なお菓子です。
-ぜひ自分の手で作ってみてくださいね。
-【あとがき】
-ブッシュドノエルは、ちょうちょとの相性がいいようです。
-</t>
-    <rPh sb="16" eb="19">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="36" eb="39">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>フウミ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>モリ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>モリ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>タノ</t>
-    </rPh>
-    <rPh sb="144" eb="147">
-      <t>シタジュンビ</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="182" eb="183">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="184" eb="185">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="214" eb="215">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="216" eb="217">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="249" eb="252">
-      <t>ハクリキコ</t>
-    </rPh>
-    <rPh sb="338" eb="340">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="355" eb="356">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="378" eb="379">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="382" eb="384">
-      <t>コナルイ</t>
-    </rPh>
-    <rPh sb="400" eb="401">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="405" eb="406">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="407" eb="408">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="411" eb="413">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="414" eb="416">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="424" eb="425">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="431" eb="432">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="434" eb="435">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="439" eb="440">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="491" eb="494">
-      <t>エキタイジョウ</t>
-    </rPh>
-    <rPh sb="539" eb="541">
-      <t>ホウジュン</t>
-    </rPh>
-    <rPh sb="542" eb="543">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="545" eb="546">
-      <t>ブカ</t>
-    </rPh>
-    <rPh sb="561" eb="563">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="569" eb="571">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="577" eb="579">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="580" eb="582">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="600" eb="602">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="603" eb="605">
-      <t>カタメン</t>
-    </rPh>
-    <rPh sb="634" eb="636">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="638" eb="640">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="658" eb="659">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="668" eb="669">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="674" eb="676">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="710" eb="711">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="714" eb="715">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="716" eb="718">
-      <t>モヨウ</t>
-    </rPh>
-    <rPh sb="730" eb="731">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="737" eb="738">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="741" eb="742">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="744" eb="746">
-      <t>ドウブツ</t>
-    </rPh>
-    <rPh sb="776" eb="778">
-      <t>カンセイ</t>
-    </rPh>
-    <rPh sb="788" eb="789">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="790" eb="791">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="793" eb="796">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="797" eb="799">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="801" eb="803">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="809" eb="811">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="812" eb="813">
-      <t>テ</t>
-    </rPh>
-    <rPh sb="814" eb="815">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="851" eb="853">
-      <t>アイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">小麦粉とバターと砂糖
 &lt;color=#BA9535FF&gt;2 : 2 : 2 &lt;/color&gt;
 で混ぜると良いらしいぜ！
@@ -5479,241 +4953,6 @@
     </rPh>
     <rPh sb="9" eb="11">
       <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【チョコレートの秘密　～その１～】
-今回の特集は.. チョコレート作りの秘訣！！
-チョコを作る際のアレンジレシピをご紹介いたします！
-※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
-今回のテーマは、「カカオマス」。
-この「カカオマス」に色んな材料を加えると、チョコに様々な変化が現れます。
-いくつか秘密をご紹介☆
-◆お抹茶チョコレート
-カカオマス　×　へんな草
-カカオマス　×　ミント
-混ぜると、緑色のチョコレートに変化します。
-◆海のチョコレート
-カカオマス　×　すみれのお花
-カカオマス　×　ブルーベリー
-カカオマス　×　ブラックベリー
-海を感じさせる青色のチョコレートに変化！
-◆純愛のチョコレート
-カカオマス　×　ストロベリー
-カカオマス　×　ラズベリー
-愛情をあらわす赤色のチョコレートに変化します！
-【苦味を加える】
-・「カカオマス」の状態で、いろんな材料を加えることができます。
-たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。</t>
-    <rPh sb="8" eb="10">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>コンカイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>トクシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ヒケツ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="90" eb="91">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>コンカイ</t>
-    </rPh>
-    <rPh sb="139" eb="140">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="142" eb="144">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="145" eb="146">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="160" eb="161">
-      <t>アラワ</t>
-    </rPh>
-    <rPh sb="170" eb="172">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="181" eb="183">
-      <t>マッチャ</t>
-    </rPh>
-    <rPh sb="202" eb="203">
-      <t>クサ</t>
-    </rPh>
-    <rPh sb="217" eb="218">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="222" eb="224">
-      <t>ミドリイロ</t>
-    </rPh>
-    <rPh sb="232" eb="234">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="241" eb="242">
-      <t>ウミ</t>
-    </rPh>
-    <rPh sb="264" eb="265">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="298" eb="299">
-      <t>ウミ</t>
-    </rPh>
-    <rPh sb="300" eb="301">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="305" eb="307">
-      <t>アオイロ</t>
-    </rPh>
-    <rPh sb="315" eb="317">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="321" eb="323">
-      <t>ジュンアイ</t>
-    </rPh>
-    <rPh sb="362" eb="364">
-      <t>アイジョウ</t>
-    </rPh>
-    <rPh sb="369" eb="371">
-      <t>アカイロ</t>
-    </rPh>
-    <rPh sb="389" eb="391">
-      <t>ニガミ</t>
-    </rPh>
-    <rPh sb="392" eb="393">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="407" eb="409">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="415" eb="417">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="418" eb="419">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="469" eb="470">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="474" eb="476">
-      <t>ニガミ</t>
-    </rPh>
-    <rPh sb="477" eb="478">
-      <t>ツヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【チョコレートの秘密　～その２～】
-今回の特集は.. チョコレート作りの秘訣！！第二弾！！
-※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
-今回のテーマは、「白いチョコレート」の作り方。
-真っ黒のチョコもおいしいですが、少し飽きてきたそこのアナタにぜひ！
-ヒア・ウィ・ゴーー！！
-【ホワイトチョコの作り方】
-・カカオマスの状態で、
-&lt;color=#BA9535FF&gt;ジャスミンのお花&lt;/color&gt;　や　&lt;color=#BA9535FF&gt;エルダフラワー&lt;/color&gt;
-&lt;color=#BA9535FF&gt;銀色の草&lt;/color&gt;　を混ぜる。
-・液体状チョコレートの状態で、
-&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
-お花のエキスがよく混ざって、なんとチョコレートが真っ白に・・！
-</t>
-    <rPh sb="8" eb="10">
-      <t>ヒミツ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>ダイニダン</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="110" eb="111">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="112" eb="113">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="117" eb="118">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="131" eb="132">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="133" eb="134">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="184" eb="186">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="214" eb="215">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="276" eb="278">
-      <t>ギンイロ</t>
-    </rPh>
-    <rPh sb="279" eb="280">
-      <t>クサ</t>
-    </rPh>
-    <rPh sb="290" eb="291">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="298" eb="300">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="300" eb="301">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="308" eb="310">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="332" eb="333">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="349" eb="351">
-      <t>スウテキ</t>
-    </rPh>
-    <rPh sb="351" eb="352">
-      <t>クワ</t>
-    </rPh>
-    <rPh sb="362" eb="363">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="370" eb="371">
-      <t>マ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8012,6 +7251,746 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t xml:space="preserve">【チョコレートの秘密　～その２～】
+今回の特集は.. 「ホワイトチョコレート」
+※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
+真っ黒のチョコもおいしいですが、少し飽きてきたそこのアナタにぜひ！
+ヒア・ウィ・ゴーー！！
+【ホワイトチョコの作り方】
+・カカオマスの状態で、
+&lt;color=#BA9535FF&gt;ジャスミンのお花&lt;/color&gt;　や　&lt;color=#BA9535FF&gt;エルダフラワー&lt;/color&gt;
+&lt;color=#BA9535FF&gt;銀色の草&lt;/color&gt;　を混ぜる。
+・液体状チョコレートの状態で、
+&lt;color=#BA9535FF&gt;お花のポーション&lt;/color&gt;を、数滴加えてみましょう。
+お花のエキスがよく混ざり、なんとチョコレートが真っ白に・・！
+</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>ギンイロ</t>
+    </rPh>
+    <rPh sb="249" eb="250">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="260" eb="261">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="268" eb="270">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="270" eb="271">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="278" eb="280">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="302" eb="303">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="319" eb="321">
+      <t>スウテキ</t>
+    </rPh>
+    <rPh sb="321" eb="322">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="332" eb="333">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="340" eb="341">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【チョコレートの秘密　～その１～】
+今回の特集は.. 「カカオマス」！！
+チョコを作る際のアレンジレシピをご紹介いたします！
+※なお、基本のチョコレートのレシピは、この本には書かれていませんので、あしからず。
+「カカオマス」に色んな材料を加えると、チョコに様々な変化が現れます。
+いくつか秘密をご紹介☆
+◆お抹茶チョコレート
+カカオマス　×　へんな草
+カカオマス　×　ミント
+混ぜると、緑色のチョコレートに変化します。
+◆海のチョコレート
+カカオマス　×　すみれのお花
+カカオマス　×　ブルーベリー
+カカオマス　×　ブラックベリー
+海を感じさせる青色のチョコレートに変化！
+カカオマス　×　マーメイドハーブ
+こちらは少し水色に近いチョコレートができます。
+◆純愛のチョコレート
+カカオマス　×　ストロベリー
+カカオマス　×　ラズベリー
+愛情をあらわす赤色のチョコレートに変化します！
+【苦味を加える】
+・「カカオマス」の状態で、いろんな材料を加えることができます。
+たとえば、&lt;color=#BA9535FF&gt;コーヒーパウダー&lt;/color&gt;を加えると、苦味が強くなるでしょう。</t>
+    <rPh sb="8" eb="10">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トクシュウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="122" eb="123">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>ヒミツ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>マッチャ</t>
+    </rPh>
+    <rPh sb="179" eb="180">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="194" eb="195">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="199" eb="201">
+      <t>ミドリイロ</t>
+    </rPh>
+    <rPh sb="209" eb="211">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="218" eb="219">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="241" eb="242">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="275" eb="276">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="277" eb="278">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="282" eb="284">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="292" eb="294">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="319" eb="320">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="321" eb="323">
+      <t>ミズイロ</t>
+    </rPh>
+    <rPh sb="324" eb="325">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="341" eb="343">
+      <t>ジュンアイ</t>
+    </rPh>
+    <rPh sb="382" eb="384">
+      <t>アイジョウ</t>
+    </rPh>
+    <rPh sb="389" eb="391">
+      <t>アカイロ</t>
+    </rPh>
+    <rPh sb="409" eb="411">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="412" eb="413">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="427" eb="429">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="435" eb="437">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="438" eb="439">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="489" eb="490">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="494" eb="496">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="497" eb="498">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【ブッシュドノエルのレシピ】
+難易度・・　中～高　ぐらい
+木を模した伝統的なケーキ菓子です。チョコレートやココアの風味が、森を思わせる・・
+森のケーキをお楽しみください。
+★魔法&lt;color=#FF5CA1FF&gt;「ウィンドロール」&lt;/color&gt;を覚えておきましょう。
+★模様をつけるため、器材&lt;color=#FF5CA1FF&gt;「フォーク」&lt;/color&gt;も買っておきましょう。
+下準備として、
+A. ココアケーキ生地
+B. チョコレートクリーム
+の２つを先に作ります。
+あとで、生地をまきまきしていきましょう♪
+【作り方】
+A. ココアケーキ生地
+①&lt;color=#BA9535FF&gt;薄力粉&lt;/color&gt;と、&lt;color=#BA9535FF&gt;ココアパウダー&lt;/color&gt;を先に混ぜておきます。
+②アパレイユを作る・・・
+ &lt;color=#BA9535FF&gt;砂糖、卵、バター&lt;/color&gt;を混ぜ、アパレイユを作ります。
+③ &lt;color=#BA9535FF&gt;アパレイユ&lt;/color&gt;に先ほどの &lt;color=#BA9535FF&gt;粉類&lt;/color&gt;をふるい入れ、&lt;color=#FF5CA1FF&gt;ウィンドミキサー&lt;/color&gt;で混ぜます。焼き上げれば生地の完成です。
+※180度で10~12分ほど焼くといい感じです。
+B.チョコレートバタークリーム
+① &lt;color=#BA9535FF&gt;卵黄&lt;/color&gt;に &lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を混ぜます。＜アパレイユ黄身＞
+さらに、少量の &lt;color=#BA9535FF&gt;液体状チョコレート&lt;/color&gt;を入れよく混ぜます。
+②ある程度混ざったら、 &lt;color=#BA9535FF&gt;バター&lt;/color&gt;を入れて、よく混ぜます。
+芳醇で味わい深いチョコレートバタークリームの完成です。
+【仕上げ】
+①Aの生地を事前にスライスします。
+②スライスした生地の片面に、Bの &lt;color=#BA9535FF&gt;チョコレートバタークリーム&lt;/color&gt;をぬっていきます。
+③できた生地に、魔法&lt;color=#FF5CA1FF&gt;「ウィンドロール」&lt;/color&gt;をかけて、きれいに巻きましょう！
+④巻いたロール生地に、さらにB &lt;color=#BA9535FF&gt;チョコレートクリーム&lt;/color&gt;をぬります。このとき、&lt;color=#FF5CA1FF&gt;「フォーク」&lt;/color&gt;を使って、木の模様をつけていきます。
+⑤上にマジパンで作ったお花や、動物などのトッピングでデコレーションすると..
+ブッシュドノエル完成で～す♪
+まさに、木を模した伝統的で森を象徴するお菓子。
+ぜひ自分の手で作ってみてくださいね。
+【あとがき】
+ブッシュドノエルは、森のお菓子。
+&lt;color=#BA9535FF&gt;ちょうちょ&lt;/color&gt;との相性がバツグンです。
+</t>
+    <rPh sb="16" eb="19">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>フウミ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>タノ</t>
+    </rPh>
+    <rPh sb="194" eb="197">
+      <t>シタジュンビ</t>
+    </rPh>
+    <rPh sb="211" eb="213">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="232" eb="233">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="234" eb="235">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="244" eb="246">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="264" eb="265">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="266" eb="267">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="299" eb="302">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="388" eb="390">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="405" eb="406">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="454" eb="455">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="476" eb="478">
+      <t>コナルイ</t>
+    </rPh>
+    <rPh sb="527" eb="528">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="532" eb="533">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="534" eb="535">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="538" eb="540">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="541" eb="543">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="551" eb="552">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="558" eb="559">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="561" eb="562">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="566" eb="567">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="689" eb="692">
+      <t>エキタイジョウ</t>
+    </rPh>
+    <rPh sb="771" eb="773">
+      <t>ホウジュン</t>
+    </rPh>
+    <rPh sb="774" eb="775">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="777" eb="778">
+      <t>ブカ</t>
+    </rPh>
+    <rPh sb="793" eb="795">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="801" eb="803">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="810" eb="812">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="813" eb="815">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="833" eb="835">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="836" eb="838">
+      <t>カタメン</t>
+    </rPh>
+    <rPh sb="896" eb="898">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="900" eb="902">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="945" eb="946">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="955" eb="956">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="961" eb="963">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1048" eb="1049">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="1052" eb="1053">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="1054" eb="1056">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="1128" eb="1129">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="1130" eb="1131">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="1133" eb="1136">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="1144" eb="1146">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="1150" eb="1152">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="1153" eb="1154">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="1155" eb="1156">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="1185" eb="1186">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="1188" eb="1190">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="1224" eb="1226">
+      <t>アイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Items/potate_jewerybox</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ザッハトルテのレシピ】
+難易度・・　高
+つやつやの滑らかで、伝統的なチョコレートケーキです。
+以下、３つの生地を作り、あとで合わせて仕上げていきます。
+A. ザッハトルテ生地
+B. コーティングチョコ生地
+C. あんずジャム
+A.
+①チョコの生地・・・卵黄・砂糖に、バターを入れて混ぜ合わせます。
+できたバタークリームに、&lt;color=#BA9535FF&gt;溶けた液体のチョコレート&lt;/color&gt;をいれて混ぜます。
+チョコレートの生地ができます。
+②事前にメレンゲを作っておきます。・・・
+&lt;color=#BA9535FF&gt;卵白&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;泡だて器&lt;/color&gt;で角が立つまで、混ぜ合わせます。
+③先ほど作った、チョコ生地とメレンゲを混ぜ合わせ、そこに薄力粉を加えて、しっかり混ぜます。
+焼き上げれば、ザッハトルテ生地は完成です！！
+※170度で約40~50分。
+あとで、スライスして、他のソースをつけていきます。今は置いておきましょう。
+B. コーティング用チョコ生地＜ザッハトルテソース＞
+①&lt;color=#BA9535FF&gt;水&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;にかけ、水あめを先に作ります。
+②&lt;color=#BA9535FF&gt;水あめ&lt;/color&gt;に、&lt;color=#BA9535FF&gt;液体チョコレート&lt;/color&gt;を混ぜ、&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;にかけて、とろとろに煮詰めましょう。
+これで、とろりとしたチョコのコーティング生地の完成です。
+C. あんずジャムの作り方
+①&lt;color=#BA9535FF&gt;あんず&lt;/color&gt;と&lt;color=#BA9535FF&gt;砂糖&lt;/color&gt;を、&lt;color=#FF5CA1FF&gt;お鍋&lt;/color&gt;に入れて、とろとろと煮詰めていきます。
+とろりしたら、完成です。
+【完成まで】
+①Aで作った生地をスライスします。
+②スライスした生地の上面に、&lt;color=#BA9535FF&gt;あんずジャム&lt;/color&gt;を塗ります。
+・再度スライスしたザッハトルテ生地を上からかぶせます。
+③できあがったケーキベースに、あんずジャムを、全体的に塗ってコーティングします。
+※1時間ほど乾燥させます。
+④コーティングした生地に、上から&lt;color=#BA9535FF&gt;Bのチョコレート生地&lt;/color&gt;をかけて、コーティングします。
+きれいに全体がチョコでコーティングされたら、完成です♪
+なめらかなチョコの艶や光沢、そしてあんずの芳醇な香り.. それらの調和をお楽しみ頂ければ幸いです。</t>
+    <rPh sb="14" eb="17">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナメ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>ランオウ</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="146" eb="147">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="148" eb="149">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="209" eb="210">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="223" eb="225">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="271" eb="273">
+      <t>ランパク</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="340" eb="341">
+      <t>ツノ</t>
+    </rPh>
+    <rPh sb="342" eb="343">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="347" eb="348">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="349" eb="350">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="358" eb="359">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="361" eb="362">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="368" eb="370">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="376" eb="377">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="378" eb="379">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="385" eb="388">
+      <t>ハクリキコ</t>
+    </rPh>
+    <rPh sb="389" eb="390">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="397" eb="398">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="404" eb="405">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="406" eb="407">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="417" eb="419">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="420" eb="422">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="431" eb="432">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="433" eb="434">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="439" eb="440">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="454" eb="455">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="468" eb="469">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="470" eb="471">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="492" eb="493">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="496" eb="498">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="528" eb="529">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="555" eb="557">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="584" eb="585">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="597" eb="598">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="601" eb="602">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="603" eb="604">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="628" eb="629">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="658" eb="660">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="675" eb="676">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="715" eb="717">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="745" eb="747">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="748" eb="750">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="766" eb="767">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="768" eb="769">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="817" eb="819">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="857" eb="858">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="866" eb="868">
+      <t>ニツ</t>
+    </rPh>
+    <rPh sb="883" eb="885">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="891" eb="893">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="901" eb="902">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="904" eb="906">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="924" eb="926">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="927" eb="929">
+      <t>ジョウメン</t>
+    </rPh>
+    <rPh sb="963" eb="964">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="971" eb="973">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="1022" eb="1025">
+      <t>ゼンタイテキ</t>
+    </rPh>
+    <rPh sb="1026" eb="1027">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="1042" eb="1044">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="1046" eb="1048">
+      <t>カンソウ</t>
+    </rPh>
+    <rPh sb="1064" eb="1066">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1068" eb="1069">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="1096" eb="1098">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="1127" eb="1129">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="1145" eb="1147">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="1161" eb="1162">
+      <t>ツヤ</t>
+    </rPh>
+    <rPh sb="1163" eb="1165">
+      <t>コウタク</t>
+    </rPh>
+    <rPh sb="1173" eb="1175">
+      <t>ホウジュン</t>
+    </rPh>
+    <rPh sb="1176" eb="1177">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="1185" eb="1187">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="1189" eb="1190">
+      <t>タノ</t>
+    </rPh>
+    <rPh sb="1192" eb="1193">
+      <t>イタダ</t>
+    </rPh>
+    <rPh sb="1196" eb="1197">
+      <t>サイワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -8054,7 +8033,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8103,6 +8082,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -8118,7 +8103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8163,6 +8148,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8525,10 +8516,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8630,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -9014,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9128,10 +9119,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9158,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>469</v>
+        <v>554</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9176,10 +9167,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9206,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>470</v>
+        <v>553</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9224,10 +9215,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E16" s="12">
         <v>500</v>
@@ -9254,7 +9245,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N16" s="12">
         <v>3130</v>
@@ -9272,10 +9263,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D17" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9302,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9317,13 +9308,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C18" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D18" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9350,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9542,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -9638,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9686,7 +9677,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10118,7 +10109,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10133,13 +10124,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C35" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D35" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10166,7 +10157,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10598,7 +10589,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10838,7 +10829,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10982,7 +10973,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11078,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11126,7 +11117,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>434</v>
+        <v>557</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11174,7 +11165,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11222,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>435</v>
+        <v>555</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11237,7 +11228,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C58" t="s">
         <v>207</v>
@@ -11270,7 +11261,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="N58">
         <v>400</v>
@@ -11318,7 +11309,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11525,13 +11516,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C64" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D64" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11558,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11573,7 +11564,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>192</v>
+        <v>556</v>
       </c>
       <c r="C65" t="s">
         <v>220</v>
@@ -11606,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -11903,51 +11894,51 @@
         <v>600</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72">
+    <row r="72" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="16">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="16">
         <v>500</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="16">
         <v>150</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
+      <c r="G72" s="16">
+        <v>0</v>
+      </c>
+      <c r="H72" s="16">
+        <v>0</v>
+      </c>
+      <c r="I72" s="16">
+        <v>0</v>
+      </c>
+      <c r="J72" s="16">
+        <v>0</v>
+      </c>
+      <c r="K72" s="16">
+        <v>0</v>
+      </c>
+      <c r="L72" s="16">
         <v>1</v>
       </c>
-      <c r="M72" s="2" t="s">
+      <c r="M72" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="N72">
+      <c r="N72" s="16">
         <v>610</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="16">
         <v>610</v>
       </c>
     </row>
@@ -12485,13 +12476,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C84" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D84" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12518,7 +12509,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12587,7 +12578,7 @@
         <v>287</v>
       </c>
       <c r="D86" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12614,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12662,7 +12653,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12710,7 +12701,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12758,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12806,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12872,10 +12863,10 @@
         <v>367</v>
       </c>
       <c r="C92" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D92" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12902,7 +12893,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12920,10 +12911,10 @@
         <v>367</v>
       </c>
       <c r="C93" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D93" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12950,7 +12941,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12968,10 +12959,10 @@
         <v>367</v>
       </c>
       <c r="C94" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D94" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12998,7 +12989,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13016,10 +13007,10 @@
         <v>367</v>
       </c>
       <c r="C95" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D95" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13046,7 +13037,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13064,10 +13055,10 @@
         <v>367</v>
       </c>
       <c r="C96" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D96" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13094,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13142,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13190,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13208,10 +13199,10 @@
         <v>367</v>
       </c>
       <c r="C99" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D99" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13238,7 +13229,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13307,7 +13298,7 @@
         <v>433</v>
       </c>
       <c r="D101" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13334,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13478,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13526,7 +13517,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13574,7 +13565,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13622,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13670,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13718,7 +13709,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13766,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13862,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13880,10 +13871,10 @@
         <v>367</v>
       </c>
       <c r="C113" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D113" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13910,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -14054,7 +14045,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14102,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14150,7 +14141,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14198,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14246,7 +14237,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14294,7 +14285,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14342,7 +14333,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14390,7 +14381,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14438,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14486,7 +14477,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14534,7 +14525,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14582,7 +14573,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14630,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14696,10 +14687,10 @@
         <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D130" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14726,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14744,10 +14735,10 @@
         <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D131" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -14774,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14792,10 +14783,10 @@
         <v>367</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E132" s="14">
         <v>500</v>
@@ -14822,7 +14813,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="15" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="N132" s="14">
         <v>5000</v>
@@ -14840,10 +14831,10 @@
         <v>367</v>
       </c>
       <c r="C133" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D133" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14870,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14888,10 +14879,10 @@
         <v>367</v>
       </c>
       <c r="C134" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D134" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14918,7 +14909,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14936,10 +14927,10 @@
         <v>367</v>
       </c>
       <c r="C135" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D135" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -14966,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N135">
         <v>5000</v>
@@ -14984,10 +14975,10 @@
         <v>367</v>
       </c>
       <c r="C136" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D136" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -15014,7 +15005,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -15032,10 +15023,10 @@
         <v>367</v>
       </c>
       <c r="C137" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D137" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E137">
         <v>500</v>
@@ -15062,7 +15053,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N137">
         <v>5000</v>
@@ -15080,10 +15071,10 @@
         <v>367</v>
       </c>
       <c r="C138" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D138" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E138">
         <v>500</v>
@@ -15110,7 +15101,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="N138">
         <v>5000</v>
@@ -15128,10 +15119,10 @@
         <v>367</v>
       </c>
       <c r="C139" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D139" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E139">
         <v>500</v>
@@ -15158,7 +15149,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N139">
         <v>5000</v>
@@ -15176,10 +15167,10 @@
         <v>367</v>
       </c>
       <c r="C140" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D140" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E140">
         <v>500</v>
@@ -15206,7 +15197,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N140">
         <v>5000</v>
@@ -15701,10 +15692,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15965,13 +15956,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D7" t="s">
         <v>480</v>
-      </c>
-      <c r="C7" t="s">
-        <v>485</v>
-      </c>
-      <c r="D7" t="s">
-        <v>484</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16013,13 +16004,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D8" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16061,13 +16052,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C9" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D9" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16445,7 +16436,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C17" t="s">
         <v>196</v>
@@ -16493,13 +16484,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C18" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D18" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454A904F-B454-46DA-B324-B7C87F42565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C95EA5-15DC-44D0-80CF-1F19141A3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2745" yWindow="870" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -5920,13 +5920,6 @@
   </si>
   <si>
     <t>マジックパティスリーの賞品（1位）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>春のおかし大祭典の賞品（2位）</t>
-    <rPh sb="9" eb="11">
-      <t>ショウヒン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7988,6 +7981,19 @@
     </rPh>
     <rPh sb="1196" eb="1197">
       <t>サイワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プリンセストータを作って高得点だと覚える</t>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>コウトクテン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オボ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9149,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9197,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9533,7 +9539,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -10973,7 +10979,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11069,7 +11075,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11117,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11165,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11213,7 +11219,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11228,7 +11234,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C58" t="s">
         <v>207</v>
@@ -11261,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N58">
         <v>400</v>
@@ -11309,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11564,7 +11570,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C65" t="s">
         <v>220</v>
@@ -13037,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -14765,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14861,7 +14867,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -15101,7 +15107,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N138">
         <v>5000</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C95EA5-15DC-44D0-80CF-1F19141A3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2522DE4B-EC8C-42B3-AC8F-1E916D5484F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="870" windowWidth="25485" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -1128,23 +1128,6 @@
 ①まずは、&lt;color=#BA9535FF&gt;砂糖と卵黄&lt;/color&gt;を先に混ぜて液体を作ります。
 ②先ほどの液体に、&lt;color=#BA9535FF&gt;小麦粉・ミルク&lt;/color&gt;を混ぜこんで、おいしいクリームの出来上がりです☆
 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">クレープを豪華にみせるための、
-秘訣がのっている。
-シンプルなクレープに、&lt;color=#BA9535FF&gt;ベリーを2種類以上&lt;/color&gt;のせると、相性がいいようです。
-さらに、&lt;color=#BA9535FF&gt;ミント&lt;/color&gt;を添えると効果的♪　クリームの色と緑色が映えます。
-仕上げ回数が足りない？　それならば..
-パティシエレベルを上げて、&lt;color=#BA9535FF&gt;仕上げ回数を増やす&lt;/color&gt;といいですよ。
-この機会に、ぜひ色んなお菓子に挑戦して、腕前をあげてくださいね♪（by タカノ)
-</t>
-    <rPh sb="5" eb="7">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヒケツ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7994,6 +7977,23 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">クレープを豪華にみせるための、
+秘訣がのっている。
+シンプルなクレープに、&lt;color=#BA9535FF&gt;ベリーを2種類以上&lt;/color&gt;のせると、相性がいいようです。
+さらに、&lt;color=#BA9535FF&gt;ミント&lt;/color&gt;を添えると効果的♪　クリームの色と緑色が映えます。
+仕上げ回数が足りない？　それならば..
+ハートのレベルを上げて、&lt;color=#BA9535FF&gt;仕上げ回数を増やす&lt;/color&gt;といいですよ。
+この機会に、ぜひ色んなお菓子に挑戦して、腕前をあげてくださいね♪（by タカノ)
+</t>
+    <rPh sb="5" eb="7">
+      <t>ゴウカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒケツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8522,10 +8522,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -8627,7 +8627,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N3">
         <v>9999</v>
@@ -8771,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -8792,7 +8792,7 @@
         <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E7">
         <v>500</v>
@@ -8819,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N7">
         <v>3000</v>
@@ -8915,7 +8915,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>157</v>
+        <v>557</v>
       </c>
       <c r="N9">
         <v>3050</v>
@@ -8963,7 +8963,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N10">
         <v>3070</v>
@@ -8978,13 +8978,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" t="s">
         <v>168</v>
-      </c>
-      <c r="D11" t="s">
-        <v>169</v>
       </c>
       <c r="E11">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9026,13 +9026,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E12">
         <v>500</v>
@@ -9059,7 +9059,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N12">
         <v>3090</v>
@@ -9074,13 +9074,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" t="s">
         <v>181</v>
-      </c>
-      <c r="D13" t="s">
-        <v>182</v>
       </c>
       <c r="E13">
         <v>500</v>
@@ -9107,7 +9107,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N13">
         <v>3100</v>
@@ -9125,10 +9125,10 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E14">
         <v>500</v>
@@ -9155,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9173,10 +9173,10 @@
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E15">
         <v>500</v>
@@ -9203,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9221,10 +9221,10 @@
         <v>91</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E16" s="12">
         <v>500</v>
@@ -9251,7 +9251,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N16" s="12">
         <v>3130</v>
@@ -9269,10 +9269,10 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E17">
         <v>500</v>
@@ -9299,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N17">
         <v>3140</v>
@@ -9314,13 +9314,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C18" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9347,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9491,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N21">
         <v>3040</v>
@@ -9539,7 +9539,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -9587,7 +9587,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N23">
         <v>20</v>
@@ -9635,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N24">
         <v>30</v>
@@ -9683,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -9698,13 +9698,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" t="s">
         <v>159</v>
-      </c>
-      <c r="C26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
       </c>
       <c r="E26">
         <v>500</v>
@@ -9731,7 +9731,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N26">
         <v>50</v>
@@ -9923,7 +9923,7 @@
         <v>1</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N30">
         <v>90</v>
@@ -10115,7 +10115,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N34">
         <v>130</v>
@@ -10130,13 +10130,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C35" t="s">
+        <v>434</v>
+      </c>
+      <c r="D35" t="s">
         <v>435</v>
-      </c>
-      <c r="D35" t="s">
-        <v>436</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -10163,7 +10163,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N35">
         <v>150</v>
@@ -10259,7 +10259,7 @@
         <v>1</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N37">
         <v>200</v>
@@ -10307,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N38">
         <v>210</v>
@@ -10547,7 +10547,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N43">
         <v>260</v>
@@ -10562,13 +10562,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" t="s">
         <v>162</v>
-      </c>
-      <c r="D44" t="s">
-        <v>163</v>
       </c>
       <c r="E44">
         <v>500</v>
@@ -10595,7 +10595,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N44">
         <v>270</v>
@@ -10610,13 +10610,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E45">
         <v>500</v>
@@ -10643,7 +10643,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N45">
         <v>280</v>
@@ -10658,13 +10658,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E46">
         <v>500</v>
@@ -10691,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N46">
         <v>290</v>
@@ -10706,13 +10706,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E47">
         <v>500</v>
@@ -10739,7 +10739,7 @@
         <v>1</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N47">
         <v>300</v>
@@ -10754,13 +10754,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E48" s="4">
         <v>500</v>
@@ -10787,7 +10787,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N48" s="4">
         <v>9999</v>
@@ -10802,13 +10802,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D49" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E49">
         <v>500</v>
@@ -10835,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10850,13 +10850,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E50">
         <v>500</v>
@@ -10883,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N50">
         <v>320</v>
@@ -10898,13 +10898,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E51">
         <v>500</v>
@@ -10931,7 +10931,7 @@
         <v>1</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N51">
         <v>330</v>
@@ -10946,13 +10946,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C52" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" t="s">
         <v>205</v>
-      </c>
-      <c r="D52" t="s">
-        <v>206</v>
       </c>
       <c r="E52">
         <v>500</v>
@@ -10979,7 +10979,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -10994,13 +10994,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E53">
         <v>500</v>
@@ -11027,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N53">
         <v>350</v>
@@ -11042,13 +11042,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E54">
         <v>500</v>
@@ -11075,7 +11075,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11090,13 +11090,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E55">
         <v>500</v>
@@ -11123,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11138,13 +11138,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E56">
         <v>500</v>
@@ -11171,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11186,13 +11186,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E57">
         <v>500</v>
@@ -11219,7 +11219,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11234,13 +11234,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C58" t="s">
+        <v>206</v>
+      </c>
+      <c r="D58" t="s">
         <v>207</v>
-      </c>
-      <c r="D58" t="s">
-        <v>208</v>
       </c>
       <c r="E58">
         <v>500</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N58">
         <v>400</v>
@@ -11282,13 +11282,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E59">
         <v>500</v>
@@ -11315,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11330,13 +11330,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E60">
         <v>500</v>
@@ -11363,7 +11363,7 @@
         <v>1</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N60">
         <v>500</v>
@@ -11378,13 +11378,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E61">
         <v>500</v>
@@ -11411,7 +11411,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N61">
         <v>510</v>
@@ -11426,13 +11426,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62">
         <v>500</v>
@@ -11459,7 +11459,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N62">
         <v>520</v>
@@ -11474,13 +11474,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E63">
         <v>500</v>
@@ -11507,7 +11507,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N63">
         <v>530</v>
@@ -11522,13 +11522,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C64" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D64" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11555,7 +11555,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11570,13 +11570,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E65">
         <v>500</v>
@@ -11603,7 +11603,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -11618,13 +11618,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C66" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D66" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E66">
         <v>500</v>
@@ -11651,7 +11651,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N66">
         <v>550</v>
@@ -11666,13 +11666,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E67">
         <v>500</v>
@@ -11699,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N67">
         <v>560</v>
@@ -11714,13 +11714,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E68">
         <v>500</v>
@@ -11747,7 +11747,7 @@
         <v>1</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N68">
         <v>570</v>
@@ -11762,13 +11762,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C69" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D69" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E69">
         <v>500</v>
@@ -11795,7 +11795,7 @@
         <v>1</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N69">
         <v>580</v>
@@ -11810,13 +11810,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D70" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E70">
         <v>500</v>
@@ -11843,7 +11843,7 @@
         <v>1</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N70">
         <v>590</v>
@@ -11858,13 +11858,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E71" s="6">
         <v>500</v>
@@ -11891,7 +11891,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N71" s="6">
         <v>600</v>
@@ -11906,13 +11906,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C72" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D72" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="E72" s="16">
         <v>500</v>
@@ -11939,7 +11939,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N72" s="16">
         <v>610</v>
@@ -11954,13 +11954,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E73" s="6">
         <v>500</v>
@@ -11987,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N73" s="6">
         <v>620</v>
@@ -12002,13 +12002,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E74">
         <v>500</v>
@@ -12035,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N74">
         <v>700</v>
@@ -12050,13 +12050,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C75" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D75" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E75">
         <v>500</v>
@@ -12083,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N75">
         <v>710</v>
@@ -12098,13 +12098,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C76" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D76" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E76">
         <v>500</v>
@@ -12131,7 +12131,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N76">
         <v>720</v>
@@ -12146,13 +12146,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C77" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D77" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E77">
         <v>500</v>
@@ -12179,7 +12179,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N77">
         <v>730</v>
@@ -12194,13 +12194,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C78" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" t="s">
         <v>242</v>
-      </c>
-      <c r="D78" t="s">
-        <v>243</v>
       </c>
       <c r="E78">
         <v>500</v>
@@ -12227,7 +12227,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N78">
         <v>740</v>
@@ -12242,13 +12242,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C79" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D79" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E79">
         <v>500</v>
@@ -12275,7 +12275,7 @@
         <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N79">
         <v>750</v>
@@ -12290,13 +12290,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C80" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D80" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E80">
         <v>500</v>
@@ -12323,7 +12323,7 @@
         <v>1</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N80">
         <v>760</v>
@@ -12338,13 +12338,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E81">
         <v>500</v>
@@ -12371,7 +12371,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N81">
         <v>770</v>
@@ -12386,13 +12386,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E82">
         <v>500</v>
@@ -12419,7 +12419,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N82">
         <v>780</v>
@@ -12434,13 +12434,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E83" s="6">
         <v>500</v>
@@ -12467,7 +12467,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N83" s="6">
         <v>790</v>
@@ -12482,13 +12482,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C84" t="s">
+        <v>470</v>
+      </c>
+      <c r="D84" t="s">
         <v>471</v>
-      </c>
-      <c r="D84" t="s">
-        <v>472</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12515,7 +12515,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12530,13 +12530,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E85" s="8">
         <v>500</v>
@@ -12563,7 +12563,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N85" s="8">
         <v>9999</v>
@@ -12578,13 +12578,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C86" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D86" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12611,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12626,13 +12626,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C87" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D87" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E87">
         <v>500</v>
@@ -12659,7 +12659,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12674,13 +12674,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C88" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D88" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E88">
         <v>500</v>
@@ -12707,7 +12707,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12722,13 +12722,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C89" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D89" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E89">
         <v>500</v>
@@ -12755,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12770,13 +12770,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C90" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D90" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E90">
         <v>500</v>
@@ -12803,7 +12803,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12818,13 +12818,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E91">
         <v>500</v>
@@ -12851,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N91">
         <v>5000</v>
@@ -12866,13 +12866,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C92" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D92" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12899,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12914,13 +12914,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C93" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D93" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12947,7 +12947,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12962,13 +12962,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C94" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D94" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12995,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13010,13 +13010,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C95" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D95" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13043,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13058,13 +13058,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C96" t="s">
+        <v>527</v>
+      </c>
+      <c r="D96" t="s">
         <v>528</v>
-      </c>
-      <c r="D96" t="s">
-        <v>529</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13091,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13106,13 +13106,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D97" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E97">
         <v>500</v>
@@ -13139,7 +13139,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N97">
         <v>5000</v>
@@ -13154,13 +13154,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C98" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D98" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E98">
         <v>500</v>
@@ -13187,7 +13187,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N98">
         <v>5000</v>
@@ -13202,13 +13202,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C99" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D99" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E99">
         <v>500</v>
@@ -13235,7 +13235,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -13250,13 +13250,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D100" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E100">
         <v>500</v>
@@ -13283,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N100">
         <v>5000</v>
@@ -13298,13 +13298,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C101" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D101" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E101">
         <v>500</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N101">
         <v>5000</v>
@@ -13346,13 +13346,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C102" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E102">
         <v>500</v>
@@ -13379,7 +13379,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N102">
         <v>5000</v>
@@ -13394,13 +13394,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C103" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D103" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E103">
         <v>500</v>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N103">
         <v>5000</v>
@@ -13442,13 +13442,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D104" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13475,7 +13475,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13490,13 +13490,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C105" t="s">
+        <v>277</v>
+      </c>
+      <c r="D105" t="s">
         <v>278</v>
-      </c>
-      <c r="D105" t="s">
-        <v>279</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13523,7 +13523,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13538,13 +13538,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C106" t="s">
+        <v>314</v>
+      </c>
+      <c r="D106" t="s">
         <v>315</v>
-      </c>
-      <c r="D106" t="s">
-        <v>316</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13571,7 +13571,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13586,13 +13586,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C107" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D107" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13619,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N107">
         <v>5000</v>
@@ -13634,13 +13634,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C108" t="s">
+        <v>308</v>
+      </c>
+      <c r="D108" t="s">
         <v>309</v>
-      </c>
-      <c r="D108" t="s">
-        <v>310</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13667,7 +13667,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N108">
         <v>5000</v>
@@ -13682,13 +13682,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C109" t="s">
+        <v>320</v>
+      </c>
+      <c r="D109" t="s">
         <v>321</v>
-      </c>
-      <c r="D109" t="s">
-        <v>322</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13715,7 +13715,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N109">
         <v>5000</v>
@@ -13730,13 +13730,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D110" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13763,7 +13763,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13778,13 +13778,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C111" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D111" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13811,7 +13811,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13826,13 +13826,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C112" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D112" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13859,7 +13859,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13874,13 +13874,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C113" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D113" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13907,7 +13907,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N113">
         <v>5000</v>
@@ -13922,13 +13922,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C114" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D114" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13955,7 +13955,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13970,13 +13970,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C115" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D115" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -14003,7 +14003,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -14018,13 +14018,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C116" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D116" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -14051,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14066,13 +14066,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C117" t="s">
+        <v>280</v>
+      </c>
+      <c r="D117" t="s">
         <v>281</v>
-      </c>
-      <c r="D117" t="s">
-        <v>282</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -14099,7 +14099,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14114,13 +14114,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C118" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D118" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14162,13 +14162,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C119" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D119" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14195,7 +14195,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N119">
         <v>5000</v>
@@ -14210,13 +14210,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C120" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D120" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14243,7 +14243,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14258,13 +14258,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C121" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D121" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14291,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14306,13 +14306,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C122" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D122" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14339,7 +14339,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N122">
         <v>5000</v>
@@ -14354,13 +14354,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C123" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D123" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14387,7 +14387,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14402,13 +14402,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C124" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D124" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14435,7 +14435,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14450,13 +14450,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C125" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D125" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14483,7 +14483,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N125">
         <v>5000</v>
@@ -14498,13 +14498,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C126" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D126" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14531,7 +14531,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14546,13 +14546,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C127" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D127" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14579,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14594,13 +14594,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C128" t="s">
+        <v>310</v>
+      </c>
+      <c r="D128" t="s">
         <v>311</v>
-      </c>
-      <c r="D128" t="s">
-        <v>312</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14627,7 +14627,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14642,13 +14642,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C129" t="s">
+        <v>303</v>
+      </c>
+      <c r="D129" t="s">
         <v>304</v>
-      </c>
-      <c r="D129" t="s">
-        <v>305</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14675,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14690,13 +14690,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C130" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D130" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14723,7 +14723,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14738,13 +14738,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C131" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D131" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -14771,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14786,13 +14786,13 @@
         <v>130</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E132" s="14">
         <v>500</v>
@@ -14819,7 +14819,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N132" s="14">
         <v>5000</v>
@@ -14834,13 +14834,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C133" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D133" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14867,7 +14867,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14882,13 +14882,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C134" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D134" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14915,7 +14915,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14930,13 +14930,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C135" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D135" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -14963,7 +14963,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N135">
         <v>5000</v>
@@ -14978,13 +14978,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C136" t="s">
+        <v>514</v>
+      </c>
+      <c r="D136" t="s">
         <v>515</v>
-      </c>
-      <c r="D136" t="s">
-        <v>516</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -15011,7 +15011,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -15026,13 +15026,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C137" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D137" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E137">
         <v>500</v>
@@ -15059,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N137">
         <v>5000</v>
@@ -15074,13 +15074,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C138" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D138" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E138">
         <v>500</v>
@@ -15107,7 +15107,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="N138">
         <v>5000</v>
@@ -15122,13 +15122,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C139" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D139" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E139">
         <v>500</v>
@@ -15155,7 +15155,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N139">
         <v>5000</v>
@@ -15170,13 +15170,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C140" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D140" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E140">
         <v>500</v>
@@ -15203,7 +15203,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N140">
         <v>5000</v>
@@ -15218,13 +15218,13 @@
         <v>139</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E141" s="10">
         <v>500</v>
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N141" s="10">
         <v>5000</v>
@@ -15266,13 +15266,13 @@
         <v>140</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E142" s="10">
         <v>500</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="M142" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N142" s="10">
         <v>5000</v>
@@ -15314,13 +15314,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E143" s="10">
         <v>500</v>
@@ -15347,7 +15347,7 @@
         <v>0</v>
       </c>
       <c r="M143" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N143" s="10">
         <v>5000</v>
@@ -15362,13 +15362,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C144" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D144" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N144">
         <v>5000</v>
@@ -15410,13 +15410,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C145" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D145" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -15443,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N145">
         <v>5000</v>
@@ -15458,13 +15458,13 @@
         <v>144</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E146" s="10">
         <v>500</v>
@@ -15491,7 +15491,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N146" s="10">
         <v>5000</v>
@@ -15506,13 +15506,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C147" t="s">
+        <v>305</v>
+      </c>
+      <c r="D147" t="s">
         <v>306</v>
-      </c>
-      <c r="D147" t="s">
-        <v>307</v>
       </c>
       <c r="E147">
         <v>500</v>
@@ -15539,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N147">
         <v>5000</v>
@@ -15554,13 +15554,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C148" t="s">
+        <v>428</v>
+      </c>
+      <c r="D148" t="s">
         <v>429</v>
-      </c>
-      <c r="D148" t="s">
-        <v>430</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -15587,7 +15587,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N148">
         <v>9999</v>
@@ -15601,13 +15601,13 @@
         <v>10000</v>
       </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C149" t="s">
+        <v>170</v>
+      </c>
+      <c r="D149" t="s">
         <v>171</v>
-      </c>
-      <c r="D149" t="s">
-        <v>172</v>
       </c>
       <c r="E149">
         <v>500</v>
@@ -15634,7 +15634,7 @@
         <v>1</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N149">
         <v>9000</v>
@@ -15698,10 +15698,10 @@
         <v>108</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -15962,13 +15962,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16010,13 +16010,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16058,13 +16058,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16442,13 +16442,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17" t="s">
         <v>196</v>
-      </c>
-      <c r="D17" t="s">
-        <v>197</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -16490,13 +16490,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C18" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D18" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2522DE4B-EC8C-42B3-AC8F-1E916D5484F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A51DE9F-2DF0-4D53-90D1-0EB8FFF8739D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="945" yWindow="525" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -4987,47 +4987,6 @@
   </si>
   <si>
     <t>cos_Equip</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">【クッキーのレシピ＜上級＞】
-☆全てのクッキーのための本☆
-・チーズクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;クリームチーズ&lt;/color&gt;
-・はちみつクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;はちみつ&lt;/color&gt;をかけて焼く。
-・ほしのクッキー　・・・　クッキーの砂糖を&lt;color=#BA9535FF&gt;スターチップシュガー&lt;/color&gt;に変えると・・。
-・ラベンダークッキー　・・・　クッキーの砂糖を&lt;color=#BA9535FF&gt;ラベンダーシュガー&lt;/color&gt;に変えると・・。
-【コラム】
-・お店のキラキラトッピング5種類で、クッキーが作れるよ。
-【コラム２　やばいクッキー】
-・クッキーの仕上げに、へんな草やむらさキノコを入れると..　。
-</t>
-    <rPh sb="10" eb="12">
-      <t>ジョウキュウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="166" eb="168">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="205" eb="206">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="289" eb="290">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="310" eb="311">
-      <t>ツク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7994,6 +7953,48 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ヒケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【クッキーのレシピ＜上級＞】
+☆全てのクッキーのための本☆
+・ナッツクッキー　・・・　クッキーに&lt;color=#BA9535FF&gt;ナッツ&lt;/color&gt;をトッピング！
+・チーズクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;クリームチーズ&lt;/color&gt;
+・はちみつクッキー　・・・　クッキーの仕上げに&lt;color=#BA9535FF&gt;はちみつ&lt;/color&gt;をかけて焼く。
+・ほしのクッキー　・・・　クッキーの砂糖を&lt;color=#BA9535FF&gt;スターチップシュガー&lt;/color&gt;に変えると・・。
+・ラベンダークッキー　・・・　クッキーの砂糖を&lt;color=#BA9535FF&gt;ラベンダーシュガー&lt;/color&gt;に変えると・・。
+【コラム】
+・お店のキラキラトッピング5種類で、クッキーが作れるよ。
+【コラム２　やばいクッキー】
+・クッキーの仕上げに、へんな草やむらさキノコを入れると..　。
+</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウキュウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="198" eb="199">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="221" eb="223">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="260" eb="261">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="344" eb="345">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="365" eb="366">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8915,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N9">
         <v>3050</v>
@@ -9011,7 +9012,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>469</v>
+        <v>557</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9155,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9203,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9314,13 +9315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D18" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E18">
         <v>500</v>
@@ -9347,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N18">
         <v>3150</v>
@@ -9539,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -9683,7 +9684,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N25">
         <v>40</v>
@@ -10835,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N49">
         <v>310</v>
@@ -10979,7 +10980,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11075,7 +11076,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11123,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11171,7 +11172,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11219,7 +11220,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11234,7 +11235,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C58" t="s">
         <v>206</v>
@@ -11267,7 +11268,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N58">
         <v>400</v>
@@ -11315,7 +11316,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11522,13 +11523,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C64" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D64" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E64">
         <v>500</v>
@@ -11555,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N64">
         <v>535</v>
@@ -11570,7 +11571,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C65" t="s">
         <v>219</v>
@@ -11603,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N65">
         <v>540</v>
@@ -12482,13 +12483,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C84" t="s">
+        <v>469</v>
+      </c>
+      <c r="D84" t="s">
         <v>470</v>
-      </c>
-      <c r="D84" t="s">
-        <v>471</v>
       </c>
       <c r="E84">
         <v>500</v>
@@ -12515,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N84">
         <v>9999</v>
@@ -12584,7 +12585,7 @@
         <v>286</v>
       </c>
       <c r="D86" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12611,7 +12612,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N86">
         <v>2000</v>
@@ -12659,7 +12660,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12707,7 +12708,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12755,7 +12756,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12803,7 +12804,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12869,10 +12870,10 @@
         <v>366</v>
       </c>
       <c r="C92" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D92" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12899,7 +12900,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -12917,10 +12918,10 @@
         <v>366</v>
       </c>
       <c r="C93" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D93" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E93">
         <v>500</v>
@@ -12947,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N93">
         <v>5000</v>
@@ -12965,10 +12966,10 @@
         <v>366</v>
       </c>
       <c r="C94" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D94" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E94">
         <v>500</v>
@@ -12995,7 +12996,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N94">
         <v>5000</v>
@@ -13013,10 +13014,10 @@
         <v>366</v>
       </c>
       <c r="C95" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D95" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E95">
         <v>500</v>
@@ -13043,7 +13044,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13061,10 +13062,10 @@
         <v>366</v>
       </c>
       <c r="C96" t="s">
+        <v>526</v>
+      </c>
+      <c r="D96" t="s">
         <v>527</v>
-      </c>
-      <c r="D96" t="s">
-        <v>528</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13091,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -13235,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N99">
         <v>5000</v>
@@ -14099,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14771,7 +14772,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14789,10 +14790,10 @@
         <v>366</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E132" s="14">
         <v>500</v>
@@ -14819,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N132" s="14">
         <v>5000</v>
@@ -14837,10 +14838,10 @@
         <v>366</v>
       </c>
       <c r="C133" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D133" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14867,7 +14868,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14885,10 +14886,10 @@
         <v>366</v>
       </c>
       <c r="C134" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D134" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14915,7 +14916,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14933,10 +14934,10 @@
         <v>366</v>
       </c>
       <c r="C135" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D135" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -14981,10 +14982,10 @@
         <v>366</v>
       </c>
       <c r="C136" t="s">
+        <v>513</v>
+      </c>
+      <c r="D136" t="s">
         <v>514</v>
-      </c>
-      <c r="D136" t="s">
-        <v>515</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -15011,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -15029,10 +15030,10 @@
         <v>366</v>
       </c>
       <c r="C137" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D137" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E137">
         <v>500</v>
@@ -15077,10 +15078,10 @@
         <v>366</v>
       </c>
       <c r="C138" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D138" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E138">
         <v>500</v>
@@ -15107,7 +15108,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N138">
         <v>5000</v>
@@ -15125,10 +15126,10 @@
         <v>366</v>
       </c>
       <c r="C139" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D139" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E139">
         <v>500</v>
@@ -15173,10 +15174,10 @@
         <v>366</v>
       </c>
       <c r="C140" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D140" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E140">
         <v>500</v>
@@ -15962,13 +15963,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -16010,13 +16011,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -16058,13 +16059,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -16442,7 +16443,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C17" t="s">
         <v>195</v>
@@ -16490,13 +16491,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C18" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D18" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E18">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A51DE9F-2DF0-4D53-90D1-0EB8FFF8739D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C933B7D-47C6-4B79-A1FF-0E899B81EE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="525" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -5533,28 +5533,6 @@
   </si>
   <si>
     <t>mg_dreamy_sapphire_book</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まだ(本入手いれてない。他、習得等の登録はOK）</t>
-    <rPh sb="3" eb="4">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ニュウシュ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ホカ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ナド</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>トウロク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7998,6 +7976,13 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>おそうじアリスからコインのお礼にくれる</t>
+    <rPh sb="14" eb="15">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -8040,7 +8025,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8080,12 +8065,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8157,10 +8136,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8916,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N9">
         <v>3050</v>
@@ -9012,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N11">
         <v>3080</v>
@@ -9156,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N14">
         <v>3110</v>
@@ -9204,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N15">
         <v>3120</v>
@@ -9540,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N22">
         <v>3060</v>
@@ -10980,7 +10959,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="N52">
         <v>340</v>
@@ -11076,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N54">
         <v>360</v>
@@ -11124,7 +11103,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N55">
         <v>370</v>
@@ -11172,7 +11151,7 @@
         <v>1</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N56">
         <v>380</v>
@@ -11220,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N57">
         <v>390</v>
@@ -11235,7 +11214,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C58" t="s">
         <v>206</v>
@@ -11268,7 +11247,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N58">
         <v>400</v>
@@ -11316,7 +11295,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N59">
         <v>410</v>
@@ -11571,7 +11550,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C65" t="s">
         <v>219</v>
@@ -11901,51 +11880,51 @@
         <v>600</v>
       </c>
     </row>
-    <row r="72" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="16">
+    <row r="72" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="14">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D72" s="16" t="s">
+      <c r="D72" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="14">
         <v>500</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="14">
         <v>150</v>
       </c>
-      <c r="G72" s="16">
-        <v>0</v>
-      </c>
-      <c r="H72" s="16">
-        <v>0</v>
-      </c>
-      <c r="I72" s="16">
-        <v>0</v>
-      </c>
-      <c r="J72" s="16">
-        <v>0</v>
-      </c>
-      <c r="K72" s="16">
-        <v>0</v>
-      </c>
-      <c r="L72" s="16">
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>0</v>
+      </c>
+      <c r="I72" s="14">
+        <v>0</v>
+      </c>
+      <c r="J72" s="14">
+        <v>0</v>
+      </c>
+      <c r="K72" s="14">
+        <v>0</v>
+      </c>
+      <c r="L72" s="14">
         <v>1</v>
       </c>
-      <c r="M72" s="17" t="s">
+      <c r="M72" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="N72" s="16">
+      <c r="N72" s="14">
         <v>610</v>
       </c>
-      <c r="O72" s="16">
+      <c r="O72" s="14">
         <v>610</v>
       </c>
     </row>
@@ -12585,7 +12564,7 @@
         <v>286</v>
       </c>
       <c r="D86" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E86">
         <v>500</v>
@@ -12660,7 +12639,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N87">
         <v>2100</v>
@@ -12708,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N88">
         <v>2200</v>
@@ -12756,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N89">
         <v>2300</v>
@@ -12804,7 +12783,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N90">
         <v>2400</v>
@@ -12873,7 +12852,7 @@
         <v>494</v>
       </c>
       <c r="D92" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E92">
         <v>500</v>
@@ -12900,7 +12879,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="N92">
         <v>5000</v>
@@ -13044,7 +13023,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N95">
         <v>5000</v>
@@ -13062,10 +13041,10 @@
         <v>366</v>
       </c>
       <c r="C96" t="s">
+        <v>525</v>
+      </c>
+      <c r="D96" t="s">
         <v>526</v>
-      </c>
-      <c r="D96" t="s">
-        <v>527</v>
       </c>
       <c r="E96">
         <v>500</v>
@@ -13092,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N96">
         <v>5000</v>
@@ -14772,7 +14751,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14781,51 +14760,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="14">
+    <row r="132" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="16">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="C132" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="D132" s="14" t="s">
+      <c r="C132" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="E132" s="14">
+      <c r="D132" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E132" s="16">
         <v>500</v>
       </c>
-      <c r="F132" s="14">
+      <c r="F132" s="16">
         <v>150</v>
       </c>
-      <c r="G132" s="14">
-        <v>0</v>
-      </c>
-      <c r="H132" s="14">
-        <v>0</v>
-      </c>
-      <c r="I132" s="14">
-        <v>0</v>
-      </c>
-      <c r="J132" s="14">
-        <v>0</v>
-      </c>
-      <c r="K132" s="14">
-        <v>0</v>
-      </c>
-      <c r="L132" s="14">
-        <v>0</v>
-      </c>
-      <c r="M132" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="N132" s="14">
+      <c r="G132" s="16">
+        <v>0</v>
+      </c>
+      <c r="H132" s="16">
+        <v>0</v>
+      </c>
+      <c r="I132" s="16">
+        <v>0</v>
+      </c>
+      <c r="J132" s="16">
+        <v>0</v>
+      </c>
+      <c r="K132" s="16">
+        <v>0</v>
+      </c>
+      <c r="L132" s="16">
+        <v>0</v>
+      </c>
+      <c r="M132" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="N132" s="16">
         <v>5000</v>
       </c>
-      <c r="O132" s="14">
+      <c r="O132" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -14868,7 +14847,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14916,7 +14895,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -15012,7 +14991,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -15108,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N138">
         <v>5000</v>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C933B7D-47C6-4B79-A1FF-0E899B81EE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0A9C78-87E4-4440-9A2A-6306BAB2CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2190" yWindow="615" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -8089,7 +8089,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8134,12 +8134,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14760,51 +14754,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="16" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="16">
+    <row r="132" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A132">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="B132" s="16" t="s">
+      <c r="B132" t="s">
         <v>366</v>
       </c>
-      <c r="C132" s="16" t="s">
+      <c r="C132" t="s">
         <v>529</v>
       </c>
-      <c r="D132" s="16" t="s">
+      <c r="D132" t="s">
         <v>528</v>
       </c>
-      <c r="E132" s="16">
+      <c r="E132">
         <v>500</v>
       </c>
-      <c r="F132" s="16">
+      <c r="F132">
         <v>150</v>
       </c>
-      <c r="G132" s="16">
-        <v>0</v>
-      </c>
-      <c r="H132" s="16">
-        <v>0</v>
-      </c>
-      <c r="I132" s="16">
-        <v>0</v>
-      </c>
-      <c r="J132" s="16">
-        <v>0</v>
-      </c>
-      <c r="K132" s="16">
-        <v>0</v>
-      </c>
-      <c r="L132" s="16">
-        <v>0</v>
-      </c>
-      <c r="M132" s="17" t="s">
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="N132" s="16">
+      <c r="N132">
         <v>5000</v>
       </c>
-      <c r="O132" s="16">
+      <c r="O132">
         <v>5000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0A9C78-87E4-4440-9A2A-6306BAB2CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099B36FF-1DB9-48BA-9A24-07AEEDE16D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="615" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="2340" yWindow="1830" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="560">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7981,6 +7981,17 @@
     <rPh sb="14" eb="15">
       <t>レイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイアアークの本</t>
+    <rPh sb="8" eb="9">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_fire_ark_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8450,7 +8461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173DA0A6-4123-4DDB-852A-62922F6582E3}">
-  <dimension ref="A1:O149"/>
+  <dimension ref="A1:O150"/>
   <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.25" customWidth="1"/>
@@ -8516,7 +8527,7 @@
     </row>
     <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A147" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A148" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -13419,10 +13430,10 @@
         <v>366</v>
       </c>
       <c r="C104" t="s">
-        <v>420</v>
+        <v>559</v>
       </c>
       <c r="D104" t="s">
-        <v>419</v>
+        <v>558</v>
       </c>
       <c r="E104">
         <v>500</v>
@@ -13449,7 +13460,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N104">
         <v>5000</v>
@@ -13467,10 +13478,10 @@
         <v>366</v>
       </c>
       <c r="C105" t="s">
-        <v>277</v>
+        <v>420</v>
       </c>
       <c r="D105" t="s">
-        <v>278</v>
+        <v>419</v>
       </c>
       <c r="E105">
         <v>500</v>
@@ -13497,7 +13508,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="N105">
         <v>5000</v>
@@ -13515,10 +13526,10 @@
         <v>366</v>
       </c>
       <c r="C106" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="D106" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="E106">
         <v>500</v>
@@ -13545,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="N106">
         <v>5000</v>
@@ -13563,10 +13574,10 @@
         <v>366</v>
       </c>
       <c r="C107" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D107" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E107">
         <v>500</v>
@@ -13611,10 +13622,10 @@
         <v>366</v>
       </c>
       <c r="C108" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D108" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E108">
         <v>500</v>
@@ -13659,10 +13670,10 @@
         <v>366</v>
       </c>
       <c r="C109" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D109" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="E109">
         <v>500</v>
@@ -13707,10 +13718,10 @@
         <v>366</v>
       </c>
       <c r="C110" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="D110" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="E110">
         <v>500</v>
@@ -13737,7 +13748,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N110">
         <v>5000</v>
@@ -13755,10 +13766,10 @@
         <v>366</v>
       </c>
       <c r="C111" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="D111" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="E111">
         <v>500</v>
@@ -13785,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="N111">
         <v>5000</v>
@@ -13803,10 +13814,10 @@
         <v>366</v>
       </c>
       <c r="C112" t="s">
-        <v>427</v>
+        <v>323</v>
       </c>
       <c r="D112" t="s">
-        <v>426</v>
+        <v>322</v>
       </c>
       <c r="E112">
         <v>500</v>
@@ -13833,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>452</v>
+        <v>412</v>
       </c>
       <c r="N112">
         <v>5000</v>
@@ -13851,10 +13862,10 @@
         <v>366</v>
       </c>
       <c r="C113" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="D113" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="E113">
         <v>500</v>
@@ -13899,10 +13910,10 @@
         <v>366</v>
       </c>
       <c r="C114" t="s">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="D114" t="s">
-        <v>328</v>
+        <v>449</v>
       </c>
       <c r="E114">
         <v>500</v>
@@ -13929,7 +13940,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="N114">
         <v>5000</v>
@@ -13947,10 +13958,10 @@
         <v>366</v>
       </c>
       <c r="C115" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D115" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E115">
         <v>500</v>
@@ -13977,7 +13988,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N115">
         <v>5000</v>
@@ -13995,10 +14006,10 @@
         <v>366</v>
       </c>
       <c r="C116" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="D116" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -14025,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="N116">
         <v>5000</v>
@@ -14043,10 +14054,10 @@
         <v>366</v>
       </c>
       <c r="C117" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="D117" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -14073,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="N117">
         <v>5000</v>
@@ -14091,10 +14102,10 @@
         <v>366</v>
       </c>
       <c r="C118" t="s">
-        <v>334</v>
+        <v>280</v>
       </c>
       <c r="D118" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -14121,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
       <c r="N118">
         <v>5000</v>
@@ -14139,10 +14150,10 @@
         <v>366</v>
       </c>
       <c r="C119" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D119" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -14187,10 +14198,10 @@
         <v>366</v>
       </c>
       <c r="C120" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D120" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -14217,7 +14228,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N120">
         <v>5000</v>
@@ -14235,10 +14246,10 @@
         <v>366</v>
       </c>
       <c r="C121" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D121" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -14265,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N121">
         <v>5000</v>
@@ -14283,10 +14294,10 @@
         <v>366</v>
       </c>
       <c r="C122" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D122" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -14331,10 +14342,10 @@
         <v>366</v>
       </c>
       <c r="C123" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D123" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -14361,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N123">
         <v>5000</v>
@@ -14379,10 +14390,10 @@
         <v>366</v>
       </c>
       <c r="C124" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D124" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -14409,7 +14420,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N124">
         <v>5000</v>
@@ -14427,10 +14438,10 @@
         <v>366</v>
       </c>
       <c r="C125" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D125" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -14475,10 +14486,10 @@
         <v>366</v>
       </c>
       <c r="C126" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D126" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -14505,7 +14516,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N126">
         <v>5000</v>
@@ -14523,10 +14534,10 @@
         <v>366</v>
       </c>
       <c r="C127" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D127" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -14553,7 +14564,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>452</v>
+        <v>538</v>
       </c>
       <c r="N127">
         <v>5000</v>
@@ -14571,10 +14582,10 @@
         <v>366</v>
       </c>
       <c r="C128" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="D128" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -14601,7 +14612,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N128">
         <v>5000</v>
@@ -14619,10 +14630,10 @@
         <v>366</v>
       </c>
       <c r="C129" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D129" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -14649,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="N129">
         <v>5000</v>
@@ -14667,10 +14678,10 @@
         <v>366</v>
       </c>
       <c r="C130" t="s">
-        <v>447</v>
+        <v>303</v>
       </c>
       <c r="D130" t="s">
-        <v>445</v>
+        <v>304</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -14697,7 +14708,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="N130">
         <v>5000</v>
@@ -14715,10 +14726,10 @@
         <v>366</v>
       </c>
       <c r="C131" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D131" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -14745,7 +14756,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>546</v>
+        <v>456</v>
       </c>
       <c r="N131">
         <v>5000</v>
@@ -14763,10 +14774,10 @@
         <v>366</v>
       </c>
       <c r="C132" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="D132" t="s">
-        <v>528</v>
+        <v>446</v>
       </c>
       <c r="E132">
         <v>500</v>
@@ -14793,7 +14804,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="N132">
         <v>5000</v>
@@ -14811,10 +14822,10 @@
         <v>366</v>
       </c>
       <c r="C133" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="D133" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -14841,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N133">
         <v>5000</v>
@@ -14859,10 +14870,10 @@
         <v>366</v>
       </c>
       <c r="C134" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D134" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -14889,7 +14900,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="N134">
         <v>5000</v>
@@ -14907,10 +14918,10 @@
         <v>366</v>
       </c>
       <c r="C135" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D135" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -14955,10 +14966,10 @@
         <v>366</v>
       </c>
       <c r="C136" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D136" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -14985,7 +14996,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>536</v>
+        <v>454</v>
       </c>
       <c r="N136">
         <v>5000</v>
@@ -15003,10 +15014,10 @@
         <v>366</v>
       </c>
       <c r="C137" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="D137" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E137">
         <v>500</v>
@@ -15033,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>454</v>
+        <v>536</v>
       </c>
       <c r="N137">
         <v>5000</v>
@@ -15051,10 +15062,10 @@
         <v>366</v>
       </c>
       <c r="C138" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D138" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E138">
         <v>500</v>
@@ -15081,7 +15092,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>539</v>
+        <v>454</v>
       </c>
       <c r="N138">
         <v>5000</v>
@@ -15099,10 +15110,10 @@
         <v>366</v>
       </c>
       <c r="C139" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D139" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E139">
         <v>500</v>
@@ -15129,7 +15140,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>454</v>
+        <v>539</v>
       </c>
       <c r="N139">
         <v>5000</v>
@@ -15147,10 +15158,10 @@
         <v>366</v>
       </c>
       <c r="C140" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D140" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E140">
         <v>500</v>
@@ -15186,51 +15197,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="141" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="10">
+    <row r="141" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="B141" s="10" t="s">
+      <c r="B141" t="s">
         <v>366</v>
       </c>
-      <c r="C141" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="D141" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="E141" s="10">
+      <c r="C141" t="s">
+        <v>524</v>
+      </c>
+      <c r="D141" t="s">
+        <v>520</v>
+      </c>
+      <c r="E141">
         <v>500</v>
       </c>
-      <c r="F141" s="10">
+      <c r="F141">
         <v>150</v>
       </c>
-      <c r="G141" s="10">
-        <v>0</v>
-      </c>
-      <c r="H141" s="10">
-        <v>0</v>
-      </c>
-      <c r="I141" s="10">
-        <v>0</v>
-      </c>
-      <c r="J141" s="10">
-        <v>0</v>
-      </c>
-      <c r="K141" s="10">
-        <v>0</v>
-      </c>
-      <c r="L141" s="10">
-        <v>0</v>
-      </c>
-      <c r="M141" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="N141" s="10">
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="N141">
         <v>5000</v>
       </c>
-      <c r="O141" s="10">
+      <c r="O141">
         <v>5000</v>
       </c>
     </row>
@@ -15243,10 +15254,10 @@
         <v>366</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E142" s="10">
         <v>500</v>
@@ -15291,10 +15302,10 @@
         <v>366</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E143" s="10">
         <v>500</v>
@@ -15330,51 +15341,51 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144">
+    <row r="144" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="10">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="C144" t="s">
-        <v>358</v>
-      </c>
-      <c r="D144" t="s">
-        <v>357</v>
-      </c>
-      <c r="E144">
+      <c r="C144" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E144" s="10">
         <v>500</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="10">
         <v>150</v>
       </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="N144">
+      <c r="G144" s="10">
+        <v>0</v>
+      </c>
+      <c r="H144" s="10">
+        <v>0</v>
+      </c>
+      <c r="I144" s="10">
+        <v>0</v>
+      </c>
+      <c r="J144" s="10">
+        <v>0</v>
+      </c>
+      <c r="K144" s="10">
+        <v>0</v>
+      </c>
+      <c r="L144" s="10">
+        <v>0</v>
+      </c>
+      <c r="M144" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="N144" s="10">
         <v>5000</v>
       </c>
-      <c r="O144">
+      <c r="O144" s="10">
         <v>5000</v>
       </c>
     </row>
@@ -15387,10 +15398,10 @@
         <v>366</v>
       </c>
       <c r="C145" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D145" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -15417,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>279</v>
+        <v>416</v>
       </c>
       <c r="N145">
         <v>5000</v>
@@ -15426,194 +15437,242 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="146" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="10">
+    <row r="146" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A146">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B146" t="s">
         <v>366</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="E146" s="10">
+      <c r="C146" t="s">
+        <v>360</v>
+      </c>
+      <c r="D146" t="s">
+        <v>359</v>
+      </c>
+      <c r="E146">
         <v>500</v>
       </c>
-      <c r="F146" s="10">
+      <c r="F146">
         <v>150</v>
       </c>
-      <c r="G146" s="10">
-        <v>0</v>
-      </c>
-      <c r="H146" s="10">
-        <v>0</v>
-      </c>
-      <c r="I146" s="10">
-        <v>0</v>
-      </c>
-      <c r="J146" s="10">
-        <v>0</v>
-      </c>
-      <c r="K146" s="10">
-        <v>0</v>
-      </c>
-      <c r="L146" s="10">
-        <v>0</v>
-      </c>
-      <c r="M146" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="N146" s="10">
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="N146">
         <v>5000</v>
       </c>
-      <c r="O146" s="10">
+      <c r="O146">
         <v>5000</v>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147">
+    <row r="147" spans="1:15" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="10">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="E147" s="10">
+        <v>500</v>
+      </c>
+      <c r="F147" s="10">
+        <v>150</v>
+      </c>
+      <c r="G147" s="10">
+        <v>0</v>
+      </c>
+      <c r="H147" s="10">
+        <v>0</v>
+      </c>
+      <c r="I147" s="10">
+        <v>0</v>
+      </c>
+      <c r="J147" s="10">
+        <v>0</v>
+      </c>
+      <c r="K147" s="10">
+        <v>0</v>
+      </c>
+      <c r="L147" s="10">
+        <v>0</v>
+      </c>
+      <c r="M147" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="N147" s="10">
+        <v>5000</v>
+      </c>
+      <c r="O147" s="10">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <f t="shared" si="0"/>
+        <v>146</v>
+      </c>
+      <c r="B148" t="s">
+        <v>366</v>
+      </c>
+      <c r="C148" t="s">
         <v>305</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D148" t="s">
         <v>306</v>
       </c>
-      <c r="E147">
+      <c r="E148">
         <v>500</v>
       </c>
-      <c r="F147">
+      <c r="F148">
         <v>150</v>
       </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147" s="2" t="s">
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="N147">
+      <c r="N148">
         <v>5000</v>
       </c>
-      <c r="O147">
+      <c r="O148">
         <v>5000</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148">
+    <row r="149" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A149">
         <f>ROW()-2</f>
-        <v>146</v>
-      </c>
-      <c r="B148" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149" t="s">
         <v>431</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C149" t="s">
         <v>428</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D149" t="s">
         <v>429</v>
       </c>
-      <c r="E148">
-        <v>0</v>
-      </c>
-      <c r="F148">
-        <v>0</v>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
         <v>1</v>
       </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148" t="s">
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149" t="s">
         <v>430</v>
       </c>
-      <c r="N148">
+      <c r="N149">
         <v>9999</v>
       </c>
-      <c r="O148">
+      <c r="O149">
         <v>9999</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149">
+    <row r="150" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A150">
         <v>10000</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B150" t="s">
         <v>166</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C150" t="s">
         <v>170</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D150" t="s">
         <v>171</v>
       </c>
-      <c r="E149">
+      <c r="E150">
         <v>500</v>
       </c>
-      <c r="F149">
+      <c r="F150">
         <v>150</v>
       </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="L149">
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
         <v>1</v>
       </c>
-      <c r="M149" s="2" t="s">
+      <c r="M150" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="N149">
+      <c r="N150">
         <v>9000</v>
       </c>
-      <c r="O149">
+      <c r="O150">
         <v>9000</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_eventItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099B36FF-1DB9-48BA-9A24-07AEEDE16D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D030B183-317A-483A-8672-9AE1B15931A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1830" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
+    <workbookView xWindow="3480" yWindow="900" windowWidth="25005" windowHeight="14370" xr2:uid="{738EF540-1617-4F63-AB66-A45177877433}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_recipi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="616">
   <si>
     <t>name</t>
     <phoneticPr fontId="3"/>
@@ -7992,6 +7992,803 @@
   </si>
   <si>
     <t>mg_fire_ark_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>magic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコレート作りに必要な魔法がのっている</t>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初歩的な風の魔法がのっている。あやしげな渦巻模様が描かれている。</t>
+    <rPh sb="0" eb="3">
+      <t>ショホテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ウズマキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初歩的な星の魔法がのっている。かなり古びている。</t>
+    <rPh sb="0" eb="3">
+      <t>ショホテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>フル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初歩的な氷の魔法がのっている。青い六角形の模様が描かれている。</t>
+    <rPh sb="0" eb="3">
+      <t>ショホテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ロッカクケイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初歩的な火の魔法がのっている。赤いひし形の模様が描かれている。</t>
+    <rPh sb="0" eb="3">
+      <t>ショホテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>演出魔法を強める効果の魔法</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>光で作ったちょうちょや葉っぱを飛ばす</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おかしの周りにキラキラした光りを飛ばす。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お菓子を作った際に、MPを少し回復する</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レアアイテムを発見したとき、個数を+1する。</t>
+    <rPh sb="7" eb="9">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼き菓子を二度焼きして、サクサク感を増す。</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガシ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ニドヤ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生地にかけると、さくさく感をアップする。</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お菓子に花火の演出効果を加える。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼く際に、温度を細かく指定できる。</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>オンド</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。</t>
+    <rPh sb